--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sexta-feira, 24 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em sábado, 25 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -519,7 +519,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -528,7 +528,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -578,7 +578,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-46</v>
+        <v>-47</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -587,7 +587,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-46</v>
+        <v>-47</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
@@ -637,7 +637,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -646,7 +646,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -696,7 +696,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -705,7 +705,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -755,7 +755,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -764,7 +764,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -814,7 +814,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>38</v>
@@ -823,7 +823,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>38</v>
@@ -873,7 +873,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>38</v>
@@ -882,7 +882,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>38</v>
@@ -932,7 +932,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>38</v>
@@ -941,7 +941,7 @@
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>38</v>
@@ -991,7 +991,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>38</v>
@@ -1000,7 +1000,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-67</v>
+        <v>-68</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>29</v>
@@ -1050,7 +1050,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>38</v>
@@ -1059,7 +1059,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-60</v>
+        <v>-61</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>29</v>
@@ -1109,7 +1109,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>38</v>
@@ -1118,7 +1118,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>38</v>
@@ -1168,7 +1168,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>38</v>
@@ -1177,7 +1177,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>38</v>
@@ -1227,7 +1227,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
@@ -1236,7 +1236,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>38</v>
@@ -1286,7 +1286,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>38</v>
@@ -1295,7 +1295,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>38</v>
@@ -1345,7 +1345,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>38</v>
@@ -1354,7 +1354,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>38</v>
@@ -1404,7 +1404,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>38</v>
@@ -1413,7 +1413,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>38</v>
@@ -1463,7 +1463,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>38</v>
@@ -1472,7 +1472,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>38</v>
@@ -1522,7 +1522,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>38</v>
@@ -1531,7 +1531,7 @@
         <v>50</v>
       </c>
       <c r="Q23" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>24</v>
@@ -1581,7 +1581,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>38</v>
@@ -1590,7 +1590,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>38</v>
@@ -1640,7 +1640,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>38</v>
@@ -1649,7 +1649,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>38</v>
@@ -1699,7 +1699,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>38</v>
@@ -1708,7 +1708,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>38</v>
@@ -1758,7 +1758,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>38</v>
@@ -1767,7 +1767,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>38</v>
@@ -1817,7 +1817,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>38</v>
@@ -1826,7 +1826,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>38</v>
@@ -1876,7 +1876,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>38</v>
@@ -1885,7 +1885,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>38</v>
@@ -1935,7 +1935,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>38</v>
@@ -1944,7 +1944,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>38</v>
@@ -1994,7 +1994,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>38</v>
@@ -2003,7 +2003,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>38</v>
@@ -2053,7 +2053,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>38</v>
@@ -2062,7 +2062,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>38</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sábado, 25 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em domingo, 26 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -519,7 +519,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -528,7 +528,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -578,7 +578,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -587,7 +587,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
@@ -637,7 +637,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -646,7 +646,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -696,7 +696,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -705,7 +705,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -755,7 +755,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -764,7 +764,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -814,7 +814,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>38</v>
@@ -823,7 +823,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>38</v>
@@ -873,7 +873,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>38</v>
@@ -882,7 +882,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>38</v>
@@ -932,7 +932,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>38</v>
@@ -941,7 +941,7 @@
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>38</v>
@@ -991,7 +991,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>38</v>
@@ -1000,7 +1000,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>29</v>
@@ -1050,7 +1050,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>38</v>
@@ -1059,7 +1059,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-61</v>
+        <v>-62</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>29</v>
@@ -1109,7 +1109,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>38</v>
@@ -1118,7 +1118,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>38</v>
@@ -1168,7 +1168,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>38</v>
@@ -1177,7 +1177,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>38</v>
@@ -1227,7 +1227,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
@@ -1236,7 +1236,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>38</v>
@@ -1286,7 +1286,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>38</v>
@@ -1295,7 +1295,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>38</v>
@@ -1345,7 +1345,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>38</v>
@@ -1354,7 +1354,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>38</v>
@@ -1404,7 +1404,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>38</v>
@@ -1413,7 +1413,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>38</v>
@@ -1463,7 +1463,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>38</v>
@@ -1472,7 +1472,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>38</v>
@@ -1522,7 +1522,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>38</v>
@@ -1531,7 +1531,7 @@
         <v>50</v>
       </c>
       <c r="Q23" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>24</v>
@@ -1581,7 +1581,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>38</v>
@@ -1590,7 +1590,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>38</v>
@@ -1640,7 +1640,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>38</v>
@@ -1649,7 +1649,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>38</v>
@@ -1699,7 +1699,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>38</v>
@@ -1708,7 +1708,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>38</v>
@@ -1758,7 +1758,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>38</v>
@@ -1767,7 +1767,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>38</v>
@@ -1817,7 +1817,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>38</v>
@@ -1826,7 +1826,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>38</v>
@@ -1876,7 +1876,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>38</v>
@@ -1885,7 +1885,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>38</v>
@@ -1935,7 +1935,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>38</v>
@@ -1944,7 +1944,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>38</v>
@@ -1994,7 +1994,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>38</v>
@@ -2003,7 +2003,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>38</v>
@@ -2053,7 +2053,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>38</v>
@@ -2062,7 +2062,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>38</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em domingo, 26 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em segunda-feira, 27 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -519,7 +519,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -528,7 +528,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -578,7 +578,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -587,7 +587,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
@@ -637,7 +637,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -646,7 +646,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -696,7 +696,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -705,7 +705,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -755,7 +755,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -764,7 +764,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -814,7 +814,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>38</v>
@@ -823,7 +823,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>38</v>
@@ -873,7 +873,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>38</v>
@@ -882,7 +882,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>38</v>
@@ -932,7 +932,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>38</v>
@@ -941,7 +941,7 @@
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>38</v>
@@ -991,7 +991,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>38</v>
@@ -1000,7 +1000,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-69</v>
+        <v>-70</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>29</v>
@@ -1050,7 +1050,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>38</v>
@@ -1059,7 +1059,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-62</v>
+        <v>-63</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>29</v>
@@ -1109,7 +1109,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>38</v>
@@ -1118,7 +1118,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>38</v>
@@ -1168,7 +1168,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>38</v>
@@ -1177,7 +1177,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>38</v>
@@ -1227,7 +1227,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>38</v>
@@ -1236,7 +1236,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>38</v>
@@ -1286,7 +1286,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>38</v>
@@ -1295,7 +1295,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>38</v>
@@ -1345,7 +1345,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>38</v>
@@ -1354,7 +1354,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>38</v>
@@ -1404,7 +1404,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>38</v>
@@ -1413,7 +1413,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>38</v>
@@ -1463,7 +1463,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>38</v>
@@ -1472,7 +1472,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>38</v>
@@ -1522,7 +1522,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>38</v>
@@ -1531,7 +1531,7 @@
         <v>50</v>
       </c>
       <c r="Q23" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>24</v>
@@ -1581,7 +1581,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>38</v>
@@ -1590,7 +1590,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>38</v>
@@ -1640,7 +1640,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>38</v>
@@ -1649,7 +1649,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>38</v>
@@ -1699,7 +1699,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>38</v>
@@ -1708,7 +1708,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>38</v>
@@ -1758,7 +1758,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>38</v>
@@ -1767,7 +1767,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>38</v>
@@ -1817,7 +1817,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>38</v>
@@ -1826,7 +1826,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>38</v>
@@ -1876,7 +1876,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>38</v>
@@ -1885,7 +1885,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>38</v>
@@ -1935,7 +1935,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>38</v>
@@ -1944,7 +1944,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>38</v>
@@ -1994,7 +1994,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>38</v>
@@ -2003,7 +2003,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>38</v>
@@ -2053,7 +2053,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>38</v>
@@ -2062,7 +2062,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>38</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$33</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$85</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,7 +36,7 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Final: 13/07/2026</t>
+      <t>Data Final: 02/08/2026</t>
     </r>
   </si>
   <si>
@@ -236,6 +236,219 @@
   </si>
   <si>
     <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11831</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11943</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11899</t>
+  </si>
+  <si>
+    <t>FA-11837</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11849</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-11881</t>
+  </si>
+  <si>
+    <t>FA-11911</t>
+  </si>
+  <si>
+    <t>FA-11915</t>
+  </si>
+  <si>
+    <t>FA-11987</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11968</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11945</t>
+  </si>
+  <si>
+    <t>FA-11969</t>
+  </si>
+  <si>
+    <t>FA-11856</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>FA-11629</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11961</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11988</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11838</t>
+  </si>
+  <si>
+    <t>FA-11839</t>
+  </si>
+  <si>
+    <t>FA-11907</t>
+  </si>
+  <si>
+    <t>FA-11949</t>
+  </si>
+  <si>
+    <t>FA-11840</t>
+  </si>
+  <si>
+    <t>FA-11989</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11906</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11886</t>
+  </si>
+  <si>
+    <t>FA-11905</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11740</t>
+  </si>
+  <si>
+    <t>FA-11855</t>
+  </si>
+  <si>
+    <t>FA-12007</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11973</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-11971</t>
+  </si>
+  <si>
+    <t>FA-11993</t>
+  </si>
+  <si>
+    <t>FA-11974</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11947</t>
+  </si>
+  <si>
+    <t>FA-11994</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11920</t>
+  </si>
+  <si>
+    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
+  </si>
+  <si>
+    <t>FA-11857</t>
+  </si>
+  <si>
+    <t>FA-11665</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-11972</t>
+  </si>
+  <si>
+    <t>FA-11992</t>
+  </si>
+  <si>
+    <t>FA-11932</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11962</t>
+  </si>
+  <si>
+    <t>FA-11865</t>
+  </si>
+  <si>
+    <t>FA-11950</t>
+  </si>
+  <si>
+    <t>FA-11653</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-11991</t>
+  </si>
+  <si>
+    <t>FA-11641</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
   </si>
 </sst>
 </file>
@@ -378,12 +591,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S33"/>
+  <dimension ref="A1:S85"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1" style="1"/>
     <col min="2" max="2" width="39" customWidth="1" style="1"/>
-    <col min="3" max="3" width="31" customWidth="1" style="1"/>
+    <col min="3" max="3" width="35" customWidth="1" style="1"/>
     <col min="4" max="4" width="14" customWidth="1" style="1"/>
     <col min="5" max="5" width="38" customWidth="1" style="1"/>
     <col min="6" max="6" width="16" customWidth="1" style="1"/>
@@ -2071,28 +2284,3096 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" ht="23" customHeight="1">
-      <c r="A33" s="10"/>
-      <c r="B33" s="10"/>
-      <c r="C33" s="10"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-      <c r="G33" s="11"/>
-      <c r="H33" s="10"/>
-      <c r="I33" s="11"/>
-      <c r="J33" s="11"/>
-      <c r="K33" s="11"/>
-      <c r="L33" s="12">
-        <f>SUM(L6:L32)</f>
-      </c>
-      <c r="M33" s="10"/>
-      <c r="N33" s="13"/>
-      <c r="O33" s="10"/>
-      <c r="P33" s="10"/>
-      <c r="Q33" s="13"/>
-      <c r="R33" s="10"/>
-      <c r="S33" s="10"/>
+    <row r="33">
+      <c r="A33" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H33" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I33" s="7">
+        <v>46209</v>
+      </c>
+      <c r="J33" s="7">
+        <v>46220</v>
+      </c>
+      <c r="K33" s="7">
+        <v>46209</v>
+      </c>
+      <c r="L33" s="8">
+        <v>600</v>
+      </c>
+      <c r="M33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N33" s="9">
+        <v>-11</v>
+      </c>
+      <c r="O33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P33" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>-22</v>
+      </c>
+      <c r="R33" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S33" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H34" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I34" s="7">
+        <v>46216</v>
+      </c>
+      <c r="J34" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K34" s="7">
+        <v>46216</v>
+      </c>
+      <c r="L34" s="8">
+        <v>40</v>
+      </c>
+      <c r="M34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N34" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P34" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q34" s="9">
+        <v>-15</v>
+      </c>
+      <c r="R34" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S34" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" s="7">
+        <v>46190</v>
+      </c>
+      <c r="H35" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I35" s="7">
+        <v>46174</v>
+      </c>
+      <c r="J35" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K35" s="7">
+        <v>46239</v>
+      </c>
+      <c r="L35" s="8">
+        <v>50</v>
+      </c>
+      <c r="M35" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N35" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O35" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P35" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="9">
+        <v>8</v>
+      </c>
+      <c r="R35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S35" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" s="7">
+        <v>46153</v>
+      </c>
+      <c r="H36" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I36" s="7">
+        <v>46143</v>
+      </c>
+      <c r="J36" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K36" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L36" s="8">
+        <v>50</v>
+      </c>
+      <c r="M36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N36" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P36" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q36" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R36" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S36" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H37" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I37" s="7">
+        <v>46209</v>
+      </c>
+      <c r="J37" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K37" s="7">
+        <v>46209</v>
+      </c>
+      <c r="L37" s="8">
+        <v>60</v>
+      </c>
+      <c r="M37" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N37" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P37" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q37" s="9">
+        <v>-22</v>
+      </c>
+      <c r="R37" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S37" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H38" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I38" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J38" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K38" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L38" s="8">
+        <v>76.01</v>
+      </c>
+      <c r="M38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N38" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P38" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q38" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R38" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S38" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I39" s="7">
+        <v>46188</v>
+      </c>
+      <c r="J39" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K39" s="7">
+        <v>46188</v>
+      </c>
+      <c r="L39" s="8">
+        <v>96.66</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N39" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O39" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P39" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q39" s="9">
+        <v>-43</v>
+      </c>
+      <c r="R39" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S39" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I40" s="7">
+        <v>46209</v>
+      </c>
+      <c r="J40" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K40" s="7">
+        <v>46209</v>
+      </c>
+      <c r="L40" s="8">
+        <v>200</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N40" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O40" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P40" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q40" s="9">
+        <v>-22</v>
+      </c>
+      <c r="R40" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S40" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H41" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I41" s="7">
+        <v>46209</v>
+      </c>
+      <c r="J41" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K41" s="7">
+        <v>46209</v>
+      </c>
+      <c r="L41" s="8">
+        <v>330</v>
+      </c>
+      <c r="M41" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N41" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O41" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P41" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q41" s="9">
+        <v>-22</v>
+      </c>
+      <c r="R41" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S41" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G42" s="7">
+        <v>46203</v>
+      </c>
+      <c r="H42" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I42" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J42" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K42" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L42" s="8">
+        <v>630</v>
+      </c>
+      <c r="M42" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N42" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O42" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P42" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q42" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R42" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S42" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G43" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H43" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I43" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J43" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K43" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L43" s="8">
+        <v>630</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N43" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O43" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P43" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q43" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R43" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S43" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F44" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G44" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H44" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I44" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J44" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K44" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L44" s="8">
+        <v>630</v>
+      </c>
+      <c r="M44" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N44" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P44" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q44" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R44" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S44" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D45" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F45" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G45" s="7">
+        <v>46212</v>
+      </c>
+      <c r="H45" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I45" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J45" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K45" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L45" s="8">
+        <v>630</v>
+      </c>
+      <c r="M45" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N45" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P45" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q45" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R45" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S45" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G46" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I46" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J46" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K46" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L46" s="8">
+        <v>650</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N46" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P46" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q46" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S46" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G47" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I47" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J47" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K47" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L47" s="8">
+        <v>650</v>
+      </c>
+      <c r="M47" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N47" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P47" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q47" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R47" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S47" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G48" s="7">
+        <v>46153</v>
+      </c>
+      <c r="H48" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I48" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J48" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K48" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L48" s="8">
+        <v>650</v>
+      </c>
+      <c r="M48" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N48" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O48" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P48" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q48" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R48" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S48" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F49" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G49" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H49" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I49" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J49" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K49" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L49" s="8">
+        <v>680</v>
+      </c>
+      <c r="M49" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N49" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O49" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P49" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q49" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R49" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S49" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F50" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G50" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I50" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J50" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K50" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L50" s="8">
+        <v>680</v>
+      </c>
+      <c r="M50" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N50" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O50" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P50" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q50" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R50" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S50" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F51" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G51" s="7">
+        <v>46182</v>
+      </c>
+      <c r="H51" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I51" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J51" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K51" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L51" s="8">
+        <v>680</v>
+      </c>
+      <c r="M51" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N51" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O51" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P51" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q51" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R51" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S51" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G52" s="7">
+        <v>46182</v>
+      </c>
+      <c r="H52" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I52" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J52" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K52" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L52" s="8">
+        <v>680</v>
+      </c>
+      <c r="M52" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N52" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O52" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P52" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q52" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R52" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S52" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F53" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G53" s="7">
+        <v>46203</v>
+      </c>
+      <c r="H53" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I53" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J53" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K53" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L53" s="8">
+        <v>700</v>
+      </c>
+      <c r="M53" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N53" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O53" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P53" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q53" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R53" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S53" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F54" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G54" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H54" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I54" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J54" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K54" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L54" s="8">
+        <v>800</v>
+      </c>
+      <c r="M54" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N54" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P54" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q54" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R54" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S54" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F55" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G55" s="7">
+        <v>46182</v>
+      </c>
+      <c r="H55" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I55" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J55" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K55" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L55" s="8">
+        <v>800</v>
+      </c>
+      <c r="M55" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N55" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P55" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q55" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R55" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S55" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G56" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H56" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I56" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J56" s="7">
+        <v>46223</v>
+      </c>
+      <c r="K56" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L56" s="8">
+        <v>1200</v>
+      </c>
+      <c r="M56" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N56" s="9">
+        <v>-8</v>
+      </c>
+      <c r="O56" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P56" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q56" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R56" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S56" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F57" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H57" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I57" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J57" s="7">
+        <v>46224</v>
+      </c>
+      <c r="K57" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L57" s="8">
+        <v>3.91</v>
+      </c>
+      <c r="M57" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N57" s="9">
+        <v>-7</v>
+      </c>
+      <c r="O57" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P57" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q57" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R57" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S57" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H58" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I58" s="7">
+        <v>46216</v>
+      </c>
+      <c r="J58" s="7">
+        <v>46224</v>
+      </c>
+      <c r="K58" s="7">
+        <v>46216</v>
+      </c>
+      <c r="L58" s="8">
+        <v>56.19</v>
+      </c>
+      <c r="M58" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N58" s="9">
+        <v>-7</v>
+      </c>
+      <c r="O58" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P58" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q58" s="9">
+        <v>-15</v>
+      </c>
+      <c r="R58" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S58" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F59" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G59" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H59" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I59" s="7">
+        <v>46223</v>
+      </c>
+      <c r="J59" s="7">
+        <v>46224</v>
+      </c>
+      <c r="K59" s="7">
+        <v>46223</v>
+      </c>
+      <c r="L59" s="8">
+        <v>71</v>
+      </c>
+      <c r="M59" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N59" s="9">
+        <v>-7</v>
+      </c>
+      <c r="O59" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P59" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q59" s="9">
+        <v>-8</v>
+      </c>
+      <c r="R59" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S59" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G60" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H60" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I60" s="7">
+        <v>46216</v>
+      </c>
+      <c r="J60" s="7">
+        <v>46224</v>
+      </c>
+      <c r="K60" s="7">
+        <v>46216</v>
+      </c>
+      <c r="L60" s="8">
+        <v>360.95</v>
+      </c>
+      <c r="M60" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N60" s="9">
+        <v>-7</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P60" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q60" s="9">
+        <v>-15</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S60" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G61" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H61" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I61" s="7">
+        <v>46216</v>
+      </c>
+      <c r="J61" s="7">
+        <v>46224</v>
+      </c>
+      <c r="K61" s="7">
+        <v>46216</v>
+      </c>
+      <c r="L61" s="8">
+        <v>550</v>
+      </c>
+      <c r="M61" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N61" s="9">
+        <v>-7</v>
+      </c>
+      <c r="O61" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P61" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q61" s="9">
+        <v>-15</v>
+      </c>
+      <c r="R61" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S61" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G62" s="7">
+        <v>46190</v>
+      </c>
+      <c r="H62" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I62" s="7">
+        <v>46174</v>
+      </c>
+      <c r="J62" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K62" s="7">
+        <v>46246</v>
+      </c>
+      <c r="L62" s="8">
+        <v>50</v>
+      </c>
+      <c r="M62" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N62" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O62" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P62" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q62" s="9">
+        <v>15</v>
+      </c>
+      <c r="R62" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S62" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E63" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F63" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="G63" s="7">
+        <v>46153</v>
+      </c>
+      <c r="H63" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I63" s="7">
+        <v>46143</v>
+      </c>
+      <c r="J63" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K63" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L63" s="8">
+        <v>50</v>
+      </c>
+      <c r="M63" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N63" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O63" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P63" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q63" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R63" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S63" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E64" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G64" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H64" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I64" s="7">
+        <v>46188</v>
+      </c>
+      <c r="J64" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K64" s="7">
+        <v>46188</v>
+      </c>
+      <c r="L64" s="8">
+        <v>116.66</v>
+      </c>
+      <c r="M64" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N64" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O64" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P64" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q64" s="9">
+        <v>-43</v>
+      </c>
+      <c r="R64" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="S64" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C65" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D65" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F65" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G65" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H65" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I65" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J65" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K65" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L65" s="8">
+        <v>600</v>
+      </c>
+      <c r="M65" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N65" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O65" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P65" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q65" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R65" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S65" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B66" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C66" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D66" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E66" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G66" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I66" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J66" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K66" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L66" s="8">
+        <v>600</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N66" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O66" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q66" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R66" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S66" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B67" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E67" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F67" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G67" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H67" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I67" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J67" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K67" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L67" s="8">
+        <v>630</v>
+      </c>
+      <c r="M67" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N67" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O67" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P67" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q67" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R67" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S67" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E68" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H68" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I68" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J68" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K68" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L68" s="8">
+        <v>630</v>
+      </c>
+      <c r="M68" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N68" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O68" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P68" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q68" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R68" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S68" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B69" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D69" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E69" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F69" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H69" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I69" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J69" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K69" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L69" s="8">
+        <v>630</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N69" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O69" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P69" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q69" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R69" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S69" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B70" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="C70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" s="7">
+        <v>46212</v>
+      </c>
+      <c r="H70" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I70" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J70" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K70" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L70" s="8">
+        <v>630</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N70" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O70" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P70" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q70" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R70" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S70" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E71" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F71" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H71" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I71" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J71" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K71" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L71" s="8">
+        <v>630</v>
+      </c>
+      <c r="M71" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N71" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O71" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P71" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q71" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R71" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S71" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D72" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E72" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F72" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G72" s="7">
+        <v>46210</v>
+      </c>
+      <c r="H72" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I72" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J72" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K72" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L72" s="8">
+        <v>650</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N72" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O72" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P72" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q72" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R72" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S72" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F73" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H73" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I73" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J73" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K73" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L73" s="8">
+        <v>650</v>
+      </c>
+      <c r="M73" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N73" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O73" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P73" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q73" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R73" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S73" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B74" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D74" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E74" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="7">
+        <v>46160</v>
+      </c>
+      <c r="H74" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I74" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J74" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K74" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L74" s="8">
+        <v>650</v>
+      </c>
+      <c r="M74" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N74" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O74" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P74" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q74" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R74" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S74" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B75" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C75" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D75" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E75" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F75" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G75" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H75" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I75" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J75" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K75" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L75" s="8">
+        <v>650</v>
+      </c>
+      <c r="M75" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N75" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O75" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P75" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q75" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R75" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S75" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I76" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J76" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K76" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L76" s="8">
+        <v>680</v>
+      </c>
+      <c r="M76" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N76" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O76" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P76" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q76" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R76" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S76" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B77" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C77" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D77" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E77" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F77" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G77" s="7">
+        <v>46212</v>
+      </c>
+      <c r="H77" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I77" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J77" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K77" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L77" s="8">
+        <v>680</v>
+      </c>
+      <c r="M77" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N77" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O77" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P77" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q77" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R77" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S77" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="B78" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C78" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D78" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E78" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F78" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G78" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H78" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I78" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J78" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K78" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L78" s="8">
+        <v>680</v>
+      </c>
+      <c r="M78" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N78" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O78" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P78" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q78" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R78" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S78" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B79" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C79" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D79" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E79" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G79" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H79" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I79" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J79" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K79" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L79" s="8">
+        <v>700</v>
+      </c>
+      <c r="M79" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N79" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O79" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P79" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q79" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R79" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S79" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B80" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D80" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E80" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G80" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H80" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I80" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J80" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K80" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L80" s="8">
+        <v>800</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N80" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O80" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P80" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q80" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R80" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S80" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B81" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C81" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D81" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E81" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F81" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="7">
+        <v>46160</v>
+      </c>
+      <c r="H81" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I81" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J81" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K81" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L81" s="8">
+        <v>1200</v>
+      </c>
+      <c r="M81" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N81" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O81" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P81" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q81" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R81" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S81" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B82" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="C82" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D82" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H82" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I82" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J82" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K82" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L82" s="8">
+        <v>1200</v>
+      </c>
+      <c r="M82" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N82" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O82" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P82" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q82" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R82" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S82" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B83" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="E83" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F83" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G83" s="7">
+        <v>46160</v>
+      </c>
+      <c r="H83" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I83" s="7">
+        <v>46230</v>
+      </c>
+      <c r="J83" s="7">
+        <v>46230</v>
+      </c>
+      <c r="K83" s="7">
+        <v>46230</v>
+      </c>
+      <c r="L83" s="8">
+        <v>1200</v>
+      </c>
+      <c r="M83" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="N83" s="9">
+        <v>-1</v>
+      </c>
+      <c r="O83" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="P83" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q83" s="9">
+        <v>-1</v>
+      </c>
+      <c r="R83" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="S83" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B84" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G84" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H84" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I84" s="7">
+        <v>45930</v>
+      </c>
+      <c r="J84" s="7">
+        <v>46233</v>
+      </c>
+      <c r="K84" s="7">
+        <v>46233</v>
+      </c>
+      <c r="L84" s="8">
+        <v>185.5</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="N84" s="9">
+        <v>2</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q84" s="9">
+        <v>2</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S84" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" ht="23" customHeight="1">
+      <c r="A85" s="10"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="10"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="11"/>
+      <c r="L85" s="12">
+        <f>SUM(L6:L84)</f>
+      </c>
+      <c r="M85" s="10"/>
+      <c r="N85" s="13"/>
+      <c r="O85" s="10"/>
+      <c r="P85" s="10"/>
+      <c r="Q85" s="13"/>
+      <c r="R85" s="10"/>
+      <c r="S85" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:S5"/>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$85</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$122</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -36,11 +36,11 @@
         <color rgb="FF808080"/>
         <sz val="11"/>
       </rPr>
-      <t>Data Final: 02/08/2026</t>
+      <t>Data Final: 31/08/2026</t>
     </r>
   </si>
   <si>
-    <t>Relatório exportado em terça-feira, 28 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em quarta-feira, 29 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -130,325 +130,445 @@
     <t>FA-11571</t>
   </si>
   <si>
-    <t>ND-11699</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
+    <t>FA-11791</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>FA-11879</t>
+  </si>
+  <si>
+    <t>VENCIDO ATÉ 30 DIAS</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
+    <t>ND-11870</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>NOTA DE DÉBITO</t>
+  </si>
+  <si>
+    <t>FA-11880</t>
+  </si>
+  <si>
+    <t>FA-11883</t>
+  </si>
+  <si>
+    <t>FA-11876</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>FA-11884</t>
+  </si>
+  <si>
+    <t>FA-11887</t>
+  </si>
+  <si>
+    <t>FA-11913</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-12012</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-11885</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11834</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11836</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11831</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11837</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11911</t>
+  </si>
+  <si>
+    <t>FA-11968</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11987</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-12013</t>
+  </si>
+  <si>
+    <t>FA-11915</t>
+  </si>
+  <si>
+    <t>FA-11969</t>
+  </si>
+  <si>
+    <t>FA-11629</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11856</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-11961</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11839</t>
+  </si>
+  <si>
+    <t>FA-11838</t>
+  </si>
+  <si>
+    <t>FA-11907</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
   </si>
   <si>
     <t>PRIVADO</t>
   </si>
   <si>
-    <t>NOTA DE DÉBITO</t>
-  </si>
-  <si>
-    <t>FA-11791</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>VENCIDO ATÉ 30 DIAS</t>
-  </si>
-  <si>
-    <t>FA-11879</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
-    <t>ND-11870</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>FA-11880</t>
-  </si>
-  <si>
-    <t>FA-11883</t>
-  </si>
-  <si>
-    <t>FA-11830</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11876</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11697</t>
-  </si>
-  <si>
-    <t>NICOLAS JUAN HENRIQUE SILVA DE MARIA</t>
-  </si>
-  <si>
-    <t>FA-11884</t>
-  </si>
-  <si>
-    <t>FA-11887</t>
-  </si>
-  <si>
-    <t>FA-11913</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11885</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11834</t>
+    <t>FA-11840</t>
+  </si>
+  <si>
+    <t>FA-11989</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11906</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11886</t>
+  </si>
+  <si>
+    <t>FA-11905</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11855</t>
+  </si>
+  <si>
+    <t>FA-11945</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11849</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-12007</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-11971</t>
+  </si>
+  <si>
+    <t>FA-11947</t>
+  </si>
+  <si>
+    <t>FA-12014</t>
+  </si>
+  <si>
+    <t>FA-11993</t>
+  </si>
+  <si>
+    <t>FA-11920</t>
+  </si>
+  <si>
+    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
+  </si>
+  <si>
+    <t>FA-11857</t>
+  </si>
+  <si>
+    <t>FA-11972</t>
+  </si>
+  <si>
+    <t>FA-11992</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11962</t>
+  </si>
+  <si>
+    <t>FA-11950</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11653</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-11991</t>
+  </si>
+  <si>
+    <t>FA-11641</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
   </si>
   <si>
     <t>FA-11903</t>
   </si>
   <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11836</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11948</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11831</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11943</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11899</t>
-  </si>
-  <si>
-    <t>FA-11837</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11849</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>FA-11881</t>
-  </si>
-  <si>
-    <t>FA-11911</t>
-  </si>
-  <si>
-    <t>FA-11915</t>
-  </si>
-  <si>
-    <t>FA-11987</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11968</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11945</t>
-  </si>
-  <si>
-    <t>FA-11969</t>
-  </si>
-  <si>
-    <t>FA-11856</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>FA-11629</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11961</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11988</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11838</t>
-  </si>
-  <si>
-    <t>FA-11839</t>
-  </si>
-  <si>
-    <t>FA-11907</t>
-  </si>
-  <si>
-    <t>FA-11949</t>
-  </si>
-  <si>
-    <t>FA-11840</t>
-  </si>
-  <si>
-    <t>FA-11989</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11906</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11886</t>
-  </si>
-  <si>
-    <t>FA-11905</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11740</t>
-  </si>
-  <si>
-    <t>FA-11855</t>
-  </si>
-  <si>
-    <t>FA-12007</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11973</t>
+    <t>FA-11977</t>
   </si>
   <si>
     <t>JOZILDO TARQUINO DE BRITO</t>
   </si>
   <si>
-    <t>FA-11971</t>
-  </si>
-  <si>
-    <t>FA-11993</t>
-  </si>
-  <si>
-    <t>FA-11974</t>
+    <t>FA-12009</t>
+  </si>
+  <si>
+    <t>FA-11997</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11995</t>
+  </si>
+  <si>
+    <t>FA-12015</t>
+  </si>
+  <si>
+    <t>FA-11975</t>
+  </si>
+  <si>
+    <t>FA-11978</t>
   </si>
   <si>
     <t>ANA FLORIPES CARVALHO DA CUNHA</t>
   </si>
   <si>
-    <t>FA-11947</t>
-  </si>
-  <si>
-    <t>FA-11994</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11920</t>
-  </si>
-  <si>
-    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
-  </si>
-  <si>
-    <t>FA-11857</t>
-  </si>
-  <si>
-    <t>FA-11665</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
-    <t>FA-11972</t>
-  </si>
-  <si>
-    <t>FA-11992</t>
-  </si>
-  <si>
-    <t>FA-11932</t>
+    <t>FA-11858</t>
+  </si>
+  <si>
+    <t>FA-11976</t>
+  </si>
+  <si>
+    <t>FA-11921</t>
+  </si>
+  <si>
+    <t>FA-11933</t>
   </si>
   <si>
     <t>WESCLY JEAN DE MEDEIROS</t>
   </si>
   <si>
-    <t>FA-11962</t>
-  </si>
-  <si>
-    <t>FA-11865</t>
-  </si>
-  <si>
-    <t>FA-11950</t>
-  </si>
-  <si>
-    <t>FA-11653</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11991</t>
-  </si>
-  <si>
-    <t>FA-11641</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+    <t>FA-11963</t>
+  </si>
+  <si>
+    <t>FA-11998</t>
+  </si>
+  <si>
+    <t>FA-11866</t>
+  </si>
+  <si>
+    <t>FA-11951</t>
+  </si>
+  <si>
+    <t>FA-11996</t>
+  </si>
+  <si>
+    <t>FA-11981</t>
+  </si>
+  <si>
+    <t>FA-12010</t>
+  </si>
+  <si>
+    <t>FA-11982</t>
+  </si>
+  <si>
+    <t>FA-12001</t>
+  </si>
+  <si>
+    <t>FA-11979</t>
+  </si>
+  <si>
+    <t>FA-12000</t>
+  </si>
+  <si>
+    <t>FA-11980</t>
+  </si>
+  <si>
+    <t>FA-11860</t>
+  </si>
+  <si>
+    <t>FA-11922</t>
+  </si>
+  <si>
+    <t>FA-12002</t>
+  </si>
+  <si>
+    <t>FA-11934</t>
+  </si>
+  <si>
+    <t>FA-11964</t>
+  </si>
+  <si>
+    <t>FA-11867</t>
+  </si>
+  <si>
+    <t>FA-11952</t>
+  </si>
+  <si>
+    <t>FA-11999</t>
+  </si>
+  <si>
+    <t>FA-11985</t>
+  </si>
+  <si>
+    <t>FA-12011</t>
+  </si>
+  <si>
+    <t>FA-11983</t>
+  </si>
+  <si>
+    <t>FA-12008</t>
+  </si>
+  <si>
+    <t>FA-11986</t>
+  </si>
+  <si>
+    <t>FA-12004</t>
+  </si>
+  <si>
+    <t>FA-11923</t>
+  </si>
+  <si>
+    <t>FA-11984</t>
+  </si>
+  <si>
+    <t>FA-11862</t>
+  </si>
+  <si>
+    <t>FA-12005</t>
+  </si>
+  <si>
+    <t>FA-11935</t>
+  </si>
+  <si>
+    <t>FA-11965</t>
+  </si>
+  <si>
+    <t>FA-11868</t>
+  </si>
+  <si>
+    <t>FA-11953</t>
+  </si>
+  <si>
+    <t>FA-12003</t>
+  </si>
+  <si>
+    <t>FA-11924</t>
+  </si>
+  <si>
+    <t>FA-11864</t>
+  </si>
+  <si>
+    <t>FA-11936</t>
+  </si>
+  <si>
+    <t>FA-11869</t>
+  </si>
+  <si>
+    <t>FA-11954</t>
+  </si>
+  <si>
+    <t>FA-11925</t>
+  </si>
+  <si>
+    <t>FA-11937</t>
+  </si>
+  <si>
+    <t>FA-11955</t>
   </si>
 </sst>
 </file>
@@ -591,7 +711,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S85"/>
+  <dimension ref="A1:S122"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1" style="1"/>
@@ -732,7 +852,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-57</v>
+        <v>-58</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -741,7 +861,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-57</v>
+        <v>-58</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -791,7 +911,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -800,7 +920,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
@@ -850,7 +970,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -859,7 +979,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -876,25 +996,25 @@
         <v>33</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G9" s="7">
-        <v>46153</v>
+        <v>46170</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I9" s="7">
-        <v>46143</v>
+        <v>46195</v>
       </c>
       <c r="J9" s="7">
         <v>46195</v>
@@ -903,13 +1023,13 @@
         <v>46195</v>
       </c>
       <c r="L9" s="8">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -918,7 +1038,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -929,13 +1049,13 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>24</v>
@@ -947,40 +1067,40 @@
         <v>26</v>
       </c>
       <c r="G10" s="7">
-        <v>46170</v>
+        <v>46198</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="J10" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="K10" s="7">
-        <v>46195</v>
+        <v>46202</v>
       </c>
       <c r="L10" s="8">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-36</v>
+        <v>-30</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-36</v>
+        <v>-30</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S10" s="6" t="s">
         <v>24</v>
@@ -988,40 +1108,40 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G11" s="7">
-        <v>46153</v>
+        <v>24</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I11" s="7">
-        <v>46143</v>
+        <v>45930</v>
       </c>
       <c r="J11" s="7">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="K11" s="7">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="L11" s="8">
-        <v>50</v>
+        <v>185.5</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>28</v>
@@ -1030,7 +1150,7 @@
         <v>-29</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>28</v>
@@ -1039,7 +1159,7 @@
         <v>-29</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S11" s="6" t="s">
         <v>24</v>
@@ -1047,7 +1167,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>23</v>
@@ -1062,25 +1182,25 @@
         <v>25</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G12" s="7">
-        <v>46198</v>
+        <v>24</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I12" s="7">
-        <v>46202</v>
+        <v>46160</v>
       </c>
       <c r="J12" s="7">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="K12" s="7">
-        <v>46202</v>
+        <v>46160</v>
       </c>
       <c r="L12" s="8">
-        <v>620</v>
+        <v>200</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>28</v>
@@ -1089,16 +1209,16 @@
         <v>-29</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-29</v>
+        <v>-72</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S12" s="6" t="s">
         <v>24</v>
@@ -1106,10 +1226,10 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>24</v>
@@ -1127,19 +1247,19 @@
         <v>24</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I13" s="7">
-        <v>45930</v>
+        <v>46167</v>
       </c>
       <c r="J13" s="7">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="K13" s="7">
-        <v>46203</v>
+        <v>46167</v>
       </c>
       <c r="L13" s="8">
-        <v>185.5</v>
+        <v>110</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>28</v>
@@ -1148,16 +1268,16 @@
         <v>-28</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-28</v>
+        <v>-65</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S13" s="6" t="s">
         <v>24</v>
@@ -1165,58 +1285,58 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>24</v>
+      <c r="G14" s="7">
+        <v>46190</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I14" s="7">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="J14" s="7">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="K14" s="7">
-        <v>46160</v>
+        <v>46225</v>
       </c>
       <c r="L14" s="8">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-28</v>
+        <v>-23</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-71</v>
+        <v>-7</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S14" s="6" t="s">
         <v>24</v>
@@ -1227,10 +1347,10 @@
         <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>24</v>
@@ -1239,43 +1359,43 @@
         <v>25</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G15" s="7">
+        <v>46198</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I15" s="7">
-        <v>46167</v>
+        <v>46209</v>
       </c>
       <c r="J15" s="7">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="K15" s="7">
-        <v>46167</v>
+        <v>46209</v>
       </c>
       <c r="L15" s="8">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-27</v>
+        <v>-23</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-64</v>
+        <v>-23</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>24</v>
@@ -1283,31 +1403,31 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G16" s="7">
-        <v>46153</v>
+        <v>46198</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I16" s="7">
-        <v>46143</v>
+        <v>46209</v>
       </c>
       <c r="J16" s="7">
         <v>46209</v>
@@ -1316,25 +1436,25 @@
         <v>46209</v>
       </c>
       <c r="L16" s="8">
-        <v>50</v>
+        <v>620</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S16" s="6" t="s">
         <v>24</v>
@@ -1342,13 +1462,13 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>24</v>
@@ -1357,43 +1477,43 @@
         <v>25</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="7">
-        <v>46190</v>
+        <v>24</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I17" s="7">
-        <v>46174</v>
+        <v>46202</v>
       </c>
       <c r="J17" s="7">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="K17" s="7">
-        <v>46225</v>
+        <v>46202</v>
       </c>
       <c r="L17" s="8">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-6</v>
+        <v>-30</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S17" s="6" t="s">
         <v>24</v>
@@ -1401,13 +1521,13 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>24</v>
@@ -1416,43 +1536,43 @@
         <v>25</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="G18" s="7">
-        <v>46198</v>
+        <v>46190</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I18" s="7">
-        <v>46209</v>
+        <v>46174</v>
       </c>
       <c r="J18" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="K18" s="7">
-        <v>46209</v>
+        <v>46232</v>
       </c>
       <c r="L18" s="8">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="Q18" s="9">
-        <v>-22</v>
+        <v>0</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S18" s="6" t="s">
         <v>24</v>
@@ -1463,10 +1583,10 @@
         <v>46</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>24</v>
@@ -1484,34 +1604,34 @@
         <v>27</v>
       </c>
       <c r="I19" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="J19" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="K19" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="L19" s="8">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S19" s="6" t="s">
         <v>24</v>
@@ -1522,7 +1642,7 @@
         <v>47</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>24</v>
@@ -1537,40 +1657,40 @@
         <v>26</v>
       </c>
       <c r="G20" s="7">
-        <v>46182</v>
+        <v>46198</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I20" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="J20" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="K20" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="L20" s="8">
-        <v>680</v>
+        <v>620</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S20" s="6" t="s">
         <v>24</v>
@@ -1578,13 +1698,13 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="C21" s="6" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>24</v>
@@ -1593,43 +1713,43 @@
         <v>25</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G21" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G21" s="7">
+        <v>46203</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I21" s="7">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="J21" s="7">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="K21" s="7">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="L21" s="8">
-        <v>300</v>
+        <v>630</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-19</v>
+        <v>-16</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-29</v>
+        <v>-16</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S21" s="6" t="s">
         <v>24</v>
@@ -1637,31 +1757,31 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G22" s="7">
-        <v>46153</v>
+        <v>46231</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I22" s="7">
-        <v>46143</v>
+        <v>46216</v>
       </c>
       <c r="J22" s="7">
         <v>46216</v>
@@ -1670,25 +1790,25 @@
         <v>46216</v>
       </c>
       <c r="L22" s="8">
-        <v>50</v>
+        <v>630</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S22" s="6" t="s">
         <v>24</v>
@@ -1696,13 +1816,13 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>24</v>
@@ -1711,43 +1831,43 @@
         <v>25</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G23" s="7">
-        <v>46190</v>
+        <v>46198</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I23" s="7">
-        <v>46174</v>
+        <v>46216</v>
       </c>
       <c r="J23" s="7">
         <v>46216</v>
       </c>
       <c r="K23" s="7">
-        <v>46232</v>
+        <v>46216</v>
       </c>
       <c r="L23" s="8">
-        <v>50</v>
+        <v>650</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>1</v>
+        <v>-16</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="S23" s="6" t="s">
         <v>24</v>
@@ -1755,10 +1875,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>24</v>
@@ -1770,43 +1890,43 @@
         <v>25</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G24" s="7">
+        <v>46182</v>
       </c>
       <c r="H24" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I24" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="J24" s="7">
         <v>46216</v>
       </c>
       <c r="K24" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="L24" s="8">
-        <v>590</v>
+        <v>680</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-22</v>
+        <v>-16</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S24" s="6" t="s">
         <v>24</v>
@@ -1814,28 +1934,28 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G25" s="7">
-        <v>46198</v>
+        <v>46182</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="I25" s="7">
         <v>46216</v>
@@ -1847,25 +1967,25 @@
         <v>46216</v>
       </c>
       <c r="L25" s="8">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>24</v>
@@ -1873,10 +1993,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>23</v>
+        <v>61</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>24</v>
@@ -1888,43 +2008,43 @@
         <v>25</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="7">
-        <v>46198</v>
+        <v>24</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I26" s="7">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="J26" s="7">
-        <v>46216</v>
+        <v>46220</v>
       </c>
       <c r="K26" s="7">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="L26" s="8">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-15</v>
+        <v>-12</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-15</v>
+        <v>-23</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>24</v>
@@ -1932,13 +2052,13 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>24</v>
@@ -1947,43 +2067,43 @@
         <v>25</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="G27" s="7">
-        <v>46203</v>
+        <v>46190</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I27" s="7">
-        <v>46216</v>
+        <v>46174</v>
       </c>
       <c r="J27" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K27" s="7">
-        <v>46216</v>
+        <v>46239</v>
       </c>
       <c r="L27" s="8">
-        <v>630</v>
+        <v>50</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q27" s="9">
-        <v>-15</v>
+        <v>7</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S27" s="6" t="s">
         <v>24</v>
@@ -1991,13 +2111,13 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>24</v>
@@ -2006,43 +2126,43 @@
         <v>25</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="7">
-        <v>46198</v>
+        <v>24</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I28" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J28" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K28" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L28" s="8">
-        <v>650</v>
+        <v>76.01</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S28" s="6" t="s">
         <v>24</v>
@@ -2050,10 +2170,10 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>24</v>
@@ -2065,43 +2185,43 @@
         <v>25</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="7">
-        <v>46182</v>
+        <v>24</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I29" s="7">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="J29" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K29" s="7">
-        <v>46216</v>
+        <v>46209</v>
       </c>
       <c r="L29" s="8">
-        <v>680</v>
+        <v>330</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-15</v>
+        <v>-23</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S29" s="6" t="s">
         <v>24</v>
@@ -2109,16 +2229,16 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>25</v>
@@ -2127,40 +2247,40 @@
         <v>26</v>
       </c>
       <c r="G30" s="7">
-        <v>46203</v>
+        <v>46225</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I30" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J30" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K30" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L30" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S30" s="6" t="s">
         <v>24</v>
@@ -2168,10 +2288,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>24</v>
@@ -2180,46 +2300,46 @@
         <v>24</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="F31" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="7">
-        <v>46182</v>
+        <v>46225</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="I31" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J31" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K31" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L31" s="8">
-        <v>800</v>
+        <v>630</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S31" s="6" t="s">
         <v>24</v>
@@ -2227,10 +2347,10 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>24</v>
@@ -2245,40 +2365,40 @@
         <v>26</v>
       </c>
       <c r="G32" s="7">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="I32" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J32" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K32" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L32" s="8">
-        <v>800</v>
+        <v>630</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S32" s="6" t="s">
         <v>24</v>
@@ -2286,10 +2406,10 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>24</v>
@@ -2301,43 +2421,43 @@
         <v>25</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G33" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G33" s="7">
+        <v>46203</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I33" s="7">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="J33" s="7">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="K33" s="7">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="L33" s="8">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-11</v>
+        <v>-9</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-22</v>
+        <v>-9</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S33" s="6" t="s">
         <v>24</v>
@@ -2345,13 +2465,13 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>24</v>
@@ -2360,43 +2480,43 @@
         <v>25</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G34" s="7">
+        <v>46225</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I34" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J34" s="7">
         <v>46223</v>
       </c>
       <c r="K34" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L34" s="8">
-        <v>40</v>
+        <v>650</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S34" s="6" t="s">
         <v>24</v>
@@ -2404,13 +2524,13 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>24</v>
@@ -2419,43 +2539,43 @@
         <v>25</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G35" s="7">
-        <v>46190</v>
+        <v>46153</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I35" s="7">
-        <v>46174</v>
+        <v>46223</v>
       </c>
       <c r="J35" s="7">
         <v>46223</v>
       </c>
       <c r="K35" s="7">
-        <v>46239</v>
+        <v>46223</v>
       </c>
       <c r="L35" s="8">
-        <v>50</v>
+        <v>650</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P35" s="6" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>8</v>
+        <v>-9</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="S35" s="6" t="s">
         <v>24</v>
@@ -2463,31 +2583,31 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G36" s="7">
-        <v>46153</v>
+        <v>46188</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I36" s="7">
-        <v>46143</v>
+        <v>46223</v>
       </c>
       <c r="J36" s="7">
         <v>46223</v>
@@ -2496,25 +2616,25 @@
         <v>46223</v>
       </c>
       <c r="L36" s="8">
-        <v>50</v>
+        <v>650</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>24</v>
@@ -2522,58 +2642,58 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G37" s="7">
+        <v>46225</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I37" s="7">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="J37" s="7">
         <v>46223</v>
       </c>
       <c r="K37" s="7">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="L37" s="8">
-        <v>60</v>
+        <v>680</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-22</v>
+        <v>-9</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S37" s="6" t="s">
         <v>24</v>
@@ -2581,10 +2701,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>24</v>
@@ -2596,10 +2716,10 @@
         <v>25</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G38" s="7">
+        <v>46182</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>27</v>
@@ -2614,25 +2734,25 @@
         <v>46223</v>
       </c>
       <c r="L38" s="8">
-        <v>76.01</v>
+        <v>680</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S38" s="6" t="s">
         <v>24</v>
@@ -2640,10 +2760,10 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>76</v>
+        <v>55</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>24</v>
@@ -2655,43 +2775,43 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G39" s="7">
+        <v>46182</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I39" s="7">
-        <v>46188</v>
+        <v>46223</v>
       </c>
       <c r="J39" s="7">
         <v>46223</v>
       </c>
       <c r="K39" s="7">
-        <v>46188</v>
+        <v>46223</v>
       </c>
       <c r="L39" s="8">
-        <v>96.66</v>
+        <v>680</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-43</v>
+        <v>-9</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S39" s="6" t="s">
         <v>24</v>
@@ -2699,58 +2819,58 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G40" s="7">
+        <v>46203</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I40" s="7">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="J40" s="7">
         <v>46223</v>
       </c>
       <c r="K40" s="7">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="L40" s="8">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-22</v>
+        <v>-9</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S40" s="6" t="s">
         <v>24</v>
@@ -2758,10 +2878,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>24</v>
@@ -2770,46 +2890,46 @@
         <v>24</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G41" s="7">
+        <v>46182</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="I41" s="7">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="J41" s="7">
         <v>46223</v>
       </c>
       <c r="K41" s="7">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="L41" s="8">
-        <v>330</v>
+        <v>800</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-22</v>
+        <v>-9</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S41" s="6" t="s">
         <v>24</v>
@@ -2817,10 +2937,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>56</v>
+        <v>87</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>24</v>
@@ -2835,10 +2955,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="7">
-        <v>46203</v>
+        <v>46225</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="I42" s="7">
         <v>46223</v>
@@ -2850,25 +2970,25 @@
         <v>46223</v>
       </c>
       <c r="L42" s="8">
-        <v>630</v>
+        <v>1200</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S42" s="6" t="s">
         <v>24</v>
@@ -2876,10 +2996,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>24</v>
@@ -2891,10 +3011,10 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>27</v>
@@ -2903,13 +3023,13 @@
         <v>46223</v>
       </c>
       <c r="J43" s="7">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K43" s="7">
         <v>46223</v>
       </c>
       <c r="L43" s="8">
-        <v>630</v>
+        <v>3.91</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>28</v>
@@ -2918,16 +3038,16 @@
         <v>-8</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S43" s="6" t="s">
         <v>24</v>
@@ -2935,10 +3055,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>24</v>
@@ -2950,25 +3070,25 @@
         <v>25</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I44" s="7">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="J44" s="7">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K44" s="7">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="L44" s="8">
-        <v>630</v>
+        <v>56.19</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>28</v>
@@ -2977,16 +3097,16 @@
         <v>-8</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S44" s="6" t="s">
         <v>24</v>
@@ -2994,13 +3114,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>24</v>
+        <v>93</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>24</v>
@@ -3009,25 +3129,25 @@
         <v>25</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="7">
-        <v>46212</v>
+        <v>24</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I45" s="7">
         <v>46223</v>
       </c>
       <c r="J45" s="7">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K45" s="7">
         <v>46223</v>
       </c>
       <c r="L45" s="8">
-        <v>630</v>
+        <v>71</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>28</v>
@@ -3036,16 +3156,16 @@
         <v>-8</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S45" s="6" t="s">
         <v>24</v>
@@ -3053,13 +3173,13 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>24</v>
@@ -3068,25 +3188,25 @@
         <v>25</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I46" s="7">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="J46" s="7">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K46" s="7">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="L46" s="8">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>28</v>
@@ -3095,16 +3215,16 @@
         <v>-8</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q46" s="9">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S46" s="6" t="s">
         <v>24</v>
@@ -3112,10 +3232,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>24</v>
@@ -3127,43 +3247,43 @@
         <v>25</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="7">
-        <v>46188</v>
+        <v>24</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I47" s="7">
         <v>46223</v>
       </c>
       <c r="J47" s="7">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="K47" s="7">
         <v>46223</v>
       </c>
       <c r="L47" s="8">
-        <v>650</v>
+        <v>480</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S47" s="6" t="s">
         <v>24</v>
@@ -3171,10 +3291,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>24</v>
@@ -3186,43 +3306,43 @@
         <v>25</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="7">
-        <v>46153</v>
+        <v>24</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I48" s="7">
-        <v>46223</v>
+        <v>46188</v>
       </c>
       <c r="J48" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K48" s="7">
-        <v>46223</v>
+        <v>46188</v>
       </c>
       <c r="L48" s="8">
-        <v>650</v>
+        <v>20.66</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>-8</v>
+        <v>-44</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S48" s="6" t="s">
         <v>24</v>
@@ -3230,13 +3350,13 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>91</v>
+        <v>39</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>92</v>
+        <v>40</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>24</v>
@@ -3245,43 +3365,43 @@
         <v>25</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="G49" s="7">
-        <v>46225</v>
+        <v>46190</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I49" s="7">
-        <v>46223</v>
+        <v>46174</v>
       </c>
       <c r="J49" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K49" s="7">
-        <v>46223</v>
+        <v>46246</v>
       </c>
       <c r="L49" s="8">
-        <v>680</v>
+        <v>50</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q49" s="9">
-        <v>-8</v>
+        <v>14</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S49" s="6" t="s">
         <v>24</v>
@@ -3289,13 +3409,13 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>24</v>
@@ -3310,37 +3430,37 @@
         <v>46225</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I50" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J50" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K50" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L50" s="8">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S50" s="6" t="s">
         <v>24</v>
@@ -3348,10 +3468,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>24</v>
@@ -3366,40 +3486,40 @@
         <v>26</v>
       </c>
       <c r="G51" s="7">
-        <v>46182</v>
+        <v>46225</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I51" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J51" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K51" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L51" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S51" s="6" t="s">
         <v>24</v>
@@ -3407,11 +3527,11 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B52" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="C52" s="6" t="s">
         <v>24</v>
       </c>
@@ -3425,40 +3545,40 @@
         <v>26</v>
       </c>
       <c r="G52" s="7">
-        <v>46182</v>
+        <v>46212</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I52" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J52" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K52" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L52" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S52" s="6" t="s">
         <v>24</v>
@@ -3466,16 +3586,16 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="E53" s="6" t="s">
         <v>25</v>
@@ -3484,40 +3604,40 @@
         <v>26</v>
       </c>
       <c r="G53" s="7">
-        <v>46203</v>
+        <v>46231</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I53" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J53" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K53" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L53" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S53" s="6" t="s">
         <v>24</v>
@@ -3525,10 +3645,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>24</v>
@@ -3546,37 +3666,37 @@
         <v>46225</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="I54" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J54" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K54" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L54" s="8">
-        <v>800</v>
+        <v>630</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S54" s="6" t="s">
         <v>24</v>
@@ -3584,10 +3704,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>24</v>
@@ -3596,46 +3716,46 @@
         <v>24</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>64</v>
+        <v>25</v>
       </c>
       <c r="F55" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="7">
-        <v>46182</v>
+        <v>46210</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="I55" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J55" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K55" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L55" s="8">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S55" s="6" t="s">
         <v>24</v>
@@ -3643,10 +3763,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>24</v>
@@ -3661,40 +3781,40 @@
         <v>26</v>
       </c>
       <c r="G56" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>102</v>
+        <v>77</v>
       </c>
       <c r="I56" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J56" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K56" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L56" s="8">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S56" s="6" t="s">
         <v>24</v>
@@ -3702,13 +3822,13 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>24</v>
@@ -3717,43 +3837,43 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G57" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G57" s="7">
+        <v>46225</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I57" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J57" s="7">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="K57" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L57" s="8">
-        <v>3.91</v>
+        <v>650</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N57" s="9">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S57" s="6" t="s">
         <v>24</v>
@@ -3761,10 +3881,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>24</v>
@@ -3776,43 +3896,43 @@
         <v>25</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G58" s="7">
+        <v>46225</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I58" s="7">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="J58" s="7">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="K58" s="7">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="L58" s="8">
-        <v>56.19</v>
+        <v>680</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N58" s="9">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q58" s="9">
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S58" s="6" t="s">
         <v>24</v>
@@ -3820,13 +3940,13 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>24</v>
@@ -3835,43 +3955,43 @@
         <v>25</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G59" s="7">
+        <v>46225</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>77</v>
       </c>
       <c r="I59" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J59" s="7">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="K59" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L59" s="8">
-        <v>71</v>
+        <v>680</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N59" s="9">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q59" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S59" s="6" t="s">
         <v>24</v>
@@ -3879,10 +3999,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
@@ -3894,43 +4014,43 @@
         <v>25</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G60" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G60" s="7">
+        <v>46225</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="I60" s="7">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="J60" s="7">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="K60" s="7">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="L60" s="8">
-        <v>360.95</v>
+        <v>800</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N60" s="9">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q60" s="9">
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S60" s="6" t="s">
         <v>24</v>
@@ -3938,58 +4058,58 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B61" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F61" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G61" s="7">
+        <v>46160</v>
+      </c>
+      <c r="H61" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="C61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G61" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H61" s="6" t="s">
-        <v>77</v>
-      </c>
       <c r="I61" s="7">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="J61" s="7">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="K61" s="7">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="L61" s="8">
-        <v>550</v>
+        <v>1200</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N61" s="9">
-        <v>-7</v>
+        <v>-2</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q61" s="9">
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S61" s="6" t="s">
         <v>24</v>
@@ -3997,13 +4117,13 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
-        <v>43</v>
+        <v>117</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>24</v>
@@ -4012,43 +4132,43 @@
         <v>25</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G62" s="7">
-        <v>46190</v>
+        <v>46225</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="I62" s="7">
-        <v>46174</v>
+        <v>46230</v>
       </c>
       <c r="J62" s="7">
         <v>46230</v>
       </c>
       <c r="K62" s="7">
-        <v>46246</v>
+        <v>46230</v>
       </c>
       <c r="L62" s="8">
-        <v>50</v>
+        <v>1200</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N62" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="Q62" s="9">
-        <v>15</v>
+        <v>-2</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="S62" s="6" t="s">
         <v>24</v>
@@ -4056,31 +4176,31 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>32</v>
+        <v>118</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>33</v>
+        <v>119</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G63" s="7">
-        <v>46153</v>
+        <v>46160</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="I63" s="7">
-        <v>46143</v>
+        <v>46230</v>
       </c>
       <c r="J63" s="7">
         <v>46230</v>
@@ -4089,25 +4209,25 @@
         <v>46230</v>
       </c>
       <c r="L63" s="8">
-        <v>50</v>
+        <v>1200</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N63" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q63" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="S63" s="6" t="s">
         <v>24</v>
@@ -4115,16 +4235,16 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>75</v>
+        <v>120</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>25</v>
@@ -4136,19 +4256,19 @@
         <v>24</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I64" s="7">
-        <v>46188</v>
+        <v>46216</v>
       </c>
       <c r="J64" s="7">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K64" s="7">
-        <v>46188</v>
+        <v>46216</v>
       </c>
       <c r="L64" s="8">
-        <v>116.66</v>
+        <v>510</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>28</v>
@@ -4157,16 +4277,16 @@
         <v>-1</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q64" s="9">
-        <v>-43</v>
+        <v>-16</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="S64" s="6" t="s">
         <v>24</v>
@@ -4174,13 +4294,13 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>111</v>
+        <v>36</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>24</v>
@@ -4189,43 +4309,43 @@
         <v>25</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G65" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G65" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I65" s="7">
-        <v>46230</v>
+        <v>45930</v>
       </c>
       <c r="J65" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="K65" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="L65" s="8">
-        <v>600</v>
+        <v>185.5</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N65" s="9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q65" s="9">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S65" s="6" t="s">
         <v>24</v>
@@ -4233,13 +4353,13 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>112</v>
+        <v>97</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>113</v>
+        <v>24</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>24</v>
@@ -4248,43 +4368,43 @@
         <v>25</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G66" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G66" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I66" s="7">
-        <v>46230</v>
+        <v>46188</v>
       </c>
       <c r="J66" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K66" s="7">
-        <v>46230</v>
+        <v>46188</v>
       </c>
       <c r="L66" s="8">
-        <v>600</v>
+        <v>116.7</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N66" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q66" s="9">
-        <v>-1</v>
+        <v>-44</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="S66" s="6" t="s">
         <v>24</v>
@@ -4292,13 +4412,13 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>24</v>
@@ -4316,34 +4436,34 @@
         <v>27</v>
       </c>
       <c r="I67" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J67" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K67" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L67" s="8">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N67" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q67" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S67" s="6" t="s">
         <v>24</v>
@@ -4351,13 +4471,13 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>24</v>
@@ -4375,34 +4495,34 @@
         <v>27</v>
       </c>
       <c r="I68" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J68" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K68" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L68" s="8">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N68" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q68" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S68" s="6" t="s">
         <v>24</v>
@@ -4410,10 +4530,10 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>24</v>
@@ -4434,34 +4554,34 @@
         <v>27</v>
       </c>
       <c r="I69" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J69" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K69" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L69" s="8">
         <v>630</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N69" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q69" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S69" s="6" t="s">
         <v>24</v>
@@ -4469,10 +4589,10 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>24</v>
@@ -4487,40 +4607,40 @@
         <v>26</v>
       </c>
       <c r="G70" s="7">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I70" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J70" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K70" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L70" s="8">
         <v>630</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N70" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q70" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S70" s="6" t="s">
         <v>24</v>
@@ -4528,10 +4648,10 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>120</v>
+        <v>51</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>24</v>
@@ -4546,40 +4666,40 @@
         <v>26</v>
       </c>
       <c r="G71" s="7">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="H71" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I71" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J71" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K71" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L71" s="8">
         <v>630</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N71" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q71" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S71" s="6" t="s">
         <v>24</v>
@@ -4587,10 +4707,10 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>24</v>
@@ -4605,40 +4725,40 @@
         <v>26</v>
       </c>
       <c r="G72" s="7">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="H72" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I72" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J72" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K72" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L72" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N72" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q72" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S72" s="6" t="s">
         <v>24</v>
@@ -4646,10 +4766,10 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>24</v>
@@ -4664,40 +4784,40 @@
         <v>26</v>
       </c>
       <c r="G73" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I73" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J73" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K73" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L73" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N73" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q73" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S73" s="6" t="s">
         <v>24</v>
@@ -4705,10 +4825,10 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>24</v>
@@ -4723,40 +4843,40 @@
         <v>26</v>
       </c>
       <c r="G74" s="7">
-        <v>46160</v>
+        <v>46188</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="I74" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J74" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K74" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L74" s="8">
         <v>650</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N74" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q74" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S74" s="6" t="s">
         <v>24</v>
@@ -4764,13 +4884,13 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>24</v>
@@ -4788,34 +4908,34 @@
         <v>27</v>
       </c>
       <c r="I75" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J75" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K75" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L75" s="8">
         <v>650</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N75" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q75" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S75" s="6" t="s">
         <v>24</v>
@@ -4823,10 +4943,10 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>24</v>
@@ -4841,40 +4961,40 @@
         <v>26</v>
       </c>
       <c r="G76" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I76" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J76" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K76" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L76" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N76" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q76" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R76" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S76" s="6" t="s">
         <v>24</v>
@@ -4882,10 +5002,10 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>24</v>
@@ -4906,34 +5026,34 @@
         <v>77</v>
       </c>
       <c r="I77" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J77" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K77" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L77" s="8">
         <v>680</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N77" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q77" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S77" s="6" t="s">
         <v>24</v>
@@ -4941,10 +5061,10 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -4965,34 +5085,34 @@
         <v>77</v>
       </c>
       <c r="I78" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J78" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K78" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L78" s="8">
         <v>680</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N78" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q78" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S78" s="6" t="s">
         <v>24</v>
@@ -5000,10 +5120,10 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
@@ -5018,40 +5138,40 @@
         <v>26</v>
       </c>
       <c r="G79" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H79" s="6" t="s">
         <v>77</v>
       </c>
       <c r="I79" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J79" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K79" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L79" s="8">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N79" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q79" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R79" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S79" s="6" t="s">
         <v>24</v>
@@ -5059,10 +5179,10 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
@@ -5077,40 +5197,40 @@
         <v>26</v>
       </c>
       <c r="G80" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="I80" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J80" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K80" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L80" s="8">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N80" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q80" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S80" s="6" t="s">
         <v>24</v>
@@ -5118,16 +5238,16 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>25</v>
@@ -5136,40 +5256,40 @@
         <v>26</v>
       </c>
       <c r="G81" s="7">
-        <v>46160</v>
+        <v>46225</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="I81" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J81" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K81" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L81" s="8">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N81" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q81" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S81" s="6" t="s">
         <v>24</v>
@@ -5177,10 +5297,10 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>24</v>
@@ -5198,37 +5318,37 @@
         <v>46225</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="I82" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J82" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K82" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L82" s="8">
         <v>1200</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N82" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q82" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S82" s="6" t="s">
         <v>24</v>
@@ -5236,16 +5356,16 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>135</v>
+        <v>24</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>25</v>
@@ -5254,40 +5374,40 @@
         <v>26</v>
       </c>
       <c r="G83" s="7">
-        <v>46160</v>
+        <v>46225</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>102</v>
+        <v>27</v>
       </c>
       <c r="I83" s="7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="J83" s="7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="K83" s="7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="L83" s="8">
-        <v>1200</v>
+        <v>600</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="N83" s="9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="Q83" s="9">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="R83" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="S83" s="6" t="s">
         <v>24</v>
@@ -5295,13 +5415,13 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>24</v>
+        <v>142</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>24</v>
+        <v>100</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>24</v>
@@ -5310,70 +5430,2253 @@
         <v>25</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G84" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G84" s="7">
+        <v>46225</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I84" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J84" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K84" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L84" s="8">
+        <v>600</v>
+      </c>
+      <c r="M84" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N84" s="9">
+        <v>12</v>
+      </c>
+      <c r="O84" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P84" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q84" s="9">
+        <v>12</v>
+      </c>
+      <c r="R84" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S84" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B85" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G85" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H85" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I85" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J85" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K85" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L85" s="8">
+        <v>630</v>
+      </c>
+      <c r="M85" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N85" s="9">
+        <v>12</v>
+      </c>
+      <c r="O85" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P85" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q85" s="9">
+        <v>12</v>
+      </c>
+      <c r="R85" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S85" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B86" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G86" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H86" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I86" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J86" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K86" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L86" s="8">
+        <v>630</v>
+      </c>
+      <c r="M86" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N86" s="9">
+        <v>12</v>
+      </c>
+      <c r="O86" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P86" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q86" s="9">
+        <v>12</v>
+      </c>
+      <c r="R86" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S86" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F87" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G87" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H87" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I87" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J87" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K87" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L87" s="8">
+        <v>630</v>
+      </c>
+      <c r="M87" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N87" s="9">
+        <v>12</v>
+      </c>
+      <c r="O87" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P87" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q87" s="9">
+        <v>12</v>
+      </c>
+      <c r="R87" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S87" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G88" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H88" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I88" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J88" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K88" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L88" s="8">
+        <v>630</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N88" s="9">
+        <v>12</v>
+      </c>
+      <c r="O88" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P88" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q88" s="9">
+        <v>12</v>
+      </c>
+      <c r="R88" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S88" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D89" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F89" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H89" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I89" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J89" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K89" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L89" s="8">
+        <v>650</v>
+      </c>
+      <c r="M89" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N89" s="9">
+        <v>12</v>
+      </c>
+      <c r="O89" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P89" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q89" s="9">
+        <v>12</v>
+      </c>
+      <c r="R89" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S89" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E90" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F90" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G90" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H90" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I90" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J90" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K90" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L90" s="8">
+        <v>650</v>
+      </c>
+      <c r="M90" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N90" s="9">
+        <v>12</v>
+      </c>
+      <c r="O90" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P90" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q90" s="9">
+        <v>12</v>
+      </c>
+      <c r="R90" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S90" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B91" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G91" s="7">
+        <v>46210</v>
+      </c>
+      <c r="H91" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I91" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J91" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K91" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L91" s="8">
+        <v>650</v>
+      </c>
+      <c r="M91" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N91" s="9">
+        <v>12</v>
+      </c>
+      <c r="O91" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P91" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q91" s="9">
+        <v>12</v>
+      </c>
+      <c r="R91" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S91" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B92" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G92" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I92" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J92" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K92" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L92" s="8">
+        <v>680</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N92" s="9">
+        <v>12</v>
+      </c>
+      <c r="O92" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P92" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q92" s="9">
+        <v>12</v>
+      </c>
+      <c r="R92" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S92" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B93" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C93" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D93" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G93" s="7">
+        <v>46212</v>
+      </c>
+      <c r="H93" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I93" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J93" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K93" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L93" s="8">
+        <v>680</v>
+      </c>
+      <c r="M93" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N93" s="9">
+        <v>12</v>
+      </c>
+      <c r="O93" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P93" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q93" s="9">
+        <v>12</v>
+      </c>
+      <c r="R93" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S93" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B94" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D94" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G94" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H94" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I94" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J94" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K94" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L94" s="8">
+        <v>680</v>
+      </c>
+      <c r="M94" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N94" s="9">
+        <v>12</v>
+      </c>
+      <c r="O94" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P94" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q94" s="9">
+        <v>12</v>
+      </c>
+      <c r="R94" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S94" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B95" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D95" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G95" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H95" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I95" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J95" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K95" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L95" s="8">
+        <v>700</v>
+      </c>
+      <c r="M95" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N95" s="9">
+        <v>12</v>
+      </c>
+      <c r="O95" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P95" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q95" s="9">
+        <v>12</v>
+      </c>
+      <c r="R95" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S95" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="B96" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D96" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G96" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H96" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I96" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J96" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K96" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L96" s="8">
+        <v>800</v>
+      </c>
+      <c r="M96" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N96" s="9">
+        <v>12</v>
+      </c>
+      <c r="O96" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P96" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q96" s="9">
+        <v>12</v>
+      </c>
+      <c r="R96" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S96" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D97" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E97" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F97" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G97" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H97" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I97" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J97" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K97" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L97" s="8">
+        <v>1200</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N97" s="9">
+        <v>12</v>
+      </c>
+      <c r="O97" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P97" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q97" s="9">
+        <v>12</v>
+      </c>
+      <c r="R97" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S97" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G98" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I98" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J98" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K98" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L98" s="8">
+        <v>600</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N98" s="9">
+        <v>19</v>
+      </c>
+      <c r="O98" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P98" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q98" s="9">
+        <v>19</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S98" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I99" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J99" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K99" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L99" s="8">
+        <v>600</v>
+      </c>
+      <c r="M99" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N99" s="9">
+        <v>19</v>
+      </c>
+      <c r="O99" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P99" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q99" s="9">
+        <v>19</v>
+      </c>
+      <c r="R99" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S99" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G100" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I100" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J100" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K100" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L100" s="8">
+        <v>630</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N100" s="9">
+        <v>19</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P100" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q100" s="9">
+        <v>19</v>
+      </c>
+      <c r="R100" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S100" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B101" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C101" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E101" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F101" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G101" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H101" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I101" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J101" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K101" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L101" s="8">
+        <v>630</v>
+      </c>
+      <c r="M101" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N101" s="9">
+        <v>19</v>
+      </c>
+      <c r="O101" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P101" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q101" s="9">
+        <v>19</v>
+      </c>
+      <c r="R101" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S101" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B102" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C102" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E102" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F102" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G102" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I102" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J102" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K102" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L102" s="8">
+        <v>630</v>
+      </c>
+      <c r="M102" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N102" s="9">
+        <v>19</v>
+      </c>
+      <c r="O102" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P102" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q102" s="9">
+        <v>19</v>
+      </c>
+      <c r="R102" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S102" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B103" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C103" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D103" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F103" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G103" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H103" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I103" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J103" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K103" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L103" s="8">
+        <v>630</v>
+      </c>
+      <c r="M103" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N103" s="9">
+        <v>19</v>
+      </c>
+      <c r="O103" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P103" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q103" s="9">
+        <v>19</v>
+      </c>
+      <c r="R103" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S103" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D104" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F104" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G104" s="7">
+        <v>46210</v>
+      </c>
+      <c r="H104" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I104" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J104" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K104" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L104" s="8">
+        <v>650</v>
+      </c>
+      <c r="M104" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N104" s="9">
+        <v>19</v>
+      </c>
+      <c r="O104" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P104" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q104" s="9">
+        <v>19</v>
+      </c>
+      <c r="R104" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S104" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F105" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G105" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H105" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I105" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J105" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K105" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L105" s="8">
+        <v>650</v>
+      </c>
+      <c r="M105" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N105" s="9">
+        <v>19</v>
+      </c>
+      <c r="O105" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P105" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q105" s="9">
+        <v>19</v>
+      </c>
+      <c r="R105" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S105" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="B106" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D106" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F106" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G106" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H106" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I106" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J106" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K106" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L106" s="8">
+        <v>650</v>
+      </c>
+      <c r="M106" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N106" s="9">
+        <v>19</v>
+      </c>
+      <c r="O106" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P106" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q106" s="9">
+        <v>19</v>
+      </c>
+      <c r="R106" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S106" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B107" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F107" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G107" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H107" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I107" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J107" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K107" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L107" s="8">
+        <v>680</v>
+      </c>
+      <c r="M107" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N107" s="9">
+        <v>19</v>
+      </c>
+      <c r="O107" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P107" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q107" s="9">
+        <v>19</v>
+      </c>
+      <c r="R107" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S107" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="B108" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E108" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G108" s="7">
+        <v>46212</v>
+      </c>
+      <c r="H108" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I108" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J108" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K108" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L108" s="8">
+        <v>680</v>
+      </c>
+      <c r="M108" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N108" s="9">
+        <v>19</v>
+      </c>
+      <c r="O108" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P108" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q108" s="9">
+        <v>19</v>
+      </c>
+      <c r="R108" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S108" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B109" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E109" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F109" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G109" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H109" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I109" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J109" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K109" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L109" s="8">
+        <v>680</v>
+      </c>
+      <c r="M109" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N109" s="9">
+        <v>19</v>
+      </c>
+      <c r="O109" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P109" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q109" s="9">
+        <v>19</v>
+      </c>
+      <c r="R109" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S109" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="B110" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E110" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F110" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G110" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H110" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I110" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J110" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K110" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L110" s="8">
+        <v>700</v>
+      </c>
+      <c r="M110" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N110" s="9">
+        <v>19</v>
+      </c>
+      <c r="O110" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P110" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q110" s="9">
+        <v>19</v>
+      </c>
+      <c r="R110" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S110" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B111" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F111" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G111" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H111" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I111" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J111" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K111" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L111" s="8">
+        <v>800</v>
+      </c>
+      <c r="M111" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N111" s="9">
+        <v>19</v>
+      </c>
+      <c r="O111" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P111" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q111" s="9">
+        <v>19</v>
+      </c>
+      <c r="R111" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S111" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="B112" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D112" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E112" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F112" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G112" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H112" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="I112" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J112" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K112" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L112" s="8">
+        <v>1200</v>
+      </c>
+      <c r="M112" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N112" s="9">
+        <v>19</v>
+      </c>
+      <c r="O112" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P112" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q112" s="9">
+        <v>19</v>
+      </c>
+      <c r="R112" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S112" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B113" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D113" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E113" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F113" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G113" s="7">
+        <v>46210</v>
+      </c>
+      <c r="H113" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I113" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J113" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K113" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L113" s="8">
+        <v>650</v>
+      </c>
+      <c r="M113" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N113" s="9">
+        <v>26</v>
+      </c>
+      <c r="O113" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P113" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q113" s="9">
+        <v>26</v>
+      </c>
+      <c r="R113" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S113" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="B114" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C114" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E114" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F114" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G114" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I114" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J114" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K114" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L114" s="8">
+        <v>650</v>
+      </c>
+      <c r="M114" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N114" s="9">
+        <v>26</v>
+      </c>
+      <c r="O114" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P114" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q114" s="9">
+        <v>26</v>
+      </c>
+      <c r="R114" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S114" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D115" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E115" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F115" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G115" s="7">
+        <v>46212</v>
+      </c>
+      <c r="H115" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I115" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J115" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K115" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L115" s="8">
+        <v>680</v>
+      </c>
+      <c r="M115" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N115" s="9">
+        <v>26</v>
+      </c>
+      <c r="O115" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P115" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q115" s="9">
+        <v>26</v>
+      </c>
+      <c r="R115" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S115" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D116" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E116" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F116" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G116" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I116" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J116" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K116" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L116" s="8">
+        <v>700</v>
+      </c>
+      <c r="M116" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N116" s="9">
+        <v>26</v>
+      </c>
+      <c r="O116" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P116" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q116" s="9">
+        <v>26</v>
+      </c>
+      <c r="R116" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S116" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B117" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E117" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G117" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H117" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I117" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J117" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K117" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L117" s="8">
+        <v>800</v>
+      </c>
+      <c r="M117" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N117" s="9">
+        <v>26</v>
+      </c>
+      <c r="O117" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P117" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q117" s="9">
+        <v>26</v>
+      </c>
+      <c r="R117" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S117" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B118" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C118" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D118" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E118" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F118" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G118" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I118" s="7">
         <v>45930</v>
       </c>
-      <c r="J84" s="7">
-        <v>46233</v>
-      </c>
-      <c r="K84" s="7">
-        <v>46233</v>
-      </c>
-      <c r="L84" s="8">
+      <c r="J118" s="7">
+        <v>46264</v>
+      </c>
+      <c r="K118" s="7">
+        <v>46264</v>
+      </c>
+      <c r="L118" s="8">
         <v>185.5</v>
       </c>
-      <c r="M84" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N84" s="9">
-        <v>2</v>
-      </c>
-      <c r="O84" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P84" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q84" s="9">
-        <v>2</v>
-      </c>
-      <c r="R84" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S84" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="85" ht="23" customHeight="1">
-      <c r="A85" s="10"/>
-      <c r="B85" s="10"/>
-      <c r="C85" s="10"/>
-      <c r="D85" s="10"/>
-      <c r="E85" s="10"/>
-      <c r="F85" s="10"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="10"/>
-      <c r="I85" s="11"/>
-      <c r="J85" s="11"/>
-      <c r="K85" s="11"/>
-      <c r="L85" s="12">
-        <f>SUM(L6:L84)</f>
-      </c>
-      <c r="M85" s="10"/>
-      <c r="N85" s="13"/>
-      <c r="O85" s="10"/>
-      <c r="P85" s="10"/>
-      <c r="Q85" s="13"/>
-      <c r="R85" s="10"/>
-      <c r="S85" s="10"/>
+      <c r="M118" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N118" s="9">
+        <v>32</v>
+      </c>
+      <c r="O118" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P118" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q118" s="9">
+        <v>32</v>
+      </c>
+      <c r="R118" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S118" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D119" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E119" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F119" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G119" s="7">
+        <v>46210</v>
+      </c>
+      <c r="H119" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I119" s="7">
+        <v>46265</v>
+      </c>
+      <c r="J119" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K119" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L119" s="8">
+        <v>650</v>
+      </c>
+      <c r="M119" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N119" s="9">
+        <v>33</v>
+      </c>
+      <c r="O119" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P119" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q119" s="9">
+        <v>33</v>
+      </c>
+      <c r="R119" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S119" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G120" s="7">
+        <v>46212</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="I120" s="7">
+        <v>46265</v>
+      </c>
+      <c r="J120" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K120" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L120" s="8">
+        <v>680</v>
+      </c>
+      <c r="M120" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N120" s="9">
+        <v>33</v>
+      </c>
+      <c r="O120" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P120" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q120" s="9">
+        <v>33</v>
+      </c>
+      <c r="R120" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S120" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B121" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C121" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D121" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E121" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F121" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G121" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I121" s="7">
+        <v>46265</v>
+      </c>
+      <c r="J121" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K121" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L121" s="8">
+        <v>800</v>
+      </c>
+      <c r="M121" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="N121" s="9">
+        <v>33</v>
+      </c>
+      <c r="O121" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P121" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q121" s="9">
+        <v>33</v>
+      </c>
+      <c r="R121" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S121" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" ht="23" customHeight="1">
+      <c r="A122" s="10"/>
+      <c r="B122" s="10"/>
+      <c r="C122" s="10"/>
+      <c r="D122" s="10"/>
+      <c r="E122" s="10"/>
+      <c r="F122" s="10"/>
+      <c r="G122" s="11"/>
+      <c r="H122" s="10"/>
+      <c r="I122" s="11"/>
+      <c r="J122" s="11"/>
+      <c r="K122" s="11"/>
+      <c r="L122" s="12">
+        <f>SUM(L6:L121)</f>
+      </c>
+      <c r="M122" s="10"/>
+      <c r="N122" s="13"/>
+      <c r="O122" s="10"/>
+      <c r="P122" s="10"/>
+      <c r="Q122" s="13"/>
+      <c r="R122" s="10"/>
+      <c r="S122" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:S5"/>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$122</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$165</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quarta-feira, 29 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em quinta-feira, 30 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -139,12 +139,12 @@
     <t>FA-11879</t>
   </si>
   <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
     <t>FA-11559</t>
   </si>
   <si>
@@ -169,291 +169,351 @@
     <t>FA-11876</t>
   </si>
   <si>
+    <t>FA-12012</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-11884</t>
+  </si>
+  <si>
+    <t>FA-11887</t>
+  </si>
+  <si>
+    <t>FA-11913</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11885</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11834</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11836</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-11831</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-11911</t>
+  </si>
+  <si>
+    <t>FA-11968</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11987</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11915</t>
+  </si>
+  <si>
+    <t>FA-11969</t>
+  </si>
+  <si>
+    <t>FA-11856</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-11961</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-11839</t>
+  </si>
+  <si>
+    <t>FA-11838</t>
+  </si>
+  <si>
+    <t>FA-11907</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11840</t>
+  </si>
+  <si>
+    <t>FA-11989</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11906</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11886</t>
+  </si>
+  <si>
+    <t>FA-11905</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11855</t>
+  </si>
+  <si>
+    <t>FA-11945</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>FA-11849</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-12018</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-12014</t>
+  </si>
+  <si>
+    <t>FA-12007</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-12047</t>
+  </si>
+  <si>
+    <t>FA-11971</t>
+  </si>
+  <si>
+    <t>FA-11947</t>
+  </si>
+  <si>
+    <t>FA-12031</t>
+  </si>
+  <si>
+    <t>FA-11993</t>
+  </si>
+  <si>
+    <t>FA-11920</t>
+  </si>
+  <si>
+    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
+  </si>
+  <si>
+    <t>FA-11857</t>
+  </si>
+  <si>
+    <t>FA-11972</t>
+  </si>
+  <si>
+    <t>FA-12044</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11992</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11962</t>
+  </si>
+  <si>
+    <t>FA-12017</t>
+  </si>
+  <si>
+    <t>FA-12019</t>
+  </si>
+  <si>
+    <t>FA-12030</t>
+  </si>
+  <si>
+    <t>FA-12046</t>
+  </si>
+  <si>
+    <t>FA-12016</t>
+  </si>
+  <si>
+    <t>FA-11653</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-11641</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11991</t>
+  </si>
+  <si>
+    <t>FA-11903</t>
+  </si>
+  <si>
     <t>HOJE</t>
   </si>
   <si>
-    <t>FA-11884</t>
-  </si>
-  <si>
-    <t>FA-11887</t>
-  </si>
-  <si>
-    <t>FA-11913</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-12012</t>
-  </si>
-  <si>
-    <t>GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t>FA-11885</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11834</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11836</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11831</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11837</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11911</t>
-  </si>
-  <si>
-    <t>FA-11968</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11987</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-12013</t>
-  </si>
-  <si>
-    <t>FA-11915</t>
-  </si>
-  <si>
-    <t>FA-11969</t>
-  </si>
-  <si>
-    <t>FA-11629</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11856</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>FA-11961</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-11839</t>
-  </si>
-  <si>
-    <t>FA-11838</t>
-  </si>
-  <si>
-    <t>FA-11907</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-11840</t>
-  </si>
-  <si>
-    <t>FA-11989</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11906</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11886</t>
-  </si>
-  <si>
-    <t>FA-11905</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11855</t>
-  </si>
-  <si>
-    <t>FA-11945</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>FA-11849</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-12007</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-11971</t>
-  </si>
-  <si>
-    <t>FA-11947</t>
-  </si>
-  <si>
-    <t>FA-12014</t>
-  </si>
-  <si>
-    <t>FA-11993</t>
-  </si>
-  <si>
-    <t>FA-11920</t>
-  </si>
-  <si>
-    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
-  </si>
-  <si>
-    <t>FA-11857</t>
-  </si>
-  <si>
-    <t>FA-11972</t>
-  </si>
-  <si>
-    <t>FA-11992</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11962</t>
-  </si>
-  <si>
-    <t>FA-11950</t>
+    <t>FA-11977</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-12009</t>
+  </si>
+  <si>
+    <t>FA-12052</t>
+  </si>
+  <si>
+    <t>FA-11975</t>
+  </si>
+  <si>
+    <t>FA-12034</t>
+  </si>
+  <si>
+    <t>FA-12015</t>
+  </si>
+  <si>
+    <t>FA-11997</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-12048</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11978</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-11995</t>
+  </si>
+  <si>
+    <t>FA-11858</t>
+  </si>
+  <si>
+    <t>FA-11976</t>
+  </si>
+  <si>
+    <t>FA-12049</t>
+  </si>
+  <si>
+    <t>FA-12062</t>
+  </si>
+  <si>
+    <t>WILSON COUTINHO BEZERRA</t>
+  </si>
+  <si>
+    <t>FA-11921</t>
+  </si>
+  <si>
+    <t>FA-12036</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12029</t>
+  </si>
+  <si>
+    <t>FA-11998</t>
+  </si>
+  <si>
+    <t>FA-11933</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-12022</t>
+  </si>
+  <si>
+    <t>FA-12035</t>
+  </si>
+  <si>
+    <t>FA-11963</t>
+  </si>
+  <si>
+    <t>FA-12021</t>
+  </si>
+  <si>
+    <t>FA-11866</t>
+  </si>
+  <si>
+    <t>FA-12050</t>
+  </si>
+  <si>
+    <t>FA-12020</t>
+  </si>
+  <si>
+    <t>FA-11951</t>
   </si>
   <si>
     <t>ANNY KATARINA ACIOLE DA SILVA</t>
   </si>
   <si>
-    <t>FA-11653</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11991</t>
-  </si>
-  <si>
-    <t>FA-11641</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11903</t>
-  </si>
-  <si>
-    <t>FA-11977</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-12009</t>
-  </si>
-  <si>
-    <t>FA-11997</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11995</t>
-  </si>
-  <si>
-    <t>FA-12015</t>
-  </si>
-  <si>
-    <t>FA-11975</t>
-  </si>
-  <si>
-    <t>FA-11978</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-11858</t>
-  </si>
-  <si>
-    <t>FA-11976</t>
-  </si>
-  <si>
-    <t>FA-11921</t>
-  </si>
-  <si>
-    <t>FA-11933</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11963</t>
-  </si>
-  <si>
-    <t>FA-11998</t>
-  </si>
-  <si>
-    <t>FA-11866</t>
-  </si>
-  <si>
-    <t>FA-11951</t>
-  </si>
-  <si>
     <t>FA-11996</t>
   </si>
   <si>
@@ -463,39 +523,75 @@
     <t>FA-12010</t>
   </si>
   <si>
+    <t>FA-12055</t>
+  </si>
+  <si>
+    <t>FA-12037</t>
+  </si>
+  <si>
+    <t>FA-12000</t>
+  </si>
+  <si>
+    <t>FA-11979</t>
+  </si>
+  <si>
+    <t>FA-12001</t>
+  </si>
+  <si>
     <t>FA-11982</t>
   </si>
   <si>
-    <t>FA-12001</t>
-  </si>
-  <si>
-    <t>FA-11979</t>
-  </si>
-  <si>
-    <t>FA-12000</t>
+    <t>FA-12053</t>
   </si>
   <si>
     <t>FA-11980</t>
   </si>
   <si>
+    <t>FA-12054</t>
+  </si>
+  <si>
+    <t>FA-11922</t>
+  </si>
+  <si>
     <t>FA-11860</t>
   </si>
   <si>
-    <t>FA-11922</t>
+    <t>FA-12063</t>
+  </si>
+  <si>
+    <t>FA-12039</t>
+  </si>
+  <si>
+    <t>FA-11934</t>
+  </si>
+  <si>
+    <t>FA-12038</t>
+  </si>
+  <si>
+    <t>FA-11964</t>
+  </si>
+  <si>
+    <t>FA-12033</t>
   </si>
   <si>
     <t>FA-12002</t>
   </si>
   <si>
-    <t>FA-11934</t>
-  </si>
-  <si>
-    <t>FA-11964</t>
+    <t>FA-12025</t>
+  </si>
+  <si>
+    <t>FA-12024</t>
+  </si>
+  <si>
+    <t>FA-12051</t>
   </si>
   <si>
     <t>FA-11867</t>
   </si>
   <si>
+    <t>FA-12023</t>
+  </si>
+  <si>
     <t>FA-11952</t>
   </si>
   <si>
@@ -508,13 +604,22 @@
     <t>FA-12011</t>
   </si>
   <si>
+    <t>FA-12059</t>
+  </si>
+  <si>
+    <t>FA-12008</t>
+  </si>
+  <si>
+    <t>FA-11986</t>
+  </si>
+  <si>
+    <t>FA-12057</t>
+  </si>
+  <si>
     <t>FA-11983</t>
   </si>
   <si>
-    <t>FA-12008</t>
-  </si>
-  <si>
-    <t>FA-11986</t>
+    <t>FA-12040</t>
   </si>
   <si>
     <t>FA-12004</t>
@@ -529,18 +634,45 @@
     <t>FA-11862</t>
   </si>
   <si>
+    <t>FA-12058</t>
+  </si>
+  <si>
+    <t>FA-12064</t>
+  </si>
+  <si>
+    <t>FA-12041</t>
+  </si>
+  <si>
+    <t>FA-12027</t>
+  </si>
+  <si>
+    <t>FA-11935</t>
+  </si>
+  <si>
+    <t>FA-12042</t>
+  </si>
+  <si>
+    <t>FA-12043</t>
+  </si>
+  <si>
+    <t>FA-12028</t>
+  </si>
+  <si>
     <t>FA-12005</t>
   </si>
   <si>
-    <t>FA-11935</t>
-  </si>
-  <si>
     <t>FA-11965</t>
   </si>
   <si>
+    <t>FA-12056</t>
+  </si>
+  <si>
     <t>FA-11868</t>
   </si>
   <si>
+    <t>FA-12026</t>
+  </si>
+  <si>
     <t>FA-11953</t>
   </si>
   <si>
@@ -553,6 +685,9 @@
     <t>FA-11864</t>
   </si>
   <si>
+    <t>FA-12065</t>
+  </si>
+  <si>
     <t>FA-11936</t>
   </si>
   <si>
@@ -560,6 +695,9 @@
   </si>
   <si>
     <t>FA-11954</t>
+  </si>
+  <si>
+    <t>FA-12066</t>
   </si>
   <si>
     <t>FA-11925</t>
@@ -711,7 +849,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S122"/>
+  <dimension ref="A1:S165"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1" style="1"/>
@@ -852,7 +990,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -861,7 +999,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-58</v>
+        <v>-59</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -911,7 +1049,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -920,7 +1058,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
@@ -970,7 +1108,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -979,7 +1117,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -1029,7 +1167,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -1038,7 +1176,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1088,19 +1226,19 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S10" s="6" t="s">
         <v>24</v>
@@ -1111,7 +1249,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>24</v>
@@ -1147,19 +1285,19 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S11" s="6" t="s">
         <v>24</v>
@@ -1206,16 +1344,16 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-72</v>
+        <v>-73</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>29</v>
@@ -1265,16 +1403,16 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-65</v>
+        <v>-66</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>29</v>
@@ -1324,19 +1462,19 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S14" s="6" t="s">
         <v>24</v>
@@ -1383,19 +1521,19 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>24</v>
@@ -1442,19 +1580,19 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S16" s="6" t="s">
         <v>24</v>
@@ -1501,19 +1639,19 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S17" s="6" t="s">
         <v>24</v>
@@ -1560,19 +1698,19 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S18" s="6" t="s">
         <v>24</v>
@@ -1580,13 +1718,13 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>40</v>
-      </c>
       <c r="C19" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>24</v>
@@ -1598,7 +1736,7 @@
         <v>26</v>
       </c>
       <c r="G19" s="7">
-        <v>46198</v>
+        <v>46231</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>27</v>
@@ -1613,25 +1751,25 @@
         <v>46216</v>
       </c>
       <c r="L19" s="8">
-        <v>600</v>
+        <v>450</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S19" s="6" t="s">
         <v>24</v>
@@ -1642,10 +1780,10 @@
         <v>47</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>24</v>
@@ -1672,25 +1810,25 @@
         <v>46216</v>
       </c>
       <c r="L20" s="8">
-        <v>620</v>
+        <v>600</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S20" s="6" t="s">
         <v>24</v>
@@ -1701,7 +1839,7 @@
         <v>48</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>49</v>
+        <v>23</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>24</v>
@@ -1716,7 +1854,7 @@
         <v>26</v>
       </c>
       <c r="G21" s="7">
-        <v>46203</v>
+        <v>46198</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>27</v>
@@ -1731,25 +1869,25 @@
         <v>46216</v>
       </c>
       <c r="L21" s="8">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S21" s="6" t="s">
         <v>24</v>
@@ -1757,11 +1895,11 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>51</v>
-      </c>
       <c r="C22" s="6" t="s">
         <v>24</v>
       </c>
@@ -1775,7 +1913,7 @@
         <v>26</v>
       </c>
       <c r="G22" s="7">
-        <v>46231</v>
+        <v>46203</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>27</v>
@@ -1796,19 +1934,19 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S22" s="6" t="s">
         <v>24</v>
@@ -1816,13 +1954,13 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B23" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>53</v>
-      </c>
       <c r="C23" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>24</v>
@@ -1855,19 +1993,19 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S23" s="6" t="s">
         <v>24</v>
@@ -1875,10 +2013,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="6" t="s">
         <v>54</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>55</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>24</v>
@@ -1914,19 +2052,19 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S24" s="6" t="s">
         <v>24</v>
@@ -1934,19 +2072,19 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="C25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E25" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>58</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>26</v>
@@ -1955,7 +2093,7 @@
         <v>46182</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I25" s="7">
         <v>46216</v>
@@ -1973,19 +2111,19 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>24</v>
@@ -1993,10 +2131,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>60</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>61</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>24</v>
@@ -2032,19 +2170,19 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>24</v>
@@ -2091,16 +2229,16 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P27" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q27" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>24</v>
@@ -2111,10 +2249,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>24</v>
@@ -2135,34 +2273,34 @@
         <v>27</v>
       </c>
       <c r="I28" s="7">
-        <v>46223</v>
+        <v>46209</v>
       </c>
       <c r="J28" s="7">
         <v>46223</v>
       </c>
       <c r="K28" s="7">
-        <v>46223</v>
+        <v>46209</v>
       </c>
       <c r="L28" s="8">
-        <v>76.01</v>
+        <v>330</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-9</v>
+        <v>-24</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S28" s="6" t="s">
         <v>24</v>
@@ -2170,10 +2308,10 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>24</v>
@@ -2185,43 +2323,43 @@
         <v>25</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G29" s="7">
+        <v>46225</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I29" s="7">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="J29" s="7">
         <v>46223</v>
       </c>
       <c r="K29" s="7">
-        <v>46209</v>
+        <v>46223</v>
       </c>
       <c r="L29" s="8">
-        <v>330</v>
+        <v>630</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-23</v>
+        <v>-10</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S29" s="6" t="s">
         <v>24</v>
@@ -2229,10 +2367,10 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>66</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>67</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>24</v>
@@ -2268,19 +2406,19 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S30" s="6" t="s">
         <v>24</v>
@@ -2288,10 +2426,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>24</v>
@@ -2306,7 +2444,7 @@
         <v>26</v>
       </c>
       <c r="G31" s="7">
-        <v>46225</v>
+        <v>46203</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>27</v>
@@ -2327,19 +2465,19 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S31" s="6" t="s">
         <v>24</v>
@@ -2347,13 +2485,13 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>24</v>
@@ -2365,7 +2503,7 @@
         <v>26</v>
       </c>
       <c r="G32" s="7">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>27</v>
@@ -2380,25 +2518,25 @@
         <v>46223</v>
       </c>
       <c r="L32" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S32" s="6" t="s">
         <v>24</v>
@@ -2406,28 +2544,28 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H33" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C33" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="7">
-        <v>46203</v>
-      </c>
-      <c r="H33" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="I33" s="7">
         <v>46223</v>
@@ -2439,25 +2577,25 @@
         <v>46223</v>
       </c>
       <c r="L33" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S33" s="6" t="s">
         <v>24</v>
@@ -2468,10 +2606,10 @@
         <v>72</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>24</v>
@@ -2486,7 +2624,7 @@
         <v>46225</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I34" s="7">
         <v>46223</v>
@@ -2498,25 +2636,25 @@
         <v>46223</v>
       </c>
       <c r="L34" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S34" s="6" t="s">
         <v>24</v>
@@ -2524,10 +2662,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>24</v>
@@ -2542,7 +2680,7 @@
         <v>26</v>
       </c>
       <c r="G35" s="7">
-        <v>46153</v>
+        <v>46182</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>27</v>
@@ -2557,25 +2695,25 @@
         <v>46223</v>
       </c>
       <c r="L35" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S35" s="6" t="s">
         <v>24</v>
@@ -2586,7 +2724,7 @@
         <v>75</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>24</v>
@@ -2601,10 +2739,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="7">
-        <v>46188</v>
+        <v>46182</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I36" s="7">
         <v>46223</v>
@@ -2616,25 +2754,25 @@
         <v>46223</v>
       </c>
       <c r="L36" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>24</v>
@@ -2642,17 +2780,17 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D37" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="E37" s="6" t="s">
         <v>25</v>
       </c>
@@ -2660,10 +2798,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="7">
-        <v>46225</v>
+        <v>46203</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I37" s="7">
         <v>46223</v>
@@ -2675,25 +2813,25 @@
         <v>46223</v>
       </c>
       <c r="L37" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S37" s="6" t="s">
         <v>24</v>
@@ -2701,10 +2839,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>24</v>
@@ -2713,7 +2851,7 @@
         <v>24</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -2722,7 +2860,7 @@
         <v>46182</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="I38" s="7">
         <v>46223</v>
@@ -2734,25 +2872,25 @@
         <v>46223</v>
       </c>
       <c r="L38" s="8">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S38" s="6" t="s">
         <v>24</v>
@@ -2760,11 +2898,11 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B39" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="C39" s="6" t="s">
         <v>24</v>
       </c>
@@ -2778,10 +2916,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="7">
-        <v>46182</v>
+        <v>46225</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="I39" s="7">
         <v>46223</v>
@@ -2793,25 +2931,25 @@
         <v>46223</v>
       </c>
       <c r="L39" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S39" s="6" t="s">
         <v>24</v>
@@ -2819,25 +2957,25 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="7">
-        <v>46203</v>
+        <v>24</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>27</v>
@@ -2846,13 +2984,13 @@
         <v>46223</v>
       </c>
       <c r="J40" s="7">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K40" s="7">
         <v>46223</v>
       </c>
       <c r="L40" s="8">
-        <v>700</v>
+        <v>3.91</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>28</v>
@@ -2861,16 +2999,16 @@
         <v>-9</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S40" s="6" t="s">
         <v>24</v>
@@ -2881,7 +3019,7 @@
         <v>85</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>24</v>
@@ -2890,28 +3028,28 @@
         <v>24</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="7">
-        <v>46182</v>
+        <v>24</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="I41" s="7">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="J41" s="7">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K41" s="7">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="L41" s="8">
-        <v>800</v>
+        <v>56.19</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>28</v>
@@ -2920,16 +3058,16 @@
         <v>-9</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S41" s="6" t="s">
         <v>24</v>
@@ -2943,7 +3081,7 @@
         <v>87</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>24</v>
@@ -2952,25 +3090,25 @@
         <v>25</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="I42" s="7">
         <v>46223</v>
       </c>
       <c r="J42" s="7">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="K42" s="7">
         <v>46223</v>
       </c>
       <c r="L42" s="8">
-        <v>1200</v>
+        <v>71</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>28</v>
@@ -2979,16 +3117,16 @@
         <v>-9</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S42" s="6" t="s">
         <v>24</v>
@@ -2996,10 +3134,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>24</v>
@@ -3017,37 +3155,37 @@
         <v>24</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I43" s="7">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="J43" s="7">
         <v>46224</v>
       </c>
       <c r="K43" s="7">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="L43" s="8">
-        <v>3.91</v>
+        <v>550</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S43" s="6" t="s">
         <v>24</v>
@@ -3055,10 +3193,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>24</v>
@@ -3079,16 +3217,16 @@
         <v>27</v>
       </c>
       <c r="I44" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J44" s="7">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="K44" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L44" s="8">
-        <v>56.19</v>
+        <v>480</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>28</v>
@@ -3097,16 +3235,16 @@
         <v>-8</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S44" s="6" t="s">
         <v>24</v>
@@ -3114,13 +3252,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B45" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="C45" s="6" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>24</v>
@@ -3135,37 +3273,37 @@
         <v>24</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I45" s="7">
-        <v>46223</v>
+        <v>46188</v>
       </c>
       <c r="J45" s="7">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="K45" s="7">
-        <v>46223</v>
+        <v>46188</v>
       </c>
       <c r="L45" s="8">
-        <v>71</v>
+        <v>20.66</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-9</v>
+        <v>-45</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="S45" s="6" t="s">
         <v>24</v>
@@ -3173,13 +3311,13 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>24</v>
@@ -3188,43 +3326,43 @@
         <v>25</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>24</v>
+        <v>41</v>
+      </c>
+      <c r="G46" s="7">
+        <v>46190</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I46" s="7">
-        <v>46216</v>
+        <v>46174</v>
       </c>
       <c r="J46" s="7">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="K46" s="7">
-        <v>46216</v>
+        <v>46246</v>
       </c>
       <c r="L46" s="8">
-        <v>550</v>
+        <v>50</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>28</v>
+        <v>61</v>
       </c>
       <c r="Q46" s="9">
-        <v>-16</v>
+        <v>13</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="S46" s="6" t="s">
         <v>24</v>
@@ -3232,10 +3370,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>24</v>
@@ -3256,34 +3394,34 @@
         <v>27</v>
       </c>
       <c r="I47" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J47" s="7">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="K47" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L47" s="8">
-        <v>480</v>
+        <v>209.41</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S47" s="6" t="s">
         <v>24</v>
@@ -3291,10 +3429,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>98</v>
+        <v>46</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>24</v>
@@ -3306,43 +3444,43 @@
         <v>25</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G48" s="7">
+        <v>46231</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I48" s="7">
-        <v>46188</v>
+        <v>46230</v>
       </c>
       <c r="J48" s="7">
         <v>46230</v>
       </c>
       <c r="K48" s="7">
-        <v>46188</v>
+        <v>46230</v>
       </c>
       <c r="L48" s="8">
-        <v>20.66</v>
+        <v>590</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>-44</v>
+        <v>-3</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="S48" s="6" t="s">
         <v>24</v>
@@ -3350,13 +3488,13 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>39</v>
+        <v>96</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>40</v>
+        <v>97</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>24</v>
@@ -3365,43 +3503,43 @@
         <v>25</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="G49" s="7">
-        <v>46190</v>
+        <v>46225</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I49" s="7">
-        <v>46174</v>
+        <v>46230</v>
       </c>
       <c r="J49" s="7">
         <v>46230</v>
       </c>
       <c r="K49" s="7">
-        <v>46246</v>
+        <v>46230</v>
       </c>
       <c r="L49" s="8">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>14</v>
+        <v>-3</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S49" s="6" t="s">
         <v>24</v>
@@ -3409,13 +3547,13 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>24</v>
@@ -3427,10 +3565,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I50" s="7">
         <v>46230</v>
@@ -3442,25 +3580,25 @@
         <v>46230</v>
       </c>
       <c r="L50" s="8">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S50" s="6" t="s">
         <v>24</v>
@@ -3468,10 +3606,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>24</v>
@@ -3507,19 +3645,19 @@
         <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S51" s="6" t="s">
         <v>24</v>
@@ -3527,10 +3665,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>24</v>
@@ -3566,19 +3704,19 @@
         <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S52" s="6" t="s">
         <v>24</v>
@@ -3586,10 +3724,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>24</v>
@@ -3604,7 +3742,7 @@
         <v>26</v>
       </c>
       <c r="G53" s="7">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>27</v>
@@ -3625,19 +3763,19 @@
         <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S53" s="6" t="s">
         <v>24</v>
@@ -3645,10 +3783,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>24</v>
@@ -3684,19 +3822,19 @@
         <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S54" s="6" t="s">
         <v>24</v>
@@ -3704,10 +3842,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>24</v>
@@ -3743,19 +3881,19 @@
         <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S55" s="6" t="s">
         <v>24</v>
@@ -3763,10 +3901,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>24</v>
@@ -3784,7 +3922,7 @@
         <v>46188</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I56" s="7">
         <v>46230</v>
@@ -3802,19 +3940,19 @@
         <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S56" s="6" t="s">
         <v>24</v>
@@ -3822,13 +3960,13 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>24</v>
@@ -3861,19 +3999,19 @@
         <v>28</v>
       </c>
       <c r="N57" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S57" s="6" t="s">
         <v>24</v>
@@ -3881,10 +4019,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>24</v>
@@ -3899,10 +4037,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I58" s="7">
         <v>46230</v>
@@ -3914,25 +4052,25 @@
         <v>46230</v>
       </c>
       <c r="L58" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N58" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q58" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S58" s="6" t="s">
         <v>24</v>
@@ -3940,10 +4078,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>24</v>
@@ -3961,7 +4099,7 @@
         <v>46225</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I59" s="7">
         <v>46230</v>
@@ -3979,19 +4117,19 @@
         <v>28</v>
       </c>
       <c r="N59" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q59" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S59" s="6" t="s">
         <v>24</v>
@@ -3999,10 +4137,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
@@ -4020,7 +4158,7 @@
         <v>46225</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I60" s="7">
         <v>46230</v>
@@ -4032,25 +4170,25 @@
         <v>46230</v>
       </c>
       <c r="L60" s="8">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N60" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q60" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S60" s="6" t="s">
         <v>24</v>
@@ -4058,16 +4196,16 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>115</v>
+        <v>54</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="E61" s="6" t="s">
         <v>25</v>
@@ -4076,10 +4214,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="7">
-        <v>46160</v>
+        <v>46232</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="I61" s="7">
         <v>46230</v>
@@ -4091,25 +4229,25 @@
         <v>46230</v>
       </c>
       <c r="L61" s="8">
-        <v>1200</v>
+        <v>680</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N61" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q61" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S61" s="6" t="s">
         <v>24</v>
@@ -4117,10 +4255,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4135,10 +4273,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="I62" s="7">
         <v>46230</v>
@@ -4150,25 +4288,25 @@
         <v>46230</v>
       </c>
       <c r="L62" s="8">
-        <v>1200</v>
+        <v>680</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N62" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q62" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S62" s="6" t="s">
         <v>24</v>
@@ -4176,16 +4314,16 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="E63" s="6" t="s">
         <v>25</v>
@@ -4194,10 +4332,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="7">
-        <v>46160</v>
+        <v>46232</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>88</v>
+        <v>27</v>
       </c>
       <c r="I63" s="7">
         <v>46230</v>
@@ -4209,25 +4347,25 @@
         <v>46230</v>
       </c>
       <c r="L63" s="8">
-        <v>1200</v>
+        <v>680</v>
       </c>
       <c r="M63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N63" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q63" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S63" s="6" t="s">
         <v>24</v>
@@ -4235,58 +4373,58 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G64" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G64" s="7">
+        <v>46232</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I64" s="7">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="J64" s="7">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="K64" s="7">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="L64" s="8">
-        <v>510</v>
+        <v>700</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N64" s="9">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q64" s="9">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="S64" s="6" t="s">
         <v>24</v>
@@ -4294,10 +4432,10 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>24</v>
@@ -4306,46 +4444,46 @@
         <v>24</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G65" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G65" s="7">
+        <v>46232</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="I65" s="7">
-        <v>45930</v>
+        <v>46230</v>
       </c>
       <c r="J65" s="7">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="K65" s="7">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="L65" s="8">
-        <v>185.5</v>
+        <v>750</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="N65" s="9">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="Q65" s="9">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S65" s="6" t="s">
         <v>24</v>
@@ -4353,58 +4491,58 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>98</v>
+        <v>118</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G66" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G66" s="7">
+        <v>46160</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="I66" s="7">
-        <v>46188</v>
+        <v>46230</v>
       </c>
       <c r="J66" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="K66" s="7">
-        <v>46188</v>
+        <v>46230</v>
       </c>
       <c r="L66" s="8">
-        <v>116.7</v>
+        <v>1200</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="N66" s="9">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q66" s="9">
-        <v>-44</v>
+        <v>-3</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="S66" s="6" t="s">
         <v>24</v>
@@ -4412,16 +4550,16 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="B67" s="6" t="s">
-        <v>122</v>
-      </c>
       <c r="C67" s="6" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>24</v>
+        <v>119</v>
       </c>
       <c r="E67" s="6" t="s">
         <v>25</v>
@@ -4430,40 +4568,40 @@
         <v>26</v>
       </c>
       <c r="G67" s="7">
-        <v>46225</v>
+        <v>46160</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="I67" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="J67" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="K67" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="L67" s="8">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="N67" s="9">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="Q67" s="9">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S67" s="6" t="s">
         <v>24</v>
@@ -4471,13 +4609,13 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>24</v>
@@ -4492,37 +4630,37 @@
         <v>46225</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="I68" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="J68" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="K68" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="L68" s="8">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="N68" s="9">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="Q68" s="9">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S68" s="6" t="s">
         <v>24</v>
@@ -4530,58 +4668,58 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>125</v>
+        <v>77</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E69" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I69" s="7">
-        <v>46237</v>
+        <v>46216</v>
       </c>
       <c r="J69" s="7">
-        <v>46237</v>
+        <v>46231</v>
       </c>
       <c r="K69" s="7">
-        <v>46237</v>
+        <v>46216</v>
       </c>
       <c r="L69" s="8">
-        <v>630</v>
+        <v>510</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="N69" s="9">
-        <v>5</v>
+        <v>-2</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="Q69" s="9">
-        <v>5</v>
+        <v>-17</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S69" s="6" t="s">
         <v>24</v>
@@ -4589,10 +4727,10 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
-        <v>126</v>
+        <v>24</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>69</v>
+        <v>35</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>24</v>
@@ -4604,40 +4742,40 @@
         <v>25</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G70" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G70" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I70" s="7">
-        <v>46237</v>
+        <v>45930</v>
       </c>
       <c r="J70" s="7">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="K70" s="7">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="L70" s="8">
-        <v>630</v>
+        <v>185.5</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="N70" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>62</v>
+        <v>124</v>
       </c>
       <c r="Q70" s="9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>24</v>
@@ -4648,10 +4786,10 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>127</v>
+        <v>91</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>24</v>
@@ -4663,43 +4801,43 @@
         <v>25</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="7">
-        <v>46231</v>
+        <v>24</v>
+      </c>
+      <c r="G71" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I71" s="7">
-        <v>46237</v>
+        <v>46188</v>
       </c>
       <c r="J71" s="7">
         <v>46237</v>
       </c>
       <c r="K71" s="7">
-        <v>46237</v>
+        <v>46188</v>
       </c>
       <c r="L71" s="8">
-        <v>630</v>
+        <v>116.7</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N71" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="Q71" s="9">
-        <v>5</v>
+        <v>-45</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="S71" s="6" t="s">
         <v>24</v>
@@ -4707,13 +4845,13 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>24</v>
@@ -4740,22 +4878,22 @@
         <v>46237</v>
       </c>
       <c r="L72" s="8">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N72" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q72" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4766,13 +4904,13 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>130</v>
+        <v>97</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>24</v>
@@ -4799,22 +4937,22 @@
         <v>46237</v>
       </c>
       <c r="L73" s="8">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N73" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q73" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4825,13 +4963,13 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>24</v>
@@ -4843,10 +4981,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I74" s="7">
         <v>46237</v>
@@ -4858,22 +4996,22 @@
         <v>46237</v>
       </c>
       <c r="L74" s="8">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N74" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q74" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -4884,13 +5022,13 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>24</v>
@@ -4917,22 +5055,22 @@
         <v>46237</v>
       </c>
       <c r="L75" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N75" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q75" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -4943,10 +5081,10 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>106</v>
+        <v>50</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>24</v>
@@ -4961,7 +5099,7 @@
         <v>26</v>
       </c>
       <c r="G76" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>27</v>
@@ -4976,22 +5114,22 @@
         <v>46237</v>
       </c>
       <c r="L76" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N76" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q76" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -5002,10 +5140,10 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>24</v>
@@ -5020,10 +5158,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="7">
-        <v>46212</v>
+        <v>46231</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I77" s="7">
         <v>46237</v>
@@ -5035,22 +5173,22 @@
         <v>46237</v>
       </c>
       <c r="L77" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N77" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q77" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5061,10 +5199,10 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -5082,7 +5220,7 @@
         <v>46225</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I78" s="7">
         <v>46237</v>
@@ -5094,22 +5232,22 @@
         <v>46237</v>
       </c>
       <c r="L78" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N78" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q78" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5120,16 +5258,16 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>25</v>
@@ -5138,10 +5276,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I79" s="7">
         <v>46237</v>
@@ -5153,22 +5291,22 @@
         <v>46237</v>
       </c>
       <c r="L79" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N79" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q79" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5179,10 +5317,10 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
@@ -5197,10 +5335,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I80" s="7">
         <v>46237</v>
@@ -5212,22 +5350,22 @@
         <v>46237</v>
       </c>
       <c r="L80" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N80" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q80" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5238,10 +5376,10 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>113</v>
+        <v>66</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5259,7 +5397,7 @@
         <v>46225</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="I81" s="7">
         <v>46237</v>
@@ -5271,22 +5409,22 @@
         <v>46237</v>
       </c>
       <c r="L81" s="8">
-        <v>800</v>
+        <v>630</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N81" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q81" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5297,10 +5435,10 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>24</v>
@@ -5315,10 +5453,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="I82" s="7">
         <v>46237</v>
@@ -5330,22 +5468,22 @@
         <v>46237</v>
       </c>
       <c r="L82" s="8">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N82" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q82" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5356,13 +5494,13 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>122</v>
+        <v>52</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>24</v>
@@ -5380,31 +5518,31 @@
         <v>27</v>
       </c>
       <c r="I83" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J83" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K83" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L83" s="8">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N83" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q83" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5415,13 +5553,13 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>24</v>
@@ -5433,37 +5571,37 @@
         <v>26</v>
       </c>
       <c r="G84" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I84" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J84" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K84" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L84" s="8">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N84" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q84" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5474,11 +5612,11 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B85" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B85" s="6" t="s">
-        <v>130</v>
-      </c>
       <c r="C85" s="6" t="s">
         <v>24</v>
       </c>
@@ -5492,37 +5630,37 @@
         <v>26</v>
       </c>
       <c r="G85" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I85" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J85" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K85" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L85" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N85" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q85" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5536,7 +5674,7 @@
         <v>144</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>24</v>
@@ -5551,37 +5689,37 @@
         <v>26</v>
       </c>
       <c r="G86" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I86" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J86" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K86" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L86" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N86" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q86" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5595,7 +5733,7 @@
         <v>145</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>67</v>
+        <v>146</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>24</v>
@@ -5610,37 +5748,37 @@
         <v>26</v>
       </c>
       <c r="G87" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H87" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I87" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J87" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K87" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L87" s="8">
-        <v>630</v>
+        <v>670</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N87" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q87" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5651,10 +5789,10 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>24</v>
@@ -5669,37 +5807,37 @@
         <v>26</v>
       </c>
       <c r="G88" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H88" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I88" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J88" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K88" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L88" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N88" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q88" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5710,13 +5848,13 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>24</v>
@@ -5731,34 +5869,34 @@
         <v>46225</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I89" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J89" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K89" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L89" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N89" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q89" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5769,10 +5907,10 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>76</v>
+        <v>150</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>24</v>
@@ -5787,37 +5925,37 @@
         <v>26</v>
       </c>
       <c r="G90" s="7">
-        <v>46188</v>
+        <v>46212</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I90" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J90" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K90" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L90" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N90" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q90" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5828,10 +5966,10 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>106</v>
+        <v>60</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>24</v>
@@ -5846,37 +5984,37 @@
         <v>26</v>
       </c>
       <c r="G91" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I91" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J91" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K91" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L91" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N91" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q91" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -5887,10 +6025,10 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>24</v>
@@ -5905,37 +6043,37 @@
         <v>26</v>
       </c>
       <c r="G92" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I92" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J92" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K92" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L92" s="8">
         <v>680</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N92" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q92" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -5946,10 +6084,10 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>135</v>
+        <v>73</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>24</v>
@@ -5964,37 +6102,37 @@
         <v>26</v>
       </c>
       <c r="G93" s="7">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I93" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J93" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K93" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L93" s="8">
         <v>680</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N93" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q93" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -6005,10 +6143,10 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>24</v>
@@ -6023,37 +6161,37 @@
         <v>26</v>
       </c>
       <c r="G94" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I94" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J94" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K94" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L94" s="8">
         <v>680</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N94" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q94" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6064,10 +6202,10 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>24</v>
@@ -6085,34 +6223,34 @@
         <v>46188</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I95" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J95" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K95" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L95" s="8">
         <v>700</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N95" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q95" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6123,16 +6261,16 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>25</v>
@@ -6141,37 +6279,37 @@
         <v>26</v>
       </c>
       <c r="G96" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="I96" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J96" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K96" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L96" s="8">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N96" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q96" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6182,10 +6320,10 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>24</v>
@@ -6194,43 +6332,43 @@
         <v>24</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>25</v>
+        <v>57</v>
       </c>
       <c r="F97" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="I97" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J97" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="K97" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L97" s="8">
-        <v>1200</v>
+        <v>750</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N97" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q97" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6241,13 +6379,13 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>122</v>
+        <v>159</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>24</v>
@@ -6262,34 +6400,34 @@
         <v>46225</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>27</v>
+        <v>58</v>
       </c>
       <c r="I98" s="7">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="J98" s="7">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="K98" s="7">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="L98" s="8">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N98" s="9">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q98" s="9">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6300,13 +6438,13 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>100</v>
+        <v>81</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>100</v>
+        <v>24</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>24</v>
@@ -6321,34 +6459,34 @@
         <v>46225</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="I99" s="7">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="J99" s="7">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="K99" s="7">
-        <v>46251</v>
+        <v>46237</v>
       </c>
       <c r="L99" s="8">
-        <v>600</v>
+        <v>1200</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N99" s="9">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q99" s="9">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6359,13 +6497,13 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>67</v>
+        <v>126</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>24</v>
+        <v>126</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>24</v>
@@ -6383,31 +6521,31 @@
         <v>27</v>
       </c>
       <c r="I100" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J100" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K100" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L100" s="8">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N100" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q100" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6418,13 +6556,13 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>125</v>
+        <v>97</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>24</v>
+        <v>97</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>24</v>
@@ -6442,31 +6580,31 @@
         <v>27</v>
       </c>
       <c r="I101" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J101" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K101" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L101" s="8">
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="M101" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N101" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q101" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6477,13 +6615,13 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>24</v>
@@ -6495,37 +6633,37 @@
         <v>26</v>
       </c>
       <c r="G102" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I102" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J102" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K102" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L102" s="8">
-        <v>630</v>
+        <v>620</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N102" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q102" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6536,10 +6674,10 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>24</v>
@@ -6554,37 +6692,37 @@
         <v>26</v>
       </c>
       <c r="G103" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H103" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I103" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J103" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K103" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L103" s="8">
         <v>630</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N103" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q103" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6595,10 +6733,10 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>106</v>
+        <v>133</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>24</v>
@@ -6613,37 +6751,37 @@
         <v>26</v>
       </c>
       <c r="G104" s="7">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I104" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J104" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K104" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L104" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N104" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q104" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6654,13 +6792,13 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>24</v>
@@ -6678,31 +6816,31 @@
         <v>27</v>
       </c>
       <c r="I105" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J105" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K105" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L105" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N105" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q105" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6713,10 +6851,10 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>24</v>
@@ -6731,37 +6869,37 @@
         <v>26</v>
       </c>
       <c r="G106" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I106" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J106" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K106" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L106" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N106" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q106" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>
@@ -6772,10 +6910,10 @@
     </row>
     <row r="107">
       <c r="A107" s="6" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>110</v>
+        <v>137</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>24</v>
@@ -6793,34 +6931,34 @@
         <v>46225</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I107" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J107" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K107" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L107" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N107" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q107" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>24</v>
@@ -6831,7 +6969,7 @@
     </row>
     <row r="108">
       <c r="A108" s="6" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>135</v>
@@ -6840,7 +6978,7 @@
         <v>24</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>25</v>
@@ -6849,37 +6987,37 @@
         <v>26</v>
       </c>
       <c r="G108" s="7">
-        <v>46212</v>
+        <v>46232</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I108" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J108" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K108" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L108" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M108" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N108" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q108" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>24</v>
@@ -6890,13 +7028,13 @@
     </row>
     <row r="109">
       <c r="A109" s="6" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>79</v>
+        <v>52</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>24</v>
@@ -6911,34 +7049,34 @@
         <v>46225</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I109" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J109" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K109" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L109" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N109" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P109" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q109" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R109" s="6" t="s">
         <v>24</v>
@@ -6949,10 +7087,10 @@
     </row>
     <row r="110">
       <c r="A110" s="6" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>24</v>
@@ -6967,37 +7105,37 @@
         <v>26</v>
       </c>
       <c r="G110" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I110" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J110" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K110" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L110" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N110" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q110" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R110" s="6" t="s">
         <v>24</v>
@@ -7008,10 +7146,10 @@
     </row>
     <row r="111">
       <c r="A111" s="6" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>24</v>
@@ -7026,37 +7164,37 @@
         <v>26</v>
       </c>
       <c r="G111" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>59</v>
+        <v>27</v>
       </c>
       <c r="I111" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J111" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K111" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L111" s="8">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="M111" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N111" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P111" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q111" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R111" s="6" t="s">
         <v>24</v>
@@ -7067,10 +7205,10 @@
     </row>
     <row r="112">
       <c r="A112" s="6" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>24</v>
@@ -7085,37 +7223,37 @@
         <v>26</v>
       </c>
       <c r="G112" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="I112" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="J112" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="K112" s="7">
-        <v>46251</v>
+        <v>46244</v>
       </c>
       <c r="L112" s="8">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N112" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q112" s="9">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="R112" s="6" t="s">
         <v>24</v>
@@ -7126,10 +7264,10 @@
     </row>
     <row r="113">
       <c r="A113" s="6" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>24</v>
@@ -7144,37 +7282,37 @@
         <v>26</v>
       </c>
       <c r="G113" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I113" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="J113" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="K113" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="L113" s="8">
         <v>650</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N113" s="9">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q113" s="9">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="R113" s="6" t="s">
         <v>24</v>
@@ -7185,10 +7323,10 @@
     </row>
     <row r="114">
       <c r="A114" s="6" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>24</v>
@@ -7203,37 +7341,37 @@
         <v>26</v>
       </c>
       <c r="G114" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I114" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="J114" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="K114" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="L114" s="8">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N114" s="9">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q114" s="9">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="R114" s="6" t="s">
         <v>24</v>
@@ -7244,10 +7382,10 @@
     </row>
     <row r="115">
       <c r="A115" s="6" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>24</v>
@@ -7265,34 +7403,34 @@
         <v>46212</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="I115" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="J115" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="K115" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="L115" s="8">
         <v>680</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N115" s="9">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="O115" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q115" s="9">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="R115" s="6" t="s">
         <v>24</v>
@@ -7303,10 +7441,10 @@
     </row>
     <row r="116">
       <c r="A116" s="6" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>24</v>
@@ -7321,37 +7459,37 @@
         <v>26</v>
       </c>
       <c r="G116" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I116" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="J116" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="K116" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="L116" s="8">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="M116" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N116" s="9">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q116" s="9">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="R116" s="6" t="s">
         <v>24</v>
@@ -7362,10 +7500,10 @@
     </row>
     <row r="117">
       <c r="A117" s="6" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>113</v>
+        <v>73</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>24</v>
@@ -7383,34 +7521,34 @@
         <v>46225</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="I117" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="J117" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="K117" s="7">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="L117" s="8">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="M117" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N117" s="9">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="O117" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P117" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q117" s="9">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="R117" s="6" t="s">
         <v>24</v>
@@ -7421,10 +7559,10 @@
     </row>
     <row r="118">
       <c r="A118" s="6" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>36</v>
+        <v>94</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>24</v>
@@ -7436,40 +7574,40 @@
         <v>25</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G118" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G118" s="7">
+        <v>46232</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I118" s="7">
-        <v>45930</v>
+        <v>46244</v>
       </c>
       <c r="J118" s="7">
-        <v>46264</v>
+        <v>46244</v>
       </c>
       <c r="K118" s="7">
-        <v>46264</v>
+        <v>46244</v>
       </c>
       <c r="L118" s="8">
-        <v>185.5</v>
+        <v>680</v>
       </c>
       <c r="M118" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N118" s="9">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q118" s="9">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="R118" s="6" t="s">
         <v>24</v>
@@ -7480,10 +7618,10 @@
     </row>
     <row r="119">
       <c r="A119" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>24</v>
@@ -7498,37 +7636,37 @@
         <v>26</v>
       </c>
       <c r="G119" s="7">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I119" s="7">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="J119" s="7">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="K119" s="7">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="L119" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M119" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N119" s="9">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="O119" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P119" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q119" s="9">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="R119" s="6" t="s">
         <v>24</v>
@@ -7539,10 +7677,10 @@
     </row>
     <row r="120">
       <c r="A120" s="6" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>135</v>
+        <v>60</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>24</v>
@@ -7557,37 +7695,37 @@
         <v>26</v>
       </c>
       <c r="G120" s="7">
-        <v>46212</v>
+        <v>46232</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="I120" s="7">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="J120" s="7">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="K120" s="7">
-        <v>46265</v>
+        <v>46244</v>
       </c>
       <c r="L120" s="8">
         <v>680</v>
       </c>
       <c r="M120" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="N120" s="9">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Q120" s="9">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="R120" s="6" t="s">
         <v>24</v>
@@ -7598,10 +7736,10 @@
     </row>
     <row r="121">
       <c r="A121" s="6" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>24</v>
@@ -7616,67 +7754,2604 @@
         <v>26</v>
       </c>
       <c r="G121" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H121" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I121" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J121" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K121" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L121" s="8">
+        <v>680</v>
+      </c>
+      <c r="M121" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N121" s="9">
+        <v>11</v>
+      </c>
+      <c r="O121" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P121" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q121" s="9">
+        <v>11</v>
+      </c>
+      <c r="R121" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S121" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B122" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C122" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D122" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E122" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F122" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G122" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H122" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I122" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J122" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K122" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L122" s="8">
+        <v>700</v>
+      </c>
+      <c r="M122" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N122" s="9">
+        <v>11</v>
+      </c>
+      <c r="O122" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P122" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q122" s="9">
+        <v>11</v>
+      </c>
+      <c r="R122" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S122" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C123" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D123" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E123" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F123" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G123" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H123" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I123" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J123" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K123" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L123" s="8">
+        <v>700</v>
+      </c>
+      <c r="M123" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N123" s="9">
+        <v>11</v>
+      </c>
+      <c r="O123" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P123" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q123" s="9">
+        <v>11</v>
+      </c>
+      <c r="R123" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S123" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B124" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C124" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D124" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E124" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F124" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G124" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I124" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J124" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K124" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L124" s="8">
+        <v>750</v>
+      </c>
+      <c r="M124" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N124" s="9">
+        <v>11</v>
+      </c>
+      <c r="O124" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P124" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q124" s="9">
+        <v>11</v>
+      </c>
+      <c r="R124" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S124" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B125" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C125" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D125" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G125" s="7">
         <v>46225</v>
       </c>
-      <c r="H121" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I121" s="7">
+      <c r="H125" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I125" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J125" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K125" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L125" s="8">
+        <v>800</v>
+      </c>
+      <c r="M125" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N125" s="9">
+        <v>11</v>
+      </c>
+      <c r="O125" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P125" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q125" s="9">
+        <v>11</v>
+      </c>
+      <c r="R125" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S125" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B126" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G126" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H126" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I126" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J126" s="7">
+        <v>46244</v>
+      </c>
+      <c r="K126" s="7">
+        <v>46244</v>
+      </c>
+      <c r="L126" s="8">
+        <v>1200</v>
+      </c>
+      <c r="M126" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N126" s="9">
+        <v>11</v>
+      </c>
+      <c r="O126" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P126" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q126" s="9">
+        <v>11</v>
+      </c>
+      <c r="R126" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S126" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B127" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G127" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H127" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I127" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J127" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K127" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L127" s="8">
+        <v>600</v>
+      </c>
+      <c r="M127" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N127" s="9">
+        <v>18</v>
+      </c>
+      <c r="O127" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P127" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q127" s="9">
+        <v>18</v>
+      </c>
+      <c r="R127" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S127" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B128" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="C128" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G128" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H128" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I128" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J128" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K128" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L128" s="8">
+        <v>600</v>
+      </c>
+      <c r="M128" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N128" s="9">
+        <v>18</v>
+      </c>
+      <c r="O128" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P128" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q128" s="9">
+        <v>18</v>
+      </c>
+      <c r="R128" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S128" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B129" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="C129" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D129" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G129" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H129" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I129" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J129" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K129" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L129" s="8">
+        <v>620</v>
+      </c>
+      <c r="M129" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N129" s="9">
+        <v>18</v>
+      </c>
+      <c r="O129" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P129" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q129" s="9">
+        <v>18</v>
+      </c>
+      <c r="R129" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S129" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="B130" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C130" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D130" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G130" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H130" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I130" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J130" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K130" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L130" s="8">
+        <v>630</v>
+      </c>
+      <c r="M130" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N130" s="9">
+        <v>18</v>
+      </c>
+      <c r="O130" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P130" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q130" s="9">
+        <v>18</v>
+      </c>
+      <c r="R130" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S130" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="B131" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D131" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G131" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H131" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I131" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J131" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K131" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L131" s="8">
+        <v>630</v>
+      </c>
+      <c r="M131" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N131" s="9">
+        <v>18</v>
+      </c>
+      <c r="O131" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P131" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q131" s="9">
+        <v>18</v>
+      </c>
+      <c r="R131" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S131" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="B132" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G132" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H132" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I132" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J132" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K132" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L132" s="8">
+        <v>630</v>
+      </c>
+      <c r="M132" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N132" s="9">
+        <v>18</v>
+      </c>
+      <c r="O132" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P132" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q132" s="9">
+        <v>18</v>
+      </c>
+      <c r="R132" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S132" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="B133" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D133" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G133" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H133" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I133" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J133" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K133" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L133" s="8">
+        <v>630</v>
+      </c>
+      <c r="M133" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N133" s="9">
+        <v>18</v>
+      </c>
+      <c r="O133" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P133" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q133" s="9">
+        <v>18</v>
+      </c>
+      <c r="R133" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S133" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="B134" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D134" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G134" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H134" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I134" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J134" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K134" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L134" s="8">
+        <v>630</v>
+      </c>
+      <c r="M134" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N134" s="9">
+        <v>18</v>
+      </c>
+      <c r="O134" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P134" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q134" s="9">
+        <v>18</v>
+      </c>
+      <c r="R134" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S134" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="B135" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D135" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G135" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H135" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I135" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J135" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K135" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L135" s="8">
+        <v>630</v>
+      </c>
+      <c r="M135" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N135" s="9">
+        <v>18</v>
+      </c>
+      <c r="O135" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P135" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q135" s="9">
+        <v>18</v>
+      </c>
+      <c r="R135" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S135" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D136" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G136" s="7">
+        <v>46210</v>
+      </c>
+      <c r="H136" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I136" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J136" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K136" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L136" s="8">
+        <v>650</v>
+      </c>
+      <c r="M136" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N136" s="9">
+        <v>18</v>
+      </c>
+      <c r="O136" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P136" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q136" s="9">
+        <v>18</v>
+      </c>
+      <c r="R136" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S136" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="B137" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D137" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G137" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H137" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I137" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J137" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K137" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L137" s="8">
+        <v>650</v>
+      </c>
+      <c r="M137" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N137" s="9">
+        <v>18</v>
+      </c>
+      <c r="O137" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P137" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q137" s="9">
+        <v>18</v>
+      </c>
+      <c r="R137" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S137" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B138" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D138" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G138" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H138" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I138" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J138" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K138" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L138" s="8">
+        <v>650</v>
+      </c>
+      <c r="M138" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N138" s="9">
+        <v>18</v>
+      </c>
+      <c r="O138" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P138" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q138" s="9">
+        <v>18</v>
+      </c>
+      <c r="R138" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S138" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="B139" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D139" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G139" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H139" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I139" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J139" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K139" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L139" s="8">
+        <v>650</v>
+      </c>
+      <c r="M139" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N139" s="9">
+        <v>18</v>
+      </c>
+      <c r="O139" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P139" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q139" s="9">
+        <v>18</v>
+      </c>
+      <c r="R139" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S139" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B140" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G140" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H140" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I140" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J140" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K140" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L140" s="8">
+        <v>650</v>
+      </c>
+      <c r="M140" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N140" s="9">
+        <v>18</v>
+      </c>
+      <c r="O140" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P140" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q140" s="9">
+        <v>18</v>
+      </c>
+      <c r="R140" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S140" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B141" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="C141" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G141" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H141" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I141" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J141" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K141" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L141" s="8">
+        <v>670</v>
+      </c>
+      <c r="M141" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N141" s="9">
+        <v>18</v>
+      </c>
+      <c r="O141" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P141" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q141" s="9">
+        <v>18</v>
+      </c>
+      <c r="R141" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S141" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B142" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G142" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H142" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I142" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J142" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K142" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L142" s="8">
+        <v>680</v>
+      </c>
+      <c r="M142" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N142" s="9">
+        <v>18</v>
+      </c>
+      <c r="O142" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P142" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q142" s="9">
+        <v>18</v>
+      </c>
+      <c r="R142" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S142" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B143" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D143" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G143" s="7">
+        <v>46212</v>
+      </c>
+      <c r="H143" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I143" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J143" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K143" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L143" s="8">
+        <v>680</v>
+      </c>
+      <c r="M143" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N143" s="9">
+        <v>18</v>
+      </c>
+      <c r="O143" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P143" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q143" s="9">
+        <v>18</v>
+      </c>
+      <c r="R143" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S143" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D144" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G144" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H144" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I144" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J144" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K144" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L144" s="8">
+        <v>680</v>
+      </c>
+      <c r="M144" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N144" s="9">
+        <v>18</v>
+      </c>
+      <c r="O144" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P144" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q144" s="9">
+        <v>18</v>
+      </c>
+      <c r="R144" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S144" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B145" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D145" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E145" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F145" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G145" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H145" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I145" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J145" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K145" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L145" s="8">
+        <v>680</v>
+      </c>
+      <c r="M145" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N145" s="9">
+        <v>18</v>
+      </c>
+      <c r="O145" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P145" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q145" s="9">
+        <v>18</v>
+      </c>
+      <c r="R145" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S145" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B146" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E146" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G146" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H146" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I146" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J146" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K146" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L146" s="8">
+        <v>680</v>
+      </c>
+      <c r="M146" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N146" s="9">
+        <v>18</v>
+      </c>
+      <c r="O146" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P146" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q146" s="9">
+        <v>18</v>
+      </c>
+      <c r="R146" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S146" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="B147" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D147" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E147" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F147" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G147" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H147" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I147" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J147" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K147" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L147" s="8">
+        <v>680</v>
+      </c>
+      <c r="M147" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N147" s="9">
+        <v>18</v>
+      </c>
+      <c r="O147" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P147" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q147" s="9">
+        <v>18</v>
+      </c>
+      <c r="R147" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S147" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B148" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D148" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E148" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F148" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G148" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H148" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I148" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J148" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K148" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L148" s="8">
+        <v>680</v>
+      </c>
+      <c r="M148" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N148" s="9">
+        <v>18</v>
+      </c>
+      <c r="O148" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P148" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q148" s="9">
+        <v>18</v>
+      </c>
+      <c r="R148" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S148" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B149" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D149" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E149" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F149" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G149" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H149" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I149" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J149" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K149" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L149" s="8">
+        <v>700</v>
+      </c>
+      <c r="M149" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N149" s="9">
+        <v>18</v>
+      </c>
+      <c r="O149" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P149" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q149" s="9">
+        <v>18</v>
+      </c>
+      <c r="R149" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S149" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="B150" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D150" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E150" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F150" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G150" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H150" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I150" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J150" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K150" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L150" s="8">
+        <v>700</v>
+      </c>
+      <c r="M150" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N150" s="9">
+        <v>18</v>
+      </c>
+      <c r="O150" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P150" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q150" s="9">
+        <v>18</v>
+      </c>
+      <c r="R150" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S150" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="B151" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D151" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E151" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="F151" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G151" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H151" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I151" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J151" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K151" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L151" s="8">
+        <v>750</v>
+      </c>
+      <c r="M151" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N151" s="9">
+        <v>18</v>
+      </c>
+      <c r="O151" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P151" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q151" s="9">
+        <v>18</v>
+      </c>
+      <c r="R151" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S151" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D152" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E152" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F152" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G152" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H152" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I152" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J152" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K152" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L152" s="8">
+        <v>800</v>
+      </c>
+      <c r="M152" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N152" s="9">
+        <v>18</v>
+      </c>
+      <c r="O152" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P152" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q152" s="9">
+        <v>18</v>
+      </c>
+      <c r="R152" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S152" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="B153" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D153" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E153" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F153" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G153" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H153" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="I153" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J153" s="7">
+        <v>46251</v>
+      </c>
+      <c r="K153" s="7">
+        <v>46251</v>
+      </c>
+      <c r="L153" s="8">
+        <v>1200</v>
+      </c>
+      <c r="M153" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N153" s="9">
+        <v>18</v>
+      </c>
+      <c r="O153" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P153" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q153" s="9">
+        <v>18</v>
+      </c>
+      <c r="R153" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S153" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B154" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D154" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E154" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F154" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G154" s="7">
+        <v>46210</v>
+      </c>
+      <c r="H154" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I154" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J154" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K154" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L154" s="8">
+        <v>650</v>
+      </c>
+      <c r="M154" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N154" s="9">
+        <v>25</v>
+      </c>
+      <c r="O154" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P154" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q154" s="9">
+        <v>25</v>
+      </c>
+      <c r="R154" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S154" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F155" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G155" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H155" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I155" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J155" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K155" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L155" s="8">
+        <v>650</v>
+      </c>
+      <c r="M155" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N155" s="9">
+        <v>25</v>
+      </c>
+      <c r="O155" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P155" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q155" s="9">
+        <v>25</v>
+      </c>
+      <c r="R155" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S155" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G156" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H156" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I156" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J156" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K156" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L156" s="8">
+        <v>650</v>
+      </c>
+      <c r="M156" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N156" s="9">
+        <v>25</v>
+      </c>
+      <c r="O156" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P156" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q156" s="9">
+        <v>25</v>
+      </c>
+      <c r="R156" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S156" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F157" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G157" s="7">
+        <v>46212</v>
+      </c>
+      <c r="H157" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I157" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J157" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K157" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L157" s="8">
+        <v>680</v>
+      </c>
+      <c r="M157" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N157" s="9">
+        <v>25</v>
+      </c>
+      <c r="O157" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P157" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q157" s="9">
+        <v>25</v>
+      </c>
+      <c r="R157" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S157" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F158" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G158" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H158" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I158" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J158" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K158" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L158" s="8">
+        <v>700</v>
+      </c>
+      <c r="M158" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N158" s="9">
+        <v>25</v>
+      </c>
+      <c r="O158" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P158" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q158" s="9">
+        <v>25</v>
+      </c>
+      <c r="R158" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S158" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B159" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D159" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E159" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F159" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G159" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H159" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I159" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J159" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K159" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L159" s="8">
+        <v>800</v>
+      </c>
+      <c r="M159" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N159" s="9">
+        <v>25</v>
+      </c>
+      <c r="O159" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P159" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q159" s="9">
+        <v>25</v>
+      </c>
+      <c r="R159" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S159" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B160" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D160" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E160" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F160" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G160" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H160" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I160" s="7">
+        <v>45930</v>
+      </c>
+      <c r="J160" s="7">
+        <v>46264</v>
+      </c>
+      <c r="K160" s="7">
+        <v>46264</v>
+      </c>
+      <c r="L160" s="8">
+        <v>185.5</v>
+      </c>
+      <c r="M160" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N160" s="9">
+        <v>31</v>
+      </c>
+      <c r="O160" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P160" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q160" s="9">
+        <v>31</v>
+      </c>
+      <c r="R160" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S160" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="B161" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D161" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E161" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F161" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G161" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H161" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I161" s="7">
         <v>46265</v>
       </c>
-      <c r="J121" s="7">
+      <c r="J161" s="7">
         <v>46265</v>
       </c>
-      <c r="K121" s="7">
+      <c r="K161" s="7">
         <v>46265</v>
       </c>
-      <c r="L121" s="8">
+      <c r="L161" s="8">
+        <v>650</v>
+      </c>
+      <c r="M161" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N161" s="9">
+        <v>32</v>
+      </c>
+      <c r="O161" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P161" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q161" s="9">
+        <v>32</v>
+      </c>
+      <c r="R161" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S161" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B162" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D162" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E162" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F162" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G162" s="7">
+        <v>46210</v>
+      </c>
+      <c r="H162" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I162" s="7">
+        <v>46265</v>
+      </c>
+      <c r="J162" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K162" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L162" s="8">
+        <v>650</v>
+      </c>
+      <c r="M162" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N162" s="9">
+        <v>32</v>
+      </c>
+      <c r="O162" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P162" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q162" s="9">
+        <v>32</v>
+      </c>
+      <c r="R162" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S162" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="C163" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D163" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E163" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F163" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G163" s="7">
+        <v>46212</v>
+      </c>
+      <c r="H163" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I163" s="7">
+        <v>46265</v>
+      </c>
+      <c r="J163" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K163" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L163" s="8">
+        <v>680</v>
+      </c>
+      <c r="M163" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N163" s="9">
+        <v>32</v>
+      </c>
+      <c r="O163" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P163" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q163" s="9">
+        <v>32</v>
+      </c>
+      <c r="R163" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S163" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="B164" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D164" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E164" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F164" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G164" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H164" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="I164" s="7">
+        <v>46265</v>
+      </c>
+      <c r="J164" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K164" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L164" s="8">
         <v>800</v>
       </c>
-      <c r="M121" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="N121" s="9">
-        <v>33</v>
-      </c>
-      <c r="O121" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P121" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q121" s="9">
-        <v>33</v>
-      </c>
-      <c r="R121" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S121" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="122" ht="23" customHeight="1">
-      <c r="A122" s="10"/>
-      <c r="B122" s="10"/>
-      <c r="C122" s="10"/>
-      <c r="D122" s="10"/>
-      <c r="E122" s="10"/>
-      <c r="F122" s="10"/>
-      <c r="G122" s="11"/>
-      <c r="H122" s="10"/>
-      <c r="I122" s="11"/>
-      <c r="J122" s="11"/>
-      <c r="K122" s="11"/>
-      <c r="L122" s="12">
-        <f>SUM(L6:L121)</f>
-      </c>
-      <c r="M122" s="10"/>
-      <c r="N122" s="13"/>
-      <c r="O122" s="10"/>
-      <c r="P122" s="10"/>
-      <c r="Q122" s="13"/>
-      <c r="R122" s="10"/>
-      <c r="S122" s="10"/>
+      <c r="M164" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="N164" s="9">
+        <v>32</v>
+      </c>
+      <c r="O164" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P164" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q164" s="9">
+        <v>32</v>
+      </c>
+      <c r="R164" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S164" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="165" ht="23" customHeight="1">
+      <c r="A165" s="10"/>
+      <c r="B165" s="10"/>
+      <c r="C165" s="10"/>
+      <c r="D165" s="10"/>
+      <c r="E165" s="10"/>
+      <c r="F165" s="10"/>
+      <c r="G165" s="11"/>
+      <c r="H165" s="10"/>
+      <c r="I165" s="11"/>
+      <c r="J165" s="11"/>
+      <c r="K165" s="11"/>
+      <c r="L165" s="12">
+        <f>SUM(L6:L164)</f>
+      </c>
+      <c r="M165" s="10"/>
+      <c r="N165" s="13"/>
+      <c r="O165" s="10"/>
+      <c r="P165" s="10"/>
+      <c r="Q165" s="13"/>
+      <c r="R165" s="10"/>
+      <c r="S165" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:S5"/>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quinta-feira, 30 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em sexta-feira, 31 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -142,15 +142,15 @@
     <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
   </si>
   <si>
+    <t>FA-11559</t>
+  </si>
+  <si>
+    <t>FA-11562</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
     <t>ND-11870</t>
   </si>
   <si>
@@ -404,9 +404,6 @@
   </si>
   <si>
     <t>FA-11903</t>
-  </si>
-  <si>
-    <t>HOJE</t>
   </si>
   <si>
     <t>FA-11977</t>
@@ -990,7 +987,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-59</v>
+        <v>-60</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -999,7 +996,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-59</v>
+        <v>-60</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -1049,7 +1046,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -1058,7 +1055,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-52</v>
+        <v>-53</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
@@ -1108,7 +1105,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -1117,7 +1114,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -1167,7 +1164,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -1176,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1226,7 +1223,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -1235,7 +1232,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -1285,19 +1282,19 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="S11" s="6" t="s">
         <v>24</v>
@@ -1305,7 +1302,7 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>23</v>
@@ -1344,16 +1341,16 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-73</v>
+        <v>-74</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>29</v>
@@ -1364,7 +1361,7 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>23</v>
@@ -1403,16 +1400,16 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-66</v>
+        <v>-67</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>29</v>
@@ -1462,19 +1459,19 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S14" s="6" t="s">
         <v>24</v>
@@ -1521,19 +1518,19 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>24</v>
@@ -1580,19 +1577,19 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S16" s="6" t="s">
         <v>24</v>
@@ -1639,16 +1636,16 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>29</v>
@@ -1698,19 +1695,19 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S18" s="6" t="s">
         <v>24</v>
@@ -1757,19 +1754,19 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S19" s="6" t="s">
         <v>24</v>
@@ -1816,19 +1813,19 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S20" s="6" t="s">
         <v>24</v>
@@ -1875,19 +1872,19 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S21" s="6" t="s">
         <v>24</v>
@@ -1934,19 +1931,19 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S22" s="6" t="s">
         <v>24</v>
@@ -1993,19 +1990,19 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S23" s="6" t="s">
         <v>24</v>
@@ -2052,19 +2049,19 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S24" s="6" t="s">
         <v>24</v>
@@ -2111,19 +2108,19 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>24</v>
@@ -2170,19 +2167,19 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>24</v>
@@ -2229,16 +2226,16 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>61</v>
       </c>
       <c r="Q27" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>24</v>
@@ -2288,19 +2285,19 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S28" s="6" t="s">
         <v>24</v>
@@ -2347,19 +2344,19 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S29" s="6" t="s">
         <v>24</v>
@@ -2406,19 +2403,19 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S30" s="6" t="s">
         <v>24</v>
@@ -2465,19 +2462,19 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S31" s="6" t="s">
         <v>24</v>
@@ -2524,19 +2521,19 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S32" s="6" t="s">
         <v>24</v>
@@ -2583,19 +2580,19 @@
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S33" s="6" t="s">
         <v>24</v>
@@ -2642,19 +2639,19 @@
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S34" s="6" t="s">
         <v>24</v>
@@ -2701,19 +2698,19 @@
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S35" s="6" t="s">
         <v>24</v>
@@ -2760,19 +2757,19 @@
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>24</v>
@@ -2819,19 +2816,19 @@
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S37" s="6" t="s">
         <v>24</v>
@@ -2878,19 +2875,19 @@
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S38" s="6" t="s">
         <v>24</v>
@@ -2937,19 +2934,19 @@
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S39" s="6" t="s">
         <v>24</v>
@@ -2996,19 +2993,19 @@
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S40" s="6" t="s">
         <v>24</v>
@@ -3055,19 +3052,19 @@
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S41" s="6" t="s">
         <v>24</v>
@@ -3114,19 +3111,19 @@
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S42" s="6" t="s">
         <v>24</v>
@@ -3173,19 +3170,19 @@
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S43" s="6" t="s">
         <v>24</v>
@@ -3232,19 +3229,19 @@
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S44" s="6" t="s">
         <v>24</v>
@@ -3291,16 +3288,16 @@
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>29</v>
@@ -3350,16 +3347,16 @@
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>61</v>
       </c>
       <c r="Q46" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>24</v>
@@ -3409,19 +3406,19 @@
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S47" s="6" t="s">
         <v>24</v>
@@ -3468,19 +3465,19 @@
         <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S48" s="6" t="s">
         <v>24</v>
@@ -3527,19 +3524,19 @@
         <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S49" s="6" t="s">
         <v>24</v>
@@ -3586,19 +3583,19 @@
         <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S50" s="6" t="s">
         <v>24</v>
@@ -3645,19 +3642,19 @@
         <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S51" s="6" t="s">
         <v>24</v>
@@ -3704,19 +3701,19 @@
         <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S52" s="6" t="s">
         <v>24</v>
@@ -3763,19 +3760,19 @@
         <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S53" s="6" t="s">
         <v>24</v>
@@ -3822,19 +3819,19 @@
         <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S54" s="6" t="s">
         <v>24</v>
@@ -3881,19 +3878,19 @@
         <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S55" s="6" t="s">
         <v>24</v>
@@ -3940,19 +3937,19 @@
         <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S56" s="6" t="s">
         <v>24</v>
@@ -3999,19 +3996,19 @@
         <v>28</v>
       </c>
       <c r="N57" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S57" s="6" t="s">
         <v>24</v>
@@ -4058,19 +4055,19 @@
         <v>28</v>
       </c>
       <c r="N58" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q58" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S58" s="6" t="s">
         <v>24</v>
@@ -4117,19 +4114,19 @@
         <v>28</v>
       </c>
       <c r="N59" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q59" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S59" s="6" t="s">
         <v>24</v>
@@ -4176,19 +4173,19 @@
         <v>28</v>
       </c>
       <c r="N60" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q60" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S60" s="6" t="s">
         <v>24</v>
@@ -4235,19 +4232,19 @@
         <v>28</v>
       </c>
       <c r="N61" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q61" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S61" s="6" t="s">
         <v>24</v>
@@ -4294,19 +4291,19 @@
         <v>28</v>
       </c>
       <c r="N62" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q62" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S62" s="6" t="s">
         <v>24</v>
@@ -4353,19 +4350,19 @@
         <v>28</v>
       </c>
       <c r="N63" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q63" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S63" s="6" t="s">
         <v>24</v>
@@ -4412,19 +4409,19 @@
         <v>28</v>
       </c>
       <c r="N64" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q64" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S64" s="6" t="s">
         <v>24</v>
@@ -4471,19 +4468,19 @@
         <v>28</v>
       </c>
       <c r="N65" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q65" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S65" s="6" t="s">
         <v>24</v>
@@ -4530,19 +4527,19 @@
         <v>28</v>
       </c>
       <c r="N66" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q66" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S66" s="6" t="s">
         <v>24</v>
@@ -4589,19 +4586,19 @@
         <v>28</v>
       </c>
       <c r="N67" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q67" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S67" s="6" t="s">
         <v>24</v>
@@ -4648,19 +4645,19 @@
         <v>28</v>
       </c>
       <c r="N68" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q68" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S68" s="6" t="s">
         <v>24</v>
@@ -4707,19 +4704,19 @@
         <v>28</v>
       </c>
       <c r="N69" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q69" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S69" s="6" t="s">
         <v>24</v>
@@ -4763,22 +4760,22 @@
         <v>185.5</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N70" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q70" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="S70" s="6" t="s">
         <v>24</v>
@@ -4825,7 +4822,7 @@
         <v>61</v>
       </c>
       <c r="N71" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
@@ -4834,7 +4831,7 @@
         <v>28</v>
       </c>
       <c r="Q71" s="9">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>29</v>
@@ -4845,13 +4842,13 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B72" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="C72" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>24</v>
@@ -4884,7 +4881,7 @@
         <v>61</v>
       </c>
       <c r="N72" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
@@ -4893,7 +4890,7 @@
         <v>61</v>
       </c>
       <c r="Q72" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4904,7 +4901,7 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>97</v>
@@ -4943,7 +4940,7 @@
         <v>61</v>
       </c>
       <c r="N73" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
@@ -4952,7 +4949,7 @@
         <v>61</v>
       </c>
       <c r="Q73" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4963,7 +4960,7 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>87</v>
@@ -5002,7 +4999,7 @@
         <v>61</v>
       </c>
       <c r="N74" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
@@ -5011,7 +5008,7 @@
         <v>61</v>
       </c>
       <c r="Q74" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -5022,7 +5019,7 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>64</v>
@@ -5061,7 +5058,7 @@
         <v>61</v>
       </c>
       <c r="N75" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
@@ -5070,7 +5067,7 @@
         <v>61</v>
       </c>
       <c r="Q75" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -5081,7 +5078,7 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>50</v>
@@ -5120,7 +5117,7 @@
         <v>61</v>
       </c>
       <c r="N76" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
@@ -5129,7 +5126,7 @@
         <v>61</v>
       </c>
       <c r="Q76" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -5140,7 +5137,7 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>46</v>
@@ -5179,7 +5176,7 @@
         <v>61</v>
       </c>
       <c r="N77" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
@@ -5188,7 +5185,7 @@
         <v>61</v>
       </c>
       <c r="Q77" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5199,10 +5196,10 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -5238,7 +5235,7 @@
         <v>61</v>
       </c>
       <c r="N78" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
@@ -5247,7 +5244,7 @@
         <v>61</v>
       </c>
       <c r="Q78" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5258,10 +5255,10 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
@@ -5297,7 +5294,7 @@
         <v>61</v>
       </c>
       <c r="N79" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
@@ -5306,7 +5303,7 @@
         <v>61</v>
       </c>
       <c r="Q79" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5317,10 +5314,10 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="B80" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="B80" s="6" t="s">
-        <v>137</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
@@ -5356,7 +5353,7 @@
         <v>61</v>
       </c>
       <c r="N80" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
@@ -5365,7 +5362,7 @@
         <v>61</v>
       </c>
       <c r="Q80" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5376,7 +5373,7 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>66</v>
@@ -5415,7 +5412,7 @@
         <v>61</v>
       </c>
       <c r="N81" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
@@ -5424,7 +5421,7 @@
         <v>61</v>
       </c>
       <c r="Q81" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5435,7 +5432,7 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>70</v>
@@ -5474,7 +5471,7 @@
         <v>61</v>
       </c>
       <c r="N82" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
@@ -5483,7 +5480,7 @@
         <v>61</v>
       </c>
       <c r="Q82" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5494,7 +5491,7 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>52</v>
@@ -5533,7 +5530,7 @@
         <v>61</v>
       </c>
       <c r="N83" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
@@ -5542,7 +5539,7 @@
         <v>61</v>
       </c>
       <c r="Q83" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5553,7 +5550,7 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>108</v>
@@ -5592,7 +5589,7 @@
         <v>61</v>
       </c>
       <c r="N84" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
@@ -5601,7 +5598,7 @@
         <v>61</v>
       </c>
       <c r="Q84" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5612,10 +5609,10 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="B85" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="B85" s="6" t="s">
-        <v>143</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>24</v>
@@ -5651,7 +5648,7 @@
         <v>61</v>
       </c>
       <c r="N85" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
@@ -5660,7 +5657,7 @@
         <v>61</v>
       </c>
       <c r="Q85" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5671,7 +5668,7 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>104</v>
@@ -5710,7 +5707,7 @@
         <v>61</v>
       </c>
       <c r="N86" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
@@ -5719,7 +5716,7 @@
         <v>61</v>
       </c>
       <c r="Q86" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5730,10 +5727,10 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B87" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>24</v>
@@ -5769,7 +5766,7 @@
         <v>61</v>
       </c>
       <c r="N87" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
@@ -5778,7 +5775,7 @@
         <v>61</v>
       </c>
       <c r="Q87" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5789,7 +5786,7 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>94</v>
@@ -5828,7 +5825,7 @@
         <v>61</v>
       </c>
       <c r="N88" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
@@ -5837,7 +5834,7 @@
         <v>61</v>
       </c>
       <c r="Q88" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5848,7 +5845,7 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>110</v>
@@ -5887,7 +5884,7 @@
         <v>61</v>
       </c>
       <c r="N89" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
@@ -5896,7 +5893,7 @@
         <v>61</v>
       </c>
       <c r="Q89" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5907,10 +5904,10 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>24</v>
@@ -5946,7 +5943,7 @@
         <v>61</v>
       </c>
       <c r="N90" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
@@ -5955,7 +5952,7 @@
         <v>61</v>
       </c>
       <c r="Q90" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5966,7 +5963,7 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>60</v>
@@ -6005,7 +6002,7 @@
         <v>61</v>
       </c>
       <c r="N91" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
@@ -6014,7 +6011,7 @@
         <v>61</v>
       </c>
       <c r="Q91" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -6025,7 +6022,7 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>84</v>
@@ -6064,7 +6061,7 @@
         <v>61</v>
       </c>
       <c r="N92" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
@@ -6073,7 +6070,7 @@
         <v>61</v>
       </c>
       <c r="Q92" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -6084,7 +6081,7 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>73</v>
@@ -6123,7 +6120,7 @@
         <v>61</v>
       </c>
       <c r="N93" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
@@ -6132,7 +6129,7 @@
         <v>61</v>
       </c>
       <c r="Q93" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -6143,7 +6140,7 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>54</v>
@@ -6182,7 +6179,7 @@
         <v>61</v>
       </c>
       <c r="N94" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
@@ -6191,7 +6188,7 @@
         <v>61</v>
       </c>
       <c r="Q94" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6202,7 +6199,7 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>92</v>
@@ -6241,7 +6238,7 @@
         <v>61</v>
       </c>
       <c r="N95" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
@@ -6250,7 +6247,7 @@
         <v>61</v>
       </c>
       <c r="Q95" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6261,7 +6258,7 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>77</v>
@@ -6300,7 +6297,7 @@
         <v>61</v>
       </c>
       <c r="N96" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
@@ -6309,7 +6306,7 @@
         <v>61</v>
       </c>
       <c r="Q96" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6320,7 +6317,7 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>56</v>
@@ -6359,7 +6356,7 @@
         <v>61</v>
       </c>
       <c r="N97" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
@@ -6368,7 +6365,7 @@
         <v>61</v>
       </c>
       <c r="Q97" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6379,10 +6376,10 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>24</v>
@@ -6418,7 +6415,7 @@
         <v>61</v>
       </c>
       <c r="N98" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
@@ -6427,7 +6424,7 @@
         <v>61</v>
       </c>
       <c r="Q98" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6438,7 +6435,7 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>81</v>
@@ -6477,7 +6474,7 @@
         <v>61</v>
       </c>
       <c r="N99" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
@@ -6486,7 +6483,7 @@
         <v>61</v>
       </c>
       <c r="Q99" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6497,13 +6494,13 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>24</v>
@@ -6536,7 +6533,7 @@
         <v>61</v>
       </c>
       <c r="N100" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
@@ -6545,7 +6542,7 @@
         <v>61</v>
       </c>
       <c r="Q100" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6556,7 +6553,7 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>97</v>
@@ -6595,7 +6592,7 @@
         <v>61</v>
       </c>
       <c r="N101" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
@@ -6604,7 +6601,7 @@
         <v>61</v>
       </c>
       <c r="Q101" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6615,7 +6612,7 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>87</v>
@@ -6654,7 +6651,7 @@
         <v>61</v>
       </c>
       <c r="N102" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
@@ -6663,7 +6660,7 @@
         <v>61</v>
       </c>
       <c r="Q102" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6674,7 +6671,7 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>50</v>
@@ -6713,7 +6710,7 @@
         <v>61</v>
       </c>
       <c r="N103" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
@@ -6722,7 +6719,7 @@
         <v>61</v>
       </c>
       <c r="Q103" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6733,10 +6730,10 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>24</v>
@@ -6772,7 +6769,7 @@
         <v>61</v>
       </c>
       <c r="N104" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
@@ -6781,7 +6778,7 @@
         <v>61</v>
       </c>
       <c r="Q104" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6792,7 +6789,7 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>64</v>
@@ -6831,7 +6828,7 @@
         <v>61</v>
       </c>
       <c r="N105" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
@@ -6840,7 +6837,7 @@
         <v>61</v>
       </c>
       <c r="Q105" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6851,7 +6848,7 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>66</v>
@@ -6890,7 +6887,7 @@
         <v>61</v>
       </c>
       <c r="N106" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
@@ -6899,7 +6896,7 @@
         <v>61</v>
       </c>
       <c r="Q106" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>
@@ -6910,10 +6907,10 @@
     </row>
     <row r="107">
       <c r="A107" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>24</v>
@@ -6949,7 +6946,7 @@
         <v>61</v>
       </c>
       <c r="N107" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>24</v>
@@ -6958,7 +6955,7 @@
         <v>61</v>
       </c>
       <c r="Q107" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>24</v>
@@ -6969,10 +6966,10 @@
     </row>
     <row r="108">
       <c r="A108" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>24</v>
@@ -7008,7 +7005,7 @@
         <v>61</v>
       </c>
       <c r="N108" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>24</v>
@@ -7017,7 +7014,7 @@
         <v>61</v>
       </c>
       <c r="Q108" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>24</v>
@@ -7028,7 +7025,7 @@
     </row>
     <row r="109">
       <c r="A109" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>52</v>
@@ -7067,7 +7064,7 @@
         <v>61</v>
       </c>
       <c r="N109" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>24</v>
@@ -7076,7 +7073,7 @@
         <v>61</v>
       </c>
       <c r="Q109" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R109" s="6" t="s">
         <v>24</v>
@@ -7087,7 +7084,7 @@
     </row>
     <row r="110">
       <c r="A110" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>108</v>
@@ -7126,7 +7123,7 @@
         <v>61</v>
       </c>
       <c r="N110" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>24</v>
@@ -7135,7 +7132,7 @@
         <v>61</v>
       </c>
       <c r="Q110" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R110" s="6" t="s">
         <v>24</v>
@@ -7146,7 +7143,7 @@
     </row>
     <row r="111">
       <c r="A111" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>104</v>
@@ -7185,7 +7182,7 @@
         <v>61</v>
       </c>
       <c r="N111" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>24</v>
@@ -7194,7 +7191,7 @@
         <v>61</v>
       </c>
       <c r="Q111" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R111" s="6" t="s">
         <v>24</v>
@@ -7205,7 +7202,7 @@
     </row>
     <row r="112">
       <c r="A112" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>70</v>
@@ -7244,7 +7241,7 @@
         <v>61</v>
       </c>
       <c r="N112" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>24</v>
@@ -7253,7 +7250,7 @@
         <v>61</v>
       </c>
       <c r="Q112" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R112" s="6" t="s">
         <v>24</v>
@@ -7264,10 +7261,10 @@
     </row>
     <row r="113">
       <c r="A113" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>24</v>
@@ -7303,7 +7300,7 @@
         <v>61</v>
       </c>
       <c r="N113" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>24</v>
@@ -7312,7 +7309,7 @@
         <v>61</v>
       </c>
       <c r="Q113" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R113" s="6" t="s">
         <v>24</v>
@@ -7323,10 +7320,10 @@
     </row>
     <row r="114">
       <c r="A114" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>24</v>
@@ -7362,7 +7359,7 @@
         <v>61</v>
       </c>
       <c r="N114" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>24</v>
@@ -7371,7 +7368,7 @@
         <v>61</v>
       </c>
       <c r="Q114" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R114" s="6" t="s">
         <v>24</v>
@@ -7382,10 +7379,10 @@
     </row>
     <row r="115">
       <c r="A115" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>24</v>
@@ -7421,7 +7418,7 @@
         <v>61</v>
       </c>
       <c r="N115" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O115" s="6" t="s">
         <v>24</v>
@@ -7430,7 +7427,7 @@
         <v>61</v>
       </c>
       <c r="Q115" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R115" s="6" t="s">
         <v>24</v>
@@ -7441,7 +7438,7 @@
     </row>
     <row r="116">
       <c r="A116" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>84</v>
@@ -7480,7 +7477,7 @@
         <v>61</v>
       </c>
       <c r="N116" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>24</v>
@@ -7489,7 +7486,7 @@
         <v>61</v>
       </c>
       <c r="Q116" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R116" s="6" t="s">
         <v>24</v>
@@ -7500,7 +7497,7 @@
     </row>
     <row r="117">
       <c r="A117" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>73</v>
@@ -7539,7 +7536,7 @@
         <v>61</v>
       </c>
       <c r="N117" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O117" s="6" t="s">
         <v>24</v>
@@ -7548,7 +7545,7 @@
         <v>61</v>
       </c>
       <c r="Q117" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R117" s="6" t="s">
         <v>24</v>
@@ -7559,7 +7556,7 @@
     </row>
     <row r="118">
       <c r="A118" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>94</v>
@@ -7598,7 +7595,7 @@
         <v>61</v>
       </c>
       <c r="N118" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>24</v>
@@ -7607,7 +7604,7 @@
         <v>61</v>
       </c>
       <c r="Q118" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R118" s="6" t="s">
         <v>24</v>
@@ -7618,7 +7615,7 @@
     </row>
     <row r="119">
       <c r="A119" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>110</v>
@@ -7657,7 +7654,7 @@
         <v>61</v>
       </c>
       <c r="N119" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O119" s="6" t="s">
         <v>24</v>
@@ -7666,7 +7663,7 @@
         <v>61</v>
       </c>
       <c r="Q119" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R119" s="6" t="s">
         <v>24</v>
@@ -7677,7 +7674,7 @@
     </row>
     <row r="120">
       <c r="A120" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>60</v>
@@ -7716,7 +7713,7 @@
         <v>61</v>
       </c>
       <c r="N120" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>24</v>
@@ -7725,7 +7722,7 @@
         <v>61</v>
       </c>
       <c r="Q120" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R120" s="6" t="s">
         <v>24</v>
@@ -7736,7 +7733,7 @@
     </row>
     <row r="121">
       <c r="A121" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>54</v>
@@ -7775,7 +7772,7 @@
         <v>61</v>
       </c>
       <c r="N121" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O121" s="6" t="s">
         <v>24</v>
@@ -7784,7 +7781,7 @@
         <v>61</v>
       </c>
       <c r="Q121" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R121" s="6" t="s">
         <v>24</v>
@@ -7795,7 +7792,7 @@
     </row>
     <row r="122">
       <c r="A122" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>77</v>
@@ -7834,7 +7831,7 @@
         <v>61</v>
       </c>
       <c r="N122" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>24</v>
@@ -7843,7 +7840,7 @@
         <v>61</v>
       </c>
       <c r="Q122" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R122" s="6" t="s">
         <v>24</v>
@@ -7854,7 +7851,7 @@
     </row>
     <row r="123">
       <c r="A123" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>92</v>
@@ -7893,7 +7890,7 @@
         <v>61</v>
       </c>
       <c r="N123" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O123" s="6" t="s">
         <v>24</v>
@@ -7902,7 +7899,7 @@
         <v>61</v>
       </c>
       <c r="Q123" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R123" s="6" t="s">
         <v>24</v>
@@ -7913,7 +7910,7 @@
     </row>
     <row r="124">
       <c r="A124" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>56</v>
@@ -7952,7 +7949,7 @@
         <v>61</v>
       </c>
       <c r="N124" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>24</v>
@@ -7961,7 +7958,7 @@
         <v>61</v>
       </c>
       <c r="Q124" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R124" s="6" t="s">
         <v>24</v>
@@ -7972,10 +7969,10 @@
     </row>
     <row r="125">
       <c r="A125" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>24</v>
@@ -8011,7 +8008,7 @@
         <v>61</v>
       </c>
       <c r="N125" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O125" s="6" t="s">
         <v>24</v>
@@ -8020,7 +8017,7 @@
         <v>61</v>
       </c>
       <c r="Q125" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R125" s="6" t="s">
         <v>24</v>
@@ -8031,7 +8028,7 @@
     </row>
     <row r="126">
       <c r="A126" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>81</v>
@@ -8070,7 +8067,7 @@
         <v>61</v>
       </c>
       <c r="N126" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>24</v>
@@ -8079,7 +8076,7 @@
         <v>61</v>
       </c>
       <c r="Q126" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R126" s="6" t="s">
         <v>24</v>
@@ -8090,13 +8087,13 @@
     </row>
     <row r="127">
       <c r="A127" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>24</v>
@@ -8129,7 +8126,7 @@
         <v>61</v>
       </c>
       <c r="N127" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O127" s="6" t="s">
         <v>24</v>
@@ -8138,7 +8135,7 @@
         <v>61</v>
       </c>
       <c r="Q127" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R127" s="6" t="s">
         <v>24</v>
@@ -8149,7 +8146,7 @@
     </row>
     <row r="128">
       <c r="A128" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>97</v>
@@ -8188,7 +8185,7 @@
         <v>61</v>
       </c>
       <c r="N128" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>24</v>
@@ -8197,7 +8194,7 @@
         <v>61</v>
       </c>
       <c r="Q128" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R128" s="6" t="s">
         <v>24</v>
@@ -8208,7 +8205,7 @@
     </row>
     <row r="129">
       <c r="A129" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>87</v>
@@ -8247,7 +8244,7 @@
         <v>61</v>
       </c>
       <c r="N129" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O129" s="6" t="s">
         <v>24</v>
@@ -8256,7 +8253,7 @@
         <v>61</v>
       </c>
       <c r="Q129" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R129" s="6" t="s">
         <v>24</v>
@@ -8267,10 +8264,10 @@
     </row>
     <row r="130">
       <c r="A130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>24</v>
@@ -8306,7 +8303,7 @@
         <v>61</v>
       </c>
       <c r="N130" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>24</v>
@@ -8315,7 +8312,7 @@
         <v>61</v>
       </c>
       <c r="Q130" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R130" s="6" t="s">
         <v>24</v>
@@ -8326,10 +8323,10 @@
     </row>
     <row r="131">
       <c r="A131" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>24</v>
@@ -8365,7 +8362,7 @@
         <v>61</v>
       </c>
       <c r="N131" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O131" s="6" t="s">
         <v>24</v>
@@ -8374,7 +8371,7 @@
         <v>61</v>
       </c>
       <c r="Q131" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R131" s="6" t="s">
         <v>24</v>
@@ -8385,10 +8382,10 @@
     </row>
     <row r="132">
       <c r="A132" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>24</v>
@@ -8424,7 +8421,7 @@
         <v>61</v>
       </c>
       <c r="N132" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>24</v>
@@ -8433,7 +8430,7 @@
         <v>61</v>
       </c>
       <c r="Q132" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R132" s="6" t="s">
         <v>24</v>
@@ -8444,7 +8441,7 @@
     </row>
     <row r="133">
       <c r="A133" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>64</v>
@@ -8483,7 +8480,7 @@
         <v>61</v>
       </c>
       <c r="N133" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O133" s="6" t="s">
         <v>24</v>
@@ -8492,7 +8489,7 @@
         <v>61</v>
       </c>
       <c r="Q133" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R133" s="6" t="s">
         <v>24</v>
@@ -8503,7 +8500,7 @@
     </row>
     <row r="134">
       <c r="A134" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>50</v>
@@ -8542,7 +8539,7 @@
         <v>61</v>
       </c>
       <c r="N134" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>24</v>
@@ -8551,7 +8548,7 @@
         <v>61</v>
       </c>
       <c r="Q134" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R134" s="6" t="s">
         <v>24</v>
@@ -8562,7 +8559,7 @@
     </row>
     <row r="135">
       <c r="A135" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>66</v>
@@ -8601,7 +8598,7 @@
         <v>61</v>
       </c>
       <c r="N135" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O135" s="6" t="s">
         <v>24</v>
@@ -8610,7 +8607,7 @@
         <v>61</v>
       </c>
       <c r="Q135" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R135" s="6" t="s">
         <v>24</v>
@@ -8621,7 +8618,7 @@
     </row>
     <row r="136">
       <c r="A136" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>104</v>
@@ -8660,7 +8657,7 @@
         <v>61</v>
       </c>
       <c r="N136" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>24</v>
@@ -8669,7 +8666,7 @@
         <v>61</v>
       </c>
       <c r="Q136" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R136" s="6" t="s">
         <v>24</v>
@@ -8680,7 +8677,7 @@
     </row>
     <row r="137">
       <c r="A137" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>52</v>
@@ -8719,7 +8716,7 @@
         <v>61</v>
       </c>
       <c r="N137" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O137" s="6" t="s">
         <v>24</v>
@@ -8728,7 +8725,7 @@
         <v>61</v>
       </c>
       <c r="Q137" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R137" s="6" t="s">
         <v>24</v>
@@ -8739,7 +8736,7 @@
     </row>
     <row r="138">
       <c r="A138" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>70</v>
@@ -8778,7 +8775,7 @@
         <v>61</v>
       </c>
       <c r="N138" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>24</v>
@@ -8787,7 +8784,7 @@
         <v>61</v>
       </c>
       <c r="Q138" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R138" s="6" t="s">
         <v>24</v>
@@ -8798,7 +8795,7 @@
     </row>
     <row r="139">
       <c r="A139" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>108</v>
@@ -8837,7 +8834,7 @@
         <v>61</v>
       </c>
       <c r="N139" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O139" s="6" t="s">
         <v>24</v>
@@ -8846,7 +8843,7 @@
         <v>61</v>
       </c>
       <c r="Q139" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R139" s="6" t="s">
         <v>24</v>
@@ -8857,10 +8854,10 @@
     </row>
     <row r="140">
       <c r="A140" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>24</v>
@@ -8896,7 +8893,7 @@
         <v>61</v>
       </c>
       <c r="N140" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>24</v>
@@ -8905,7 +8902,7 @@
         <v>61</v>
       </c>
       <c r="Q140" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R140" s="6" t="s">
         <v>24</v>
@@ -8916,10 +8913,10 @@
     </row>
     <row r="141">
       <c r="A141" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>24</v>
@@ -8955,7 +8952,7 @@
         <v>61</v>
       </c>
       <c r="N141" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O141" s="6" t="s">
         <v>24</v>
@@ -8964,7 +8961,7 @@
         <v>61</v>
       </c>
       <c r="Q141" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R141" s="6" t="s">
         <v>24</v>
@@ -8975,7 +8972,7 @@
     </row>
     <row r="142">
       <c r="A142" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>60</v>
@@ -9014,7 +9011,7 @@
         <v>61</v>
       </c>
       <c r="N142" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>24</v>
@@ -9023,7 +9020,7 @@
         <v>61</v>
       </c>
       <c r="Q142" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R142" s="6" t="s">
         <v>24</v>
@@ -9034,10 +9031,10 @@
     </row>
     <row r="143">
       <c r="A143" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>24</v>
@@ -9073,7 +9070,7 @@
         <v>61</v>
       </c>
       <c r="N143" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O143" s="6" t="s">
         <v>24</v>
@@ -9082,7 +9079,7 @@
         <v>61</v>
       </c>
       <c r="Q143" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R143" s="6" t="s">
         <v>24</v>
@@ -9093,7 +9090,7 @@
     </row>
     <row r="144">
       <c r="A144" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>84</v>
@@ -9132,7 +9129,7 @@
         <v>61</v>
       </c>
       <c r="N144" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>24</v>
@@ -9141,7 +9138,7 @@
         <v>61</v>
       </c>
       <c r="Q144" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R144" s="6" t="s">
         <v>24</v>
@@ -9152,7 +9149,7 @@
     </row>
     <row r="145">
       <c r="A145" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>94</v>
@@ -9191,7 +9188,7 @@
         <v>61</v>
       </c>
       <c r="N145" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O145" s="6" t="s">
         <v>24</v>
@@ -9200,7 +9197,7 @@
         <v>61</v>
       </c>
       <c r="Q145" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R145" s="6" t="s">
         <v>24</v>
@@ -9211,7 +9208,7 @@
     </row>
     <row r="146">
       <c r="A146" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>54</v>
@@ -9250,7 +9247,7 @@
         <v>61</v>
       </c>
       <c r="N146" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O146" s="6" t="s">
         <v>24</v>
@@ -9259,7 +9256,7 @@
         <v>61</v>
       </c>
       <c r="Q146" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R146" s="6" t="s">
         <v>24</v>
@@ -9270,7 +9267,7 @@
     </row>
     <row r="147">
       <c r="A147" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>110</v>
@@ -9309,7 +9306,7 @@
         <v>61</v>
       </c>
       <c r="N147" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O147" s="6" t="s">
         <v>24</v>
@@ -9318,7 +9315,7 @@
         <v>61</v>
       </c>
       <c r="Q147" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R147" s="6" t="s">
         <v>24</v>
@@ -9329,7 +9326,7 @@
     </row>
     <row r="148">
       <c r="A148" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>73</v>
@@ -9368,7 +9365,7 @@
         <v>61</v>
       </c>
       <c r="N148" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>24</v>
@@ -9377,7 +9374,7 @@
         <v>61</v>
       </c>
       <c r="Q148" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R148" s="6" t="s">
         <v>24</v>
@@ -9388,7 +9385,7 @@
     </row>
     <row r="149">
       <c r="A149" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>77</v>
@@ -9427,7 +9424,7 @@
         <v>61</v>
       </c>
       <c r="N149" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>24</v>
@@ -9436,7 +9433,7 @@
         <v>61</v>
       </c>
       <c r="Q149" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R149" s="6" t="s">
         <v>24</v>
@@ -9447,7 +9444,7 @@
     </row>
     <row r="150">
       <c r="A150" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>92</v>
@@ -9486,7 +9483,7 @@
         <v>61</v>
       </c>
       <c r="N150" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>24</v>
@@ -9495,7 +9492,7 @@
         <v>61</v>
       </c>
       <c r="Q150" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R150" s="6" t="s">
         <v>24</v>
@@ -9506,7 +9503,7 @@
     </row>
     <row r="151">
       <c r="A151" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>56</v>
@@ -9545,7 +9542,7 @@
         <v>61</v>
       </c>
       <c r="N151" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O151" s="6" t="s">
         <v>24</v>
@@ -9554,7 +9551,7 @@
         <v>61</v>
       </c>
       <c r="Q151" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R151" s="6" t="s">
         <v>24</v>
@@ -9565,10 +9562,10 @@
     </row>
     <row r="152">
       <c r="A152" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>24</v>
@@ -9604,7 +9601,7 @@
         <v>61</v>
       </c>
       <c r="N152" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>24</v>
@@ -9613,7 +9610,7 @@
         <v>61</v>
       </c>
       <c r="Q152" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R152" s="6" t="s">
         <v>24</v>
@@ -9624,7 +9621,7 @@
     </row>
     <row r="153">
       <c r="A153" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>81</v>
@@ -9663,7 +9660,7 @@
         <v>61</v>
       </c>
       <c r="N153" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O153" s="6" t="s">
         <v>24</v>
@@ -9672,7 +9669,7 @@
         <v>61</v>
       </c>
       <c r="Q153" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R153" s="6" t="s">
         <v>24</v>
@@ -9683,7 +9680,7 @@
     </row>
     <row r="154">
       <c r="A154" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>104</v>
@@ -9722,7 +9719,7 @@
         <v>61</v>
       </c>
       <c r="N154" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>24</v>
@@ -9731,7 +9728,7 @@
         <v>61</v>
       </c>
       <c r="Q154" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R154" s="6" t="s">
         <v>24</v>
@@ -9742,7 +9739,7 @@
     </row>
     <row r="155">
       <c r="A155" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>70</v>
@@ -9781,7 +9778,7 @@
         <v>61</v>
       </c>
       <c r="N155" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O155" s="6" t="s">
         <v>24</v>
@@ -9790,7 +9787,7 @@
         <v>61</v>
       </c>
       <c r="Q155" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R155" s="6" t="s">
         <v>24</v>
@@ -9801,10 +9798,10 @@
     </row>
     <row r="156">
       <c r="A156" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>24</v>
@@ -9840,7 +9837,7 @@
         <v>61</v>
       </c>
       <c r="N156" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O156" s="6" t="s">
         <v>24</v>
@@ -9849,7 +9846,7 @@
         <v>61</v>
       </c>
       <c r="Q156" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R156" s="6" t="s">
         <v>24</v>
@@ -9860,10 +9857,10 @@
     </row>
     <row r="157">
       <c r="A157" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>24</v>
@@ -9899,7 +9896,7 @@
         <v>61</v>
       </c>
       <c r="N157" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O157" s="6" t="s">
         <v>24</v>
@@ -9908,7 +9905,7 @@
         <v>61</v>
       </c>
       <c r="Q157" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R157" s="6" t="s">
         <v>24</v>
@@ -9919,7 +9916,7 @@
     </row>
     <row r="158">
       <c r="A158" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>92</v>
@@ -9958,7 +9955,7 @@
         <v>61</v>
       </c>
       <c r="N158" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O158" s="6" t="s">
         <v>24</v>
@@ -9967,7 +9964,7 @@
         <v>61</v>
       </c>
       <c r="Q158" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R158" s="6" t="s">
         <v>24</v>
@@ -9978,10 +9975,10 @@
     </row>
     <row r="159">
       <c r="A159" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>24</v>
@@ -10017,7 +10014,7 @@
         <v>61</v>
       </c>
       <c r="N159" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="O159" s="6" t="s">
         <v>24</v>
@@ -10026,7 +10023,7 @@
         <v>61</v>
       </c>
       <c r="Q159" s="9">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="R159" s="6" t="s">
         <v>24</v>
@@ -10076,7 +10073,7 @@
         <v>61</v>
       </c>
       <c r="N160" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>24</v>
@@ -10085,7 +10082,7 @@
         <v>61</v>
       </c>
       <c r="Q160" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R160" s="6" t="s">
         <v>24</v>
@@ -10096,10 +10093,10 @@
     </row>
     <row r="161">
       <c r="A161" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>24</v>
@@ -10135,7 +10132,7 @@
         <v>61</v>
       </c>
       <c r="N161" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O161" s="6" t="s">
         <v>24</v>
@@ -10144,7 +10141,7 @@
         <v>61</v>
       </c>
       <c r="Q161" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R161" s="6" t="s">
         <v>24</v>
@@ -10155,7 +10152,7 @@
     </row>
     <row r="162">
       <c r="A162" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>104</v>
@@ -10194,7 +10191,7 @@
         <v>61</v>
       </c>
       <c r="N162" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>24</v>
@@ -10203,7 +10200,7 @@
         <v>61</v>
       </c>
       <c r="Q162" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R162" s="6" t="s">
         <v>24</v>
@@ -10214,10 +10211,10 @@
     </row>
     <row r="163">
       <c r="A163" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>24</v>
@@ -10253,7 +10250,7 @@
         <v>61</v>
       </c>
       <c r="N163" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O163" s="6" t="s">
         <v>24</v>
@@ -10262,7 +10259,7 @@
         <v>61</v>
       </c>
       <c r="Q163" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R163" s="6" t="s">
         <v>24</v>
@@ -10273,10 +10270,10 @@
     </row>
     <row r="164">
       <c r="A164" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>24</v>
@@ -10312,7 +10309,7 @@
         <v>61</v>
       </c>
       <c r="N164" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="O164" s="6" t="s">
         <v>24</v>
@@ -10321,7 +10318,7 @@
         <v>61</v>
       </c>
       <c r="Q164" s="9">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="R164" s="6" t="s">
         <v>24</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sexta-feira, 31 de julho de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em sábado, 1 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -148,18 +148,18 @@
     <t>FA-11562</t>
   </si>
   <si>
+    <t>ND-11870</t>
+  </si>
+  <si>
+    <t>DIEGO TAYAO DANTAS</t>
+  </si>
+  <si>
+    <t>NOTA DE DÉBITO</t>
+  </si>
+  <si>
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>ND-11870</t>
-  </si>
-  <si>
-    <t>DIEGO TAYAO DANTAS</t>
-  </si>
-  <si>
-    <t>NOTA DE DÉBITO</t>
-  </si>
-  <si>
     <t>FA-11880</t>
   </si>
   <si>
@@ -229,27 +229,27 @@
     <t>ADRIANO SANTOS DE CARVALHO</t>
   </si>
   <si>
+    <t>FA-11915</t>
+  </si>
+  <si>
     <t>FA-11987</t>
   </si>
   <si>
     <t>MARIO EWERTON CANDIDO DE SOUZA</t>
   </si>
   <si>
-    <t>FA-11915</t>
+    <t>FA-11856</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
   </si>
   <si>
     <t>FA-11969</t>
   </si>
   <si>
-    <t>FA-11856</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
     <t>FA-11961</t>
   </si>
   <si>
@@ -334,13 +334,25 @@
     <t>FA-11971</t>
   </si>
   <si>
+    <t>FA-11993</t>
+  </si>
+  <si>
     <t>FA-11947</t>
   </si>
   <si>
     <t>FA-12031</t>
   </si>
   <si>
-    <t>FA-11993</t>
+    <t>FA-12044</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11857</t>
+  </si>
+  <si>
+    <t>FA-11972</t>
   </si>
   <si>
     <t>FA-11920</t>
@@ -349,16 +361,10 @@
     <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
   </si>
   <si>
-    <t>FA-11857</t>
-  </si>
-  <si>
-    <t>FA-11972</t>
-  </si>
-  <si>
-    <t>FA-12044</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
+    <t>FA-12017</t>
+  </si>
+  <si>
+    <t>FA-12030</t>
   </si>
   <si>
     <t>FA-11992</t>
@@ -370,15 +376,9 @@
     <t>FA-11962</t>
   </si>
   <si>
-    <t>FA-12017</t>
-  </si>
-  <si>
     <t>FA-12019</t>
   </si>
   <si>
-    <t>FA-12030</t>
-  </si>
-  <si>
     <t>FA-12046</t>
   </si>
   <si>
@@ -418,51 +418,51 @@
     <t>FA-12052</t>
   </si>
   <si>
+    <t>FA-12015</t>
+  </si>
+  <si>
+    <t>FA-12034</t>
+  </si>
+  <si>
+    <t>FA-11995</t>
+  </si>
+  <si>
+    <t>FA-11997</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-12048</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
     <t>FA-11975</t>
   </si>
   <si>
-    <t>FA-12034</t>
-  </si>
-  <si>
-    <t>FA-12015</t>
-  </si>
-  <si>
-    <t>FA-11997</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-12048</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
     <t>FA-11978</t>
   </si>
   <si>
     <t>ANA FLORIPES CARVALHO DA CUNHA</t>
   </si>
   <si>
-    <t>FA-11995</t>
+    <t>FA-12062</t>
+  </si>
+  <si>
+    <t>WILSON COUTINHO BEZERRA</t>
   </si>
   <si>
     <t>FA-11858</t>
   </si>
   <si>
+    <t>FA-12049</t>
+  </si>
+  <si>
     <t>FA-11976</t>
   </si>
   <si>
-    <t>FA-12049</t>
-  </si>
-  <si>
-    <t>FA-12062</t>
-  </si>
-  <si>
-    <t>WILSON COUTINHO BEZERRA</t>
-  </si>
-  <si>
     <t>FA-11921</t>
   </si>
   <si>
@@ -472,36 +472,36 @@
     <t>RAYANE ROBERTA DA SILVA</t>
   </si>
   <si>
+    <t>FA-11963</t>
+  </si>
+  <si>
+    <t>FA-11998</t>
+  </si>
+  <si>
+    <t>FA-11933</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-12022</t>
+  </si>
+  <si>
+    <t>FA-12035</t>
+  </si>
+  <si>
     <t>FA-12029</t>
   </si>
   <si>
-    <t>FA-11998</t>
-  </si>
-  <si>
-    <t>FA-11933</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-12022</t>
-  </si>
-  <si>
-    <t>FA-12035</t>
-  </si>
-  <si>
-    <t>FA-11963</t>
-  </si>
-  <si>
     <t>FA-12021</t>
   </si>
   <si>
+    <t>FA-12050</t>
+  </si>
+  <si>
     <t>FA-11866</t>
   </si>
   <si>
-    <t>FA-12050</t>
-  </si>
-  <si>
     <t>FA-12020</t>
   </si>
   <si>
@@ -523,33 +523,33 @@
     <t>FA-12055</t>
   </si>
   <si>
+    <t>FA-12053</t>
+  </si>
+  <si>
+    <t>FA-12000</t>
+  </si>
+  <si>
+    <t>FA-11979</t>
+  </si>
+  <si>
     <t>FA-12037</t>
   </si>
   <si>
-    <t>FA-12000</t>
-  </si>
-  <si>
-    <t>FA-11979</t>
+    <t>FA-11982</t>
   </si>
   <si>
     <t>FA-12001</t>
   </si>
   <si>
-    <t>FA-11982</t>
-  </si>
-  <si>
-    <t>FA-12053</t>
+    <t>FA-12054</t>
+  </si>
+  <si>
+    <t>FA-11922</t>
   </si>
   <si>
     <t>FA-11980</t>
   </si>
   <si>
-    <t>FA-12054</t>
-  </si>
-  <si>
-    <t>FA-11922</t>
-  </si>
-  <si>
     <t>FA-11860</t>
   </si>
   <si>
@@ -559,33 +559,33 @@
     <t>FA-12039</t>
   </si>
   <si>
+    <t>FA-11964</t>
+  </si>
+  <si>
+    <t>FA-12024</t>
+  </si>
+  <si>
+    <t>FA-12025</t>
+  </si>
+  <si>
+    <t>FA-12033</t>
+  </si>
+  <si>
+    <t>FA-12038</t>
+  </si>
+  <si>
+    <t>FA-12002</t>
+  </si>
+  <si>
     <t>FA-11934</t>
   </si>
   <si>
-    <t>FA-12038</t>
-  </si>
-  <si>
-    <t>FA-11964</t>
-  </si>
-  <si>
-    <t>FA-12033</t>
-  </si>
-  <si>
-    <t>FA-12002</t>
-  </si>
-  <si>
-    <t>FA-12025</t>
-  </si>
-  <si>
-    <t>FA-12024</t>
+    <t>FA-11867</t>
   </si>
   <si>
     <t>FA-12051</t>
   </si>
   <si>
-    <t>FA-11867</t>
-  </si>
-  <si>
     <t>FA-12023</t>
   </si>
   <si>
@@ -604,69 +604,69 @@
     <t>FA-12059</t>
   </si>
   <si>
+    <t>FA-12057</t>
+  </si>
+  <si>
+    <t>FA-11983</t>
+  </si>
+  <si>
+    <t>FA-12004</t>
+  </si>
+  <si>
+    <t>FA-12040</t>
+  </si>
+  <si>
+    <t>FA-11986</t>
+  </si>
+  <si>
     <t>FA-12008</t>
   </si>
   <si>
-    <t>FA-11986</t>
-  </si>
-  <si>
-    <t>FA-12057</t>
-  </si>
-  <si>
-    <t>FA-11983</t>
-  </si>
-  <si>
-    <t>FA-12040</t>
-  </si>
-  <si>
-    <t>FA-12004</t>
+    <t>FA-12064</t>
+  </si>
+  <si>
+    <t>FA-12058</t>
+  </si>
+  <si>
+    <t>FA-11984</t>
   </si>
   <si>
     <t>FA-11923</t>
   </si>
   <si>
-    <t>FA-11984</t>
-  </si>
-  <si>
     <t>FA-11862</t>
   </si>
   <si>
-    <t>FA-12058</t>
-  </si>
-  <si>
-    <t>FA-12064</t>
-  </si>
-  <si>
     <t>FA-12041</t>
   </si>
   <si>
+    <t>FA-11935</t>
+  </si>
+  <si>
     <t>FA-12027</t>
   </si>
   <si>
-    <t>FA-11935</t>
+    <t>FA-12005</t>
+  </si>
+  <si>
+    <t>FA-12043</t>
+  </si>
+  <si>
+    <t>FA-12028</t>
+  </si>
+  <si>
+    <t>FA-11965</t>
   </si>
   <si>
     <t>FA-12042</t>
   </si>
   <si>
-    <t>FA-12043</t>
-  </si>
-  <si>
-    <t>FA-12028</t>
-  </si>
-  <si>
-    <t>FA-12005</t>
-  </si>
-  <si>
-    <t>FA-11965</t>
+    <t>FA-11868</t>
   </si>
   <si>
     <t>FA-12056</t>
   </si>
   <si>
-    <t>FA-11868</t>
-  </si>
-  <si>
     <t>FA-12026</t>
   </si>
   <si>
@@ -676,13 +676,13 @@
     <t>FA-12003</t>
   </si>
   <si>
+    <t>FA-11864</t>
+  </si>
+  <si>
+    <t>FA-12065</t>
+  </si>
+  <si>
     <t>FA-11924</t>
-  </si>
-  <si>
-    <t>FA-11864</t>
-  </si>
-  <si>
-    <t>FA-12065</t>
   </si>
   <si>
     <t>FA-11936</t>
@@ -987,7 +987,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-60</v>
+        <v>-61</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -996,7 +996,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-60</v>
+        <v>-61</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -1046,7 +1046,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -1055,7 +1055,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
@@ -1105,7 +1105,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-46</v>
+        <v>-47</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -1114,7 +1114,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-46</v>
+        <v>-47</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -1164,7 +1164,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -1173,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1223,7 +1223,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -1232,7 +1232,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -1282,7 +1282,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>29</v>
@@ -1291,7 +1291,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>29</v>
@@ -1341,7 +1341,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>29</v>
@@ -1350,7 +1350,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-74</v>
+        <v>-75</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>29</v>
@@ -1400,16 +1400,16 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-67</v>
+        <v>-68</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>29</v>
@@ -1420,22 +1420,22 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="C14" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="G14" s="7">
         <v>46190</v>
@@ -1459,19 +1459,19 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S14" s="6" t="s">
         <v>24</v>
@@ -1482,10 +1482,10 @@
         <v>42</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>24</v>
@@ -1518,19 +1518,19 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>24</v>
@@ -1577,19 +1577,19 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S16" s="6" t="s">
         <v>24</v>
@@ -1600,10 +1600,10 @@
         <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>24</v>
@@ -1636,16 +1636,16 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>29</v>
@@ -1656,22 +1656,22 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="G18" s="7">
         <v>46190</v>
@@ -1695,19 +1695,19 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S18" s="6" t="s">
         <v>24</v>
@@ -1754,19 +1754,19 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S19" s="6" t="s">
         <v>24</v>
@@ -1777,10 +1777,10 @@
         <v>47</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>24</v>
@@ -1813,19 +1813,19 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S20" s="6" t="s">
         <v>24</v>
@@ -1872,19 +1872,19 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S21" s="6" t="s">
         <v>24</v>
@@ -1931,19 +1931,19 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S22" s="6" t="s">
         <v>24</v>
@@ -1990,19 +1990,19 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S23" s="6" t="s">
         <v>24</v>
@@ -2049,19 +2049,19 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S24" s="6" t="s">
         <v>24</v>
@@ -2108,19 +2108,19 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>24</v>
@@ -2167,19 +2167,19 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>24</v>
@@ -2187,22 +2187,22 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="C27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E27" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="G27" s="7">
         <v>46190</v>
@@ -2226,16 +2226,16 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>61</v>
       </c>
       <c r="Q27" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>24</v>
@@ -2285,19 +2285,19 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S28" s="6" t="s">
         <v>24</v>
@@ -2344,19 +2344,19 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S29" s="6" t="s">
         <v>24</v>
@@ -2367,7 +2367,7 @@
         <v>65</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>24</v>
@@ -2382,7 +2382,7 @@
         <v>26</v>
       </c>
       <c r="G30" s="7">
-        <v>46225</v>
+        <v>46203</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>27</v>
@@ -2403,19 +2403,19 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S30" s="6" t="s">
         <v>24</v>
@@ -2423,11 +2423,11 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="C31" s="6" t="s">
         <v>24</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>26</v>
       </c>
       <c r="G31" s="7">
-        <v>46203</v>
+        <v>46225</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>27</v>
@@ -2462,19 +2462,19 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S31" s="6" t="s">
         <v>24</v>
@@ -2485,10 +2485,10 @@
         <v>68</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>24</v>
@@ -2500,10 +2500,10 @@
         <v>26</v>
       </c>
       <c r="G32" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I32" s="7">
         <v>46223</v>
@@ -2521,19 +2521,19 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S32" s="6" t="s">
         <v>24</v>
@@ -2541,13 +2541,13 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>24</v>
@@ -2559,10 +2559,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I33" s="7">
         <v>46223</v>
@@ -2580,19 +2580,19 @@
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S33" s="6" t="s">
         <v>24</v>
@@ -2621,7 +2621,7 @@
         <v>46225</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I34" s="7">
         <v>46223</v>
@@ -2639,19 +2639,19 @@
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S34" s="6" t="s">
         <v>24</v>
@@ -2698,19 +2698,19 @@
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S35" s="6" t="s">
         <v>24</v>
@@ -2757,19 +2757,19 @@
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>24</v>
@@ -2816,19 +2816,19 @@
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S37" s="6" t="s">
         <v>24</v>
@@ -2875,19 +2875,19 @@
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S38" s="6" t="s">
         <v>24</v>
@@ -2934,19 +2934,19 @@
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S39" s="6" t="s">
         <v>24</v>
@@ -2993,19 +2993,19 @@
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S40" s="6" t="s">
         <v>24</v>
@@ -3016,7 +3016,7 @@
         <v>85</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>24</v>
@@ -3052,19 +3052,19 @@
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S41" s="6" t="s">
         <v>24</v>
@@ -3093,7 +3093,7 @@
         <v>24</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I42" s="7">
         <v>46223</v>
@@ -3111,19 +3111,19 @@
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S42" s="6" t="s">
         <v>24</v>
@@ -3134,25 +3134,25 @@
         <v>88</v>
       </c>
       <c r="B43" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H43" s="6" t="s">
         <v>70</v>
-      </c>
-      <c r="C43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H43" s="6" t="s">
-        <v>71</v>
       </c>
       <c r="I43" s="7">
         <v>46216</v>
@@ -3170,19 +3170,19 @@
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S43" s="6" t="s">
         <v>24</v>
@@ -3229,19 +3229,19 @@
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S44" s="6" t="s">
         <v>24</v>
@@ -3270,7 +3270,7 @@
         <v>24</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I45" s="7">
         <v>46188</v>
@@ -3288,16 +3288,16 @@
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-46</v>
+        <v>-47</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>29</v>
@@ -3308,22 +3308,22 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="C46" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="C46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="G46" s="7">
         <v>46190</v>
@@ -3347,16 +3347,16 @@
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>61</v>
       </c>
       <c r="Q46" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>24</v>
@@ -3406,19 +3406,19 @@
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S47" s="6" t="s">
         <v>24</v>
@@ -3465,19 +3465,19 @@
         <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S48" s="6" t="s">
         <v>24</v>
@@ -3524,19 +3524,19 @@
         <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S49" s="6" t="s">
         <v>24</v>
@@ -3565,7 +3565,7 @@
         <v>46232</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I50" s="7">
         <v>46230</v>
@@ -3583,19 +3583,19 @@
         <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S50" s="6" t="s">
         <v>24</v>
@@ -3642,19 +3642,19 @@
         <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S51" s="6" t="s">
         <v>24</v>
@@ -3665,7 +3665,7 @@
         <v>100</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>24</v>
@@ -3680,7 +3680,7 @@
         <v>26</v>
       </c>
       <c r="G52" s="7">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>27</v>
@@ -3701,19 +3701,19 @@
         <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S52" s="6" t="s">
         <v>24</v>
@@ -3724,7 +3724,7 @@
         <v>101</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>24</v>
@@ -3739,7 +3739,7 @@
         <v>26</v>
       </c>
       <c r="G53" s="7">
-        <v>46232</v>
+        <v>46212</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>27</v>
@@ -3760,19 +3760,19 @@
         <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S53" s="6" t="s">
         <v>24</v>
@@ -3783,7 +3783,7 @@
         <v>102</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>24</v>
@@ -3798,7 +3798,7 @@
         <v>26</v>
       </c>
       <c r="G54" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>27</v>
@@ -3819,19 +3819,19 @@
         <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S54" s="6" t="s">
         <v>24</v>
@@ -3857,7 +3857,7 @@
         <v>26</v>
       </c>
       <c r="G55" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>27</v>
@@ -3878,19 +3878,19 @@
         <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S55" s="6" t="s">
         <v>24</v>
@@ -3901,7 +3901,7 @@
         <v>105</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>24</v>
@@ -3919,7 +3919,7 @@
         <v>46188</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I56" s="7">
         <v>46230</v>
@@ -3937,19 +3937,19 @@
         <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S56" s="6" t="s">
         <v>24</v>
@@ -3996,19 +3996,19 @@
         <v>28</v>
       </c>
       <c r="N57" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S57" s="6" t="s">
         <v>24</v>
@@ -4034,7 +4034,7 @@
         <v>26</v>
       </c>
       <c r="G58" s="7">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>27</v>
@@ -4055,19 +4055,19 @@
         <v>28</v>
       </c>
       <c r="N58" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q58" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S58" s="6" t="s">
         <v>24</v>
@@ -4078,7 +4078,7 @@
         <v>109</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>110</v>
+        <v>54</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>24</v>
@@ -4093,10 +4093,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I59" s="7">
         <v>46230</v>
@@ -4114,19 +4114,19 @@
         <v>28</v>
       </c>
       <c r="N59" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q59" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S59" s="6" t="s">
         <v>24</v>
@@ -4134,10 +4134,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
@@ -4152,10 +4152,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I60" s="7">
         <v>46230</v>
@@ -4173,19 +4173,19 @@
         <v>28</v>
       </c>
       <c r="N60" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q60" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S60" s="6" t="s">
         <v>24</v>
@@ -4193,11 +4193,11 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="B61" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="B61" s="6" t="s">
-        <v>54</v>
-      </c>
       <c r="C61" s="6" t="s">
         <v>24</v>
       </c>
@@ -4211,10 +4211,10 @@
         <v>26</v>
       </c>
       <c r="G61" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I61" s="7">
         <v>46230</v>
@@ -4232,19 +4232,19 @@
         <v>28</v>
       </c>
       <c r="N61" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q61" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S61" s="6" t="s">
         <v>24</v>
@@ -4255,7 +4255,7 @@
         <v>113</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4270,10 +4270,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I62" s="7">
         <v>46230</v>
@@ -4291,19 +4291,19 @@
         <v>28</v>
       </c>
       <c r="N62" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q62" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S62" s="6" t="s">
         <v>24</v>
@@ -4314,7 +4314,7 @@
         <v>114</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>24</v>
@@ -4350,19 +4350,19 @@
         <v>28</v>
       </c>
       <c r="N63" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P63" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q63" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S63" s="6" t="s">
         <v>24</v>
@@ -4409,19 +4409,19 @@
         <v>28</v>
       </c>
       <c r="N64" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q64" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S64" s="6" t="s">
         <v>24</v>
@@ -4468,19 +4468,19 @@
         <v>28</v>
       </c>
       <c r="N65" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P65" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q65" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S65" s="6" t="s">
         <v>24</v>
@@ -4527,19 +4527,19 @@
         <v>28</v>
       </c>
       <c r="N66" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P66" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q66" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S66" s="6" t="s">
         <v>24</v>
@@ -4586,19 +4586,19 @@
         <v>28</v>
       </c>
       <c r="N67" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P67" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q67" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S67" s="6" t="s">
         <v>24</v>
@@ -4645,19 +4645,19 @@
         <v>28</v>
       </c>
       <c r="N68" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P68" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q68" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S68" s="6" t="s">
         <v>24</v>
@@ -4704,19 +4704,19 @@
         <v>28</v>
       </c>
       <c r="N69" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P69" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q69" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S69" s="6" t="s">
         <v>24</v>
@@ -4763,19 +4763,19 @@
         <v>28</v>
       </c>
       <c r="N70" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="P70" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q70" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="S70" s="6" t="s">
         <v>24</v>
@@ -4804,7 +4804,7 @@
         <v>24</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I71" s="7">
         <v>46188</v>
@@ -4822,7 +4822,7 @@
         <v>61</v>
       </c>
       <c r="N71" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
@@ -4831,7 +4831,7 @@
         <v>28</v>
       </c>
       <c r="Q71" s="9">
-        <v>-46</v>
+        <v>-47</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>29</v>
@@ -4881,7 +4881,7 @@
         <v>61</v>
       </c>
       <c r="N72" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
@@ -4890,7 +4890,7 @@
         <v>61</v>
       </c>
       <c r="Q72" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4940,7 +4940,7 @@
         <v>61</v>
       </c>
       <c r="N73" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
@@ -4949,7 +4949,7 @@
         <v>61</v>
       </c>
       <c r="Q73" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4981,7 +4981,7 @@
         <v>46232</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I74" s="7">
         <v>46237</v>
@@ -4999,7 +4999,7 @@
         <v>61</v>
       </c>
       <c r="N74" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
@@ -5008,7 +5008,7 @@
         <v>61</v>
       </c>
       <c r="Q74" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -5022,7 +5022,7 @@
         <v>128</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>24</v>
@@ -5037,7 +5037,7 @@
         <v>26</v>
       </c>
       <c r="G75" s="7">
-        <v>46225</v>
+        <v>46231</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>27</v>
@@ -5058,7 +5058,7 @@
         <v>61</v>
       </c>
       <c r="N75" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
@@ -5067,7 +5067,7 @@
         <v>61</v>
       </c>
       <c r="Q75" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -5117,7 +5117,7 @@
         <v>61</v>
       </c>
       <c r="N76" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
@@ -5126,7 +5126,7 @@
         <v>61</v>
       </c>
       <c r="Q76" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -5140,7 +5140,7 @@
         <v>130</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>24</v>
@@ -5155,7 +5155,7 @@
         <v>26</v>
       </c>
       <c r="G77" s="7">
-        <v>46231</v>
+        <v>46225</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>27</v>
@@ -5176,7 +5176,7 @@
         <v>61</v>
       </c>
       <c r="N77" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
@@ -5185,7 +5185,7 @@
         <v>61</v>
       </c>
       <c r="Q77" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5235,7 +5235,7 @@
         <v>61</v>
       </c>
       <c r="N78" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
@@ -5244,7 +5244,7 @@
         <v>61</v>
       </c>
       <c r="Q78" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5294,7 +5294,7 @@
         <v>61</v>
       </c>
       <c r="N79" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
@@ -5303,7 +5303,7 @@
         <v>61</v>
       </c>
       <c r="Q79" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5317,7 +5317,7 @@
         <v>135</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
@@ -5353,7 +5353,7 @@
         <v>61</v>
       </c>
       <c r="N80" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
@@ -5362,7 +5362,7 @@
         <v>61</v>
       </c>
       <c r="Q80" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5373,10 +5373,10 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B81" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5412,7 +5412,7 @@
         <v>61</v>
       </c>
       <c r="N81" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
@@ -5421,7 +5421,7 @@
         <v>61</v>
       </c>
       <c r="Q81" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5435,7 +5435,7 @@
         <v>138</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>24</v>
@@ -5450,10 +5450,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I82" s="7">
         <v>46237</v>
@@ -5471,7 +5471,7 @@
         <v>61</v>
       </c>
       <c r="N82" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
@@ -5480,7 +5480,7 @@
         <v>61</v>
       </c>
       <c r="Q82" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5491,13 +5491,13 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>24</v>
@@ -5509,10 +5509,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I83" s="7">
         <v>46237</v>
@@ -5530,7 +5530,7 @@
         <v>61</v>
       </c>
       <c r="N83" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
@@ -5539,7 +5539,7 @@
         <v>61</v>
       </c>
       <c r="Q83" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>24</v>
@@ -5589,7 +5589,7 @@
         <v>61</v>
       </c>
       <c r="N84" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
@@ -5598,7 +5598,7 @@
         <v>61</v>
       </c>
       <c r="Q84" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5609,13 +5609,13 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>142</v>
+        <v>52</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>24</v>
@@ -5627,7 +5627,7 @@
         <v>26</v>
       </c>
       <c r="G85" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>27</v>
@@ -5648,7 +5648,7 @@
         <v>61</v>
       </c>
       <c r="N85" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
@@ -5657,7 +5657,7 @@
         <v>61</v>
       </c>
       <c r="Q85" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5671,7 +5671,7 @@
         <v>143</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>24</v>
@@ -5707,7 +5707,7 @@
         <v>61</v>
       </c>
       <c r="N86" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
@@ -5716,7 +5716,7 @@
         <v>61</v>
       </c>
       <c r="Q86" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5766,7 +5766,7 @@
         <v>61</v>
       </c>
       <c r="N87" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
@@ -5775,7 +5775,7 @@
         <v>61</v>
       </c>
       <c r="Q87" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5789,7 +5789,7 @@
         <v>146</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>24</v>
@@ -5804,10 +5804,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I88" s="7">
         <v>46237</v>
@@ -5825,7 +5825,7 @@
         <v>61</v>
       </c>
       <c r="N88" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
@@ -5834,7 +5834,7 @@
         <v>61</v>
       </c>
       <c r="Q88" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5848,7 +5848,7 @@
         <v>147</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>24</v>
@@ -5866,7 +5866,7 @@
         <v>46225</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I89" s="7">
         <v>46237</v>
@@ -5884,7 +5884,7 @@
         <v>61</v>
       </c>
       <c r="N89" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
@@ -5893,7 +5893,7 @@
         <v>61</v>
       </c>
       <c r="Q89" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5925,7 +5925,7 @@
         <v>46212</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I90" s="7">
         <v>46237</v>
@@ -5943,7 +5943,7 @@
         <v>61</v>
       </c>
       <c r="N90" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
@@ -5952,7 +5952,7 @@
         <v>61</v>
       </c>
       <c r="Q90" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -6002,7 +6002,7 @@
         <v>61</v>
       </c>
       <c r="N91" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
@@ -6011,7 +6011,7 @@
         <v>61</v>
       </c>
       <c r="Q91" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -6061,7 +6061,7 @@
         <v>61</v>
       </c>
       <c r="N92" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
@@ -6070,7 +6070,7 @@
         <v>61</v>
       </c>
       <c r="Q92" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -6084,7 +6084,7 @@
         <v>152</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>73</v>
+        <v>94</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>24</v>
@@ -6099,10 +6099,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I93" s="7">
         <v>46237</v>
@@ -6120,7 +6120,7 @@
         <v>61</v>
       </c>
       <c r="N93" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
@@ -6129,7 +6129,7 @@
         <v>61</v>
       </c>
       <c r="Q93" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -6179,7 +6179,7 @@
         <v>61</v>
       </c>
       <c r="N94" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
@@ -6188,7 +6188,7 @@
         <v>61</v>
       </c>
       <c r="Q94" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6202,13 +6202,13 @@
         <v>154</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>25</v>
@@ -6217,10 +6217,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I95" s="7">
         <v>46237</v>
@@ -6238,7 +6238,7 @@
         <v>61</v>
       </c>
       <c r="N95" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
@@ -6247,7 +6247,7 @@
         <v>61</v>
       </c>
       <c r="Q95" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6261,13 +6261,13 @@
         <v>155</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>25</v>
@@ -6276,10 +6276,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I96" s="7">
         <v>46237</v>
@@ -6297,7 +6297,7 @@
         <v>61</v>
       </c>
       <c r="N96" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
@@ -6306,7 +6306,7 @@
         <v>61</v>
       </c>
       <c r="Q96" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6356,7 +6356,7 @@
         <v>61</v>
       </c>
       <c r="N97" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
@@ -6365,7 +6365,7 @@
         <v>61</v>
       </c>
       <c r="Q97" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6415,7 +6415,7 @@
         <v>61</v>
       </c>
       <c r="N98" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
@@ -6424,7 +6424,7 @@
         <v>61</v>
       </c>
       <c r="Q98" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6474,7 +6474,7 @@
         <v>61</v>
       </c>
       <c r="N99" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
@@ -6483,7 +6483,7 @@
         <v>61</v>
       </c>
       <c r="Q99" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6533,7 +6533,7 @@
         <v>61</v>
       </c>
       <c r="N100" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
@@ -6542,7 +6542,7 @@
         <v>61</v>
       </c>
       <c r="Q100" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6592,7 +6592,7 @@
         <v>61</v>
       </c>
       <c r="N101" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
@@ -6601,7 +6601,7 @@
         <v>61</v>
       </c>
       <c r="Q101" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6633,7 +6633,7 @@
         <v>46232</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I102" s="7">
         <v>46244</v>
@@ -6651,7 +6651,7 @@
         <v>61</v>
       </c>
       <c r="N102" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
@@ -6660,7 +6660,7 @@
         <v>61</v>
       </c>
       <c r="Q102" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6674,13 +6674,13 @@
         <v>163</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>50</v>
+        <v>134</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>25</v>
@@ -6710,7 +6710,7 @@
         <v>61</v>
       </c>
       <c r="N103" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
@@ -6719,7 +6719,7 @@
         <v>61</v>
       </c>
       <c r="Q103" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6769,7 +6769,7 @@
         <v>61</v>
       </c>
       <c r="N104" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
@@ -6778,7 +6778,7 @@
         <v>61</v>
       </c>
       <c r="Q104" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6828,7 +6828,7 @@
         <v>61</v>
       </c>
       <c r="N105" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
@@ -6837,7 +6837,7 @@
         <v>61</v>
       </c>
       <c r="Q105" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6851,7 +6851,7 @@
         <v>166</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>24</v>
@@ -6866,7 +6866,7 @@
         <v>26</v>
       </c>
       <c r="G106" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>27</v>
@@ -6887,7 +6887,7 @@
         <v>61</v>
       </c>
       <c r="N106" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
@@ -6896,7 +6896,7 @@
         <v>61</v>
       </c>
       <c r="Q106" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>
@@ -6910,7 +6910,7 @@
         <v>167</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>24</v>
@@ -6946,7 +6946,7 @@
         <v>61</v>
       </c>
       <c r="N107" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>24</v>
@@ -6955,7 +6955,7 @@
         <v>61</v>
       </c>
       <c r="Q107" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>24</v>
@@ -6969,13 +6969,13 @@
         <v>168</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>25</v>
@@ -6984,7 +6984,7 @@
         <v>26</v>
       </c>
       <c r="G108" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>27</v>
@@ -7005,7 +7005,7 @@
         <v>61</v>
       </c>
       <c r="N108" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>24</v>
@@ -7014,7 +7014,7 @@
         <v>61</v>
       </c>
       <c r="Q108" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>24</v>
@@ -7028,10 +7028,10 @@
         <v>169</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>24</v>
@@ -7043,7 +7043,7 @@
         <v>26</v>
       </c>
       <c r="G109" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H109" s="6" t="s">
         <v>27</v>
@@ -7064,7 +7064,7 @@
         <v>61</v>
       </c>
       <c r="N109" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>24</v>
@@ -7073,7 +7073,7 @@
         <v>61</v>
       </c>
       <c r="Q109" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R109" s="6" t="s">
         <v>24</v>
@@ -7102,7 +7102,7 @@
         <v>26</v>
       </c>
       <c r="G110" s="7">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="H110" s="6" t="s">
         <v>27</v>
@@ -7123,7 +7123,7 @@
         <v>61</v>
       </c>
       <c r="N110" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>24</v>
@@ -7132,7 +7132,7 @@
         <v>61</v>
       </c>
       <c r="Q110" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R110" s="6" t="s">
         <v>24</v>
@@ -7146,10 +7146,10 @@
         <v>171</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>24</v>
@@ -7161,7 +7161,7 @@
         <v>26</v>
       </c>
       <c r="G111" s="7">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="H111" s="6" t="s">
         <v>27</v>
@@ -7182,7 +7182,7 @@
         <v>61</v>
       </c>
       <c r="N111" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>24</v>
@@ -7191,7 +7191,7 @@
         <v>61</v>
       </c>
       <c r="Q111" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R111" s="6" t="s">
         <v>24</v>
@@ -7205,7 +7205,7 @@
         <v>172</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>24</v>
@@ -7223,7 +7223,7 @@
         <v>46188</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I112" s="7">
         <v>46244</v>
@@ -7241,7 +7241,7 @@
         <v>61</v>
       </c>
       <c r="N112" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>24</v>
@@ -7250,7 +7250,7 @@
         <v>61</v>
       </c>
       <c r="Q112" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R112" s="6" t="s">
         <v>24</v>
@@ -7264,7 +7264,7 @@
         <v>173</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>24</v>
@@ -7300,7 +7300,7 @@
         <v>61</v>
       </c>
       <c r="N113" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>24</v>
@@ -7309,7 +7309,7 @@
         <v>61</v>
       </c>
       <c r="Q113" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R113" s="6" t="s">
         <v>24</v>
@@ -7359,7 +7359,7 @@
         <v>61</v>
       </c>
       <c r="N114" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>24</v>
@@ -7368,7 +7368,7 @@
         <v>61</v>
       </c>
       <c r="Q114" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R114" s="6" t="s">
         <v>24</v>
@@ -7382,7 +7382,7 @@
         <v>175</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>24</v>
@@ -7397,10 +7397,10 @@
         <v>26</v>
       </c>
       <c r="G115" s="7">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="H115" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I115" s="7">
         <v>46244</v>
@@ -7418,7 +7418,7 @@
         <v>61</v>
       </c>
       <c r="N115" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O115" s="6" t="s">
         <v>24</v>
@@ -7427,7 +7427,7 @@
         <v>61</v>
       </c>
       <c r="Q115" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R115" s="6" t="s">
         <v>24</v>
@@ -7441,7 +7441,7 @@
         <v>176</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>24</v>
@@ -7477,7 +7477,7 @@
         <v>61</v>
       </c>
       <c r="N116" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>24</v>
@@ -7486,7 +7486,7 @@
         <v>61</v>
       </c>
       <c r="Q116" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R116" s="6" t="s">
         <v>24</v>
@@ -7500,7 +7500,7 @@
         <v>177</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>24</v>
@@ -7515,10 +7515,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I117" s="7">
         <v>46244</v>
@@ -7536,7 +7536,7 @@
         <v>61</v>
       </c>
       <c r="N117" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O117" s="6" t="s">
         <v>24</v>
@@ -7545,7 +7545,7 @@
         <v>61</v>
       </c>
       <c r="Q117" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R117" s="6" t="s">
         <v>24</v>
@@ -7595,7 +7595,7 @@
         <v>61</v>
       </c>
       <c r="N118" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>24</v>
@@ -7604,7 +7604,7 @@
         <v>61</v>
       </c>
       <c r="Q118" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R118" s="6" t="s">
         <v>24</v>
@@ -7618,7 +7618,7 @@
         <v>179</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>24</v>
@@ -7633,10 +7633,10 @@
         <v>26</v>
       </c>
       <c r="G119" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I119" s="7">
         <v>46244</v>
@@ -7654,7 +7654,7 @@
         <v>61</v>
       </c>
       <c r="N119" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O119" s="6" t="s">
         <v>24</v>
@@ -7663,7 +7663,7 @@
         <v>61</v>
       </c>
       <c r="Q119" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R119" s="6" t="s">
         <v>24</v>
@@ -7677,7 +7677,7 @@
         <v>180</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>60</v>
+        <v>112</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>24</v>
@@ -7692,10 +7692,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I120" s="7">
         <v>46244</v>
@@ -7713,7 +7713,7 @@
         <v>61</v>
       </c>
       <c r="N120" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>24</v>
@@ -7722,7 +7722,7 @@
         <v>61</v>
       </c>
       <c r="Q120" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R120" s="6" t="s">
         <v>24</v>
@@ -7736,7 +7736,7 @@
         <v>181</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>54</v>
+        <v>149</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>24</v>
@@ -7751,10 +7751,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="7">
-        <v>46232</v>
+        <v>46212</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I121" s="7">
         <v>46244</v>
@@ -7772,7 +7772,7 @@
         <v>61</v>
       </c>
       <c r="N121" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O121" s="6" t="s">
         <v>24</v>
@@ -7781,7 +7781,7 @@
         <v>61</v>
       </c>
       <c r="Q121" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R121" s="6" t="s">
         <v>24</v>
@@ -7795,13 +7795,13 @@
         <v>182</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>25</v>
@@ -7810,10 +7810,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I122" s="7">
         <v>46244</v>
@@ -7831,7 +7831,7 @@
         <v>61</v>
       </c>
       <c r="N122" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>24</v>
@@ -7840,7 +7840,7 @@
         <v>61</v>
       </c>
       <c r="Q122" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R122" s="6" t="s">
         <v>24</v>
@@ -7854,13 +7854,13 @@
         <v>183</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E123" s="6" t="s">
         <v>25</v>
@@ -7869,10 +7869,10 @@
         <v>26</v>
       </c>
       <c r="G123" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I123" s="7">
         <v>46244</v>
@@ -7890,7 +7890,7 @@
         <v>61</v>
       </c>
       <c r="N123" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O123" s="6" t="s">
         <v>24</v>
@@ -7899,7 +7899,7 @@
         <v>61</v>
       </c>
       <c r="Q123" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R123" s="6" t="s">
         <v>24</v>
@@ -7949,7 +7949,7 @@
         <v>61</v>
       </c>
       <c r="N124" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>24</v>
@@ -7958,7 +7958,7 @@
         <v>61</v>
       </c>
       <c r="Q124" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R124" s="6" t="s">
         <v>24</v>
@@ -8008,7 +8008,7 @@
         <v>61</v>
       </c>
       <c r="N125" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O125" s="6" t="s">
         <v>24</v>
@@ -8017,7 +8017,7 @@
         <v>61</v>
       </c>
       <c r="Q125" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R125" s="6" t="s">
         <v>24</v>
@@ -8067,7 +8067,7 @@
         <v>61</v>
       </c>
       <c r="N126" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>24</v>
@@ -8076,7 +8076,7 @@
         <v>61</v>
       </c>
       <c r="Q126" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R126" s="6" t="s">
         <v>24</v>
@@ -8126,7 +8126,7 @@
         <v>61</v>
       </c>
       <c r="N127" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O127" s="6" t="s">
         <v>24</v>
@@ -8135,7 +8135,7 @@
         <v>61</v>
       </c>
       <c r="Q127" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R127" s="6" t="s">
         <v>24</v>
@@ -8185,7 +8185,7 @@
         <v>61</v>
       </c>
       <c r="N128" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>24</v>
@@ -8194,7 +8194,7 @@
         <v>61</v>
       </c>
       <c r="Q128" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R128" s="6" t="s">
         <v>24</v>
@@ -8226,7 +8226,7 @@
         <v>46232</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I129" s="7">
         <v>46251</v>
@@ -8244,7 +8244,7 @@
         <v>61</v>
       </c>
       <c r="N129" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O129" s="6" t="s">
         <v>24</v>
@@ -8253,7 +8253,7 @@
         <v>61</v>
       </c>
       <c r="Q129" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R129" s="6" t="s">
         <v>24</v>
@@ -8267,13 +8267,13 @@
         <v>190</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>25</v>
@@ -8282,7 +8282,7 @@
         <v>26</v>
       </c>
       <c r="G130" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H130" s="6" t="s">
         <v>27</v>
@@ -8303,7 +8303,7 @@
         <v>61</v>
       </c>
       <c r="N130" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>24</v>
@@ -8312,7 +8312,7 @@
         <v>61</v>
       </c>
       <c r="Q130" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R130" s="6" t="s">
         <v>24</v>
@@ -8326,7 +8326,7 @@
         <v>191</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>24</v>
@@ -8362,7 +8362,7 @@
         <v>61</v>
       </c>
       <c r="N131" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O131" s="6" t="s">
         <v>24</v>
@@ -8371,7 +8371,7 @@
         <v>61</v>
       </c>
       <c r="Q131" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R131" s="6" t="s">
         <v>24</v>
@@ -8385,13 +8385,13 @@
         <v>192</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>134</v>
+        <v>67</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>25</v>
@@ -8400,7 +8400,7 @@
         <v>26</v>
       </c>
       <c r="G132" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H132" s="6" t="s">
         <v>27</v>
@@ -8421,7 +8421,7 @@
         <v>61</v>
       </c>
       <c r="N132" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>24</v>
@@ -8430,7 +8430,7 @@
         <v>61</v>
       </c>
       <c r="Q132" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R132" s="6" t="s">
         <v>24</v>
@@ -8444,7 +8444,7 @@
         <v>193</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>24</v>
@@ -8459,7 +8459,7 @@
         <v>26</v>
       </c>
       <c r="G133" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H133" s="6" t="s">
         <v>27</v>
@@ -8480,7 +8480,7 @@
         <v>61</v>
       </c>
       <c r="N133" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O133" s="6" t="s">
         <v>24</v>
@@ -8489,7 +8489,7 @@
         <v>61</v>
       </c>
       <c r="Q133" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R133" s="6" t="s">
         <v>24</v>
@@ -8503,7 +8503,7 @@
         <v>194</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>24</v>
@@ -8518,7 +8518,7 @@
         <v>26</v>
       </c>
       <c r="G134" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H134" s="6" t="s">
         <v>27</v>
@@ -8539,7 +8539,7 @@
         <v>61</v>
       </c>
       <c r="N134" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>24</v>
@@ -8548,7 +8548,7 @@
         <v>61</v>
       </c>
       <c r="Q134" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R134" s="6" t="s">
         <v>24</v>
@@ -8562,7 +8562,7 @@
         <v>195</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>24</v>
@@ -8598,7 +8598,7 @@
         <v>61</v>
       </c>
       <c r="N135" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O135" s="6" t="s">
         <v>24</v>
@@ -8607,7 +8607,7 @@
         <v>61</v>
       </c>
       <c r="Q135" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R135" s="6" t="s">
         <v>24</v>
@@ -8621,7 +8621,7 @@
         <v>196</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>24</v>
@@ -8636,7 +8636,7 @@
         <v>26</v>
       </c>
       <c r="G136" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H136" s="6" t="s">
         <v>27</v>
@@ -8657,7 +8657,7 @@
         <v>61</v>
       </c>
       <c r="N136" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>24</v>
@@ -8666,7 +8666,7 @@
         <v>61</v>
       </c>
       <c r="Q136" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R136" s="6" t="s">
         <v>24</v>
@@ -8680,10 +8680,10 @@
         <v>197</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>24</v>
@@ -8695,7 +8695,7 @@
         <v>26</v>
       </c>
       <c r="G137" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H137" s="6" t="s">
         <v>27</v>
@@ -8716,7 +8716,7 @@
         <v>61</v>
       </c>
       <c r="N137" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O137" s="6" t="s">
         <v>24</v>
@@ -8725,7 +8725,7 @@
         <v>61</v>
       </c>
       <c r="Q137" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R137" s="6" t="s">
         <v>24</v>
@@ -8739,10 +8739,10 @@
         <v>198</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>24</v>
@@ -8754,10 +8754,10 @@
         <v>26</v>
       </c>
       <c r="G138" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I138" s="7">
         <v>46251</v>
@@ -8775,7 +8775,7 @@
         <v>61</v>
       </c>
       <c r="N138" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>24</v>
@@ -8784,7 +8784,7 @@
         <v>61</v>
       </c>
       <c r="Q138" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R138" s="6" t="s">
         <v>24</v>
@@ -8813,7 +8813,7 @@
         <v>26</v>
       </c>
       <c r="G139" s="7">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="H139" s="6" t="s">
         <v>27</v>
@@ -8834,7 +8834,7 @@
         <v>61</v>
       </c>
       <c r="N139" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O139" s="6" t="s">
         <v>24</v>
@@ -8843,7 +8843,7 @@
         <v>61</v>
       </c>
       <c r="Q139" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R139" s="6" t="s">
         <v>24</v>
@@ -8857,7 +8857,7 @@
         <v>200</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>142</v>
+        <v>69</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>24</v>
@@ -8872,10 +8872,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I140" s="7">
         <v>46251</v>
@@ -8893,7 +8893,7 @@
         <v>61</v>
       </c>
       <c r="N140" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>24</v>
@@ -8902,7 +8902,7 @@
         <v>61</v>
       </c>
       <c r="Q140" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R140" s="6" t="s">
         <v>24</v>
@@ -8952,7 +8952,7 @@
         <v>61</v>
       </c>
       <c r="N141" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O141" s="6" t="s">
         <v>24</v>
@@ -8961,7 +8961,7 @@
         <v>61</v>
       </c>
       <c r="Q141" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R141" s="6" t="s">
         <v>24</v>
@@ -8975,7 +8975,7 @@
         <v>202</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>60</v>
+        <v>149</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>24</v>
@@ -8990,10 +8990,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="7">
-        <v>46232</v>
+        <v>46212</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I142" s="7">
         <v>46251</v>
@@ -9011,7 +9011,7 @@
         <v>61</v>
       </c>
       <c r="N142" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>24</v>
@@ -9020,7 +9020,7 @@
         <v>61</v>
       </c>
       <c r="Q142" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R142" s="6" t="s">
         <v>24</v>
@@ -9034,7 +9034,7 @@
         <v>203</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>24</v>
@@ -9049,10 +9049,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="7">
-        <v>46212</v>
+        <v>46232</v>
       </c>
       <c r="H143" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I143" s="7">
         <v>46251</v>
@@ -9070,7 +9070,7 @@
         <v>61</v>
       </c>
       <c r="N143" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O143" s="6" t="s">
         <v>24</v>
@@ -9079,7 +9079,7 @@
         <v>61</v>
       </c>
       <c r="Q143" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R143" s="6" t="s">
         <v>24</v>
@@ -9093,7 +9093,7 @@
         <v>204</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>24</v>
@@ -9108,10 +9108,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I144" s="7">
         <v>46251</v>
@@ -9129,7 +9129,7 @@
         <v>61</v>
       </c>
       <c r="N144" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>24</v>
@@ -9138,7 +9138,7 @@
         <v>61</v>
       </c>
       <c r="Q144" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R144" s="6" t="s">
         <v>24</v>
@@ -9188,7 +9188,7 @@
         <v>61</v>
       </c>
       <c r="N145" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O145" s="6" t="s">
         <v>24</v>
@@ -9197,7 +9197,7 @@
         <v>61</v>
       </c>
       <c r="Q145" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R145" s="6" t="s">
         <v>24</v>
@@ -9247,7 +9247,7 @@
         <v>61</v>
       </c>
       <c r="N146" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O146" s="6" t="s">
         <v>24</v>
@@ -9256,7 +9256,7 @@
         <v>61</v>
       </c>
       <c r="Q146" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R146" s="6" t="s">
         <v>24</v>
@@ -9270,7 +9270,7 @@
         <v>207</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>24</v>
@@ -9288,7 +9288,7 @@
         <v>46225</v>
       </c>
       <c r="H147" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I147" s="7">
         <v>46251</v>
@@ -9306,7 +9306,7 @@
         <v>61</v>
       </c>
       <c r="N147" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O147" s="6" t="s">
         <v>24</v>
@@ -9315,7 +9315,7 @@
         <v>61</v>
       </c>
       <c r="Q147" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R147" s="6" t="s">
         <v>24</v>
@@ -9329,7 +9329,7 @@
         <v>208</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>24</v>
@@ -9344,10 +9344,10 @@
         <v>26</v>
       </c>
       <c r="G148" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I148" s="7">
         <v>46251</v>
@@ -9365,7 +9365,7 @@
         <v>61</v>
       </c>
       <c r="N148" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>24</v>
@@ -9374,7 +9374,7 @@
         <v>61</v>
       </c>
       <c r="Q148" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R148" s="6" t="s">
         <v>24</v>
@@ -9388,13 +9388,13 @@
         <v>209</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="E149" s="6" t="s">
         <v>25</v>
@@ -9403,10 +9403,10 @@
         <v>26</v>
       </c>
       <c r="G149" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H149" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I149" s="7">
         <v>46251</v>
@@ -9424,7 +9424,7 @@
         <v>61</v>
       </c>
       <c r="N149" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>24</v>
@@ -9433,7 +9433,7 @@
         <v>61</v>
       </c>
       <c r="Q149" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R149" s="6" t="s">
         <v>24</v>
@@ -9447,13 +9447,13 @@
         <v>210</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>25</v>
@@ -9462,10 +9462,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I150" s="7">
         <v>46251</v>
@@ -9483,7 +9483,7 @@
         <v>61</v>
       </c>
       <c r="N150" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>24</v>
@@ -9492,7 +9492,7 @@
         <v>61</v>
       </c>
       <c r="Q150" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R150" s="6" t="s">
         <v>24</v>
@@ -9542,7 +9542,7 @@
         <v>61</v>
       </c>
       <c r="N151" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O151" s="6" t="s">
         <v>24</v>
@@ -9551,7 +9551,7 @@
         <v>61</v>
       </c>
       <c r="Q151" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R151" s="6" t="s">
         <v>24</v>
@@ -9601,7 +9601,7 @@
         <v>61</v>
       </c>
       <c r="N152" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>24</v>
@@ -9610,7 +9610,7 @@
         <v>61</v>
       </c>
       <c r="Q152" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R152" s="6" t="s">
         <v>24</v>
@@ -9660,7 +9660,7 @@
         <v>61</v>
       </c>
       <c r="N153" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O153" s="6" t="s">
         <v>24</v>
@@ -9669,7 +9669,7 @@
         <v>61</v>
       </c>
       <c r="Q153" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R153" s="6" t="s">
         <v>24</v>
@@ -9683,7 +9683,7 @@
         <v>214</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>24</v>
@@ -9698,10 +9698,10 @@
         <v>26</v>
       </c>
       <c r="G154" s="7">
-        <v>46210</v>
+        <v>46188</v>
       </c>
       <c r="H154" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I154" s="7">
         <v>46258</v>
@@ -9719,7 +9719,7 @@
         <v>61</v>
       </c>
       <c r="N154" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>24</v>
@@ -9728,7 +9728,7 @@
         <v>61</v>
       </c>
       <c r="Q154" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R154" s="6" t="s">
         <v>24</v>
@@ -9742,7 +9742,7 @@
         <v>215</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>70</v>
+        <v>139</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>24</v>
@@ -9757,10 +9757,10 @@
         <v>26</v>
       </c>
       <c r="G155" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H155" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I155" s="7">
         <v>46258</v>
@@ -9778,7 +9778,7 @@
         <v>61</v>
       </c>
       <c r="N155" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O155" s="6" t="s">
         <v>24</v>
@@ -9787,7 +9787,7 @@
         <v>61</v>
       </c>
       <c r="Q155" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R155" s="6" t="s">
         <v>24</v>
@@ -9801,7 +9801,7 @@
         <v>216</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>142</v>
+        <v>108</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>24</v>
@@ -9816,7 +9816,7 @@
         <v>26</v>
       </c>
       <c r="G156" s="7">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="H156" s="6" t="s">
         <v>27</v>
@@ -9837,7 +9837,7 @@
         <v>61</v>
       </c>
       <c r="N156" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O156" s="6" t="s">
         <v>24</v>
@@ -9846,7 +9846,7 @@
         <v>61</v>
       </c>
       <c r="Q156" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R156" s="6" t="s">
         <v>24</v>
@@ -9878,7 +9878,7 @@
         <v>46212</v>
       </c>
       <c r="H157" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I157" s="7">
         <v>46258</v>
@@ -9896,7 +9896,7 @@
         <v>61</v>
       </c>
       <c r="N157" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O157" s="6" t="s">
         <v>24</v>
@@ -9905,7 +9905,7 @@
         <v>61</v>
       </c>
       <c r="Q157" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R157" s="6" t="s">
         <v>24</v>
@@ -9937,7 +9937,7 @@
         <v>46188</v>
       </c>
       <c r="H158" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I158" s="7">
         <v>46258</v>
@@ -9955,7 +9955,7 @@
         <v>61</v>
       </c>
       <c r="N158" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O158" s="6" t="s">
         <v>24</v>
@@ -9964,7 +9964,7 @@
         <v>61</v>
       </c>
       <c r="Q158" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R158" s="6" t="s">
         <v>24</v>
@@ -10014,7 +10014,7 @@
         <v>61</v>
       </c>
       <c r="N159" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O159" s="6" t="s">
         <v>24</v>
@@ -10023,7 +10023,7 @@
         <v>61</v>
       </c>
       <c r="Q159" s="9">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R159" s="6" t="s">
         <v>24</v>
@@ -10073,7 +10073,7 @@
         <v>61</v>
       </c>
       <c r="N160" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>24</v>
@@ -10082,7 +10082,7 @@
         <v>61</v>
       </c>
       <c r="Q160" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R160" s="6" t="s">
         <v>24</v>
@@ -10096,7 +10096,7 @@
         <v>220</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>24</v>
@@ -10132,7 +10132,7 @@
         <v>61</v>
       </c>
       <c r="N161" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O161" s="6" t="s">
         <v>24</v>
@@ -10141,7 +10141,7 @@
         <v>61</v>
       </c>
       <c r="Q161" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R161" s="6" t="s">
         <v>24</v>
@@ -10155,7 +10155,7 @@
         <v>221</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>24</v>
@@ -10191,7 +10191,7 @@
         <v>61</v>
       </c>
       <c r="N162" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>24</v>
@@ -10200,7 +10200,7 @@
         <v>61</v>
       </c>
       <c r="Q162" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R162" s="6" t="s">
         <v>24</v>
@@ -10232,7 +10232,7 @@
         <v>46212</v>
       </c>
       <c r="H163" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I163" s="7">
         <v>46265</v>
@@ -10250,7 +10250,7 @@
         <v>61</v>
       </c>
       <c r="N163" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O163" s="6" t="s">
         <v>24</v>
@@ -10259,7 +10259,7 @@
         <v>61</v>
       </c>
       <c r="Q163" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R163" s="6" t="s">
         <v>24</v>
@@ -10309,7 +10309,7 @@
         <v>61</v>
       </c>
       <c r="N164" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="O164" s="6" t="s">
         <v>24</v>
@@ -10318,7 +10318,7 @@
         <v>61</v>
       </c>
       <c r="Q164" s="9">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="R164" s="6" t="s">
         <v>24</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sábado, 1 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em domingo, 2 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -529,16 +529,16 @@
     <t>FA-12000</t>
   </si>
   <si>
+    <t>FA-11982</t>
+  </si>
+  <si>
+    <t>FA-12037</t>
+  </si>
+  <si>
+    <t>FA-12001</t>
+  </si>
+  <si>
     <t>FA-11979</t>
-  </si>
-  <si>
-    <t>FA-12037</t>
-  </si>
-  <si>
-    <t>FA-11982</t>
-  </si>
-  <si>
-    <t>FA-12001</t>
   </si>
   <si>
     <t>FA-12054</t>
@@ -987,7 +987,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-61</v>
+        <v>-62</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -996,7 +996,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-61</v>
+        <v>-62</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -1046,7 +1046,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -1055,7 +1055,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
@@ -1105,7 +1105,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -1114,7 +1114,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -1164,7 +1164,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -1173,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1223,7 +1223,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -1232,7 +1232,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -1282,7 +1282,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>29</v>
@@ -1291,7 +1291,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>29</v>
@@ -1341,7 +1341,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>29</v>
@@ -1350,7 +1350,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-75</v>
+        <v>-76</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>29</v>
@@ -1400,7 +1400,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>29</v>
@@ -1409,7 +1409,7 @@
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-68</v>
+        <v>-69</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>29</v>
@@ -1459,7 +1459,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>41</v>
@@ -1468,7 +1468,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>41</v>
@@ -1518,7 +1518,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>41</v>
@@ -1527,7 +1527,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>41</v>
@@ -1577,7 +1577,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>41</v>
@@ -1586,7 +1586,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>41</v>
@@ -1636,7 +1636,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>41</v>
@@ -1645,7 +1645,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>29</v>
@@ -1695,7 +1695,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>41</v>
@@ -1704,7 +1704,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>41</v>
@@ -1754,7 +1754,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>41</v>
@@ -1763,7 +1763,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>41</v>
@@ -1813,7 +1813,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>41</v>
@@ -1822,7 +1822,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>41</v>
@@ -1872,7 +1872,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>41</v>
@@ -1881,7 +1881,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>41</v>
@@ -1931,7 +1931,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>41</v>
@@ -1940,7 +1940,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>41</v>
@@ -1990,7 +1990,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>41</v>
@@ -1999,7 +1999,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>41</v>
@@ -2049,7 +2049,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>41</v>
@@ -2058,7 +2058,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>41</v>
@@ -2108,7 +2108,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>41</v>
@@ -2117,7 +2117,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>41</v>
@@ -2167,7 +2167,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>41</v>
@@ -2176,7 +2176,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>41</v>
@@ -2226,7 +2226,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>41</v>
@@ -2235,7 +2235,7 @@
         <v>61</v>
       </c>
       <c r="Q27" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>24</v>
@@ -2285,7 +2285,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>41</v>
@@ -2294,7 +2294,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>41</v>
@@ -2344,7 +2344,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>41</v>
@@ -2353,7 +2353,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>41</v>
@@ -2403,7 +2403,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>41</v>
@@ -2412,7 +2412,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>41</v>
@@ -2462,7 +2462,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>41</v>
@@ -2471,7 +2471,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>41</v>
@@ -2521,7 +2521,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>41</v>
@@ -2530,7 +2530,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>41</v>
@@ -2580,7 +2580,7 @@
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>41</v>
@@ -2589,7 +2589,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>41</v>
@@ -2639,7 +2639,7 @@
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>41</v>
@@ -2648,7 +2648,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>41</v>
@@ -2698,7 +2698,7 @@
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>41</v>
@@ -2707,7 +2707,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>41</v>
@@ -2757,7 +2757,7 @@
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>41</v>
@@ -2766,7 +2766,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>41</v>
@@ -2816,7 +2816,7 @@
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>41</v>
@@ -2825,7 +2825,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>41</v>
@@ -2875,7 +2875,7 @@
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>41</v>
@@ -2884,7 +2884,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>41</v>
@@ -2934,7 +2934,7 @@
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>41</v>
@@ -2943,7 +2943,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>41</v>
@@ -2993,7 +2993,7 @@
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>41</v>
@@ -3002,7 +3002,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>41</v>
@@ -3052,7 +3052,7 @@
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>41</v>
@@ -3061,7 +3061,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>41</v>
@@ -3111,7 +3111,7 @@
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>41</v>
@@ -3120,7 +3120,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>41</v>
@@ -3170,7 +3170,7 @@
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>41</v>
@@ -3179,7 +3179,7 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>41</v>
@@ -3229,7 +3229,7 @@
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>41</v>
@@ -3238,7 +3238,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>41</v>
@@ -3288,7 +3288,7 @@
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>41</v>
@@ -3297,7 +3297,7 @@
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>29</v>
@@ -3347,7 +3347,7 @@
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>41</v>
@@ -3356,7 +3356,7 @@
         <v>61</v>
       </c>
       <c r="Q46" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>24</v>
@@ -3406,7 +3406,7 @@
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>41</v>
@@ -3415,7 +3415,7 @@
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>41</v>
@@ -3465,7 +3465,7 @@
         <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>41</v>
@@ -3474,7 +3474,7 @@
         <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>41</v>
@@ -3524,7 +3524,7 @@
         <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>41</v>
@@ -3533,7 +3533,7 @@
         <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>41</v>
@@ -3583,7 +3583,7 @@
         <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>41</v>
@@ -3592,7 +3592,7 @@
         <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>41</v>
@@ -3642,7 +3642,7 @@
         <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O51" s="6" t="s">
         <v>41</v>
@@ -3651,7 +3651,7 @@
         <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>41</v>
@@ -3701,7 +3701,7 @@
         <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>41</v>
@@ -3710,7 +3710,7 @@
         <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>41</v>
@@ -3760,7 +3760,7 @@
         <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>41</v>
@@ -3769,7 +3769,7 @@
         <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>41</v>
@@ -3819,7 +3819,7 @@
         <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>41</v>
@@ -3828,7 +3828,7 @@
         <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>41</v>
@@ -3878,7 +3878,7 @@
         <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>41</v>
@@ -3887,7 +3887,7 @@
         <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>41</v>
@@ -3937,7 +3937,7 @@
         <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>41</v>
@@ -3946,7 +3946,7 @@
         <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>41</v>
@@ -3996,7 +3996,7 @@
         <v>28</v>
       </c>
       <c r="N57" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O57" s="6" t="s">
         <v>41</v>
@@ -4005,7 +4005,7 @@
         <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>41</v>
@@ -4055,7 +4055,7 @@
         <v>28</v>
       </c>
       <c r="N58" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>41</v>
@@ -4064,7 +4064,7 @@
         <v>28</v>
       </c>
       <c r="Q58" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>41</v>
@@ -4114,7 +4114,7 @@
         <v>28</v>
       </c>
       <c r="N59" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O59" s="6" t="s">
         <v>41</v>
@@ -4123,7 +4123,7 @@
         <v>28</v>
       </c>
       <c r="Q59" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>41</v>
@@ -4173,7 +4173,7 @@
         <v>28</v>
       </c>
       <c r="N60" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>41</v>
@@ -4182,7 +4182,7 @@
         <v>28</v>
       </c>
       <c r="Q60" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>41</v>
@@ -4232,7 +4232,7 @@
         <v>28</v>
       </c>
       <c r="N61" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O61" s="6" t="s">
         <v>41</v>
@@ -4241,7 +4241,7 @@
         <v>28</v>
       </c>
       <c r="Q61" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>41</v>
@@ -4291,7 +4291,7 @@
         <v>28</v>
       </c>
       <c r="N62" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>41</v>
@@ -4300,7 +4300,7 @@
         <v>28</v>
       </c>
       <c r="Q62" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>41</v>
@@ -4350,7 +4350,7 @@
         <v>28</v>
       </c>
       <c r="N63" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O63" s="6" t="s">
         <v>41</v>
@@ -4359,7 +4359,7 @@
         <v>28</v>
       </c>
       <c r="Q63" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>41</v>
@@ -4409,7 +4409,7 @@
         <v>28</v>
       </c>
       <c r="N64" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>41</v>
@@ -4418,7 +4418,7 @@
         <v>28</v>
       </c>
       <c r="Q64" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R64" s="6" t="s">
         <v>41</v>
@@ -4468,7 +4468,7 @@
         <v>28</v>
       </c>
       <c r="N65" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O65" s="6" t="s">
         <v>41</v>
@@ -4477,7 +4477,7 @@
         <v>28</v>
       </c>
       <c r="Q65" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>41</v>
@@ -4527,7 +4527,7 @@
         <v>28</v>
       </c>
       <c r="N66" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>41</v>
@@ -4536,7 +4536,7 @@
         <v>28</v>
       </c>
       <c r="Q66" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>41</v>
@@ -4586,7 +4586,7 @@
         <v>28</v>
       </c>
       <c r="N67" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>41</v>
@@ -4595,7 +4595,7 @@
         <v>28</v>
       </c>
       <c r="Q67" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>41</v>
@@ -4645,7 +4645,7 @@
         <v>28</v>
       </c>
       <c r="N68" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>41</v>
@@ -4654,7 +4654,7 @@
         <v>28</v>
       </c>
       <c r="Q68" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>41</v>
@@ -4704,7 +4704,7 @@
         <v>28</v>
       </c>
       <c r="N69" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>41</v>
@@ -4713,7 +4713,7 @@
         <v>28</v>
       </c>
       <c r="Q69" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>41</v>
@@ -4763,7 +4763,7 @@
         <v>28</v>
       </c>
       <c r="N70" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>41</v>
@@ -4772,7 +4772,7 @@
         <v>28</v>
       </c>
       <c r="Q70" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>41</v>
@@ -4822,7 +4822,7 @@
         <v>61</v>
       </c>
       <c r="N71" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
@@ -4831,7 +4831,7 @@
         <v>28</v>
       </c>
       <c r="Q71" s="9">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>29</v>
@@ -4881,7 +4881,7 @@
         <v>61</v>
       </c>
       <c r="N72" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
@@ -4890,7 +4890,7 @@
         <v>61</v>
       </c>
       <c r="Q72" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4940,7 +4940,7 @@
         <v>61</v>
       </c>
       <c r="N73" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
@@ -4949,7 +4949,7 @@
         <v>61</v>
       </c>
       <c r="Q73" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4999,7 +4999,7 @@
         <v>61</v>
       </c>
       <c r="N74" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
@@ -5008,7 +5008,7 @@
         <v>61</v>
       </c>
       <c r="Q74" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -5058,7 +5058,7 @@
         <v>61</v>
       </c>
       <c r="N75" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
@@ -5067,7 +5067,7 @@
         <v>61</v>
       </c>
       <c r="Q75" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -5117,7 +5117,7 @@
         <v>61</v>
       </c>
       <c r="N76" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
@@ -5126,7 +5126,7 @@
         <v>61</v>
       </c>
       <c r="Q76" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -5176,7 +5176,7 @@
         <v>61</v>
       </c>
       <c r="N77" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
@@ -5185,7 +5185,7 @@
         <v>61</v>
       </c>
       <c r="Q77" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5235,7 +5235,7 @@
         <v>61</v>
       </c>
       <c r="N78" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
@@ -5244,7 +5244,7 @@
         <v>61</v>
       </c>
       <c r="Q78" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5294,7 +5294,7 @@
         <v>61</v>
       </c>
       <c r="N79" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
@@ -5303,7 +5303,7 @@
         <v>61</v>
       </c>
       <c r="Q79" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5353,7 +5353,7 @@
         <v>61</v>
       </c>
       <c r="N80" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
@@ -5362,7 +5362,7 @@
         <v>61</v>
       </c>
       <c r="Q80" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5412,7 +5412,7 @@
         <v>61</v>
       </c>
       <c r="N81" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
@@ -5421,7 +5421,7 @@
         <v>61</v>
       </c>
       <c r="Q81" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5471,7 +5471,7 @@
         <v>61</v>
       </c>
       <c r="N82" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
@@ -5480,7 +5480,7 @@
         <v>61</v>
       </c>
       <c r="Q82" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5530,7 +5530,7 @@
         <v>61</v>
       </c>
       <c r="N83" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
@@ -5539,7 +5539,7 @@
         <v>61</v>
       </c>
       <c r="Q83" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5589,7 +5589,7 @@
         <v>61</v>
       </c>
       <c r="N84" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
@@ -5598,7 +5598,7 @@
         <v>61</v>
       </c>
       <c r="Q84" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5648,7 +5648,7 @@
         <v>61</v>
       </c>
       <c r="N85" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
@@ -5657,7 +5657,7 @@
         <v>61</v>
       </c>
       <c r="Q85" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5707,7 +5707,7 @@
         <v>61</v>
       </c>
       <c r="N86" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
@@ -5716,7 +5716,7 @@
         <v>61</v>
       </c>
       <c r="Q86" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5766,7 +5766,7 @@
         <v>61</v>
       </c>
       <c r="N87" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
@@ -5775,7 +5775,7 @@
         <v>61</v>
       </c>
       <c r="Q87" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5825,7 +5825,7 @@
         <v>61</v>
       </c>
       <c r="N88" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
@@ -5834,7 +5834,7 @@
         <v>61</v>
       </c>
       <c r="Q88" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5884,7 +5884,7 @@
         <v>61</v>
       </c>
       <c r="N89" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
@@ -5893,7 +5893,7 @@
         <v>61</v>
       </c>
       <c r="Q89" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5943,7 +5943,7 @@
         <v>61</v>
       </c>
       <c r="N90" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
@@ -5952,7 +5952,7 @@
         <v>61</v>
       </c>
       <c r="Q90" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -6002,7 +6002,7 @@
         <v>61</v>
       </c>
       <c r="N91" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
@@ -6011,7 +6011,7 @@
         <v>61</v>
       </c>
       <c r="Q91" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -6061,7 +6061,7 @@
         <v>61</v>
       </c>
       <c r="N92" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
@@ -6070,7 +6070,7 @@
         <v>61</v>
       </c>
       <c r="Q92" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -6120,7 +6120,7 @@
         <v>61</v>
       </c>
       <c r="N93" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
@@ -6129,7 +6129,7 @@
         <v>61</v>
       </c>
       <c r="Q93" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -6179,7 +6179,7 @@
         <v>61</v>
       </c>
       <c r="N94" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
@@ -6188,7 +6188,7 @@
         <v>61</v>
       </c>
       <c r="Q94" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6238,7 +6238,7 @@
         <v>61</v>
       </c>
       <c r="N95" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
@@ -6247,7 +6247,7 @@
         <v>61</v>
       </c>
       <c r="Q95" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6297,7 +6297,7 @@
         <v>61</v>
       </c>
       <c r="N96" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
@@ -6306,7 +6306,7 @@
         <v>61</v>
       </c>
       <c r="Q96" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6356,7 +6356,7 @@
         <v>61</v>
       </c>
       <c r="N97" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
@@ -6365,7 +6365,7 @@
         <v>61</v>
       </c>
       <c r="Q97" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6415,7 +6415,7 @@
         <v>61</v>
       </c>
       <c r="N98" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
@@ -6424,7 +6424,7 @@
         <v>61</v>
       </c>
       <c r="Q98" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6474,7 +6474,7 @@
         <v>61</v>
       </c>
       <c r="N99" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
@@ -6483,7 +6483,7 @@
         <v>61</v>
       </c>
       <c r="Q99" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6533,7 +6533,7 @@
         <v>61</v>
       </c>
       <c r="N100" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
@@ -6542,7 +6542,7 @@
         <v>61</v>
       </c>
       <c r="Q100" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6592,7 +6592,7 @@
         <v>61</v>
       </c>
       <c r="N101" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
@@ -6601,7 +6601,7 @@
         <v>61</v>
       </c>
       <c r="Q101" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6651,7 +6651,7 @@
         <v>61</v>
       </c>
       <c r="N102" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
@@ -6660,7 +6660,7 @@
         <v>61</v>
       </c>
       <c r="Q102" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6710,7 +6710,7 @@
         <v>61</v>
       </c>
       <c r="N103" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
@@ -6719,7 +6719,7 @@
         <v>61</v>
       </c>
       <c r="Q103" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6769,7 +6769,7 @@
         <v>61</v>
       </c>
       <c r="N104" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
@@ -6778,7 +6778,7 @@
         <v>61</v>
       </c>
       <c r="Q104" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6792,7 +6792,7 @@
         <v>165</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>64</v>
+        <v>137</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>24</v>
@@ -6828,7 +6828,7 @@
         <v>61</v>
       </c>
       <c r="N105" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
@@ -6837,7 +6837,7 @@
         <v>61</v>
       </c>
       <c r="Q105" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6887,7 +6887,7 @@
         <v>61</v>
       </c>
       <c r="N106" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
@@ -6896,7 +6896,7 @@
         <v>61</v>
       </c>
       <c r="Q106" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>
@@ -6910,7 +6910,7 @@
         <v>167</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>137</v>
+        <v>67</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>24</v>
@@ -6946,7 +6946,7 @@
         <v>61</v>
       </c>
       <c r="N107" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>24</v>
@@ -6955,7 +6955,7 @@
         <v>61</v>
       </c>
       <c r="Q107" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>24</v>
@@ -6969,7 +6969,7 @@
         <v>168</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>24</v>
@@ -7005,7 +7005,7 @@
         <v>61</v>
       </c>
       <c r="N108" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>24</v>
@@ -7014,7 +7014,7 @@
         <v>61</v>
       </c>
       <c r="Q108" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>24</v>
@@ -7064,7 +7064,7 @@
         <v>61</v>
       </c>
       <c r="N109" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>24</v>
@@ -7073,7 +7073,7 @@
         <v>61</v>
       </c>
       <c r="Q109" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R109" s="6" t="s">
         <v>24</v>
@@ -7123,7 +7123,7 @@
         <v>61</v>
       </c>
       <c r="N110" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>24</v>
@@ -7132,7 +7132,7 @@
         <v>61</v>
       </c>
       <c r="Q110" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R110" s="6" t="s">
         <v>24</v>
@@ -7182,7 +7182,7 @@
         <v>61</v>
       </c>
       <c r="N111" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>24</v>
@@ -7191,7 +7191,7 @@
         <v>61</v>
       </c>
       <c r="Q111" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R111" s="6" t="s">
         <v>24</v>
@@ -7241,7 +7241,7 @@
         <v>61</v>
       </c>
       <c r="N112" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>24</v>
@@ -7250,7 +7250,7 @@
         <v>61</v>
       </c>
       <c r="Q112" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R112" s="6" t="s">
         <v>24</v>
@@ -7300,7 +7300,7 @@
         <v>61</v>
       </c>
       <c r="N113" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>24</v>
@@ -7309,7 +7309,7 @@
         <v>61</v>
       </c>
       <c r="Q113" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R113" s="6" t="s">
         <v>24</v>
@@ -7359,7 +7359,7 @@
         <v>61</v>
       </c>
       <c r="N114" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>24</v>
@@ -7368,7 +7368,7 @@
         <v>61</v>
       </c>
       <c r="Q114" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R114" s="6" t="s">
         <v>24</v>
@@ -7418,7 +7418,7 @@
         <v>61</v>
       </c>
       <c r="N115" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O115" s="6" t="s">
         <v>24</v>
@@ -7427,7 +7427,7 @@
         <v>61</v>
       </c>
       <c r="Q115" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R115" s="6" t="s">
         <v>24</v>
@@ -7477,7 +7477,7 @@
         <v>61</v>
       </c>
       <c r="N116" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>24</v>
@@ -7486,7 +7486,7 @@
         <v>61</v>
       </c>
       <c r="Q116" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R116" s="6" t="s">
         <v>24</v>
@@ -7536,7 +7536,7 @@
         <v>61</v>
       </c>
       <c r="N117" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O117" s="6" t="s">
         <v>24</v>
@@ -7545,7 +7545,7 @@
         <v>61</v>
       </c>
       <c r="Q117" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R117" s="6" t="s">
         <v>24</v>
@@ -7595,7 +7595,7 @@
         <v>61</v>
       </c>
       <c r="N118" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>24</v>
@@ -7604,7 +7604,7 @@
         <v>61</v>
       </c>
       <c r="Q118" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R118" s="6" t="s">
         <v>24</v>
@@ -7654,7 +7654,7 @@
         <v>61</v>
       </c>
       <c r="N119" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O119" s="6" t="s">
         <v>24</v>
@@ -7663,7 +7663,7 @@
         <v>61</v>
       </c>
       <c r="Q119" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R119" s="6" t="s">
         <v>24</v>
@@ -7713,7 +7713,7 @@
         <v>61</v>
       </c>
       <c r="N120" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>24</v>
@@ -7722,7 +7722,7 @@
         <v>61</v>
       </c>
       <c r="Q120" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R120" s="6" t="s">
         <v>24</v>
@@ -7772,7 +7772,7 @@
         <v>61</v>
       </c>
       <c r="N121" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O121" s="6" t="s">
         <v>24</v>
@@ -7781,7 +7781,7 @@
         <v>61</v>
       </c>
       <c r="Q121" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R121" s="6" t="s">
         <v>24</v>
@@ -7831,7 +7831,7 @@
         <v>61</v>
       </c>
       <c r="N122" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>24</v>
@@ -7840,7 +7840,7 @@
         <v>61</v>
       </c>
       <c r="Q122" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R122" s="6" t="s">
         <v>24</v>
@@ -7890,7 +7890,7 @@
         <v>61</v>
       </c>
       <c r="N123" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O123" s="6" t="s">
         <v>24</v>
@@ -7899,7 +7899,7 @@
         <v>61</v>
       </c>
       <c r="Q123" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R123" s="6" t="s">
         <v>24</v>
@@ -7949,7 +7949,7 @@
         <v>61</v>
       </c>
       <c r="N124" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>24</v>
@@ -7958,7 +7958,7 @@
         <v>61</v>
       </c>
       <c r="Q124" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R124" s="6" t="s">
         <v>24</v>
@@ -8008,7 +8008,7 @@
         <v>61</v>
       </c>
       <c r="N125" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O125" s="6" t="s">
         <v>24</v>
@@ -8017,7 +8017,7 @@
         <v>61</v>
       </c>
       <c r="Q125" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R125" s="6" t="s">
         <v>24</v>
@@ -8067,7 +8067,7 @@
         <v>61</v>
       </c>
       <c r="N126" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>24</v>
@@ -8076,7 +8076,7 @@
         <v>61</v>
       </c>
       <c r="Q126" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R126" s="6" t="s">
         <v>24</v>
@@ -8126,7 +8126,7 @@
         <v>61</v>
       </c>
       <c r="N127" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O127" s="6" t="s">
         <v>24</v>
@@ -8135,7 +8135,7 @@
         <v>61</v>
       </c>
       <c r="Q127" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R127" s="6" t="s">
         <v>24</v>
@@ -8185,7 +8185,7 @@
         <v>61</v>
       </c>
       <c r="N128" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>24</v>
@@ -8194,7 +8194,7 @@
         <v>61</v>
       </c>
       <c r="Q128" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R128" s="6" t="s">
         <v>24</v>
@@ -8244,7 +8244,7 @@
         <v>61</v>
       </c>
       <c r="N129" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O129" s="6" t="s">
         <v>24</v>
@@ -8253,7 +8253,7 @@
         <v>61</v>
       </c>
       <c r="Q129" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R129" s="6" t="s">
         <v>24</v>
@@ -8303,7 +8303,7 @@
         <v>61</v>
       </c>
       <c r="N130" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>24</v>
@@ -8312,7 +8312,7 @@
         <v>61</v>
       </c>
       <c r="Q130" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R130" s="6" t="s">
         <v>24</v>
@@ -8362,7 +8362,7 @@
         <v>61</v>
       </c>
       <c r="N131" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O131" s="6" t="s">
         <v>24</v>
@@ -8371,7 +8371,7 @@
         <v>61</v>
       </c>
       <c r="Q131" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R131" s="6" t="s">
         <v>24</v>
@@ -8421,7 +8421,7 @@
         <v>61</v>
       </c>
       <c r="N132" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>24</v>
@@ -8430,7 +8430,7 @@
         <v>61</v>
       </c>
       <c r="Q132" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R132" s="6" t="s">
         <v>24</v>
@@ -8480,7 +8480,7 @@
         <v>61</v>
       </c>
       <c r="N133" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O133" s="6" t="s">
         <v>24</v>
@@ -8489,7 +8489,7 @@
         <v>61</v>
       </c>
       <c r="Q133" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R133" s="6" t="s">
         <v>24</v>
@@ -8539,7 +8539,7 @@
         <v>61</v>
       </c>
       <c r="N134" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>24</v>
@@ -8548,7 +8548,7 @@
         <v>61</v>
       </c>
       <c r="Q134" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R134" s="6" t="s">
         <v>24</v>
@@ -8598,7 +8598,7 @@
         <v>61</v>
       </c>
       <c r="N135" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O135" s="6" t="s">
         <v>24</v>
@@ -8607,7 +8607,7 @@
         <v>61</v>
       </c>
       <c r="Q135" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R135" s="6" t="s">
         <v>24</v>
@@ -8657,7 +8657,7 @@
         <v>61</v>
       </c>
       <c r="N136" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>24</v>
@@ -8666,7 +8666,7 @@
         <v>61</v>
       </c>
       <c r="Q136" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R136" s="6" t="s">
         <v>24</v>
@@ -8716,7 +8716,7 @@
         <v>61</v>
       </c>
       <c r="N137" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O137" s="6" t="s">
         <v>24</v>
@@ -8725,7 +8725,7 @@
         <v>61</v>
       </c>
       <c r="Q137" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R137" s="6" t="s">
         <v>24</v>
@@ -8775,7 +8775,7 @@
         <v>61</v>
       </c>
       <c r="N138" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>24</v>
@@ -8784,7 +8784,7 @@
         <v>61</v>
       </c>
       <c r="Q138" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R138" s="6" t="s">
         <v>24</v>
@@ -8834,7 +8834,7 @@
         <v>61</v>
       </c>
       <c r="N139" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O139" s="6" t="s">
         <v>24</v>
@@ -8843,7 +8843,7 @@
         <v>61</v>
       </c>
       <c r="Q139" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R139" s="6" t="s">
         <v>24</v>
@@ -8893,7 +8893,7 @@
         <v>61</v>
       </c>
       <c r="N140" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>24</v>
@@ -8902,7 +8902,7 @@
         <v>61</v>
       </c>
       <c r="Q140" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R140" s="6" t="s">
         <v>24</v>
@@ -8952,7 +8952,7 @@
         <v>61</v>
       </c>
       <c r="N141" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O141" s="6" t="s">
         <v>24</v>
@@ -8961,7 +8961,7 @@
         <v>61</v>
       </c>
       <c r="Q141" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R141" s="6" t="s">
         <v>24</v>
@@ -9011,7 +9011,7 @@
         <v>61</v>
       </c>
       <c r="N142" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>24</v>
@@ -9020,7 +9020,7 @@
         <v>61</v>
       </c>
       <c r="Q142" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R142" s="6" t="s">
         <v>24</v>
@@ -9070,7 +9070,7 @@
         <v>61</v>
       </c>
       <c r="N143" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O143" s="6" t="s">
         <v>24</v>
@@ -9079,7 +9079,7 @@
         <v>61</v>
       </c>
       <c r="Q143" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R143" s="6" t="s">
         <v>24</v>
@@ -9129,7 +9129,7 @@
         <v>61</v>
       </c>
       <c r="N144" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>24</v>
@@ -9138,7 +9138,7 @@
         <v>61</v>
       </c>
       <c r="Q144" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R144" s="6" t="s">
         <v>24</v>
@@ -9188,7 +9188,7 @@
         <v>61</v>
       </c>
       <c r="N145" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O145" s="6" t="s">
         <v>24</v>
@@ -9197,7 +9197,7 @@
         <v>61</v>
       </c>
       <c r="Q145" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R145" s="6" t="s">
         <v>24</v>
@@ -9247,7 +9247,7 @@
         <v>61</v>
       </c>
       <c r="N146" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O146" s="6" t="s">
         <v>24</v>
@@ -9256,7 +9256,7 @@
         <v>61</v>
       </c>
       <c r="Q146" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R146" s="6" t="s">
         <v>24</v>
@@ -9306,7 +9306,7 @@
         <v>61</v>
       </c>
       <c r="N147" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O147" s="6" t="s">
         <v>24</v>
@@ -9315,7 +9315,7 @@
         <v>61</v>
       </c>
       <c r="Q147" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R147" s="6" t="s">
         <v>24</v>
@@ -9365,7 +9365,7 @@
         <v>61</v>
       </c>
       <c r="N148" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>24</v>
@@ -9374,7 +9374,7 @@
         <v>61</v>
       </c>
       <c r="Q148" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R148" s="6" t="s">
         <v>24</v>
@@ -9424,7 +9424,7 @@
         <v>61</v>
       </c>
       <c r="N149" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>24</v>
@@ -9433,7 +9433,7 @@
         <v>61</v>
       </c>
       <c r="Q149" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R149" s="6" t="s">
         <v>24</v>
@@ -9483,7 +9483,7 @@
         <v>61</v>
       </c>
       <c r="N150" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>24</v>
@@ -9492,7 +9492,7 @@
         <v>61</v>
       </c>
       <c r="Q150" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R150" s="6" t="s">
         <v>24</v>
@@ -9542,7 +9542,7 @@
         <v>61</v>
       </c>
       <c r="N151" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O151" s="6" t="s">
         <v>24</v>
@@ -9551,7 +9551,7 @@
         <v>61</v>
       </c>
       <c r="Q151" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R151" s="6" t="s">
         <v>24</v>
@@ -9601,7 +9601,7 @@
         <v>61</v>
       </c>
       <c r="N152" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>24</v>
@@ -9610,7 +9610,7 @@
         <v>61</v>
       </c>
       <c r="Q152" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R152" s="6" t="s">
         <v>24</v>
@@ -9660,7 +9660,7 @@
         <v>61</v>
       </c>
       <c r="N153" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O153" s="6" t="s">
         <v>24</v>
@@ -9669,7 +9669,7 @@
         <v>61</v>
       </c>
       <c r="Q153" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R153" s="6" t="s">
         <v>24</v>
@@ -9719,7 +9719,7 @@
         <v>61</v>
       </c>
       <c r="N154" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>24</v>
@@ -9728,7 +9728,7 @@
         <v>61</v>
       </c>
       <c r="Q154" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R154" s="6" t="s">
         <v>24</v>
@@ -9778,7 +9778,7 @@
         <v>61</v>
       </c>
       <c r="N155" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O155" s="6" t="s">
         <v>24</v>
@@ -9787,7 +9787,7 @@
         <v>61</v>
       </c>
       <c r="Q155" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R155" s="6" t="s">
         <v>24</v>
@@ -9837,7 +9837,7 @@
         <v>61</v>
       </c>
       <c r="N156" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O156" s="6" t="s">
         <v>24</v>
@@ -9846,7 +9846,7 @@
         <v>61</v>
       </c>
       <c r="Q156" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R156" s="6" t="s">
         <v>24</v>
@@ -9896,7 +9896,7 @@
         <v>61</v>
       </c>
       <c r="N157" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O157" s="6" t="s">
         <v>24</v>
@@ -9905,7 +9905,7 @@
         <v>61</v>
       </c>
       <c r="Q157" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R157" s="6" t="s">
         <v>24</v>
@@ -9955,7 +9955,7 @@
         <v>61</v>
       </c>
       <c r="N158" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O158" s="6" t="s">
         <v>24</v>
@@ -9964,7 +9964,7 @@
         <v>61</v>
       </c>
       <c r="Q158" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R158" s="6" t="s">
         <v>24</v>
@@ -10014,7 +10014,7 @@
         <v>61</v>
       </c>
       <c r="N159" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O159" s="6" t="s">
         <v>24</v>
@@ -10023,7 +10023,7 @@
         <v>61</v>
       </c>
       <c r="Q159" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R159" s="6" t="s">
         <v>24</v>
@@ -10073,7 +10073,7 @@
         <v>61</v>
       </c>
       <c r="N160" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>24</v>
@@ -10082,7 +10082,7 @@
         <v>61</v>
       </c>
       <c r="Q160" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R160" s="6" t="s">
         <v>24</v>
@@ -10132,7 +10132,7 @@
         <v>61</v>
       </c>
       <c r="N161" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O161" s="6" t="s">
         <v>24</v>
@@ -10141,7 +10141,7 @@
         <v>61</v>
       </c>
       <c r="Q161" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R161" s="6" t="s">
         <v>24</v>
@@ -10191,7 +10191,7 @@
         <v>61</v>
       </c>
       <c r="N162" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>24</v>
@@ -10200,7 +10200,7 @@
         <v>61</v>
       </c>
       <c r="Q162" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R162" s="6" t="s">
         <v>24</v>
@@ -10250,7 +10250,7 @@
         <v>61</v>
       </c>
       <c r="N163" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O163" s="6" t="s">
         <v>24</v>
@@ -10259,7 +10259,7 @@
         <v>61</v>
       </c>
       <c r="Q163" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R163" s="6" t="s">
         <v>24</v>
@@ -10309,7 +10309,7 @@
         <v>61</v>
       </c>
       <c r="N164" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O164" s="6" t="s">
         <v>24</v>
@@ -10318,7 +10318,7 @@
         <v>61</v>
       </c>
       <c r="Q164" s="9">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R164" s="6" t="s">
         <v>24</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em domingo, 2 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em segunda-feira, 3 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -361,21 +361,21 @@
     <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
   </si>
   <si>
+    <t>FA-11962</t>
+  </si>
+  <si>
+    <t>FA-12030</t>
+  </si>
+  <si>
+    <t>FA-11992</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
     <t>FA-12017</t>
   </si>
   <si>
-    <t>FA-12030</t>
-  </si>
-  <si>
-    <t>FA-11992</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11962</t>
-  </si>
-  <si>
     <t>FA-12019</t>
   </si>
   <si>
@@ -406,6 +406,9 @@
     <t>FA-11903</t>
   </si>
   <si>
+    <t>HOJE</t>
+  </si>
+  <si>
     <t>FA-11977</t>
   </si>
   <si>
@@ -448,24 +451,24 @@
     <t>ANA FLORIPES CARVALHO DA CUNHA</t>
   </si>
   <si>
+    <t>FA-12049</t>
+  </si>
+  <si>
+    <t>FA-11858</t>
+  </si>
+  <si>
+    <t>FA-11976</t>
+  </si>
+  <si>
+    <t>FA-11921</t>
+  </si>
+  <si>
     <t>FA-12062</t>
   </si>
   <si>
     <t>WILSON COUTINHO BEZERRA</t>
   </si>
   <si>
-    <t>FA-11858</t>
-  </si>
-  <si>
-    <t>FA-12049</t>
-  </si>
-  <si>
-    <t>FA-11976</t>
-  </si>
-  <si>
-    <t>FA-11921</t>
-  </si>
-  <si>
     <t>FA-12036</t>
   </si>
   <si>
@@ -526,15 +529,15 @@
     <t>FA-12053</t>
   </si>
   <si>
+    <t>FA-12037</t>
+  </si>
+  <si>
+    <t>FA-11982</t>
+  </si>
+  <si>
     <t>FA-12000</t>
   </si>
   <si>
-    <t>FA-11982</t>
-  </si>
-  <si>
-    <t>FA-12037</t>
-  </si>
-  <si>
     <t>FA-12001</t>
   </si>
   <si>
@@ -562,19 +565,19 @@
     <t>FA-11964</t>
   </si>
   <si>
+    <t>FA-12002</t>
+  </si>
+  <si>
+    <t>FA-12025</t>
+  </si>
+  <si>
+    <t>FA-12033</t>
+  </si>
+  <si>
+    <t>FA-12038</t>
+  </si>
+  <si>
     <t>FA-12024</t>
-  </si>
-  <si>
-    <t>FA-12025</t>
-  </si>
-  <si>
-    <t>FA-12033</t>
-  </si>
-  <si>
-    <t>FA-12038</t>
-  </si>
-  <si>
-    <t>FA-12002</t>
   </si>
   <si>
     <t>FA-11934</t>
@@ -987,7 +990,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-62</v>
+        <v>-63</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -996,7 +999,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-62</v>
+        <v>-63</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -1046,7 +1049,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -1055,7 +1058,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
@@ -1105,7 +1108,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -1114,7 +1117,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -1164,7 +1167,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -1173,7 +1176,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1223,7 +1226,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -1232,7 +1235,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -1282,7 +1285,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>29</v>
@@ -1291,7 +1294,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>29</v>
@@ -1341,7 +1344,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>29</v>
@@ -1350,7 +1353,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-76</v>
+        <v>-77</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>29</v>
@@ -1400,7 +1403,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>29</v>
@@ -1409,7 +1412,7 @@
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-69</v>
+        <v>-70</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>29</v>
@@ -1459,7 +1462,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>41</v>
@@ -1468,7 +1471,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>41</v>
@@ -1518,7 +1521,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>41</v>
@@ -1527,7 +1530,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>41</v>
@@ -1577,7 +1580,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>41</v>
@@ -1586,7 +1589,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>41</v>
@@ -1636,7 +1639,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>41</v>
@@ -1645,7 +1648,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>29</v>
@@ -1695,7 +1698,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>41</v>
@@ -1704,7 +1707,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>41</v>
@@ -1754,7 +1757,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>41</v>
@@ -1763,7 +1766,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>41</v>
@@ -1813,7 +1816,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>41</v>
@@ -1822,7 +1825,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>41</v>
@@ -1872,7 +1875,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>41</v>
@@ -1881,7 +1884,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>41</v>
@@ -1931,7 +1934,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>41</v>
@@ -1940,7 +1943,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>41</v>
@@ -1990,7 +1993,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>41</v>
@@ -1999,7 +2002,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>41</v>
@@ -2049,7 +2052,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>41</v>
@@ -2058,7 +2061,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>41</v>
@@ -2108,7 +2111,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>41</v>
@@ -2117,7 +2120,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>41</v>
@@ -2167,7 +2170,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>41</v>
@@ -2176,7 +2179,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>41</v>
@@ -2226,7 +2229,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>41</v>
@@ -2235,7 +2238,7 @@
         <v>61</v>
       </c>
       <c r="Q27" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>24</v>
@@ -2285,7 +2288,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>41</v>
@@ -2294,7 +2297,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>41</v>
@@ -2344,7 +2347,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>41</v>
@@ -2353,7 +2356,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>41</v>
@@ -2403,7 +2406,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>41</v>
@@ -2412,7 +2415,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>41</v>
@@ -2462,7 +2465,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>41</v>
@@ -2471,7 +2474,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>41</v>
@@ -2521,7 +2524,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>41</v>
@@ -2530,7 +2533,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>41</v>
@@ -2580,7 +2583,7 @@
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>41</v>
@@ -2589,7 +2592,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>41</v>
@@ -2639,7 +2642,7 @@
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>41</v>
@@ -2648,7 +2651,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>41</v>
@@ -2698,7 +2701,7 @@
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>41</v>
@@ -2707,7 +2710,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>41</v>
@@ -2757,7 +2760,7 @@
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>41</v>
@@ -2766,7 +2769,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>41</v>
@@ -2816,7 +2819,7 @@
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>41</v>
@@ -2825,7 +2828,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>41</v>
@@ -2875,7 +2878,7 @@
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>41</v>
@@ -2884,7 +2887,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>41</v>
@@ -2934,7 +2937,7 @@
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>41</v>
@@ -2943,7 +2946,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>41</v>
@@ -2993,7 +2996,7 @@
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>41</v>
@@ -3002,7 +3005,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>41</v>
@@ -3052,7 +3055,7 @@
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>41</v>
@@ -3061,7 +3064,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>41</v>
@@ -3111,7 +3114,7 @@
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>41</v>
@@ -3120,7 +3123,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>41</v>
@@ -3170,7 +3173,7 @@
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>41</v>
@@ -3179,7 +3182,7 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>41</v>
@@ -3229,7 +3232,7 @@
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>41</v>
@@ -3238,7 +3241,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>41</v>
@@ -3288,7 +3291,7 @@
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>41</v>
@@ -3297,7 +3300,7 @@
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>29</v>
@@ -3347,7 +3350,7 @@
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>41</v>
@@ -3356,7 +3359,7 @@
         <v>61</v>
       </c>
       <c r="Q46" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>24</v>
@@ -3406,7 +3409,7 @@
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>41</v>
@@ -3415,7 +3418,7 @@
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>41</v>
@@ -3465,7 +3468,7 @@
         <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>41</v>
@@ -3474,7 +3477,7 @@
         <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>41</v>
@@ -3524,7 +3527,7 @@
         <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>41</v>
@@ -3533,7 +3536,7 @@
         <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>41</v>
@@ -3583,7 +3586,7 @@
         <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>41</v>
@@ -3592,7 +3595,7 @@
         <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>41</v>
@@ -3642,7 +3645,7 @@
         <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O51" s="6" t="s">
         <v>41</v>
@@ -3651,7 +3654,7 @@
         <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>41</v>
@@ -3701,7 +3704,7 @@
         <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>41</v>
@@ -3710,7 +3713,7 @@
         <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>41</v>
@@ -3760,7 +3763,7 @@
         <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>41</v>
@@ -3769,7 +3772,7 @@
         <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>41</v>
@@ -3819,7 +3822,7 @@
         <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>41</v>
@@ -3828,7 +3831,7 @@
         <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>41</v>
@@ -3878,7 +3881,7 @@
         <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>41</v>
@@ -3887,7 +3890,7 @@
         <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>41</v>
@@ -3937,7 +3940,7 @@
         <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>41</v>
@@ -3946,7 +3949,7 @@
         <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>41</v>
@@ -3996,7 +3999,7 @@
         <v>28</v>
       </c>
       <c r="N57" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O57" s="6" t="s">
         <v>41</v>
@@ -4005,7 +4008,7 @@
         <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>41</v>
@@ -4055,7 +4058,7 @@
         <v>28</v>
       </c>
       <c r="N58" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>41</v>
@@ -4064,7 +4067,7 @@
         <v>28</v>
       </c>
       <c r="Q58" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>41</v>
@@ -4078,7 +4081,7 @@
         <v>109</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>24</v>
@@ -4093,10 +4096,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I59" s="7">
         <v>46230</v>
@@ -4114,7 +4117,7 @@
         <v>28</v>
       </c>
       <c r="N59" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O59" s="6" t="s">
         <v>41</v>
@@ -4123,7 +4126,7 @@
         <v>28</v>
       </c>
       <c r="Q59" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>41</v>
@@ -4173,7 +4176,7 @@
         <v>28</v>
       </c>
       <c r="N60" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>41</v>
@@ -4182,7 +4185,7 @@
         <v>28</v>
       </c>
       <c r="Q60" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>41</v>
@@ -4232,7 +4235,7 @@
         <v>28</v>
       </c>
       <c r="N61" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O61" s="6" t="s">
         <v>41</v>
@@ -4241,7 +4244,7 @@
         <v>28</v>
       </c>
       <c r="Q61" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>41</v>
@@ -4255,7 +4258,7 @@
         <v>113</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4270,10 +4273,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="I62" s="7">
         <v>46230</v>
@@ -4291,7 +4294,7 @@
         <v>28</v>
       </c>
       <c r="N62" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>41</v>
@@ -4300,7 +4303,7 @@
         <v>28</v>
       </c>
       <c r="Q62" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>41</v>
@@ -4350,7 +4353,7 @@
         <v>28</v>
       </c>
       <c r="N63" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O63" s="6" t="s">
         <v>41</v>
@@ -4359,7 +4362,7 @@
         <v>28</v>
       </c>
       <c r="Q63" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>41</v>
@@ -4409,7 +4412,7 @@
         <v>28</v>
       </c>
       <c r="N64" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>41</v>
@@ -4418,7 +4421,7 @@
         <v>28</v>
       </c>
       <c r="Q64" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R64" s="6" t="s">
         <v>41</v>
@@ -4468,7 +4471,7 @@
         <v>28</v>
       </c>
       <c r="N65" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O65" s="6" t="s">
         <v>41</v>
@@ -4477,7 +4480,7 @@
         <v>28</v>
       </c>
       <c r="Q65" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>41</v>
@@ -4527,7 +4530,7 @@
         <v>28</v>
       </c>
       <c r="N66" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>41</v>
@@ -4536,7 +4539,7 @@
         <v>28</v>
       </c>
       <c r="Q66" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>41</v>
@@ -4586,7 +4589,7 @@
         <v>28</v>
       </c>
       <c r="N67" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>41</v>
@@ -4595,7 +4598,7 @@
         <v>28</v>
       </c>
       <c r="Q67" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>41</v>
@@ -4645,7 +4648,7 @@
         <v>28</v>
       </c>
       <c r="N68" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>41</v>
@@ -4654,7 +4657,7 @@
         <v>28</v>
       </c>
       <c r="Q68" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>41</v>
@@ -4704,7 +4707,7 @@
         <v>28</v>
       </c>
       <c r="N69" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>41</v>
@@ -4713,7 +4716,7 @@
         <v>28</v>
       </c>
       <c r="Q69" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>41</v>
@@ -4763,7 +4766,7 @@
         <v>28</v>
       </c>
       <c r="N70" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>41</v>
@@ -4772,7 +4775,7 @@
         <v>28</v>
       </c>
       <c r="Q70" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>41</v>
@@ -4819,10 +4822,10 @@
         <v>116.7</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N71" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
@@ -4831,7 +4834,7 @@
         <v>28</v>
       </c>
       <c r="Q71" s="9">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>29</v>
@@ -4842,13 +4845,13 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>24</v>
@@ -4878,19 +4881,19 @@
         <v>600</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N72" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q72" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4901,7 +4904,7 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>97</v>
@@ -4937,19 +4940,19 @@
         <v>600</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N73" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q73" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4960,7 +4963,7 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>87</v>
@@ -4996,19 +4999,19 @@
         <v>620</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N74" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q74" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -5019,7 +5022,7 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>46</v>
@@ -5055,19 +5058,19 @@
         <v>630</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N75" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q75" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -5078,7 +5081,7 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>50</v>
@@ -5114,19 +5117,19 @@
         <v>630</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N76" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q76" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -5137,7 +5140,7 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>67</v>
@@ -5173,19 +5176,19 @@
         <v>630</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N77" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q77" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5196,10 +5199,10 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -5232,19 +5235,19 @@
         <v>630</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N78" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q78" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5255,10 +5258,10 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
@@ -5291,19 +5294,19 @@
         <v>630</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N79" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q79" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5314,7 +5317,7 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>64</v>
@@ -5350,19 +5353,19 @@
         <v>630</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N80" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q80" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5373,10 +5376,10 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5409,19 +5412,19 @@
         <v>630</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N81" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q81" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5432,10 +5435,10 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>139</v>
+        <v>104</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>24</v>
@@ -5468,19 +5471,19 @@
         <v>650</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N82" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q82" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5527,19 +5530,19 @@
         <v>650</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N83" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q83" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5553,10 +5556,10 @@
         <v>141</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>24</v>
@@ -5568,7 +5571,7 @@
         <v>26</v>
       </c>
       <c r="G84" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>27</v>
@@ -5586,19 +5589,19 @@
         <v>650</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N84" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q84" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5612,10 +5615,10 @@
         <v>142</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>52</v>
+        <v>108</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>24</v>
@@ -5627,7 +5630,7 @@
         <v>26</v>
       </c>
       <c r="G85" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>27</v>
@@ -5645,19 +5648,19 @@
         <v>650</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N85" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q85" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5671,7 +5674,7 @@
         <v>143</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>24</v>
@@ -5686,7 +5689,7 @@
         <v>26</v>
       </c>
       <c r="G86" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>27</v>
@@ -5704,19 +5707,19 @@
         <v>650</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N86" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q86" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5727,10 +5730,10 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>24</v>
@@ -5763,19 +5766,19 @@
         <v>670</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N87" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q87" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5786,7 +5789,7 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>73</v>
@@ -5822,19 +5825,19 @@
         <v>680</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N88" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q88" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5845,7 +5848,7 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>112</v>
@@ -5881,19 +5884,19 @@
         <v>680</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N89" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q89" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5904,10 +5907,10 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>24</v>
@@ -5940,19 +5943,19 @@
         <v>680</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N90" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q90" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5963,7 +5966,7 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>60</v>
@@ -5999,19 +6002,19 @@
         <v>680</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N91" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q91" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -6022,7 +6025,7 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>84</v>
@@ -6058,19 +6061,19 @@
         <v>680</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N92" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q92" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -6081,7 +6084,7 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>94</v>
@@ -6117,19 +6120,19 @@
         <v>680</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N93" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q93" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -6140,7 +6143,7 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>54</v>
@@ -6176,19 +6179,19 @@
         <v>680</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N94" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q94" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6199,7 +6202,7 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>77</v>
@@ -6235,19 +6238,19 @@
         <v>700</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N95" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q95" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6258,7 +6261,7 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>92</v>
@@ -6294,19 +6297,19 @@
         <v>700</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N96" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q96" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6317,7 +6320,7 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>56</v>
@@ -6353,19 +6356,19 @@
         <v>750</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N97" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q97" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6376,10 +6379,10 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>24</v>
@@ -6412,19 +6415,19 @@
         <v>800</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N98" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q98" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6435,7 +6438,7 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>81</v>
@@ -6471,19 +6474,19 @@
         <v>1200</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="N99" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>61</v>
+        <v>124</v>
       </c>
       <c r="Q99" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6494,13 +6497,13 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>24</v>
@@ -6533,7 +6536,7 @@
         <v>61</v>
       </c>
       <c r="N100" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
@@ -6542,7 +6545,7 @@
         <v>61</v>
       </c>
       <c r="Q100" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6553,7 +6556,7 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>97</v>
@@ -6592,7 +6595,7 @@
         <v>61</v>
       </c>
       <c r="N101" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
@@ -6601,7 +6604,7 @@
         <v>61</v>
       </c>
       <c r="Q101" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6612,7 +6615,7 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>87</v>
@@ -6651,7 +6654,7 @@
         <v>61</v>
       </c>
       <c r="N102" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
@@ -6660,7 +6663,7 @@
         <v>61</v>
       </c>
       <c r="Q102" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6671,10 +6674,10 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>24</v>
@@ -6710,7 +6713,7 @@
         <v>61</v>
       </c>
       <c r="N103" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
@@ -6719,7 +6722,7 @@
         <v>61</v>
       </c>
       <c r="Q103" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6730,10 +6733,10 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>132</v>
+        <v>50</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>24</v>
@@ -6748,7 +6751,7 @@
         <v>26</v>
       </c>
       <c r="G104" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>27</v>
@@ -6769,7 +6772,7 @@
         <v>61</v>
       </c>
       <c r="N104" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
@@ -6778,7 +6781,7 @@
         <v>61</v>
       </c>
       <c r="Q104" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6789,10 +6792,10 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>24</v>
@@ -6828,7 +6831,7 @@
         <v>61</v>
       </c>
       <c r="N105" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
@@ -6837,7 +6840,7 @@
         <v>61</v>
       </c>
       <c r="Q105" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6848,10 +6851,10 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>50</v>
+        <v>133</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>24</v>
@@ -6866,7 +6869,7 @@
         <v>26</v>
       </c>
       <c r="G106" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>27</v>
@@ -6887,7 +6890,7 @@
         <v>61</v>
       </c>
       <c r="N106" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
@@ -6896,7 +6899,7 @@
         <v>61</v>
       </c>
       <c r="Q106" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>
@@ -6907,7 +6910,7 @@
     </row>
     <row r="107">
       <c r="A107" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>67</v>
@@ -6946,7 +6949,7 @@
         <v>61</v>
       </c>
       <c r="N107" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>24</v>
@@ -6955,7 +6958,7 @@
         <v>61</v>
       </c>
       <c r="Q107" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>24</v>
@@ -6966,7 +6969,7 @@
     </row>
     <row r="108">
       <c r="A108" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>64</v>
@@ -7005,7 +7008,7 @@
         <v>61</v>
       </c>
       <c r="N108" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>24</v>
@@ -7014,7 +7017,7 @@
         <v>61</v>
       </c>
       <c r="Q108" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>24</v>
@@ -7025,7 +7028,7 @@
     </row>
     <row r="109">
       <c r="A109" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>104</v>
@@ -7064,7 +7067,7 @@
         <v>61</v>
       </c>
       <c r="N109" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>24</v>
@@ -7073,7 +7076,7 @@
         <v>61</v>
       </c>
       <c r="Q109" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R109" s="6" t="s">
         <v>24</v>
@@ -7084,7 +7087,7 @@
     </row>
     <row r="110">
       <c r="A110" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>108</v>
@@ -7123,7 +7126,7 @@
         <v>61</v>
       </c>
       <c r="N110" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>24</v>
@@ -7132,7 +7135,7 @@
         <v>61</v>
       </c>
       <c r="Q110" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R110" s="6" t="s">
         <v>24</v>
@@ -7143,7 +7146,7 @@
     </row>
     <row r="111">
       <c r="A111" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>52</v>
@@ -7182,7 +7185,7 @@
         <v>61</v>
       </c>
       <c r="N111" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>24</v>
@@ -7191,7 +7194,7 @@
         <v>61</v>
       </c>
       <c r="Q111" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R111" s="6" t="s">
         <v>24</v>
@@ -7202,7 +7205,7 @@
     </row>
     <row r="112">
       <c r="A112" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>69</v>
@@ -7241,7 +7244,7 @@
         <v>61</v>
       </c>
       <c r="N112" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>24</v>
@@ -7250,7 +7253,7 @@
         <v>61</v>
       </c>
       <c r="Q112" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R112" s="6" t="s">
         <v>24</v>
@@ -7261,10 +7264,10 @@
     </row>
     <row r="113">
       <c r="A113" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>24</v>
@@ -7300,7 +7303,7 @@
         <v>61</v>
       </c>
       <c r="N113" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>24</v>
@@ -7309,7 +7312,7 @@
         <v>61</v>
       </c>
       <c r="Q113" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R113" s="6" t="s">
         <v>24</v>
@@ -7320,10 +7323,10 @@
     </row>
     <row r="114">
       <c r="A114" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>24</v>
@@ -7359,7 +7362,7 @@
         <v>61</v>
       </c>
       <c r="N114" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>24</v>
@@ -7368,7 +7371,7 @@
         <v>61</v>
       </c>
       <c r="Q114" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R114" s="6" t="s">
         <v>24</v>
@@ -7379,7 +7382,7 @@
     </row>
     <row r="115">
       <c r="A115" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>73</v>
@@ -7418,7 +7421,7 @@
         <v>61</v>
       </c>
       <c r="N115" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O115" s="6" t="s">
         <v>24</v>
@@ -7427,7 +7430,7 @@
         <v>61</v>
       </c>
       <c r="Q115" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R115" s="6" t="s">
         <v>24</v>
@@ -7438,10 +7441,10 @@
     </row>
     <row r="116">
       <c r="A116" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>24</v>
@@ -7456,10 +7459,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I116" s="7">
         <v>46244</v>
@@ -7477,7 +7480,7 @@
         <v>61</v>
       </c>
       <c r="N116" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>24</v>
@@ -7486,7 +7489,7 @@
         <v>61</v>
       </c>
       <c r="Q116" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R116" s="6" t="s">
         <v>24</v>
@@ -7497,7 +7500,7 @@
     </row>
     <row r="117">
       <c r="A117" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>60</v>
@@ -7536,7 +7539,7 @@
         <v>61</v>
       </c>
       <c r="N117" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O117" s="6" t="s">
         <v>24</v>
@@ -7545,7 +7548,7 @@
         <v>61</v>
       </c>
       <c r="Q117" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R117" s="6" t="s">
         <v>24</v>
@@ -7556,7 +7559,7 @@
     </row>
     <row r="118">
       <c r="A118" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>94</v>
@@ -7595,7 +7598,7 @@
         <v>61</v>
       </c>
       <c r="N118" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>24</v>
@@ -7604,7 +7607,7 @@
         <v>61</v>
       </c>
       <c r="Q118" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R118" s="6" t="s">
         <v>24</v>
@@ -7615,7 +7618,7 @@
     </row>
     <row r="119">
       <c r="A119" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>84</v>
@@ -7654,7 +7657,7 @@
         <v>61</v>
       </c>
       <c r="N119" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O119" s="6" t="s">
         <v>24</v>
@@ -7663,7 +7666,7 @@
         <v>61</v>
       </c>
       <c r="Q119" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R119" s="6" t="s">
         <v>24</v>
@@ -7674,10 +7677,10 @@
     </row>
     <row r="120">
       <c r="A120" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>24</v>
@@ -7692,10 +7695,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="I120" s="7">
         <v>46244</v>
@@ -7713,7 +7716,7 @@
         <v>61</v>
       </c>
       <c r="N120" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>24</v>
@@ -7722,7 +7725,7 @@
         <v>61</v>
       </c>
       <c r="Q120" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R120" s="6" t="s">
         <v>24</v>
@@ -7733,10 +7736,10 @@
     </row>
     <row r="121">
       <c r="A121" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>24</v>
@@ -7772,7 +7775,7 @@
         <v>61</v>
       </c>
       <c r="N121" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O121" s="6" t="s">
         <v>24</v>
@@ -7781,7 +7784,7 @@
         <v>61</v>
       </c>
       <c r="Q121" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R121" s="6" t="s">
         <v>24</v>
@@ -7792,7 +7795,7 @@
     </row>
     <row r="122">
       <c r="A122" s="6" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>92</v>
@@ -7831,7 +7834,7 @@
         <v>61</v>
       </c>
       <c r="N122" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>24</v>
@@ -7840,7 +7843,7 @@
         <v>61</v>
       </c>
       <c r="Q122" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R122" s="6" t="s">
         <v>24</v>
@@ -7851,7 +7854,7 @@
     </row>
     <row r="123">
       <c r="A123" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>77</v>
@@ -7890,7 +7893,7 @@
         <v>61</v>
       </c>
       <c r="N123" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O123" s="6" t="s">
         <v>24</v>
@@ -7899,7 +7902,7 @@
         <v>61</v>
       </c>
       <c r="Q123" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R123" s="6" t="s">
         <v>24</v>
@@ -7910,7 +7913,7 @@
     </row>
     <row r="124">
       <c r="A124" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>56</v>
@@ -7949,7 +7952,7 @@
         <v>61</v>
       </c>
       <c r="N124" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>24</v>
@@ -7958,7 +7961,7 @@
         <v>61</v>
       </c>
       <c r="Q124" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R124" s="6" t="s">
         <v>24</v>
@@ -7969,10 +7972,10 @@
     </row>
     <row r="125">
       <c r="A125" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>24</v>
@@ -8008,7 +8011,7 @@
         <v>61</v>
       </c>
       <c r="N125" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O125" s="6" t="s">
         <v>24</v>
@@ -8017,7 +8020,7 @@
         <v>61</v>
       </c>
       <c r="Q125" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R125" s="6" t="s">
         <v>24</v>
@@ -8028,7 +8031,7 @@
     </row>
     <row r="126">
       <c r="A126" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>81</v>
@@ -8067,7 +8070,7 @@
         <v>61</v>
       </c>
       <c r="N126" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>24</v>
@@ -8076,7 +8079,7 @@
         <v>61</v>
       </c>
       <c r="Q126" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R126" s="6" t="s">
         <v>24</v>
@@ -8087,13 +8090,13 @@
     </row>
     <row r="127">
       <c r="A127" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>24</v>
@@ -8126,7 +8129,7 @@
         <v>61</v>
       </c>
       <c r="N127" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O127" s="6" t="s">
         <v>24</v>
@@ -8135,7 +8138,7 @@
         <v>61</v>
       </c>
       <c r="Q127" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R127" s="6" t="s">
         <v>24</v>
@@ -8146,7 +8149,7 @@
     </row>
     <row r="128">
       <c r="A128" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>97</v>
@@ -8185,7 +8188,7 @@
         <v>61</v>
       </c>
       <c r="N128" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>24</v>
@@ -8194,7 +8197,7 @@
         <v>61</v>
       </c>
       <c r="Q128" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R128" s="6" t="s">
         <v>24</v>
@@ -8205,7 +8208,7 @@
     </row>
     <row r="129">
       <c r="A129" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>87</v>
@@ -8244,7 +8247,7 @@
         <v>61</v>
       </c>
       <c r="N129" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O129" s="6" t="s">
         <v>24</v>
@@ -8253,7 +8256,7 @@
         <v>61</v>
       </c>
       <c r="Q129" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R129" s="6" t="s">
         <v>24</v>
@@ -8264,10 +8267,10 @@
     </row>
     <row r="130">
       <c r="A130" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>24</v>
@@ -8303,7 +8306,7 @@
         <v>61</v>
       </c>
       <c r="N130" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>24</v>
@@ -8312,7 +8315,7 @@
         <v>61</v>
       </c>
       <c r="Q130" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R130" s="6" t="s">
         <v>24</v>
@@ -8323,7 +8326,7 @@
     </row>
     <row r="131">
       <c r="A131" s="6" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>64</v>
@@ -8362,7 +8365,7 @@
         <v>61</v>
       </c>
       <c r="N131" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O131" s="6" t="s">
         <v>24</v>
@@ -8371,7 +8374,7 @@
         <v>61</v>
       </c>
       <c r="Q131" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R131" s="6" t="s">
         <v>24</v>
@@ -8382,7 +8385,7 @@
     </row>
     <row r="132">
       <c r="A132" s="6" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>67</v>
@@ -8421,7 +8424,7 @@
         <v>61</v>
       </c>
       <c r="N132" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>24</v>
@@ -8430,7 +8433,7 @@
         <v>61</v>
       </c>
       <c r="Q132" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R132" s="6" t="s">
         <v>24</v>
@@ -8441,7 +8444,7 @@
     </row>
     <row r="133">
       <c r="A133" s="6" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>50</v>
@@ -8480,7 +8483,7 @@
         <v>61</v>
       </c>
       <c r="N133" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O133" s="6" t="s">
         <v>24</v>
@@ -8489,7 +8492,7 @@
         <v>61</v>
       </c>
       <c r="Q133" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R133" s="6" t="s">
         <v>24</v>
@@ -8500,10 +8503,10 @@
     </row>
     <row r="134">
       <c r="A134" s="6" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>24</v>
@@ -8539,7 +8542,7 @@
         <v>61</v>
       </c>
       <c r="N134" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>24</v>
@@ -8548,7 +8551,7 @@
         <v>61</v>
       </c>
       <c r="Q134" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R134" s="6" t="s">
         <v>24</v>
@@ -8559,10 +8562,10 @@
     </row>
     <row r="135">
       <c r="A135" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>24</v>
@@ -8598,7 +8601,7 @@
         <v>61</v>
       </c>
       <c r="N135" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O135" s="6" t="s">
         <v>24</v>
@@ -8607,7 +8610,7 @@
         <v>61</v>
       </c>
       <c r="Q135" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R135" s="6" t="s">
         <v>24</v>
@@ -8618,10 +8621,10 @@
     </row>
     <row r="136">
       <c r="A136" s="6" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>24</v>
@@ -8657,7 +8660,7 @@
         <v>61</v>
       </c>
       <c r="N136" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>24</v>
@@ -8666,7 +8669,7 @@
         <v>61</v>
       </c>
       <c r="Q136" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R136" s="6" t="s">
         <v>24</v>
@@ -8677,7 +8680,7 @@
     </row>
     <row r="137">
       <c r="A137" s="6" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>104</v>
@@ -8716,7 +8719,7 @@
         <v>61</v>
       </c>
       <c r="N137" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O137" s="6" t="s">
         <v>24</v>
@@ -8725,7 +8728,7 @@
         <v>61</v>
       </c>
       <c r="Q137" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R137" s="6" t="s">
         <v>24</v>
@@ -8736,7 +8739,7 @@
     </row>
     <row r="138">
       <c r="A138" s="6" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>52</v>
@@ -8775,7 +8778,7 @@
         <v>61</v>
       </c>
       <c r="N138" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>24</v>
@@ -8784,7 +8787,7 @@
         <v>61</v>
       </c>
       <c r="Q138" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R138" s="6" t="s">
         <v>24</v>
@@ -8795,7 +8798,7 @@
     </row>
     <row r="139">
       <c r="A139" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>108</v>
@@ -8834,7 +8837,7 @@
         <v>61</v>
       </c>
       <c r="N139" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O139" s="6" t="s">
         <v>24</v>
@@ -8843,7 +8846,7 @@
         <v>61</v>
       </c>
       <c r="Q139" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R139" s="6" t="s">
         <v>24</v>
@@ -8854,7 +8857,7 @@
     </row>
     <row r="140">
       <c r="A140" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>69</v>
@@ -8893,7 +8896,7 @@
         <v>61</v>
       </c>
       <c r="N140" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>24</v>
@@ -8902,7 +8905,7 @@
         <v>61</v>
       </c>
       <c r="Q140" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R140" s="6" t="s">
         <v>24</v>
@@ -8913,10 +8916,10 @@
     </row>
     <row r="141">
       <c r="A141" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>24</v>
@@ -8952,7 +8955,7 @@
         <v>61</v>
       </c>
       <c r="N141" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O141" s="6" t="s">
         <v>24</v>
@@ -8961,7 +8964,7 @@
         <v>61</v>
       </c>
       <c r="Q141" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R141" s="6" t="s">
         <v>24</v>
@@ -8972,10 +8975,10 @@
     </row>
     <row r="142">
       <c r="A142" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>24</v>
@@ -9011,7 +9014,7 @@
         <v>61</v>
       </c>
       <c r="N142" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>24</v>
@@ -9020,7 +9023,7 @@
         <v>61</v>
       </c>
       <c r="Q142" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R142" s="6" t="s">
         <v>24</v>
@@ -9031,7 +9034,7 @@
     </row>
     <row r="143">
       <c r="A143" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>60</v>
@@ -9070,7 +9073,7 @@
         <v>61</v>
       </c>
       <c r="N143" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O143" s="6" t="s">
         <v>24</v>
@@ -9079,7 +9082,7 @@
         <v>61</v>
       </c>
       <c r="Q143" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R143" s="6" t="s">
         <v>24</v>
@@ -9090,7 +9093,7 @@
     </row>
     <row r="144">
       <c r="A144" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>112</v>
@@ -9129,7 +9132,7 @@
         <v>61</v>
       </c>
       <c r="N144" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>24</v>
@@ -9138,7 +9141,7 @@
         <v>61</v>
       </c>
       <c r="Q144" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R144" s="6" t="s">
         <v>24</v>
@@ -9149,7 +9152,7 @@
     </row>
     <row r="145">
       <c r="A145" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>94</v>
@@ -9188,7 +9191,7 @@
         <v>61</v>
       </c>
       <c r="N145" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O145" s="6" t="s">
         <v>24</v>
@@ -9197,7 +9200,7 @@
         <v>61</v>
       </c>
       <c r="Q145" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R145" s="6" t="s">
         <v>24</v>
@@ -9208,7 +9211,7 @@
     </row>
     <row r="146">
       <c r="A146" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>54</v>
@@ -9247,7 +9250,7 @@
         <v>61</v>
       </c>
       <c r="N146" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O146" s="6" t="s">
         <v>24</v>
@@ -9256,7 +9259,7 @@
         <v>61</v>
       </c>
       <c r="Q146" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R146" s="6" t="s">
         <v>24</v>
@@ -9267,7 +9270,7 @@
     </row>
     <row r="147">
       <c r="A147" s="6" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>73</v>
@@ -9306,7 +9309,7 @@
         <v>61</v>
       </c>
       <c r="N147" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O147" s="6" t="s">
         <v>24</v>
@@ -9315,7 +9318,7 @@
         <v>61</v>
       </c>
       <c r="Q147" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R147" s="6" t="s">
         <v>24</v>
@@ -9326,7 +9329,7 @@
     </row>
     <row r="148">
       <c r="A148" s="6" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>84</v>
@@ -9365,7 +9368,7 @@
         <v>61</v>
       </c>
       <c r="N148" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>24</v>
@@ -9374,7 +9377,7 @@
         <v>61</v>
       </c>
       <c r="Q148" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R148" s="6" t="s">
         <v>24</v>
@@ -9385,7 +9388,7 @@
     </row>
     <row r="149">
       <c r="A149" s="6" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>92</v>
@@ -9424,7 +9427,7 @@
         <v>61</v>
       </c>
       <c r="N149" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>24</v>
@@ -9433,7 +9436,7 @@
         <v>61</v>
       </c>
       <c r="Q149" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R149" s="6" t="s">
         <v>24</v>
@@ -9444,7 +9447,7 @@
     </row>
     <row r="150">
       <c r="A150" s="6" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>77</v>
@@ -9483,7 +9486,7 @@
         <v>61</v>
       </c>
       <c r="N150" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>24</v>
@@ -9492,7 +9495,7 @@
         <v>61</v>
       </c>
       <c r="Q150" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R150" s="6" t="s">
         <v>24</v>
@@ -9503,7 +9506,7 @@
     </row>
     <row r="151">
       <c r="A151" s="6" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>56</v>
@@ -9542,7 +9545,7 @@
         <v>61</v>
       </c>
       <c r="N151" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O151" s="6" t="s">
         <v>24</v>
@@ -9551,7 +9554,7 @@
         <v>61</v>
       </c>
       <c r="Q151" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R151" s="6" t="s">
         <v>24</v>
@@ -9562,10 +9565,10 @@
     </row>
     <row r="152">
       <c r="A152" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>24</v>
@@ -9601,7 +9604,7 @@
         <v>61</v>
       </c>
       <c r="N152" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>24</v>
@@ -9610,7 +9613,7 @@
         <v>61</v>
       </c>
       <c r="Q152" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R152" s="6" t="s">
         <v>24</v>
@@ -9621,7 +9624,7 @@
     </row>
     <row r="153">
       <c r="A153" s="6" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>81</v>
@@ -9660,7 +9663,7 @@
         <v>61</v>
       </c>
       <c r="N153" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O153" s="6" t="s">
         <v>24</v>
@@ -9669,7 +9672,7 @@
         <v>61</v>
       </c>
       <c r="Q153" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R153" s="6" t="s">
         <v>24</v>
@@ -9680,7 +9683,7 @@
     </row>
     <row r="154">
       <c r="A154" s="6" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>69</v>
@@ -9719,7 +9722,7 @@
         <v>61</v>
       </c>
       <c r="N154" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>24</v>
@@ -9728,7 +9731,7 @@
         <v>61</v>
       </c>
       <c r="Q154" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R154" s="6" t="s">
         <v>24</v>
@@ -9739,10 +9742,10 @@
     </row>
     <row r="155">
       <c r="A155" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>24</v>
@@ -9778,7 +9781,7 @@
         <v>61</v>
       </c>
       <c r="N155" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O155" s="6" t="s">
         <v>24</v>
@@ -9787,7 +9790,7 @@
         <v>61</v>
       </c>
       <c r="Q155" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R155" s="6" t="s">
         <v>24</v>
@@ -9798,7 +9801,7 @@
     </row>
     <row r="156">
       <c r="A156" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>108</v>
@@ -9837,7 +9840,7 @@
         <v>61</v>
       </c>
       <c r="N156" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O156" s="6" t="s">
         <v>24</v>
@@ -9846,7 +9849,7 @@
         <v>61</v>
       </c>
       <c r="Q156" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R156" s="6" t="s">
         <v>24</v>
@@ -9857,10 +9860,10 @@
     </row>
     <row r="157">
       <c r="A157" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>24</v>
@@ -9896,7 +9899,7 @@
         <v>61</v>
       </c>
       <c r="N157" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O157" s="6" t="s">
         <v>24</v>
@@ -9905,7 +9908,7 @@
         <v>61</v>
       </c>
       <c r="Q157" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R157" s="6" t="s">
         <v>24</v>
@@ -9916,7 +9919,7 @@
     </row>
     <row r="158">
       <c r="A158" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>92</v>
@@ -9955,7 +9958,7 @@
         <v>61</v>
       </c>
       <c r="N158" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O158" s="6" t="s">
         <v>24</v>
@@ -9964,7 +9967,7 @@
         <v>61</v>
       </c>
       <c r="Q158" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R158" s="6" t="s">
         <v>24</v>
@@ -9975,10 +9978,10 @@
     </row>
     <row r="159">
       <c r="A159" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>24</v>
@@ -10014,7 +10017,7 @@
         <v>61</v>
       </c>
       <c r="N159" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O159" s="6" t="s">
         <v>24</v>
@@ -10023,7 +10026,7 @@
         <v>61</v>
       </c>
       <c r="Q159" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R159" s="6" t="s">
         <v>24</v>
@@ -10073,7 +10076,7 @@
         <v>61</v>
       </c>
       <c r="N160" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>24</v>
@@ -10082,7 +10085,7 @@
         <v>61</v>
       </c>
       <c r="Q160" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R160" s="6" t="s">
         <v>24</v>
@@ -10093,10 +10096,10 @@
     </row>
     <row r="161">
       <c r="A161" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>24</v>
@@ -10132,7 +10135,7 @@
         <v>61</v>
       </c>
       <c r="N161" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O161" s="6" t="s">
         <v>24</v>
@@ -10141,7 +10144,7 @@
         <v>61</v>
       </c>
       <c r="Q161" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R161" s="6" t="s">
         <v>24</v>
@@ -10152,7 +10155,7 @@
     </row>
     <row r="162">
       <c r="A162" s="6" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>108</v>
@@ -10191,7 +10194,7 @@
         <v>61</v>
       </c>
       <c r="N162" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>24</v>
@@ -10200,7 +10203,7 @@
         <v>61</v>
       </c>
       <c r="Q162" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R162" s="6" t="s">
         <v>24</v>
@@ -10211,10 +10214,10 @@
     </row>
     <row r="163">
       <c r="A163" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>24</v>
@@ -10250,7 +10253,7 @@
         <v>61</v>
       </c>
       <c r="N163" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O163" s="6" t="s">
         <v>24</v>
@@ -10259,7 +10262,7 @@
         <v>61</v>
       </c>
       <c r="Q163" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R163" s="6" t="s">
         <v>24</v>
@@ -10270,10 +10273,10 @@
     </row>
     <row r="164">
       <c r="A164" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>24</v>
@@ -10309,7 +10312,7 @@
         <v>61</v>
       </c>
       <c r="N164" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="O164" s="6" t="s">
         <v>24</v>
@@ -10318,7 +10321,7 @@
         <v>61</v>
       </c>
       <c r="Q164" s="9">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="R164" s="6" t="s">
         <v>24</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="224">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em segunda-feira, 3 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em terça-feira, 4 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -361,21 +361,21 @@
     <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
   </si>
   <si>
+    <t>FA-12017</t>
+  </si>
+  <si>
+    <t>FA-12030</t>
+  </si>
+  <si>
+    <t>FA-11992</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
     <t>FA-11962</t>
   </si>
   <si>
-    <t>FA-12030</t>
-  </si>
-  <si>
-    <t>FA-11992</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12017</t>
-  </si>
-  <si>
     <t>FA-12019</t>
   </si>
   <si>
@@ -406,9 +406,6 @@
     <t>FA-11903</t>
   </si>
   <si>
-    <t>HOJE</t>
-  </si>
-  <si>
     <t>FA-11977</t>
   </si>
   <si>
@@ -451,24 +448,24 @@
     <t>ANA FLORIPES CARVALHO DA CUNHA</t>
   </si>
   <si>
+    <t>FA-12062</t>
+  </si>
+  <si>
+    <t>WILSON COUTINHO BEZERRA</t>
+  </si>
+  <si>
+    <t>FA-11858</t>
+  </si>
+  <si>
     <t>FA-12049</t>
   </si>
   <si>
-    <t>FA-11858</t>
-  </si>
-  <si>
     <t>FA-11976</t>
   </si>
   <si>
     <t>FA-11921</t>
   </si>
   <si>
-    <t>FA-12062</t>
-  </si>
-  <si>
-    <t>WILSON COUTINHO BEZERRA</t>
-  </si>
-  <si>
     <t>FA-12036</t>
   </si>
   <si>
@@ -529,21 +526,21 @@
     <t>FA-12053</t>
   </si>
   <si>
+    <t>FA-12000</t>
+  </si>
+  <si>
+    <t>FA-11979</t>
+  </si>
+  <si>
     <t>FA-12037</t>
   </si>
   <si>
     <t>FA-11982</t>
   </si>
   <si>
-    <t>FA-12000</t>
-  </si>
-  <si>
     <t>FA-12001</t>
   </si>
   <si>
-    <t>FA-11979</t>
-  </si>
-  <si>
     <t>FA-12054</t>
   </si>
   <si>
@@ -565,19 +562,19 @@
     <t>FA-11964</t>
   </si>
   <si>
+    <t>FA-12024</t>
+  </si>
+  <si>
+    <t>FA-12025</t>
+  </si>
+  <si>
+    <t>FA-12033</t>
+  </si>
+  <si>
+    <t>FA-12038</t>
+  </si>
+  <si>
     <t>FA-12002</t>
-  </si>
-  <si>
-    <t>FA-12025</t>
-  </si>
-  <si>
-    <t>FA-12033</t>
-  </si>
-  <si>
-    <t>FA-12038</t>
-  </si>
-  <si>
-    <t>FA-12024</t>
   </si>
   <si>
     <t>FA-11934</t>
@@ -990,7 +987,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-63</v>
+        <v>-64</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -999,7 +996,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-63</v>
+        <v>-64</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -1049,7 +1046,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -1058,7 +1055,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
@@ -1108,7 +1105,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -1117,7 +1114,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -1167,7 +1164,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -1176,7 +1173,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1226,7 +1223,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -1235,7 +1232,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -1285,7 +1282,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>29</v>
@@ -1294,7 +1291,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>29</v>
@@ -1344,7 +1341,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>29</v>
@@ -1353,7 +1350,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-77</v>
+        <v>-78</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>29</v>
@@ -1403,7 +1400,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>29</v>
@@ -1412,7 +1409,7 @@
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-70</v>
+        <v>-71</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>29</v>
@@ -1462,7 +1459,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>41</v>
@@ -1471,7 +1468,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>41</v>
@@ -1521,7 +1518,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>41</v>
@@ -1530,7 +1527,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>41</v>
@@ -1580,7 +1577,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>41</v>
@@ -1589,7 +1586,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>41</v>
@@ -1639,7 +1636,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>41</v>
@@ -1648,7 +1645,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>29</v>
@@ -1698,7 +1695,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>41</v>
@@ -1707,7 +1704,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>41</v>
@@ -1757,7 +1754,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>41</v>
@@ -1766,7 +1763,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>41</v>
@@ -1816,7 +1813,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>41</v>
@@ -1825,7 +1822,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>41</v>
@@ -1875,7 +1872,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>41</v>
@@ -1884,7 +1881,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>41</v>
@@ -1934,7 +1931,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>41</v>
@@ -1943,7 +1940,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>41</v>
@@ -1993,7 +1990,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>41</v>
@@ -2002,7 +1999,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>41</v>
@@ -2052,7 +2049,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>41</v>
@@ -2061,7 +2058,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>41</v>
@@ -2111,7 +2108,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>41</v>
@@ -2120,7 +2117,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>41</v>
@@ -2170,7 +2167,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>41</v>
@@ -2179,7 +2176,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>41</v>
@@ -2229,7 +2226,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>41</v>
@@ -2238,7 +2235,7 @@
         <v>61</v>
       </c>
       <c r="Q27" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>24</v>
@@ -2288,7 +2285,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>41</v>
@@ -2297,7 +2294,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>41</v>
@@ -2347,7 +2344,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>41</v>
@@ -2356,7 +2353,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>41</v>
@@ -2406,7 +2403,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>41</v>
@@ -2415,7 +2412,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>41</v>
@@ -2465,7 +2462,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>41</v>
@@ -2474,7 +2471,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>41</v>
@@ -2524,7 +2521,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>41</v>
@@ -2533,7 +2530,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>41</v>
@@ -2583,7 +2580,7 @@
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>41</v>
@@ -2592,7 +2589,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>41</v>
@@ -2642,7 +2639,7 @@
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>41</v>
@@ -2651,7 +2648,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>41</v>
@@ -2701,7 +2698,7 @@
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>41</v>
@@ -2710,7 +2707,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>41</v>
@@ -2760,7 +2757,7 @@
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>41</v>
@@ -2769,7 +2766,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>41</v>
@@ -2819,7 +2816,7 @@
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>41</v>
@@ -2828,7 +2825,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>41</v>
@@ -2878,7 +2875,7 @@
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>41</v>
@@ -2887,7 +2884,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>41</v>
@@ -2937,7 +2934,7 @@
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>41</v>
@@ -2946,7 +2943,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>41</v>
@@ -2996,7 +2993,7 @@
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>41</v>
@@ -3005,7 +3002,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>41</v>
@@ -3055,7 +3052,7 @@
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>41</v>
@@ -3064,7 +3061,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>41</v>
@@ -3114,7 +3111,7 @@
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>41</v>
@@ -3123,7 +3120,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>41</v>
@@ -3173,7 +3170,7 @@
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>41</v>
@@ -3182,7 +3179,7 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>41</v>
@@ -3232,7 +3229,7 @@
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>41</v>
@@ -3241,7 +3238,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>41</v>
@@ -3291,7 +3288,7 @@
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>41</v>
@@ -3300,7 +3297,7 @@
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>29</v>
@@ -3350,7 +3347,7 @@
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>41</v>
@@ -3359,7 +3356,7 @@
         <v>61</v>
       </c>
       <c r="Q46" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>24</v>
@@ -3409,7 +3406,7 @@
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>41</v>
@@ -3418,7 +3415,7 @@
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>41</v>
@@ -3468,7 +3465,7 @@
         <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>41</v>
@@ -3477,7 +3474,7 @@
         <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>41</v>
@@ -3527,7 +3524,7 @@
         <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>41</v>
@@ -3536,7 +3533,7 @@
         <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>41</v>
@@ -3586,7 +3583,7 @@
         <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>41</v>
@@ -3595,7 +3592,7 @@
         <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>41</v>
@@ -3645,7 +3642,7 @@
         <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O51" s="6" t="s">
         <v>41</v>
@@ -3654,7 +3651,7 @@
         <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>41</v>
@@ -3704,7 +3701,7 @@
         <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>41</v>
@@ -3713,7 +3710,7 @@
         <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>41</v>
@@ -3763,7 +3760,7 @@
         <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>41</v>
@@ -3772,7 +3769,7 @@
         <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>41</v>
@@ -3822,7 +3819,7 @@
         <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>41</v>
@@ -3831,7 +3828,7 @@
         <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>41</v>
@@ -3881,7 +3878,7 @@
         <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>41</v>
@@ -3890,7 +3887,7 @@
         <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>41</v>
@@ -3940,7 +3937,7 @@
         <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>41</v>
@@ -3949,7 +3946,7 @@
         <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>41</v>
@@ -3999,7 +3996,7 @@
         <v>28</v>
       </c>
       <c r="N57" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O57" s="6" t="s">
         <v>41</v>
@@ -4008,7 +4005,7 @@
         <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>41</v>
@@ -4058,7 +4055,7 @@
         <v>28</v>
       </c>
       <c r="N58" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>41</v>
@@ -4067,7 +4064,7 @@
         <v>28</v>
       </c>
       <c r="Q58" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>41</v>
@@ -4081,7 +4078,7 @@
         <v>109</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>24</v>
@@ -4096,10 +4093,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="I59" s="7">
         <v>46230</v>
@@ -4117,7 +4114,7 @@
         <v>28</v>
       </c>
       <c r="N59" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O59" s="6" t="s">
         <v>41</v>
@@ -4126,7 +4123,7 @@
         <v>28</v>
       </c>
       <c r="Q59" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>41</v>
@@ -4176,7 +4173,7 @@
         <v>28</v>
       </c>
       <c r="N60" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>41</v>
@@ -4185,7 +4182,7 @@
         <v>28</v>
       </c>
       <c r="Q60" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>41</v>
@@ -4235,7 +4232,7 @@
         <v>28</v>
       </c>
       <c r="N61" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O61" s="6" t="s">
         <v>41</v>
@@ -4244,7 +4241,7 @@
         <v>28</v>
       </c>
       <c r="Q61" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>41</v>
@@ -4258,7 +4255,7 @@
         <v>113</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4273,10 +4270,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I62" s="7">
         <v>46230</v>
@@ -4294,7 +4291,7 @@
         <v>28</v>
       </c>
       <c r="N62" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>41</v>
@@ -4303,7 +4300,7 @@
         <v>28</v>
       </c>
       <c r="Q62" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>41</v>
@@ -4353,7 +4350,7 @@
         <v>28</v>
       </c>
       <c r="N63" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O63" s="6" t="s">
         <v>41</v>
@@ -4362,7 +4359,7 @@
         <v>28</v>
       </c>
       <c r="Q63" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>41</v>
@@ -4412,7 +4409,7 @@
         <v>28</v>
       </c>
       <c r="N64" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>41</v>
@@ -4421,7 +4418,7 @@
         <v>28</v>
       </c>
       <c r="Q64" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R64" s="6" t="s">
         <v>41</v>
@@ -4471,7 +4468,7 @@
         <v>28</v>
       </c>
       <c r="N65" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O65" s="6" t="s">
         <v>41</v>
@@ -4480,7 +4477,7 @@
         <v>28</v>
       </c>
       <c r="Q65" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>41</v>
@@ -4530,7 +4527,7 @@
         <v>28</v>
       </c>
       <c r="N66" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>41</v>
@@ -4539,7 +4536,7 @@
         <v>28</v>
       </c>
       <c r="Q66" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>41</v>
@@ -4589,7 +4586,7 @@
         <v>28</v>
       </c>
       <c r="N67" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>41</v>
@@ -4598,7 +4595,7 @@
         <v>28</v>
       </c>
       <c r="Q67" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>41</v>
@@ -4648,7 +4645,7 @@
         <v>28</v>
       </c>
       <c r="N68" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>41</v>
@@ -4657,7 +4654,7 @@
         <v>28</v>
       </c>
       <c r="Q68" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>41</v>
@@ -4707,7 +4704,7 @@
         <v>28</v>
       </c>
       <c r="N69" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>41</v>
@@ -4716,7 +4713,7 @@
         <v>28</v>
       </c>
       <c r="Q69" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>41</v>
@@ -4766,7 +4763,7 @@
         <v>28</v>
       </c>
       <c r="N70" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>41</v>
@@ -4775,7 +4772,7 @@
         <v>28</v>
       </c>
       <c r="Q70" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>41</v>
@@ -4822,19 +4819,19 @@
         <v>116.7</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N71" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P71" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q71" s="9">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>29</v>
@@ -4845,13 +4842,13 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B72" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="C72" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>24</v>
@@ -4881,22 +4878,22 @@
         <v>600</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N72" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q72" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S72" s="6" t="s">
         <v>24</v>
@@ -4904,7 +4901,7 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>97</v>
@@ -4940,22 +4937,22 @@
         <v>600</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N73" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q73" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S73" s="6" t="s">
         <v>24</v>
@@ -4963,7 +4960,7 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>87</v>
@@ -4999,22 +4996,22 @@
         <v>620</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N74" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q74" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S74" s="6" t="s">
         <v>24</v>
@@ -5022,7 +5019,7 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>46</v>
@@ -5058,22 +5055,22 @@
         <v>630</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N75" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O75" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q75" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R75" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S75" s="6" t="s">
         <v>24</v>
@@ -5081,7 +5078,7 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>50</v>
@@ -5117,22 +5114,22 @@
         <v>630</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N76" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q76" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R76" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S76" s="6" t="s">
         <v>24</v>
@@ -5140,7 +5137,7 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>67</v>
@@ -5176,22 +5173,22 @@
         <v>630</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N77" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O77" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q77" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R77" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S77" s="6" t="s">
         <v>24</v>
@@ -5199,10 +5196,10 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -5235,22 +5232,22 @@
         <v>630</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N78" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q78" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R78" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S78" s="6" t="s">
         <v>24</v>
@@ -5258,10 +5255,10 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B79" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
@@ -5294,22 +5291,22 @@
         <v>630</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N79" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O79" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q79" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R79" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S79" s="6" t="s">
         <v>24</v>
@@ -5317,7 +5314,7 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>64</v>
@@ -5353,22 +5350,22 @@
         <v>630</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N80" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q80" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R80" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S80" s="6" t="s">
         <v>24</v>
@@ -5376,10 +5373,10 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B81" s="6" t="s">
         <v>137</v>
-      </c>
-      <c r="B81" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5412,22 +5409,22 @@
         <v>630</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N81" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O81" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q81" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S81" s="6" t="s">
         <v>24</v>
@@ -5435,10 +5432,10 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>24</v>
@@ -5471,22 +5468,22 @@
         <v>650</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N82" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q82" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R82" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S82" s="6" t="s">
         <v>24</v>
@@ -5530,22 +5527,22 @@
         <v>650</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N83" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O83" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q83" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R83" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S83" s="6" t="s">
         <v>24</v>
@@ -5556,10 +5553,10 @@
         <v>141</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>24</v>
@@ -5571,7 +5568,7 @@
         <v>26</v>
       </c>
       <c r="G84" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H84" s="6" t="s">
         <v>27</v>
@@ -5589,22 +5586,22 @@
         <v>650</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N84" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q84" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R84" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S84" s="6" t="s">
         <v>24</v>
@@ -5615,10 +5612,10 @@
         <v>142</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>24</v>
@@ -5630,7 +5627,7 @@
         <v>26</v>
       </c>
       <c r="G85" s="7">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>27</v>
@@ -5648,22 +5645,22 @@
         <v>650</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N85" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O85" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q85" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R85" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S85" s="6" t="s">
         <v>24</v>
@@ -5674,7 +5671,7 @@
         <v>143</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>24</v>
@@ -5689,7 +5686,7 @@
         <v>26</v>
       </c>
       <c r="G86" s="7">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>27</v>
@@ -5707,22 +5704,22 @@
         <v>650</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N86" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q86" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R86" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S86" s="6" t="s">
         <v>24</v>
@@ -5730,10 +5727,10 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B87" s="6" t="s">
         <v>145</v>
-      </c>
-      <c r="B87" s="6" t="s">
-        <v>146</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>24</v>
@@ -5766,22 +5763,22 @@
         <v>670</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N87" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O87" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q87" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R87" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S87" s="6" t="s">
         <v>24</v>
@@ -5789,7 +5786,7 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>73</v>
@@ -5825,22 +5822,22 @@
         <v>680</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N88" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q88" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R88" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S88" s="6" t="s">
         <v>24</v>
@@ -5848,7 +5845,7 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>112</v>
@@ -5884,22 +5881,22 @@
         <v>680</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N89" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O89" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q89" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R89" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S89" s="6" t="s">
         <v>24</v>
@@ -5907,10 +5904,10 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B90" s="6" t="s">
         <v>149</v>
-      </c>
-      <c r="B90" s="6" t="s">
-        <v>150</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>24</v>
@@ -5943,22 +5940,22 @@
         <v>680</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N90" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q90" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R90" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S90" s="6" t="s">
         <v>24</v>
@@ -5966,7 +5963,7 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>60</v>
@@ -6002,22 +5999,22 @@
         <v>680</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N91" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O91" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q91" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R91" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S91" s="6" t="s">
         <v>24</v>
@@ -6025,7 +6022,7 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>84</v>
@@ -6061,22 +6058,22 @@
         <v>680</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N92" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q92" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R92" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S92" s="6" t="s">
         <v>24</v>
@@ -6084,7 +6081,7 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>94</v>
@@ -6120,22 +6117,22 @@
         <v>680</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N93" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O93" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q93" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R93" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S93" s="6" t="s">
         <v>24</v>
@@ -6143,7 +6140,7 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>54</v>
@@ -6179,22 +6176,22 @@
         <v>680</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N94" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q94" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R94" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S94" s="6" t="s">
         <v>24</v>
@@ -6202,7 +6199,7 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>77</v>
@@ -6238,22 +6235,22 @@
         <v>700</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N95" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O95" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q95" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R95" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S95" s="6" t="s">
         <v>24</v>
@@ -6261,7 +6258,7 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>92</v>
@@ -6297,22 +6294,22 @@
         <v>700</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N96" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q96" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R96" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S96" s="6" t="s">
         <v>24</v>
@@ -6320,7 +6317,7 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>56</v>
@@ -6356,22 +6353,22 @@
         <v>750</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N97" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O97" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q97" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R97" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S97" s="6" t="s">
         <v>24</v>
@@ -6379,10 +6376,10 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B98" s="6" t="s">
         <v>158</v>
-      </c>
-      <c r="B98" s="6" t="s">
-        <v>159</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>24</v>
@@ -6415,22 +6412,22 @@
         <v>800</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N98" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q98" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R98" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S98" s="6" t="s">
         <v>24</v>
@@ -6438,7 +6435,7 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>81</v>
@@ -6474,22 +6471,22 @@
         <v>1200</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="N99" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O99" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>124</v>
+        <v>28</v>
       </c>
       <c r="Q99" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="S99" s="6" t="s">
         <v>24</v>
@@ -6497,13 +6494,13 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>24</v>
@@ -6536,7 +6533,7 @@
         <v>61</v>
       </c>
       <c r="N100" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
@@ -6545,7 +6542,7 @@
         <v>61</v>
       </c>
       <c r="Q100" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6556,7 +6553,7 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>97</v>
@@ -6595,7 +6592,7 @@
         <v>61</v>
       </c>
       <c r="N101" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
@@ -6604,7 +6601,7 @@
         <v>61</v>
       </c>
       <c r="Q101" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6615,7 +6612,7 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>87</v>
@@ -6654,7 +6651,7 @@
         <v>61</v>
       </c>
       <c r="N102" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
@@ -6663,7 +6660,7 @@
         <v>61</v>
       </c>
       <c r="Q102" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6674,10 +6671,10 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>24</v>
@@ -6713,7 +6710,7 @@
         <v>61</v>
       </c>
       <c r="N103" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
@@ -6722,7 +6719,7 @@
         <v>61</v>
       </c>
       <c r="Q103" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6733,10 +6730,10 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>24</v>
@@ -6751,7 +6748,7 @@
         <v>26</v>
       </c>
       <c r="G104" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>27</v>
@@ -6772,7 +6769,7 @@
         <v>61</v>
       </c>
       <c r="N104" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
@@ -6781,7 +6778,7 @@
         <v>61</v>
       </c>
       <c r="Q104" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6792,10 +6789,10 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>138</v>
+        <v>64</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>24</v>
@@ -6831,7 +6828,7 @@
         <v>61</v>
       </c>
       <c r="N105" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
@@ -6840,7 +6837,7 @@
         <v>61</v>
       </c>
       <c r="Q105" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6851,10 +6848,10 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>133</v>
+        <v>50</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>24</v>
@@ -6869,7 +6866,7 @@
         <v>26</v>
       </c>
       <c r="G106" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>27</v>
@@ -6890,7 +6887,7 @@
         <v>61</v>
       </c>
       <c r="N106" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
@@ -6899,7 +6896,7 @@
         <v>61</v>
       </c>
       <c r="Q106" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>
@@ -6910,10 +6907,10 @@
     </row>
     <row r="107">
       <c r="A107" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>24</v>
@@ -6949,7 +6946,7 @@
         <v>61</v>
       </c>
       <c r="N107" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>24</v>
@@ -6958,7 +6955,7 @@
         <v>61</v>
       </c>
       <c r="Q107" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>24</v>
@@ -6969,10 +6966,10 @@
     </row>
     <row r="108">
       <c r="A108" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>24</v>
@@ -7008,7 +7005,7 @@
         <v>61</v>
       </c>
       <c r="N108" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>24</v>
@@ -7017,7 +7014,7 @@
         <v>61</v>
       </c>
       <c r="Q108" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>24</v>
@@ -7028,7 +7025,7 @@
     </row>
     <row r="109">
       <c r="A109" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>104</v>
@@ -7067,7 +7064,7 @@
         <v>61</v>
       </c>
       <c r="N109" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>24</v>
@@ -7076,7 +7073,7 @@
         <v>61</v>
       </c>
       <c r="Q109" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R109" s="6" t="s">
         <v>24</v>
@@ -7087,7 +7084,7 @@
     </row>
     <row r="110">
       <c r="A110" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>108</v>
@@ -7126,7 +7123,7 @@
         <v>61</v>
       </c>
       <c r="N110" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>24</v>
@@ -7135,7 +7132,7 @@
         <v>61</v>
       </c>
       <c r="Q110" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R110" s="6" t="s">
         <v>24</v>
@@ -7146,7 +7143,7 @@
     </row>
     <row r="111">
       <c r="A111" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>52</v>
@@ -7185,7 +7182,7 @@
         <v>61</v>
       </c>
       <c r="N111" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>24</v>
@@ -7194,7 +7191,7 @@
         <v>61</v>
       </c>
       <c r="Q111" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R111" s="6" t="s">
         <v>24</v>
@@ -7205,7 +7202,7 @@
     </row>
     <row r="112">
       <c r="A112" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>69</v>
@@ -7244,7 +7241,7 @@
         <v>61</v>
       </c>
       <c r="N112" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>24</v>
@@ -7253,7 +7250,7 @@
         <v>61</v>
       </c>
       <c r="Q112" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R112" s="6" t="s">
         <v>24</v>
@@ -7264,10 +7261,10 @@
     </row>
     <row r="113">
       <c r="A113" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>24</v>
@@ -7303,7 +7300,7 @@
         <v>61</v>
       </c>
       <c r="N113" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>24</v>
@@ -7312,7 +7309,7 @@
         <v>61</v>
       </c>
       <c r="Q113" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R113" s="6" t="s">
         <v>24</v>
@@ -7323,10 +7320,10 @@
     </row>
     <row r="114">
       <c r="A114" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>24</v>
@@ -7362,7 +7359,7 @@
         <v>61</v>
       </c>
       <c r="N114" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>24</v>
@@ -7371,7 +7368,7 @@
         <v>61</v>
       </c>
       <c r="Q114" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R114" s="6" t="s">
         <v>24</v>
@@ -7382,7 +7379,7 @@
     </row>
     <row r="115">
       <c r="A115" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>73</v>
@@ -7421,7 +7418,7 @@
         <v>61</v>
       </c>
       <c r="N115" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O115" s="6" t="s">
         <v>24</v>
@@ -7430,7 +7427,7 @@
         <v>61</v>
       </c>
       <c r="Q115" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R115" s="6" t="s">
         <v>24</v>
@@ -7441,10 +7438,10 @@
     </row>
     <row r="116">
       <c r="A116" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>24</v>
@@ -7459,10 +7456,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="I116" s="7">
         <v>46244</v>
@@ -7480,7 +7477,7 @@
         <v>61</v>
       </c>
       <c r="N116" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>24</v>
@@ -7489,7 +7486,7 @@
         <v>61</v>
       </c>
       <c r="Q116" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R116" s="6" t="s">
         <v>24</v>
@@ -7500,7 +7497,7 @@
     </row>
     <row r="117">
       <c r="A117" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>60</v>
@@ -7539,7 +7536,7 @@
         <v>61</v>
       </c>
       <c r="N117" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O117" s="6" t="s">
         <v>24</v>
@@ -7548,7 +7545,7 @@
         <v>61</v>
       </c>
       <c r="Q117" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R117" s="6" t="s">
         <v>24</v>
@@ -7559,7 +7556,7 @@
     </row>
     <row r="118">
       <c r="A118" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>94</v>
@@ -7598,7 +7595,7 @@
         <v>61</v>
       </c>
       <c r="N118" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>24</v>
@@ -7607,7 +7604,7 @@
         <v>61</v>
       </c>
       <c r="Q118" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R118" s="6" t="s">
         <v>24</v>
@@ -7618,7 +7615,7 @@
     </row>
     <row r="119">
       <c r="A119" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>84</v>
@@ -7657,7 +7654,7 @@
         <v>61</v>
       </c>
       <c r="N119" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O119" s="6" t="s">
         <v>24</v>
@@ -7666,7 +7663,7 @@
         <v>61</v>
       </c>
       <c r="Q119" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R119" s="6" t="s">
         <v>24</v>
@@ -7677,10 +7674,10 @@
     </row>
     <row r="120">
       <c r="A120" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>54</v>
+        <v>112</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>24</v>
@@ -7695,10 +7692,10 @@
         <v>26</v>
       </c>
       <c r="G120" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I120" s="7">
         <v>46244</v>
@@ -7716,7 +7713,7 @@
         <v>61</v>
       </c>
       <c r="N120" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>24</v>
@@ -7725,7 +7722,7 @@
         <v>61</v>
       </c>
       <c r="Q120" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R120" s="6" t="s">
         <v>24</v>
@@ -7736,10 +7733,10 @@
     </row>
     <row r="121">
       <c r="A121" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>24</v>
@@ -7775,7 +7772,7 @@
         <v>61</v>
       </c>
       <c r="N121" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O121" s="6" t="s">
         <v>24</v>
@@ -7784,7 +7781,7 @@
         <v>61</v>
       </c>
       <c r="Q121" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R121" s="6" t="s">
         <v>24</v>
@@ -7795,7 +7792,7 @@
     </row>
     <row r="122">
       <c r="A122" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>92</v>
@@ -7834,7 +7831,7 @@
         <v>61</v>
       </c>
       <c r="N122" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>24</v>
@@ -7843,7 +7840,7 @@
         <v>61</v>
       </c>
       <c r="Q122" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R122" s="6" t="s">
         <v>24</v>
@@ -7854,7 +7851,7 @@
     </row>
     <row r="123">
       <c r="A123" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>77</v>
@@ -7893,7 +7890,7 @@
         <v>61</v>
       </c>
       <c r="N123" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O123" s="6" t="s">
         <v>24</v>
@@ -7902,7 +7899,7 @@
         <v>61</v>
       </c>
       <c r="Q123" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R123" s="6" t="s">
         <v>24</v>
@@ -7913,7 +7910,7 @@
     </row>
     <row r="124">
       <c r="A124" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>56</v>
@@ -7952,7 +7949,7 @@
         <v>61</v>
       </c>
       <c r="N124" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>24</v>
@@ -7961,7 +7958,7 @@
         <v>61</v>
       </c>
       <c r="Q124" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R124" s="6" t="s">
         <v>24</v>
@@ -7972,10 +7969,10 @@
     </row>
     <row r="125">
       <c r="A125" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>24</v>
@@ -8011,7 +8008,7 @@
         <v>61</v>
       </c>
       <c r="N125" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O125" s="6" t="s">
         <v>24</v>
@@ -8020,7 +8017,7 @@
         <v>61</v>
       </c>
       <c r="Q125" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R125" s="6" t="s">
         <v>24</v>
@@ -8031,7 +8028,7 @@
     </row>
     <row r="126">
       <c r="A126" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>81</v>
@@ -8070,7 +8067,7 @@
         <v>61</v>
       </c>
       <c r="N126" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>24</v>
@@ -8079,7 +8076,7 @@
         <v>61</v>
       </c>
       <c r="Q126" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R126" s="6" t="s">
         <v>24</v>
@@ -8090,13 +8087,13 @@
     </row>
     <row r="127">
       <c r="A127" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D127" s="6" t="s">
         <v>24</v>
@@ -8129,7 +8126,7 @@
         <v>61</v>
       </c>
       <c r="N127" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O127" s="6" t="s">
         <v>24</v>
@@ -8138,7 +8135,7 @@
         <v>61</v>
       </c>
       <c r="Q127" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R127" s="6" t="s">
         <v>24</v>
@@ -8149,7 +8146,7 @@
     </row>
     <row r="128">
       <c r="A128" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>97</v>
@@ -8188,7 +8185,7 @@
         <v>61</v>
       </c>
       <c r="N128" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>24</v>
@@ -8197,7 +8194,7 @@
         <v>61</v>
       </c>
       <c r="Q128" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R128" s="6" t="s">
         <v>24</v>
@@ -8208,7 +8205,7 @@
     </row>
     <row r="129">
       <c r="A129" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>87</v>
@@ -8247,7 +8244,7 @@
         <v>61</v>
       </c>
       <c r="N129" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O129" s="6" t="s">
         <v>24</v>
@@ -8256,7 +8253,7 @@
         <v>61</v>
       </c>
       <c r="Q129" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R129" s="6" t="s">
         <v>24</v>
@@ -8267,10 +8264,10 @@
     </row>
     <row r="130">
       <c r="A130" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>24</v>
@@ -8306,7 +8303,7 @@
         <v>61</v>
       </c>
       <c r="N130" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>24</v>
@@ -8315,7 +8312,7 @@
         <v>61</v>
       </c>
       <c r="Q130" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R130" s="6" t="s">
         <v>24</v>
@@ -8326,7 +8323,7 @@
     </row>
     <row r="131">
       <c r="A131" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>64</v>
@@ -8365,7 +8362,7 @@
         <v>61</v>
       </c>
       <c r="N131" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O131" s="6" t="s">
         <v>24</v>
@@ -8374,7 +8371,7 @@
         <v>61</v>
       </c>
       <c r="Q131" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R131" s="6" t="s">
         <v>24</v>
@@ -8385,7 +8382,7 @@
     </row>
     <row r="132">
       <c r="A132" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>67</v>
@@ -8424,7 +8421,7 @@
         <v>61</v>
       </c>
       <c r="N132" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>24</v>
@@ -8433,7 +8430,7 @@
         <v>61</v>
       </c>
       <c r="Q132" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R132" s="6" t="s">
         <v>24</v>
@@ -8444,7 +8441,7 @@
     </row>
     <row r="133">
       <c r="A133" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>50</v>
@@ -8483,7 +8480,7 @@
         <v>61</v>
       </c>
       <c r="N133" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O133" s="6" t="s">
         <v>24</v>
@@ -8492,7 +8489,7 @@
         <v>61</v>
       </c>
       <c r="Q133" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R133" s="6" t="s">
         <v>24</v>
@@ -8503,10 +8500,10 @@
     </row>
     <row r="134">
       <c r="A134" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>24</v>
@@ -8542,7 +8539,7 @@
         <v>61</v>
       </c>
       <c r="N134" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>24</v>
@@ -8551,7 +8548,7 @@
         <v>61</v>
       </c>
       <c r="Q134" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R134" s="6" t="s">
         <v>24</v>
@@ -8562,10 +8559,10 @@
     </row>
     <row r="135">
       <c r="A135" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>24</v>
@@ -8601,7 +8598,7 @@
         <v>61</v>
       </c>
       <c r="N135" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O135" s="6" t="s">
         <v>24</v>
@@ -8610,7 +8607,7 @@
         <v>61</v>
       </c>
       <c r="Q135" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R135" s="6" t="s">
         <v>24</v>
@@ -8621,10 +8618,10 @@
     </row>
     <row r="136">
       <c r="A136" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>24</v>
@@ -8660,7 +8657,7 @@
         <v>61</v>
       </c>
       <c r="N136" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>24</v>
@@ -8669,7 +8666,7 @@
         <v>61</v>
       </c>
       <c r="Q136" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R136" s="6" t="s">
         <v>24</v>
@@ -8680,7 +8677,7 @@
     </row>
     <row r="137">
       <c r="A137" s="6" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>104</v>
@@ -8719,7 +8716,7 @@
         <v>61</v>
       </c>
       <c r="N137" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O137" s="6" t="s">
         <v>24</v>
@@ -8728,7 +8725,7 @@
         <v>61</v>
       </c>
       <c r="Q137" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R137" s="6" t="s">
         <v>24</v>
@@ -8739,7 +8736,7 @@
     </row>
     <row r="138">
       <c r="A138" s="6" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>52</v>
@@ -8778,7 +8775,7 @@
         <v>61</v>
       </c>
       <c r="N138" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>24</v>
@@ -8787,7 +8784,7 @@
         <v>61</v>
       </c>
       <c r="Q138" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R138" s="6" t="s">
         <v>24</v>
@@ -8798,7 +8795,7 @@
     </row>
     <row r="139">
       <c r="A139" s="6" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>108</v>
@@ -8837,7 +8834,7 @@
         <v>61</v>
       </c>
       <c r="N139" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O139" s="6" t="s">
         <v>24</v>
@@ -8846,7 +8843,7 @@
         <v>61</v>
       </c>
       <c r="Q139" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R139" s="6" t="s">
         <v>24</v>
@@ -8857,7 +8854,7 @@
     </row>
     <row r="140">
       <c r="A140" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>69</v>
@@ -8896,7 +8893,7 @@
         <v>61</v>
       </c>
       <c r="N140" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>24</v>
@@ -8905,7 +8902,7 @@
         <v>61</v>
       </c>
       <c r="Q140" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R140" s="6" t="s">
         <v>24</v>
@@ -8916,10 +8913,10 @@
     </row>
     <row r="141">
       <c r="A141" s="6" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>24</v>
@@ -8955,7 +8952,7 @@
         <v>61</v>
       </c>
       <c r="N141" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O141" s="6" t="s">
         <v>24</v>
@@ -8964,7 +8961,7 @@
         <v>61</v>
       </c>
       <c r="Q141" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R141" s="6" t="s">
         <v>24</v>
@@ -8975,10 +8972,10 @@
     </row>
     <row r="142">
       <c r="A142" s="6" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>24</v>
@@ -9014,7 +9011,7 @@
         <v>61</v>
       </c>
       <c r="N142" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O142" s="6" t="s">
         <v>24</v>
@@ -9023,7 +9020,7 @@
         <v>61</v>
       </c>
       <c r="Q142" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R142" s="6" t="s">
         <v>24</v>
@@ -9034,7 +9031,7 @@
     </row>
     <row r="143">
       <c r="A143" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>60</v>
@@ -9073,7 +9070,7 @@
         <v>61</v>
       </c>
       <c r="N143" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O143" s="6" t="s">
         <v>24</v>
@@ -9082,7 +9079,7 @@
         <v>61</v>
       </c>
       <c r="Q143" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R143" s="6" t="s">
         <v>24</v>
@@ -9093,7 +9090,7 @@
     </row>
     <row r="144">
       <c r="A144" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>112</v>
@@ -9132,7 +9129,7 @@
         <v>61</v>
       </c>
       <c r="N144" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>24</v>
@@ -9141,7 +9138,7 @@
         <v>61</v>
       </c>
       <c r="Q144" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R144" s="6" t="s">
         <v>24</v>
@@ -9152,7 +9149,7 @@
     </row>
     <row r="145">
       <c r="A145" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>94</v>
@@ -9191,7 +9188,7 @@
         <v>61</v>
       </c>
       <c r="N145" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O145" s="6" t="s">
         <v>24</v>
@@ -9200,7 +9197,7 @@
         <v>61</v>
       </c>
       <c r="Q145" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R145" s="6" t="s">
         <v>24</v>
@@ -9211,7 +9208,7 @@
     </row>
     <row r="146">
       <c r="A146" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>54</v>
@@ -9250,7 +9247,7 @@
         <v>61</v>
       </c>
       <c r="N146" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O146" s="6" t="s">
         <v>24</v>
@@ -9259,7 +9256,7 @@
         <v>61</v>
       </c>
       <c r="Q146" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R146" s="6" t="s">
         <v>24</v>
@@ -9270,7 +9267,7 @@
     </row>
     <row r="147">
       <c r="A147" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>73</v>
@@ -9309,7 +9306,7 @@
         <v>61</v>
       </c>
       <c r="N147" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O147" s="6" t="s">
         <v>24</v>
@@ -9318,7 +9315,7 @@
         <v>61</v>
       </c>
       <c r="Q147" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R147" s="6" t="s">
         <v>24</v>
@@ -9329,7 +9326,7 @@
     </row>
     <row r="148">
       <c r="A148" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>84</v>
@@ -9368,7 +9365,7 @@
         <v>61</v>
       </c>
       <c r="N148" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>24</v>
@@ -9377,7 +9374,7 @@
         <v>61</v>
       </c>
       <c r="Q148" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R148" s="6" t="s">
         <v>24</v>
@@ -9388,7 +9385,7 @@
     </row>
     <row r="149">
       <c r="A149" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>92</v>
@@ -9427,7 +9424,7 @@
         <v>61</v>
       </c>
       <c r="N149" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O149" s="6" t="s">
         <v>24</v>
@@ -9436,7 +9433,7 @@
         <v>61</v>
       </c>
       <c r="Q149" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R149" s="6" t="s">
         <v>24</v>
@@ -9447,7 +9444,7 @@
     </row>
     <row r="150">
       <c r="A150" s="6" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>77</v>
@@ -9486,7 +9483,7 @@
         <v>61</v>
       </c>
       <c r="N150" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>24</v>
@@ -9495,7 +9492,7 @@
         <v>61</v>
       </c>
       <c r="Q150" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R150" s="6" t="s">
         <v>24</v>
@@ -9506,7 +9503,7 @@
     </row>
     <row r="151">
       <c r="A151" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>56</v>
@@ -9545,7 +9542,7 @@
         <v>61</v>
       </c>
       <c r="N151" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O151" s="6" t="s">
         <v>24</v>
@@ -9554,7 +9551,7 @@
         <v>61</v>
       </c>
       <c r="Q151" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R151" s="6" t="s">
         <v>24</v>
@@ -9565,10 +9562,10 @@
     </row>
     <row r="152">
       <c r="A152" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>24</v>
@@ -9604,7 +9601,7 @@
         <v>61</v>
       </c>
       <c r="N152" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>24</v>
@@ -9613,7 +9610,7 @@
         <v>61</v>
       </c>
       <c r="Q152" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R152" s="6" t="s">
         <v>24</v>
@@ -9624,7 +9621,7 @@
     </row>
     <row r="153">
       <c r="A153" s="6" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>81</v>
@@ -9663,7 +9660,7 @@
         <v>61</v>
       </c>
       <c r="N153" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O153" s="6" t="s">
         <v>24</v>
@@ -9672,7 +9669,7 @@
         <v>61</v>
       </c>
       <c r="Q153" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R153" s="6" t="s">
         <v>24</v>
@@ -9683,7 +9680,7 @@
     </row>
     <row r="154">
       <c r="A154" s="6" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>69</v>
@@ -9722,7 +9719,7 @@
         <v>61</v>
       </c>
       <c r="N154" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O154" s="6" t="s">
         <v>24</v>
@@ -9731,7 +9728,7 @@
         <v>61</v>
       </c>
       <c r="Q154" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R154" s="6" t="s">
         <v>24</v>
@@ -9742,10 +9739,10 @@
     </row>
     <row r="155">
       <c r="A155" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>24</v>
@@ -9781,7 +9778,7 @@
         <v>61</v>
       </c>
       <c r="N155" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O155" s="6" t="s">
         <v>24</v>
@@ -9790,7 +9787,7 @@
         <v>61</v>
       </c>
       <c r="Q155" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R155" s="6" t="s">
         <v>24</v>
@@ -9801,7 +9798,7 @@
     </row>
     <row r="156">
       <c r="A156" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>108</v>
@@ -9840,7 +9837,7 @@
         <v>61</v>
       </c>
       <c r="N156" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O156" s="6" t="s">
         <v>24</v>
@@ -9849,7 +9846,7 @@
         <v>61</v>
       </c>
       <c r="Q156" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R156" s="6" t="s">
         <v>24</v>
@@ -9860,10 +9857,10 @@
     </row>
     <row r="157">
       <c r="A157" s="6" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>24</v>
@@ -9899,7 +9896,7 @@
         <v>61</v>
       </c>
       <c r="N157" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O157" s="6" t="s">
         <v>24</v>
@@ -9908,7 +9905,7 @@
         <v>61</v>
       </c>
       <c r="Q157" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R157" s="6" t="s">
         <v>24</v>
@@ -9919,7 +9916,7 @@
     </row>
     <row r="158">
       <c r="A158" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>92</v>
@@ -9958,7 +9955,7 @@
         <v>61</v>
       </c>
       <c r="N158" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O158" s="6" t="s">
         <v>24</v>
@@ -9967,7 +9964,7 @@
         <v>61</v>
       </c>
       <c r="Q158" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R158" s="6" t="s">
         <v>24</v>
@@ -9978,10 +9975,10 @@
     </row>
     <row r="159">
       <c r="A159" s="6" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>24</v>
@@ -10017,7 +10014,7 @@
         <v>61</v>
       </c>
       <c r="N159" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O159" s="6" t="s">
         <v>24</v>
@@ -10026,7 +10023,7 @@
         <v>61</v>
       </c>
       <c r="Q159" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R159" s="6" t="s">
         <v>24</v>
@@ -10076,7 +10073,7 @@
         <v>61</v>
       </c>
       <c r="N160" s="9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="O160" s="6" t="s">
         <v>24</v>
@@ -10085,7 +10082,7 @@
         <v>61</v>
       </c>
       <c r="Q160" s="9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="R160" s="6" t="s">
         <v>24</v>
@@ -10096,10 +10093,10 @@
     </row>
     <row r="161">
       <c r="A161" s="6" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>24</v>
@@ -10135,7 +10132,7 @@
         <v>61</v>
       </c>
       <c r="N161" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O161" s="6" t="s">
         <v>24</v>
@@ -10144,7 +10141,7 @@
         <v>61</v>
       </c>
       <c r="Q161" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R161" s="6" t="s">
         <v>24</v>
@@ -10155,7 +10152,7 @@
     </row>
     <row r="162">
       <c r="A162" s="6" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>108</v>
@@ -10194,7 +10191,7 @@
         <v>61</v>
       </c>
       <c r="N162" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O162" s="6" t="s">
         <v>24</v>
@@ -10203,7 +10200,7 @@
         <v>61</v>
       </c>
       <c r="Q162" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R162" s="6" t="s">
         <v>24</v>
@@ -10214,10 +10211,10 @@
     </row>
     <row r="163">
       <c r="A163" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>24</v>
@@ -10253,7 +10250,7 @@
         <v>61</v>
       </c>
       <c r="N163" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O163" s="6" t="s">
         <v>24</v>
@@ -10262,7 +10259,7 @@
         <v>61</v>
       </c>
       <c r="Q163" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R163" s="6" t="s">
         <v>24</v>
@@ -10273,10 +10270,10 @@
     </row>
     <row r="164">
       <c r="A164" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>24</v>
@@ -10312,7 +10309,7 @@
         <v>61</v>
       </c>
       <c r="N164" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O164" s="6" t="s">
         <v>24</v>
@@ -10321,7 +10318,7 @@
         <v>61</v>
       </c>
       <c r="Q164" s="9">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="R164" s="6" t="s">
         <v>24</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$147</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$141</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quarta-feira, 5 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em quinta-feira, 6 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -100,48 +100,36 @@
     <t>Observações</t>
   </si>
   <si>
-    <t>FA-11565</t>
+    <t>FA-11791</t>
+  </si>
+  <si>
+    <t>YAGO ELIAS COSTA BATISTA</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
+  </si>
+  <si>
+    <t>FATURA</t>
+  </si>
+  <si>
+    <t>ATIVUZ VEÍCULOS</t>
+  </si>
+  <si>
+    <t>VENCIDO</t>
+  </si>
+  <si>
+    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
+  </si>
+  <si>
+    <t>FA-11559</t>
   </si>
   <si>
     <t>YURI BATISTA DA COSTA</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>1.0 [OFICIAL] SICREDI | BANCO GESTOR</t>
-  </si>
-  <si>
-    <t>FATURA</t>
-  </si>
-  <si>
-    <t>ATIVUZ VEÍCULOS</t>
-  </si>
-  <si>
-    <t>VENCIDO</t>
-  </si>
-  <si>
-    <t>VENCIDO ENTRE 31 A 90 DIAS</t>
-  </si>
-  <si>
-    <t>FA-11568</t>
-  </si>
-  <si>
-    <t>FA-11571</t>
-  </si>
-  <si>
-    <t>FA-11791</t>
-  </si>
-  <si>
-    <t>YAGO ELIAS COSTA BATISTA</t>
-  </si>
-  <si>
-    <t>FA-11879</t>
-  </si>
-  <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
     <t>FA-11562</t>
   </si>
   <si>
@@ -157,18 +145,12 @@
     <t>VENCIDO ATÉ 30 DIAS</t>
   </si>
   <si>
-    <t>FA-11883</t>
-  </si>
-  <si>
     <t>FA-11876</t>
   </si>
   <si>
     <t>FA-11884</t>
   </si>
   <si>
-    <t>FA-11887</t>
-  </si>
-  <si>
     <t>FA-11834</t>
   </si>
   <si>
@@ -187,9 +169,6 @@
     <t>JOÃO PAULO CONSÓRCIOS</t>
   </si>
   <si>
-    <t>HOJE</t>
-  </si>
-  <si>
     <t>FA-11968</t>
   </si>
   <si>
@@ -241,18 +220,18 @@
     <t>FA-11947</t>
   </si>
   <si>
+    <t>FA-11972</t>
+  </si>
+  <si>
+    <t>FA-11857</t>
+  </si>
+  <si>
     <t>FA-12044</t>
   </si>
   <si>
     <t>DANILO DE ALMEIDA TORRES</t>
   </si>
   <si>
-    <t>FA-11857</t>
-  </si>
-  <si>
-    <t>FA-11972</t>
-  </si>
-  <si>
     <t>FA-11962</t>
   </si>
   <si>
@@ -280,6 +259,96 @@
     <t>FA-12016</t>
   </si>
   <si>
+    <t>FA-11849</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-12030</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11993</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-11839</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>FA-11885</t>
+  </si>
+  <si>
+    <t>FA-11907</t>
+  </si>
+  <si>
+    <t>FA-11977</t>
+  </si>
+  <si>
+    <t>JOZILDO TARQUINO DE BRITO</t>
+  </si>
+  <si>
+    <t>FA-12052</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11995</t>
+  </si>
+  <si>
+    <t>FA-11975</t>
+  </si>
+  <si>
+    <t>FA-12034</t>
+  </si>
+  <si>
+    <t>FA-11997</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-12049</t>
+  </si>
+  <si>
+    <t>FA-11858</t>
+  </si>
+  <si>
+    <t>FA-11976</t>
+  </si>
+  <si>
+    <t>FA-11921</t>
+  </si>
+  <si>
+    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
+  </si>
+  <si>
+    <t>FA-11963</t>
+  </si>
+  <si>
+    <t>FA-11998</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12021</t>
+  </si>
+  <si>
+    <t>FA-12022</t>
+  </si>
+  <si>
+    <t>FA-12035</t>
+  </si>
+  <si>
     <t>FA-11991</t>
   </si>
   <si>
@@ -289,96 +358,6 @@
     <t>LUZ DIVINA LTDA</t>
   </si>
   <si>
-    <t>FA-11849</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-12030</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11993</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11839</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>FA-11885</t>
-  </si>
-  <si>
-    <t>FA-11907</t>
-  </si>
-  <si>
-    <t>FA-11977</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-12052</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11995</t>
-  </si>
-  <si>
-    <t>FA-12034</t>
-  </si>
-  <si>
-    <t>FA-11997</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11975</t>
-  </si>
-  <si>
-    <t>FA-12049</t>
-  </si>
-  <si>
-    <t>FA-11858</t>
-  </si>
-  <si>
-    <t>FA-11976</t>
-  </si>
-  <si>
-    <t>FA-11921</t>
-  </si>
-  <si>
-    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
-  </si>
-  <si>
-    <t>FA-11963</t>
-  </si>
-  <si>
-    <t>FA-11998</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12021</t>
-  </si>
-  <si>
-    <t>FA-12022</t>
-  </si>
-  <si>
-    <t>FA-12035</t>
-  </si>
-  <si>
     <t>FA-12050</t>
   </si>
   <si>
@@ -391,15 +370,15 @@
     <t>FA-11996</t>
   </si>
   <si>
+    <t>FA-11981</t>
+  </si>
+  <si>
     <t>FA-12010</t>
   </si>
   <si>
     <t>ROBERTO MURATORI</t>
   </si>
   <si>
-    <t>FA-11981</t>
-  </si>
-  <si>
     <t>FA-12055</t>
   </si>
   <si>
@@ -418,15 +397,15 @@
     <t>FA-12037</t>
   </si>
   <si>
+    <t>FA-11982</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
     <t>FA-12001</t>
   </si>
   <si>
-    <t>FA-11982</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
     <t>FA-12054</t>
   </si>
   <si>
@@ -556,30 +535,30 @@
     <t>FA-11984</t>
   </si>
   <si>
+    <t>FA-11923</t>
+  </si>
+  <si>
     <t>FA-11862</t>
   </si>
   <si>
-    <t>FA-11923</t>
-  </si>
-  <si>
     <t>FA-12041</t>
   </si>
   <si>
+    <t>FA-11935</t>
+  </si>
+  <si>
+    <t>FA-12027</t>
+  </si>
+  <si>
+    <t>FA-12005</t>
+  </si>
+  <si>
+    <t>FA-12043</t>
+  </si>
+  <si>
     <t>FA-12028</t>
   </si>
   <si>
-    <t>FA-12027</t>
-  </si>
-  <si>
-    <t>FA-12005</t>
-  </si>
-  <si>
-    <t>FA-12043</t>
-  </si>
-  <si>
-    <t>FA-11935</t>
-  </si>
-  <si>
     <t>FA-11965</t>
   </si>
   <si>
@@ -589,12 +568,12 @@
     <t>FA-11868</t>
   </si>
   <si>
+    <t>FA-12056</t>
+  </si>
+  <si>
     <t>FA-12081</t>
   </si>
   <si>
-    <t>FA-12056</t>
-  </si>
-  <si>
     <t>FA-12026</t>
   </si>
   <si>
@@ -610,13 +589,13 @@
     <t>FA-12079</t>
   </si>
   <si>
+    <t>FA-11864</t>
+  </si>
+  <si>
+    <t>FA-12065</t>
+  </si>
+  <si>
     <t>FA-11924</t>
-  </si>
-  <si>
-    <t>FA-12065</t>
-  </si>
-  <si>
-    <t>FA-11864</t>
   </si>
   <si>
     <t>FA-11936</t>
@@ -798,7 +777,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S147"/>
+  <dimension ref="A1:S141"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1" style="1"/>
@@ -906,7 +885,7 @@
         <v>23</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>24</v>
@@ -918,28 +897,28 @@
         <v>26</v>
       </c>
       <c r="G6" s="7">
-        <v>46141</v>
+        <v>46170</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I6" s="7">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="J6" s="7">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="K6" s="7">
-        <v>46174</v>
+        <v>46195</v>
       </c>
       <c r="L6" s="8">
-        <v>310</v>
+        <v>600</v>
       </c>
       <c r="M6" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-65</v>
+        <v>-45</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -948,7 +927,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-65</v>
+        <v>-45</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -962,7 +941,7 @@
         <v>30</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>24</v>
@@ -974,31 +953,31 @@
         <v>25</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G7" s="7">
-        <v>46141</v>
+        <v>24</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I7" s="7">
-        <v>46181</v>
+        <v>46160</v>
       </c>
       <c r="J7" s="7">
-        <v>46181</v>
+        <v>46203</v>
       </c>
       <c r="K7" s="7">
-        <v>46181</v>
+        <v>46160</v>
       </c>
       <c r="L7" s="8">
-        <v>310</v>
+        <v>200</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-58</v>
+        <v>-37</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -1007,7 +986,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-58</v>
+        <v>-80</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>29</v>
@@ -1018,11 +997,11 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="C8" s="6" t="s">
         <v>24</v>
       </c>
@@ -1033,31 +1012,31 @@
         <v>25</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G8" s="7">
-        <v>46141</v>
+        <v>24</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I8" s="7">
-        <v>46188</v>
+        <v>46167</v>
       </c>
       <c r="J8" s="7">
-        <v>46188</v>
+        <v>46204</v>
       </c>
       <c r="K8" s="7">
-        <v>46188</v>
+        <v>46167</v>
       </c>
       <c r="L8" s="8">
-        <v>310</v>
+        <v>110</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-51</v>
+        <v>-36</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -1066,7 +1045,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-51</v>
+        <v>-73</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -1077,13 +1056,13 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -1092,31 +1071,31 @@
         <v>25</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G9" s="7">
-        <v>46170</v>
+        <v>46190</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I9" s="7">
-        <v>46195</v>
+        <v>46174</v>
       </c>
       <c r="J9" s="7">
-        <v>46195</v>
+        <v>46209</v>
       </c>
       <c r="K9" s="7">
-        <v>46195</v>
+        <v>46225</v>
       </c>
       <c r="L9" s="8">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-44</v>
+        <v>-31</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -1125,10 +1104,10 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-44</v>
+        <v>-15</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="S9" s="6" t="s">
         <v>24</v>
@@ -1136,13 +1115,13 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>23</v>
-      </c>
       <c r="C10" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>24</v>
@@ -1151,10 +1130,10 @@
         <v>25</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G10" s="7">
-        <v>46198</v>
+        <v>24</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>27</v>
@@ -1163,28 +1142,28 @@
         <v>46202</v>
       </c>
       <c r="J10" s="7">
-        <v>46202</v>
+        <v>46212</v>
       </c>
       <c r="K10" s="7">
         <v>46202</v>
       </c>
       <c r="L10" s="8">
-        <v>620</v>
+        <v>300</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-37</v>
+        <v>-28</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -1195,58 +1174,58 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>24</v>
+      <c r="G11" s="7">
+        <v>46190</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I11" s="7">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="J11" s="7">
-        <v>46203</v>
+        <v>46216</v>
       </c>
       <c r="K11" s="7">
-        <v>46160</v>
+        <v>46232</v>
       </c>
       <c r="L11" s="8">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-36</v>
+        <v>-24</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-79</v>
+        <v>-8</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="S11" s="6" t="s">
         <v>24</v>
@@ -1254,13 +1233,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>24</v>
@@ -1269,43 +1248,43 @@
         <v>25</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G12" s="7">
+        <v>46198</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I12" s="7">
-        <v>46167</v>
+        <v>46216</v>
       </c>
       <c r="J12" s="7">
-        <v>46204</v>
+        <v>46216</v>
       </c>
       <c r="K12" s="7">
-        <v>46167</v>
+        <v>46216</v>
       </c>
       <c r="L12" s="8">
-        <v>110</v>
+        <v>600</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-35</v>
+        <v>-24</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-72</v>
+        <v>-24</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="S12" s="6" t="s">
         <v>24</v>
@@ -1313,13 +1292,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>24</v>
@@ -1328,43 +1307,43 @@
         <v>25</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G13" s="7">
-        <v>46190</v>
+        <v>46182</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I13" s="7">
-        <v>46174</v>
+        <v>46216</v>
       </c>
       <c r="J13" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="K13" s="7">
-        <v>46225</v>
+        <v>46216</v>
       </c>
       <c r="L13" s="8">
-        <v>50</v>
+        <v>680</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-30</v>
+        <v>-24</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-14</v>
+        <v>-24</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S13" s="6" t="s">
         <v>24</v>
@@ -1375,7 +1354,7 @@
         <v>41</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>24</v>
@@ -1384,46 +1363,46 @@
         <v>24</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="7">
-        <v>46198</v>
+        <v>46182</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I14" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="J14" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="K14" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="L14" s="8">
-        <v>620</v>
+        <v>800</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-30</v>
+        <v>-24</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-30</v>
+        <v>-24</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S14" s="6" t="s">
         <v>24</v>
@@ -1431,13 +1410,13 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>24</v>
@@ -1446,43 +1425,43 @@
         <v>25</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>24</v>
+        <v>35</v>
+      </c>
+      <c r="G15" s="7">
+        <v>46190</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I15" s="7">
-        <v>46202</v>
+        <v>46174</v>
       </c>
       <c r="J15" s="7">
-        <v>46212</v>
+        <v>46223</v>
       </c>
       <c r="K15" s="7">
-        <v>46202</v>
+        <v>46239</v>
       </c>
       <c r="L15" s="8">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-27</v>
+        <v>-17</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-37</v>
+        <v>-1</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>24</v>
@@ -1490,13 +1469,13 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>24</v>
@@ -1505,43 +1484,43 @@
         <v>25</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G16" s="7">
-        <v>46190</v>
+        <v>46225</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I16" s="7">
-        <v>46174</v>
+        <v>46223</v>
       </c>
       <c r="J16" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K16" s="7">
-        <v>46232</v>
+        <v>46223</v>
       </c>
       <c r="L16" s="8">
-        <v>50</v>
+        <v>630</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-7</v>
+        <v>-17</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S16" s="6" t="s">
         <v>24</v>
@@ -1549,13 +1528,13 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>24</v>
@@ -1567,40 +1546,40 @@
         <v>26</v>
       </c>
       <c r="G17" s="7">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I17" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J17" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K17" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L17" s="8">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S17" s="6" t="s">
         <v>24</v>
@@ -1608,10 +1587,10 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>24</v>
@@ -1626,40 +1605,40 @@
         <v>26</v>
       </c>
       <c r="G18" s="7">
-        <v>46198</v>
+        <v>46188</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I18" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J18" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K18" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L18" s="8">
-        <v>620</v>
+        <v>650</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S18" s="6" t="s">
         <v>24</v>
@@ -1667,13 +1646,13 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>24</v>
@@ -1685,40 +1664,40 @@
         <v>26</v>
       </c>
       <c r="G19" s="7">
-        <v>46182</v>
+        <v>46225</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J19" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K19" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L19" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S19" s="6" t="s">
         <v>24</v>
@@ -1726,10 +1705,10 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>24</v>
@@ -1738,7 +1717,7 @@
         <v>24</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -1747,37 +1726,37 @@
         <v>46182</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="I20" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J20" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K20" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L20" s="8">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-23</v>
+        <v>-17</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S20" s="6" t="s">
         <v>24</v>
@@ -1785,58 +1764,58 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G21" s="7">
-        <v>46190</v>
+        <v>46182</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I21" s="7">
-        <v>46174</v>
+        <v>46223</v>
       </c>
       <c r="J21" s="7">
         <v>46223</v>
       </c>
       <c r="K21" s="7">
-        <v>46239</v>
+        <v>46223</v>
       </c>
       <c r="L21" s="8">
-        <v>50</v>
+        <v>800</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P21" s="6" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>0</v>
+        <v>-17</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S21" s="6" t="s">
         <v>24</v>
@@ -1844,10 +1823,10 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>24</v>
@@ -1859,10 +1838,10 @@
         <v>25</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>27</v>
@@ -1871,31 +1850,31 @@
         <v>46223</v>
       </c>
       <c r="J22" s="7">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="K22" s="7">
         <v>46223</v>
       </c>
       <c r="L22" s="8">
-        <v>630</v>
+        <v>480</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-16</v>
+        <v>-15</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S22" s="6" t="s">
         <v>24</v>
@@ -1903,13 +1882,13 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>24</v>
@@ -1918,43 +1897,43 @@
         <v>25</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="G23" s="7">
-        <v>46203</v>
+        <v>46190</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I23" s="7">
-        <v>46223</v>
+        <v>46174</v>
       </c>
       <c r="J23" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K23" s="7">
-        <v>46223</v>
+        <v>46246</v>
       </c>
       <c r="L23" s="8">
-        <v>630</v>
+        <v>50</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="Q23" s="9">
-        <v>-16</v>
+        <v>6</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="S23" s="6" t="s">
         <v>24</v>
@@ -1962,10 +1941,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>24</v>
@@ -1980,40 +1959,40 @@
         <v>26</v>
       </c>
       <c r="G24" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I24" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J24" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K24" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L24" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S24" s="6" t="s">
         <v>24</v>
@@ -2021,13 +2000,13 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>24</v>
@@ -2039,40 +2018,40 @@
         <v>26</v>
       </c>
       <c r="G25" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I25" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J25" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K25" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L25" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>24</v>
@@ -2083,7 +2062,7 @@
         <v>61</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>24</v>
@@ -2098,40 +2077,40 @@
         <v>26</v>
       </c>
       <c r="G26" s="7">
-        <v>46182</v>
+        <v>46212</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I26" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J26" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K26" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L26" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>24</v>
@@ -2142,55 +2121,55 @@
         <v>62</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G27" s="7">
-        <v>46182</v>
+        <v>46225</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="I27" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J27" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K27" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L27" s="8">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S27" s="6" t="s">
         <v>24</v>
@@ -2201,7 +2180,7 @@
         <v>63</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>24</v>
@@ -2213,43 +2192,43 @@
         <v>25</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G28" s="7">
+        <v>46188</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I28" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J28" s="7">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="K28" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L28" s="8">
-        <v>480</v>
+        <v>650</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S28" s="6" t="s">
         <v>24</v>
@@ -2257,13 +2236,13 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>24</v>
@@ -2272,43 +2251,43 @@
         <v>25</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G29" s="7">
-        <v>46190</v>
+        <v>46232</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I29" s="7">
-        <v>46174</v>
+        <v>46230</v>
       </c>
       <c r="J29" s="7">
         <v>46230</v>
       </c>
       <c r="K29" s="7">
-        <v>46246</v>
+        <v>46230</v>
       </c>
       <c r="L29" s="8">
-        <v>50</v>
+        <v>650</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P29" s="6" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S29" s="6" t="s">
         <v>24</v>
@@ -2319,7 +2298,7 @@
         <v>66</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>24</v>
@@ -2337,7 +2316,7 @@
         <v>46225</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I30" s="7">
         <v>46230</v>
@@ -2349,25 +2328,25 @@
         <v>46230</v>
       </c>
       <c r="L30" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S30" s="6" t="s">
         <v>24</v>
@@ -2375,10 +2354,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>24</v>
@@ -2408,25 +2387,25 @@
         <v>46230</v>
       </c>
       <c r="L31" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S31" s="6" t="s">
         <v>24</v>
@@ -2434,10 +2413,10 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>24</v>
@@ -2452,7 +2431,7 @@
         <v>26</v>
       </c>
       <c r="G32" s="7">
-        <v>46212</v>
+        <v>46232</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>27</v>
@@ -2467,25 +2446,25 @@
         <v>46230</v>
       </c>
       <c r="L32" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S32" s="6" t="s">
         <v>24</v>
@@ -2493,16 +2472,16 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>25</v>
@@ -2526,25 +2505,25 @@
         <v>46230</v>
       </c>
       <c r="L33" s="8">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S33" s="6" t="s">
         <v>24</v>
@@ -2552,10 +2531,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>24</v>
@@ -2564,16 +2543,16 @@
         <v>24</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="I34" s="7">
         <v>46230</v>
@@ -2585,25 +2564,25 @@
         <v>46230</v>
       </c>
       <c r="L34" s="8">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S34" s="6" t="s">
         <v>24</v>
@@ -2611,13 +2590,13 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>60</v>
+        <v>76</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>24</v>
@@ -2626,25 +2605,25 @@
         <v>25</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I35" s="7">
-        <v>46230</v>
+        <v>46188</v>
       </c>
       <c r="J35" s="7">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K35" s="7">
-        <v>46230</v>
+        <v>46188</v>
       </c>
       <c r="L35" s="8">
-        <v>650</v>
+        <v>16.66</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>28</v>
@@ -2653,16 +2632,16 @@
         <v>-9</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-9</v>
+        <v>-52</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="S35" s="6" t="s">
         <v>24</v>
@@ -2670,10 +2649,10 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>24</v>
@@ -2685,25 +2664,25 @@
         <v>25</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I36" s="7">
         <v>46230</v>
       </c>
       <c r="J36" s="7">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K36" s="7">
         <v>46230</v>
       </c>
       <c r="L36" s="8">
-        <v>680</v>
+        <v>42.03</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>28</v>
@@ -2712,16 +2691,16 @@
         <v>-9</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>24</v>
@@ -2729,10 +2708,10 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>24</v>
@@ -2744,10 +2723,10 @@
         <v>25</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>27</v>
@@ -2756,31 +2735,31 @@
         <v>46230</v>
       </c>
       <c r="J37" s="7">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="K37" s="7">
         <v>46230</v>
       </c>
       <c r="L37" s="8">
-        <v>680</v>
+        <v>495.15</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S37" s="6" t="s">
         <v>24</v>
@@ -2788,10 +2767,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>24</v>
@@ -2803,43 +2782,43 @@
         <v>25</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I38" s="7">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="J38" s="7">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="K38" s="7">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="L38" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-9</v>
+        <v>-8</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S38" s="6" t="s">
         <v>24</v>
@@ -2847,58 +2826,58 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="E39" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G39" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I39" s="7">
-        <v>46230</v>
+        <v>45930</v>
       </c>
       <c r="J39" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="K39" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="L39" s="8">
-        <v>700</v>
+        <v>185.5</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S39" s="6" t="s">
         <v>24</v>
@@ -2906,58 +2885,58 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="I40" s="7">
-        <v>46230</v>
+        <v>46216</v>
       </c>
       <c r="J40" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="K40" s="7">
-        <v>46230</v>
+        <v>46216</v>
       </c>
       <c r="L40" s="8">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-9</v>
+        <v>-24</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S40" s="6" t="s">
         <v>24</v>
@@ -2965,58 +2944,58 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="I41" s="7">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="J41" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="K41" s="7">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="L41" s="8">
-        <v>1200</v>
+        <v>560</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-9</v>
+        <v>-7</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-9</v>
+        <v>-17</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S41" s="6" t="s">
         <v>24</v>
@@ -3024,10 +3003,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>24</v>
@@ -3045,34 +3024,34 @@
         <v>24</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I42" s="7">
         <v>46188</v>
       </c>
       <c r="J42" s="7">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="K42" s="7">
         <v>46188</v>
       </c>
       <c r="L42" s="8">
-        <v>16.66</v>
+        <v>116.7</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>29</v>
@@ -3083,13 +3062,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>24</v>
@@ -3098,43 +3077,43 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G43" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G43" s="7">
+        <v>46225</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I43" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J43" s="7">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="K43" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L43" s="8">
-        <v>42.03</v>
+        <v>600</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S43" s="6" t="s">
         <v>24</v>
@@ -3142,13 +3121,13 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>24</v>
@@ -3157,43 +3136,43 @@
         <v>25</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G44" s="7">
+        <v>46232</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I44" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J44" s="7">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="K44" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L44" s="8">
-        <v>495.15</v>
+        <v>620</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-9</v>
+        <v>-3</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S44" s="6" t="s">
         <v>24</v>
@@ -3201,10 +3180,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>24</v>
@@ -3216,22 +3195,22 @@
         <v>25</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G45" s="7">
+        <v>46225</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I45" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="J45" s="7">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="K45" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="L45" s="8">
         <v>630</v>
@@ -3240,19 +3219,19 @@
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S45" s="6" t="s">
         <v>24</v>
@@ -3260,10 +3239,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>24</v>
+        <v>90</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>92</v>
+        <v>46</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>24</v>
@@ -3275,43 +3254,43 @@
         <v>25</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G46" s="7">
+        <v>46225</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I46" s="7">
-        <v>45930</v>
+        <v>46237</v>
       </c>
       <c r="J46" s="7">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="K46" s="7">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="L46" s="8">
-        <v>185.5</v>
+        <v>630</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q46" s="9">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S46" s="6" t="s">
         <v>24</v>
@@ -3319,13 +3298,13 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>24</v>
@@ -3334,43 +3313,43 @@
         <v>25</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G47" s="7">
+        <v>46232</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I47" s="7">
-        <v>46216</v>
+        <v>46237</v>
       </c>
       <c r="J47" s="7">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="K47" s="7">
-        <v>46216</v>
+        <v>46237</v>
       </c>
       <c r="L47" s="8">
-        <v>250</v>
+        <v>630</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-23</v>
+        <v>-3</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S47" s="6" t="s">
         <v>24</v>
@@ -3378,58 +3357,58 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G48" s="7">
+        <v>46225</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I48" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="J48" s="7">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="K48" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="L48" s="8">
-        <v>560</v>
+        <v>630</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>-16</v>
+        <v>-3</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S48" s="6" t="s">
         <v>24</v>
@@ -3437,10 +3416,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>24</v>
@@ -3452,43 +3431,43 @@
         <v>25</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G49" s="7">
+        <v>46232</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I49" s="7">
-        <v>46188</v>
+        <v>46237</v>
       </c>
       <c r="J49" s="7">
         <v>46237</v>
       </c>
       <c r="K49" s="7">
-        <v>46188</v>
+        <v>46237</v>
       </c>
       <c r="L49" s="8">
-        <v>116.7</v>
+        <v>650</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>-51</v>
+        <v>-3</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="S49" s="6" t="s">
         <v>24</v>
@@ -3499,10 +3478,10 @@
         <v>95</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>24</v>
@@ -3514,10 +3493,10 @@
         <v>26</v>
       </c>
       <c r="G50" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I50" s="7">
         <v>46237</v>
@@ -3529,25 +3508,25 @@
         <v>46237</v>
       </c>
       <c r="L50" s="8">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S50" s="6" t="s">
         <v>24</v>
@@ -3555,13 +3534,13 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>24</v>
@@ -3573,10 +3552,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I51" s="7">
         <v>46237</v>
@@ -3588,25 +3567,25 @@
         <v>46237</v>
       </c>
       <c r="L51" s="8">
-        <v>620</v>
+        <v>650</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S51" s="6" t="s">
         <v>24</v>
@@ -3614,10 +3593,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>24</v>
@@ -3632,7 +3611,7 @@
         <v>26</v>
       </c>
       <c r="G52" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>27</v>
@@ -3647,25 +3626,25 @@
         <v>46237</v>
       </c>
       <c r="L52" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S52" s="6" t="s">
         <v>24</v>
@@ -3673,10 +3652,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>24</v>
@@ -3691,10 +3670,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I53" s="7">
         <v>46237</v>
@@ -3706,25 +3685,25 @@
         <v>46237</v>
       </c>
       <c r="L53" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S53" s="6" t="s">
         <v>24</v>
@@ -3732,10 +3711,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>102</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>24</v>
@@ -3753,7 +3732,7 @@
         <v>46225</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I54" s="7">
         <v>46237</v>
@@ -3765,25 +3744,25 @@
         <v>46237</v>
       </c>
       <c r="L54" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S54" s="6" t="s">
         <v>24</v>
@@ -3791,10 +3770,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>24</v>
@@ -3809,7 +3788,7 @@
         <v>26</v>
       </c>
       <c r="G55" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>27</v>
@@ -3824,25 +3803,25 @@
         <v>46237</v>
       </c>
       <c r="L55" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S55" s="6" t="s">
         <v>24</v>
@@ -3850,10 +3829,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>24</v>
@@ -3883,25 +3862,25 @@
         <v>46237</v>
       </c>
       <c r="L56" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S56" s="6" t="s">
         <v>24</v>
@@ -3909,10 +3888,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>24</v>
@@ -3927,10 +3906,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I57" s="7">
         <v>46237</v>
@@ -3942,25 +3921,25 @@
         <v>46237</v>
       </c>
       <c r="L57" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N57" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P57" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S57" s="6" t="s">
         <v>24</v>
@@ -3968,13 +3947,13 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="C58" s="6" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>24</v>
@@ -3983,43 +3962,43 @@
         <v>25</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G58" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G58" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="I58" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="J58" s="7">
         <v>46237</v>
       </c>
       <c r="K58" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="L58" s="8">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="M58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N58" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q58" s="9">
-        <v>-2</v>
+        <v>-10</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S58" s="6" t="s">
         <v>24</v>
@@ -4027,16 +4006,16 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>25</v>
@@ -4045,7 +4024,7 @@
         <v>26</v>
       </c>
       <c r="G59" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>27</v>
@@ -4060,25 +4039,25 @@
         <v>46237</v>
       </c>
       <c r="L59" s="8">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="M59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N59" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P59" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q59" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S59" s="6" t="s">
         <v>24</v>
@@ -4089,7 +4068,7 @@
         <v>109</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
@@ -4104,10 +4083,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I60" s="7">
         <v>46237</v>
@@ -4119,25 +4098,25 @@
         <v>46237</v>
       </c>
       <c r="L60" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N60" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q60" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S60" s="6" t="s">
         <v>24</v>
@@ -4148,7 +4127,7 @@
         <v>110</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>111</v>
+        <v>42</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>24</v>
@@ -4157,16 +4136,16 @@
         <v>24</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="I61" s="7">
         <v>46237</v>
@@ -4178,25 +4157,25 @@
         <v>46237</v>
       </c>
       <c r="L61" s="8">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="M61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N61" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P61" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q61" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S61" s="6" t="s">
         <v>24</v>
@@ -4204,10 +4183,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>46</v>
+        <v>106</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4222,10 +4201,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="I62" s="7">
         <v>46237</v>
@@ -4237,25 +4216,25 @@
         <v>46237</v>
       </c>
       <c r="L62" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N62" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="P62" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q62" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="S62" s="6" t="s">
         <v>24</v>
@@ -4263,13 +4242,13 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>24</v>
@@ -4281,40 +4260,40 @@
         <v>26</v>
       </c>
       <c r="G63" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I63" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J63" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K63" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L63" s="8">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="N63" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="Q63" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="S63" s="6" t="s">
         <v>24</v>
@@ -4322,13 +4301,13 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B64" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B64" s="6" t="s">
-        <v>88</v>
-      </c>
       <c r="C64" s="6" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>24</v>
@@ -4340,40 +4319,40 @@
         <v>26</v>
       </c>
       <c r="G64" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I64" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J64" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K64" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L64" s="8">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="N64" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="Q64" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="S64" s="6" t="s">
         <v>24</v>
@@ -4384,13 +4363,13 @@
         <v>115</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>25</v>
@@ -4402,37 +4381,37 @@
         <v>46232</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I65" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J65" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K65" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L65" s="8">
-        <v>700</v>
+        <v>620</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="N65" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="Q65" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="S65" s="6" t="s">
         <v>24</v>
@@ -4443,13 +4422,13 @@
         <v>116</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>25</v>
@@ -4458,40 +4437,40 @@
         <v>26</v>
       </c>
       <c r="G66" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I66" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J66" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K66" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L66" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="N66" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="Q66" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="S66" s="6" t="s">
         <v>24</v>
@@ -4499,10 +4478,10 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>48</v>
+        <v>93</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>24</v>
@@ -4511,46 +4490,46 @@
         <v>24</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F67" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G67" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="I67" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J67" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K67" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L67" s="8">
-        <v>750</v>
+        <v>630</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="N67" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="Q67" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="S67" s="6" t="s">
         <v>24</v>
@@ -4558,10 +4537,10 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>24</v>
@@ -4579,37 +4558,37 @@
         <v>46225</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="I68" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J68" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K68" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L68" s="8">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="N68" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="Q68" s="9">
-        <v>-2</v>
+        <v>4</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="S68" s="6" t="s">
         <v>24</v>
@@ -4617,13 +4596,13 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>24</v>
@@ -4635,7 +4614,7 @@
         <v>26</v>
       </c>
       <c r="G69" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>27</v>
@@ -4650,22 +4629,22 @@
         <v>46244</v>
       </c>
       <c r="L69" s="8">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N69" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q69" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>24</v>
@@ -4679,10 +4658,10 @@
         <v>121</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>24</v>
@@ -4709,22 +4688,22 @@
         <v>46244</v>
       </c>
       <c r="L70" s="8">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N70" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q70" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>24</v>
@@ -4735,13 +4714,13 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>24</v>
@@ -4753,10 +4732,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I71" s="7">
         <v>46244</v>
@@ -4768,22 +4747,22 @@
         <v>46244</v>
       </c>
       <c r="L71" s="8">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N71" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q71" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>24</v>
@@ -4794,16 +4773,16 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>124</v>
+        <v>65</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>25</v>
@@ -4827,22 +4806,22 @@
         <v>46244</v>
       </c>
       <c r="L72" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N72" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q72" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4856,7 +4835,7 @@
         <v>125</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>24</v>
@@ -4871,10 +4850,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I73" s="7">
         <v>46244</v>
@@ -4886,22 +4865,22 @@
         <v>46244</v>
       </c>
       <c r="L73" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N73" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q73" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4918,7 +4897,7 @@
         <v>53</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>24</v>
@@ -4945,22 +4924,22 @@
         <v>46244</v>
       </c>
       <c r="L74" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N74" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q74" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -4974,7 +4953,7 @@
         <v>127</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>24</v>
@@ -4989,7 +4968,7 @@
         <v>26</v>
       </c>
       <c r="G75" s="7">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>27</v>
@@ -5004,22 +4983,22 @@
         <v>46244</v>
       </c>
       <c r="L75" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N75" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q75" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -5033,7 +5012,7 @@
         <v>128</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>24</v>
@@ -5048,7 +5027,7 @@
         <v>26</v>
       </c>
       <c r="G76" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H76" s="6" t="s">
         <v>27</v>
@@ -5063,22 +5042,22 @@
         <v>46244</v>
       </c>
       <c r="L76" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N76" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q76" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -5089,10 +5068,10 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>24</v>
@@ -5107,7 +5086,7 @@
         <v>26</v>
       </c>
       <c r="G77" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>27</v>
@@ -5122,22 +5101,22 @@
         <v>46244</v>
       </c>
       <c r="L77" s="8">
-        <v>630</v>
+        <v>670</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N77" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q77" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5148,10 +5127,10 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -5166,10 +5145,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I78" s="7">
         <v>46244</v>
@@ -5181,22 +5160,22 @@
         <v>46244</v>
       </c>
       <c r="L78" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N78" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q78" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5207,10 +5186,10 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
@@ -5225,10 +5204,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I79" s="7">
         <v>46244</v>
@@ -5240,22 +5219,22 @@
         <v>46244</v>
       </c>
       <c r="L79" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N79" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q79" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5266,13 +5245,13 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>24</v>
@@ -5284,7 +5263,7 @@
         <v>26</v>
       </c>
       <c r="G80" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>27</v>
@@ -5299,22 +5278,22 @@
         <v>46244</v>
       </c>
       <c r="L80" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N80" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q80" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5325,10 +5304,10 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5343,7 +5322,7 @@
         <v>26</v>
       </c>
       <c r="G81" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>27</v>
@@ -5358,22 +5337,22 @@
         <v>46244</v>
       </c>
       <c r="L81" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N81" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q81" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5384,10 +5363,10 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>24</v>
@@ -5417,22 +5396,22 @@
         <v>46244</v>
       </c>
       <c r="L82" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N82" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q82" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5443,10 +5422,10 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>138</v>
+        <v>101</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>24</v>
@@ -5461,10 +5440,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I83" s="7">
         <v>46244</v>
@@ -5476,22 +5455,22 @@
         <v>46244</v>
       </c>
       <c r="L83" s="8">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N83" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q83" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5505,7 +5484,7 @@
         <v>139</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>24</v>
@@ -5520,10 +5499,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="7">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="I84" s="7">
         <v>46244</v>
@@ -5538,19 +5517,19 @@
         <v>680</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N84" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q84" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5561,10 +5540,10 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>46</v>
+        <v>142</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>24</v>
@@ -5579,7 +5558,7 @@
         <v>26</v>
       </c>
       <c r="G85" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>27</v>
@@ -5594,22 +5573,22 @@
         <v>46244</v>
       </c>
       <c r="L85" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N85" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q85" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5620,7 +5599,7 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>76</v>
@@ -5638,10 +5617,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I86" s="7">
         <v>46244</v>
@@ -5653,22 +5632,22 @@
         <v>46244</v>
       </c>
       <c r="L86" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N86" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q86" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5679,16 +5658,16 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>143</v>
+        <v>72</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>25</v>
@@ -5712,22 +5691,22 @@
         <v>46244</v>
       </c>
       <c r="L87" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N87" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q87" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5738,10 +5717,10 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>24</v>
@@ -5750,7 +5729,7 @@
         <v>24</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
@@ -5759,7 +5738,7 @@
         <v>46232</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I88" s="7">
         <v>46244</v>
@@ -5771,22 +5750,22 @@
         <v>46244</v>
       </c>
       <c r="L88" s="8">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N88" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q88" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5797,10 +5776,10 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>24</v>
@@ -5818,7 +5797,7 @@
         <v>46225</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="I89" s="7">
         <v>46244</v>
@@ -5830,22 +5809,22 @@
         <v>46244</v>
       </c>
       <c r="L89" s="8">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N89" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q89" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5856,16 +5835,16 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>25</v>
@@ -5874,10 +5853,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="7">
-        <v>46212</v>
+        <v>46238</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="I90" s="7">
         <v>46244</v>
@@ -5889,22 +5868,22 @@
         <v>46244</v>
       </c>
       <c r="L90" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N90" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q90" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5915,16 +5894,16 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>25</v>
@@ -5936,7 +5915,7 @@
         <v>46238</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="I91" s="7">
         <v>46244</v>
@@ -5948,22 +5927,22 @@
         <v>46244</v>
       </c>
       <c r="L91" s="8">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N91" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q91" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -5974,10 +5953,10 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>24</v>
@@ -5992,10 +5971,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="I92" s="7">
         <v>46244</v>
@@ -6007,22 +5986,22 @@
         <v>46244</v>
       </c>
       <c r="L92" s="8">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N92" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q92" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -6033,43 +6012,43 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G93" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G93" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I93" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J93" s="7">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K93" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L93" s="8">
-        <v>700</v>
+        <v>316.64</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N93" s="9">
         <v>5</v>
@@ -6078,13 +6057,13 @@
         <v>24</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="Q93" s="9">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="R93" s="6" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="S93" s="6" t="s">
         <v>24</v>
@@ -6092,55 +6071,55 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>48</v>
+        <v>114</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="I94" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J94" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K94" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L94" s="8">
-        <v>750</v>
+        <v>600</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N94" s="9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q94" s="9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6151,13 +6130,13 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>154</v>
+        <v>86</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>24</v>
+        <v>86</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>24</v>
@@ -6172,34 +6151,34 @@
         <v>46225</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="I95" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J95" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K95" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L95" s="8">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N95" s="9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q95" s="9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6210,16 +6189,16 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>156</v>
+        <v>88</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>157</v>
+        <v>24</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>25</v>
@@ -6228,37 +6207,37 @@
         <v>26</v>
       </c>
       <c r="G96" s="7">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="I96" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J96" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K96" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L96" s="8">
-        <v>1200</v>
+        <v>620</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N96" s="9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q96" s="9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6272,13 +6251,13 @@
         <v>158</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>159</v>
+        <v>117</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>157</v>
+        <v>73</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>25</v>
@@ -6287,37 +6266,37 @@
         <v>26</v>
       </c>
       <c r="G97" s="7">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="I97" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J97" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K97" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L97" s="8">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N97" s="9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q97" s="9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6328,10 +6307,10 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>24</v>
@@ -6349,34 +6328,34 @@
         <v>46225</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="I98" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J98" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K98" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L98" s="8">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N98" s="9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q98" s="9">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6387,10 +6366,10 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>143</v>
+        <v>80</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>24</v>
@@ -6402,43 +6381,43 @@
         <v>25</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G99" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G99" s="7">
+        <v>46225</v>
       </c>
       <c r="H99" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I99" s="7">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="J99" s="7">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="K99" s="7">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="L99" s="8">
-        <v>316.64</v>
+        <v>630</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N99" s="9">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="Q99" s="9">
-        <v>-2</v>
+        <v>11</v>
       </c>
       <c r="R99" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="S99" s="6" t="s">
         <v>24</v>
@@ -6446,13 +6425,13 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>24</v>
@@ -6464,7 +6443,7 @@
         <v>26</v>
       </c>
       <c r="G100" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H100" s="6" t="s">
         <v>27</v>
@@ -6479,22 +6458,22 @@
         <v>46251</v>
       </c>
       <c r="L100" s="8">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N100" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q100" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6505,13 +6484,13 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="D101" s="6" t="s">
         <v>24</v>
@@ -6538,22 +6517,22 @@
         <v>46251</v>
       </c>
       <c r="L101" s="8">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="M101" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N101" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q101" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6564,13 +6543,13 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>24</v>
@@ -6582,10 +6561,10 @@
         <v>26</v>
       </c>
       <c r="G102" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I102" s="7">
         <v>46251</v>
@@ -6597,22 +6576,22 @@
         <v>46251</v>
       </c>
       <c r="L102" s="8">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N102" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q102" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6623,16 +6602,16 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>25</v>
@@ -6656,22 +6635,22 @@
         <v>46251</v>
       </c>
       <c r="L103" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N103" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q103" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6682,10 +6661,10 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>24</v>
@@ -6700,7 +6679,7 @@
         <v>26</v>
       </c>
       <c r="G104" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H104" s="6" t="s">
         <v>27</v>
@@ -6715,22 +6694,22 @@
         <v>46251</v>
       </c>
       <c r="L104" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N104" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q104" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6741,13 +6720,13 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="D105" s="6" t="s">
         <v>24</v>
@@ -6774,22 +6753,22 @@
         <v>46251</v>
       </c>
       <c r="L105" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N105" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q105" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6800,10 +6779,10 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>55</v>
+        <v>98</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>24</v>
@@ -6818,7 +6797,7 @@
         <v>26</v>
       </c>
       <c r="G106" s="7">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>27</v>
@@ -6833,22 +6812,22 @@
         <v>46251</v>
       </c>
       <c r="L106" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N106" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q106" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>
@@ -6859,10 +6838,10 @@
     </row>
     <row r="107">
       <c r="A107" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>24</v>
@@ -6877,10 +6856,10 @@
         <v>26</v>
       </c>
       <c r="G107" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I107" s="7">
         <v>46251</v>
@@ -6892,22 +6871,22 @@
         <v>46251</v>
       </c>
       <c r="L107" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N107" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q107" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>24</v>
@@ -6918,10 +6897,10 @@
     </row>
     <row r="108">
       <c r="A108" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>102</v>
+        <v>131</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>24</v>
@@ -6936,7 +6915,7 @@
         <v>26</v>
       </c>
       <c r="G108" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H108" s="6" t="s">
         <v>27</v>
@@ -6951,22 +6930,22 @@
         <v>46251</v>
       </c>
       <c r="L108" s="8">
-        <v>630</v>
+        <v>670</v>
       </c>
       <c r="M108" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N108" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q108" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>24</v>
@@ -6977,10 +6956,10 @@
     </row>
     <row r="109">
       <c r="A109" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>24</v>
@@ -6995,10 +6974,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="7">
-        <v>46232</v>
+        <v>46212</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I109" s="7">
         <v>46251</v>
@@ -7010,22 +6989,22 @@
         <v>46251</v>
       </c>
       <c r="L109" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N109" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P109" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q109" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R109" s="6" t="s">
         <v>24</v>
@@ -7036,10 +7015,10 @@
     </row>
     <row r="110">
       <c r="A110" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>24</v>
@@ -7069,22 +7048,22 @@
         <v>46251</v>
       </c>
       <c r="L110" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N110" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q110" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R110" s="6" t="s">
         <v>24</v>
@@ -7095,13 +7074,13 @@
     </row>
     <row r="111">
       <c r="A111" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>60</v>
+        <v>101</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>24</v>
@@ -7116,7 +7095,7 @@
         <v>46225</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I111" s="7">
         <v>46251</v>
@@ -7128,22 +7107,22 @@
         <v>46251</v>
       </c>
       <c r="L111" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M111" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N111" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P111" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q111" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R111" s="6" t="s">
         <v>24</v>
@@ -7154,10 +7133,10 @@
     </row>
     <row r="112">
       <c r="A112" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>57</v>
+        <v>136</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>24</v>
@@ -7172,10 +7151,10 @@
         <v>26</v>
       </c>
       <c r="G112" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I112" s="7">
         <v>46251</v>
@@ -7187,22 +7166,22 @@
         <v>46251</v>
       </c>
       <c r="L112" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N112" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q112" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R112" s="6" t="s">
         <v>24</v>
@@ -7213,10 +7192,10 @@
     </row>
     <row r="113">
       <c r="A113" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>108</v>
+        <v>40</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>24</v>
@@ -7231,7 +7210,7 @@
         <v>26</v>
       </c>
       <c r="G113" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H113" s="6" t="s">
         <v>27</v>
@@ -7246,22 +7225,22 @@
         <v>46251</v>
       </c>
       <c r="L113" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N113" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q113" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R113" s="6" t="s">
         <v>24</v>
@@ -7272,10 +7251,10 @@
     </row>
     <row r="114">
       <c r="A114" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>138</v>
+        <v>67</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>24</v>
@@ -7290,10 +7269,10 @@
         <v>26</v>
       </c>
       <c r="G114" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I114" s="7">
         <v>46251</v>
@@ -7305,22 +7284,22 @@
         <v>46251</v>
       </c>
       <c r="L114" s="8">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N114" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q114" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R114" s="6" t="s">
         <v>24</v>
@@ -7331,10 +7310,10 @@
     </row>
     <row r="115">
       <c r="A115" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>24</v>
@@ -7367,19 +7346,19 @@
         <v>680</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N115" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O115" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q115" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R115" s="6" t="s">
         <v>24</v>
@@ -7390,7 +7369,7 @@
     </row>
     <row r="116">
       <c r="A116" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>76</v>
@@ -7408,10 +7387,10 @@
         <v>26</v>
       </c>
       <c r="G116" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I116" s="7">
         <v>46251</v>
@@ -7423,22 +7402,22 @@
         <v>46251</v>
       </c>
       <c r="L116" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M116" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N116" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q116" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R116" s="6" t="s">
         <v>24</v>
@@ -7449,16 +7428,16 @@
     </row>
     <row r="117">
       <c r="A117" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>25</v>
@@ -7467,10 +7446,10 @@
         <v>26</v>
       </c>
       <c r="G117" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I117" s="7">
         <v>46251</v>
@@ -7482,22 +7461,22 @@
         <v>46251</v>
       </c>
       <c r="L117" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M117" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N117" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O117" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P117" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q117" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R117" s="6" t="s">
         <v>24</v>
@@ -7508,10 +7487,10 @@
     </row>
     <row r="118">
       <c r="A118" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>24</v>
@@ -7526,7 +7505,7 @@
         <v>26</v>
       </c>
       <c r="G118" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H118" s="6" t="s">
         <v>27</v>
@@ -7541,22 +7520,22 @@
         <v>46251</v>
       </c>
       <c r="L118" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M118" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N118" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q118" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R118" s="6" t="s">
         <v>24</v>
@@ -7567,10 +7546,10 @@
     </row>
     <row r="119">
       <c r="A119" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>147</v>
+        <v>42</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>24</v>
@@ -7579,16 +7558,16 @@
         <v>24</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="7">
-        <v>46212</v>
+        <v>46232</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="I119" s="7">
         <v>46251</v>
@@ -7600,22 +7579,22 @@
         <v>46251</v>
       </c>
       <c r="L119" s="8">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="M119" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N119" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O119" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P119" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q119" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R119" s="6" t="s">
         <v>24</v>
@@ -7626,10 +7605,10 @@
     </row>
     <row r="120">
       <c r="A120" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>24</v>
@@ -7647,7 +7626,7 @@
         <v>46225</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="I120" s="7">
         <v>46251</v>
@@ -7659,22 +7638,22 @@
         <v>46251</v>
       </c>
       <c r="L120" s="8">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="M120" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N120" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q120" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R120" s="6" t="s">
         <v>24</v>
@@ -7685,16 +7664,16 @@
     </row>
     <row r="121">
       <c r="A121" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>88</v>
+        <v>152</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>25</v>
@@ -7703,10 +7682,10 @@
         <v>26</v>
       </c>
       <c r="G121" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="I121" s="7">
         <v>46251</v>
@@ -7718,22 +7697,22 @@
         <v>46251</v>
       </c>
       <c r="L121" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M121" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N121" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O121" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P121" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q121" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R121" s="6" t="s">
         <v>24</v>
@@ -7744,10 +7723,10 @@
     </row>
     <row r="122">
       <c r="A122" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>24</v>
@@ -7762,10 +7741,10 @@
         <v>26</v>
       </c>
       <c r="G122" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="I122" s="7">
         <v>46251</v>
@@ -7777,22 +7756,22 @@
         <v>46251</v>
       </c>
       <c r="L122" s="8">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="M122" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N122" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q122" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R122" s="6" t="s">
         <v>24</v>
@@ -7803,7 +7782,7 @@
     </row>
     <row r="123">
       <c r="A123" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>149</v>
@@ -7812,7 +7791,7 @@
         <v>24</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="E123" s="6" t="s">
         <v>25</v>
@@ -7824,7 +7803,7 @@
         <v>46238</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="I123" s="7">
         <v>46251</v>
@@ -7836,22 +7815,22 @@
         <v>46251</v>
       </c>
       <c r="L123" s="8">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="M123" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N123" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O123" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P123" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q123" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R123" s="6" t="s">
         <v>24</v>
@@ -7862,16 +7841,16 @@
     </row>
     <row r="124">
       <c r="A124" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>80</v>
+        <v>24</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>25</v>
@@ -7880,37 +7859,37 @@
         <v>26</v>
       </c>
       <c r="G124" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="I124" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J124" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K124" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L124" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M124" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N124" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q124" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R124" s="6" t="s">
         <v>24</v>
@@ -7921,10 +7900,10 @@
     </row>
     <row r="125">
       <c r="A125" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>48</v>
+        <v>129</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>24</v>
@@ -7933,7 +7912,7 @@
         <v>24</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="F125" s="6" t="s">
         <v>26</v>
@@ -7942,34 +7921,34 @@
         <v>46232</v>
       </c>
       <c r="H125" s="6" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="I125" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J125" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K125" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L125" s="8">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="M125" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N125" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O125" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P125" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q125" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R125" s="6" t="s">
         <v>24</v>
@@ -7980,10 +7959,10 @@
     </row>
     <row r="126">
       <c r="A126" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>24</v>
@@ -7998,37 +7977,37 @@
         <v>26</v>
       </c>
       <c r="G126" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="I126" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J126" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K126" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L126" s="8">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="M126" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N126" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q126" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R126" s="6" t="s">
         <v>24</v>
@@ -8039,16 +8018,16 @@
     </row>
     <row r="127">
       <c r="A127" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>159</v>
+        <v>140</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>157</v>
+        <v>24</v>
       </c>
       <c r="E127" s="6" t="s">
         <v>25</v>
@@ -8057,37 +8036,37 @@
         <v>26</v>
       </c>
       <c r="G127" s="7">
-        <v>46238</v>
+        <v>46212</v>
       </c>
       <c r="H127" s="6" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="I127" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J127" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K127" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L127" s="8">
-        <v>1200</v>
+        <v>680</v>
       </c>
       <c r="M127" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N127" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O127" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P127" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q127" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R127" s="6" t="s">
         <v>24</v>
@@ -8098,10 +8077,10 @@
     </row>
     <row r="128">
       <c r="A128" s="6" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>24</v>
@@ -8116,37 +8095,37 @@
         <v>26</v>
       </c>
       <c r="G128" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="I128" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J128" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K128" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L128" s="8">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="M128" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N128" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q128" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R128" s="6" t="s">
         <v>24</v>
@@ -8157,16 +8136,16 @@
     </row>
     <row r="129">
       <c r="A129" s="6" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>156</v>
+        <v>142</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>157</v>
+        <v>24</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>25</v>
@@ -8178,34 +8157,34 @@
         <v>46238</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="I129" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J129" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K129" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L129" s="8">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="M129" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N129" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="O129" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P129" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q129" s="9">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="R129" s="6" t="s">
         <v>24</v>
@@ -8216,10 +8195,10 @@
     </row>
     <row r="130">
       <c r="A130" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>108</v>
+        <v>147</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>24</v>
@@ -8234,10 +8213,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="7">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I130" s="7">
         <v>46258</v>
@@ -8249,22 +8228,22 @@
         <v>46258</v>
       </c>
       <c r="L130" s="8">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="M130" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N130" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q130" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R130" s="6" t="s">
         <v>24</v>
@@ -8275,16 +8254,16 @@
     </row>
     <row r="131">
       <c r="A131" s="6" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="E131" s="6" t="s">
         <v>25</v>
@@ -8293,10 +8272,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H131" s="6" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="I131" s="7">
         <v>46258</v>
@@ -8308,22 +8287,22 @@
         <v>46258</v>
       </c>
       <c r="L131" s="8">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="M131" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N131" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O131" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P131" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q131" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R131" s="6" t="s">
         <v>24</v>
@@ -8334,16 +8313,16 @@
     </row>
     <row r="132">
       <c r="A132" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>25</v>
@@ -8352,10 +8331,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="7">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="I132" s="7">
         <v>46258</v>
@@ -8367,22 +8346,22 @@
         <v>46258</v>
       </c>
       <c r="L132" s="8">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="M132" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N132" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q132" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R132" s="6" t="s">
         <v>24</v>
@@ -8393,10 +8372,10 @@
     </row>
     <row r="133">
       <c r="A133" s="6" t="s">
-        <v>195</v>
+        <v>24</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>147</v>
+        <v>82</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>24</v>
@@ -8408,40 +8387,40 @@
         <v>25</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G133" s="7">
-        <v>46212</v>
+        <v>24</v>
+      </c>
+      <c r="G133" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H133" s="6" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="I133" s="7">
-        <v>46258</v>
+        <v>45930</v>
       </c>
       <c r="J133" s="7">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="K133" s="7">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="L133" s="8">
-        <v>680</v>
+        <v>185.5</v>
       </c>
       <c r="M133" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N133" s="9">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="O133" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P133" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q133" s="9">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="R133" s="6" t="s">
         <v>24</v>
@@ -8452,10 +8431,10 @@
     </row>
     <row r="134">
       <c r="A134" s="6" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>86</v>
+        <v>129</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>24</v>
@@ -8470,37 +8449,37 @@
         <v>26</v>
       </c>
       <c r="G134" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="I134" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J134" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K134" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L134" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M134" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N134" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q134" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="R134" s="6" t="s">
         <v>24</v>
@@ -8511,10 +8490,10 @@
     </row>
     <row r="135">
       <c r="A135" s="6" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>24</v>
@@ -8529,37 +8508,37 @@
         <v>26</v>
       </c>
       <c r="G135" s="7">
-        <v>46238</v>
+        <v>46210</v>
       </c>
       <c r="H135" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I135" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J135" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K135" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L135" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M135" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N135" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O135" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P135" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q135" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="R135" s="6" t="s">
         <v>24</v>
@@ -8570,10 +8549,10 @@
     </row>
     <row r="136">
       <c r="A136" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>154</v>
+        <v>140</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>24</v>
@@ -8588,37 +8567,37 @@
         <v>26</v>
       </c>
       <c r="G136" s="7">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I136" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J136" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K136" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L136" s="8">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="M136" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N136" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O136" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q136" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="R136" s="6" t="s">
         <v>24</v>
@@ -8629,16 +8608,16 @@
     </row>
     <row r="137">
       <c r="A137" s="6" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>159</v>
+        <v>142</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>157</v>
+        <v>24</v>
       </c>
       <c r="E137" s="6" t="s">
         <v>25</v>
@@ -8650,34 +8629,34 @@
         <v>46238</v>
       </c>
       <c r="H137" s="6" t="s">
-        <v>84</v>
+        <v>27</v>
       </c>
       <c r="I137" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J137" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K137" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L137" s="8">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="M137" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N137" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O137" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P137" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q137" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="R137" s="6" t="s">
         <v>24</v>
@@ -8688,16 +8667,16 @@
     </row>
     <row r="138">
       <c r="A138" s="6" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>157</v>
+        <v>24</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>25</v>
@@ -8706,37 +8685,37 @@
         <v>26</v>
       </c>
       <c r="G138" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>84</v>
+        <v>44</v>
       </c>
       <c r="I138" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J138" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K138" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L138" s="8">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="M138" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N138" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q138" s="9">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="R138" s="6" t="s">
         <v>24</v>
@@ -8747,43 +8726,43 @@
     </row>
     <row r="139">
       <c r="A139" s="6" t="s">
-        <v>24</v>
+        <v>199</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>92</v>
+        <v>149</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="E139" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G139" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G139" s="7">
+        <v>46238</v>
       </c>
       <c r="H139" s="6" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="I139" s="7">
-        <v>45930</v>
+        <v>46265</v>
       </c>
       <c r="J139" s="7">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="K139" s="7">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="L139" s="8">
-        <v>185.5</v>
+        <v>1200</v>
       </c>
       <c r="M139" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N139" s="9">
         <v>25</v>
@@ -8792,7 +8771,7 @@
         <v>24</v>
       </c>
       <c r="P139" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q139" s="9">
         <v>25</v>
@@ -8806,16 +8785,16 @@
     </row>
     <row r="140">
       <c r="A140" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>24</v>
+        <v>150</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>25</v>
@@ -8824,10 +8803,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
       <c r="I140" s="7">
         <v>46265</v>
@@ -8839,22 +8818,22 @@
         <v>46265</v>
       </c>
       <c r="L140" s="8">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="M140" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="N140" s="9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="O140" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="Q140" s="9">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="R140" s="6" t="s">
         <v>24</v>
@@ -8863,382 +8842,28 @@
         <v>24</v>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="B141" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C141" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D141" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E141" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F141" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G141" s="7">
-        <v>46210</v>
-      </c>
-      <c r="H141" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I141" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J141" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K141" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L141" s="8">
-        <v>650</v>
-      </c>
-      <c r="M141" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="N141" s="9">
-        <v>26</v>
-      </c>
-      <c r="O141" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P141" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q141" s="9">
-        <v>26</v>
-      </c>
-      <c r="R141" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S141" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="B142" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E142" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F142" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G142" s="7">
-        <v>46212</v>
-      </c>
-      <c r="H142" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="I142" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J142" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K142" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L142" s="8">
-        <v>680</v>
-      </c>
-      <c r="M142" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="N142" s="9">
-        <v>26</v>
-      </c>
-      <c r="O142" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P142" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q142" s="9">
-        <v>26</v>
-      </c>
-      <c r="R142" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S142" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="6" t="s">
-        <v>204</v>
-      </c>
-      <c r="B143" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C143" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D143" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E143" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F143" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G143" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H143" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I143" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J143" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K143" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L143" s="8">
-        <v>700</v>
-      </c>
-      <c r="M143" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="N143" s="9">
-        <v>26</v>
-      </c>
-      <c r="O143" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P143" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q143" s="9">
-        <v>26</v>
-      </c>
-      <c r="R143" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S143" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="6" t="s">
-        <v>205</v>
-      </c>
-      <c r="B144" s="6" t="s">
-        <v>154</v>
-      </c>
-      <c r="C144" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D144" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E144" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F144" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G144" s="7">
-        <v>46225</v>
-      </c>
-      <c r="H144" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="I144" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J144" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K144" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L144" s="8">
-        <v>800</v>
-      </c>
-      <c r="M144" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="N144" s="9">
-        <v>26</v>
-      </c>
-      <c r="O144" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P144" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q144" s="9">
-        <v>26</v>
-      </c>
-      <c r="R144" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S144" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="B145" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="C145" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E145" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G145" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H145" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I145" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J145" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K145" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L145" s="8">
-        <v>1200</v>
-      </c>
-      <c r="M145" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="N145" s="9">
-        <v>26</v>
-      </c>
-      <c r="O145" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P145" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q145" s="9">
-        <v>26</v>
-      </c>
-      <c r="R145" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S145" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="B146" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="C146" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D146" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E146" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F146" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G146" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H146" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="I146" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J146" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K146" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L146" s="8">
-        <v>1200</v>
-      </c>
-      <c r="M146" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="N146" s="9">
-        <v>26</v>
-      </c>
-      <c r="O146" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P146" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q146" s="9">
-        <v>26</v>
-      </c>
-      <c r="R146" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S146" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="147" ht="23" customHeight="1">
-      <c r="A147" s="10"/>
-      <c r="B147" s="10"/>
-      <c r="C147" s="10"/>
-      <c r="D147" s="10"/>
-      <c r="E147" s="10"/>
-      <c r="F147" s="10"/>
-      <c r="G147" s="11"/>
-      <c r="H147" s="10"/>
-      <c r="I147" s="11"/>
-      <c r="J147" s="11"/>
-      <c r="K147" s="11"/>
-      <c r="L147" s="12">
-        <f>SUM(L6:L146)</f>
-      </c>
-      <c r="M147" s="10"/>
-      <c r="N147" s="13"/>
-      <c r="O147" s="10"/>
-      <c r="P147" s="10"/>
-      <c r="Q147" s="13"/>
-      <c r="R147" s="10"/>
-      <c r="S147" s="10"/>
+    <row r="141" ht="23" customHeight="1">
+      <c r="A141" s="10"/>
+      <c r="B141" s="10"/>
+      <c r="C141" s="10"/>
+      <c r="D141" s="10"/>
+      <c r="E141" s="10"/>
+      <c r="F141" s="10"/>
+      <c r="G141" s="11"/>
+      <c r="H141" s="10"/>
+      <c r="I141" s="11"/>
+      <c r="J141" s="11"/>
+      <c r="K141" s="11"/>
+      <c r="L141" s="12">
+        <f>SUM(L6:L140)</f>
+      </c>
+      <c r="M141" s="10"/>
+      <c r="N141" s="13"/>
+      <c r="O141" s="10"/>
+      <c r="P141" s="10"/>
+      <c r="Q141" s="13"/>
+      <c r="R141" s="10"/>
+      <c r="S141" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:S5"/>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$141</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$131</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="190">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quinta-feira, 6 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em sexta-feira, 7 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -124,15 +124,6 @@
     <t>VENCIDO ENTRE 31 A 90 DIAS</t>
   </si>
   <si>
-    <t>FA-11559</t>
-  </si>
-  <si>
-    <t>YURI BATISTA DA COSTA</t>
-  </si>
-  <si>
-    <t>FA-11562</t>
-  </si>
-  <si>
     <t>ND-11870</t>
   </si>
   <si>
@@ -151,13 +142,67 @@
     <t>FA-11884</t>
   </si>
   <si>
-    <t>FA-11834</t>
+    <t>FA-11838</t>
   </si>
   <si>
     <t>LEONARDO GOMES DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11836</t>
+    <t>FA-11945</t>
+  </si>
+  <si>
+    <t>RICARDO ARAUJO DE MIRANDA</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-12031</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11947</t>
+  </si>
+  <si>
+    <t>FA-11971</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11972</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11857</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-12017</t>
+  </si>
+  <si>
+    <t>FA-12019</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-11962</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-12016</t>
   </si>
   <si>
     <t>ELIONILSON CORDEIRO BARBOSA</t>
@@ -169,246 +214,162 @@
     <t>JOÃO PAULO CONSÓRCIOS</t>
   </si>
   <si>
-    <t>FA-11968</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
+    <t>FA-11849</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-12030</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>FA-11839</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>FA-12046</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-12052</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-11995</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-12034</t>
+  </si>
+  <si>
+    <t>FA-11975</t>
+  </si>
+  <si>
+    <t>FA-11976</t>
+  </si>
+  <si>
+    <t>FA-11858</t>
+  </si>
+  <si>
+    <t>FA-11921</t>
+  </si>
+  <si>
+    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
+  </si>
+  <si>
+    <t>FA-11963</t>
+  </si>
+  <si>
+    <t>FA-11998</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12021</t>
+  </si>
+  <si>
+    <t>FA-12022</t>
+  </si>
+  <si>
+    <t>FA-12035</t>
+  </si>
+  <si>
+    <t>FA-11991</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-12050</t>
+  </si>
+  <si>
+    <t>FA-12020</t>
+  </si>
+  <si>
+    <t>FA-11996</t>
+  </si>
+  <si>
+    <t>FA-11993</t>
+  </si>
+  <si>
+    <t>FA-11866</t>
+  </si>
+  <si>
+    <t>FA-11969</t>
+  </si>
+  <si>
+    <t>FA-11856</t>
+  </si>
+  <si>
+    <t>FA-12107</t>
+  </si>
+  <si>
+    <t>EDCARLOS MARTINS DA SILVA</t>
   </si>
   <si>
     <t>FA-11915</t>
   </si>
   <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11856</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>FA-11969</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11838</t>
-  </si>
-  <si>
-    <t>FA-11840</t>
-  </si>
-  <si>
-    <t>FA-11945</t>
-  </si>
-  <si>
-    <t>RICARDO ARAUJO DE MIRANDA</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-11971</t>
-  </si>
-  <si>
-    <t>FA-12031</t>
-  </si>
-  <si>
-    <t>FA-11947</t>
-  </si>
-  <si>
-    <t>FA-11972</t>
-  </si>
-  <si>
-    <t>FA-11857</t>
-  </si>
-  <si>
-    <t>FA-12044</t>
+    <t>FA-12010</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-12055</t>
+  </si>
+  <si>
+    <t>FA-12053</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12037</t>
+  </si>
+  <si>
+    <t>FA-11979</t>
+  </si>
+  <si>
+    <t>FA-12000</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11982</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-12001</t>
+  </si>
+  <si>
+    <t>FA-12054</t>
   </si>
   <si>
     <t>DANILO DE ALMEIDA TORRES</t>
   </si>
   <si>
-    <t>FA-11962</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-12019</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-12017</t>
-  </si>
-  <si>
-    <t>FA-12046</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-12016</t>
-  </si>
-  <si>
-    <t>FA-11849</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-12030</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>FA-11993</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11839</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>FA-11885</t>
-  </si>
-  <si>
-    <t>FA-11907</t>
-  </si>
-  <si>
-    <t>FA-11977</t>
-  </si>
-  <si>
-    <t>JOZILDO TARQUINO DE BRITO</t>
-  </si>
-  <si>
-    <t>FA-12052</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-11995</t>
-  </si>
-  <si>
-    <t>FA-11975</t>
-  </si>
-  <si>
-    <t>FA-12034</t>
-  </si>
-  <si>
-    <t>FA-11997</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-12049</t>
-  </si>
-  <si>
-    <t>FA-11858</t>
-  </si>
-  <si>
-    <t>FA-11976</t>
-  </si>
-  <si>
-    <t>FA-11921</t>
-  </si>
-  <si>
-    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
-  </si>
-  <si>
-    <t>FA-11963</t>
-  </si>
-  <si>
-    <t>FA-11998</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12021</t>
-  </si>
-  <si>
-    <t>FA-12022</t>
-  </si>
-  <si>
-    <t>FA-12035</t>
-  </si>
-  <si>
-    <t>FA-11991</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-12050</t>
-  </si>
-  <si>
-    <t>FA-11866</t>
-  </si>
-  <si>
-    <t>FA-12020</t>
-  </si>
-  <si>
-    <t>FA-11996</t>
-  </si>
-  <si>
-    <t>FA-11981</t>
-  </si>
-  <si>
-    <t>FA-12010</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-12055</t>
-  </si>
-  <si>
-    <t>FA-12053</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12000</t>
-  </si>
-  <si>
-    <t>FA-11979</t>
-  </si>
-  <si>
-    <t>FA-12037</t>
-  </si>
-  <si>
-    <t>FA-11982</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-12001</t>
-  </si>
-  <si>
-    <t>FA-12054</t>
-  </si>
-  <si>
     <t>FA-11860</t>
   </si>
   <si>
@@ -478,33 +439,30 @@
     <t>ANNY KATARINA ACIOLE DA SILVA</t>
   </si>
   <si>
+    <t>FA-11999</t>
+  </si>
+  <si>
+    <t>FA-12076</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
     <t>FA-12077</t>
   </si>
   <si>
     <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
   </si>
   <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-12076</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11999</t>
-  </si>
-  <si>
     <t>FA-12029</t>
   </si>
   <si>
     <t>FA-12011</t>
   </si>
   <si>
-    <t>FA-11985</t>
-  </si>
-  <si>
     <t>FA-12059</t>
   </si>
   <si>
@@ -514,51 +472,54 @@
     <t>FA-11983</t>
   </si>
   <si>
+    <t>FA-11986</t>
+  </si>
+  <si>
+    <t>FA-12040</t>
+  </si>
+  <si>
     <t>FA-12004</t>
   </si>
   <si>
-    <t>FA-12040</t>
-  </si>
-  <si>
-    <t>FA-11986</t>
-  </si>
-  <si>
     <t>FA-12008</t>
   </si>
   <si>
     <t>FA-12064</t>
   </si>
   <si>
+    <t>FA-12109</t>
+  </si>
+  <si>
+    <t>FA-11984</t>
+  </si>
+  <si>
+    <t>FA-11923</t>
+  </si>
+  <si>
     <t>FA-12058</t>
   </si>
   <si>
-    <t>FA-11984</t>
-  </si>
-  <si>
-    <t>FA-11923</t>
-  </si>
-  <si>
     <t>FA-11862</t>
   </si>
   <si>
     <t>FA-12041</t>
   </si>
   <si>
+    <t>FA-12028</t>
+  </si>
+  <si>
+    <t>FA-12027</t>
+  </si>
+  <si>
+    <t>FA-12005</t>
+  </si>
+  <si>
+    <t>FA-12043</t>
+  </si>
+  <si>
     <t>FA-11935</t>
   </si>
   <si>
-    <t>FA-12027</t>
-  </si>
-  <si>
-    <t>FA-12005</t>
-  </si>
-  <si>
-    <t>FA-12043</t>
-  </si>
-  <si>
-    <t>FA-12028</t>
-  </si>
-  <si>
     <t>FA-11965</t>
   </si>
   <si>
@@ -598,6 +559,9 @@
     <t>FA-11924</t>
   </si>
   <si>
+    <t>FA-12110</t>
+  </si>
+  <si>
     <t>FA-11936</t>
   </si>
   <si>
@@ -616,10 +580,13 @@
     <t>FA-12082</t>
   </si>
   <si>
+    <t>FA-12111</t>
+  </si>
+  <si>
+    <t>FA-11925</t>
+  </si>
+  <si>
     <t>FA-12066</t>
-  </si>
-  <si>
-    <t>FA-11925</t>
   </si>
   <si>
     <t>FA-11937</t>
@@ -777,7 +744,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S141"/>
+  <dimension ref="A1:S131"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1" style="1"/>
@@ -918,7 +885,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -927,7 +894,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-45</v>
+        <v>-46</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -944,7 +911,7 @@
         <v>31</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>24</v>
@@ -953,31 +920,31 @@
         <v>25</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>24</v>
+        <v>32</v>
+      </c>
+      <c r="G7" s="7">
+        <v>46190</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I7" s="7">
-        <v>46160</v>
+        <v>46174</v>
       </c>
       <c r="J7" s="7">
-        <v>46203</v>
+        <v>46209</v>
       </c>
       <c r="K7" s="7">
-        <v>46160</v>
+        <v>46225</v>
       </c>
       <c r="L7" s="8">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-37</v>
+        <v>-32</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -986,10 +953,10 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-80</v>
+        <v>-16</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>24</v>
@@ -997,13 +964,13 @@
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>24</v>
@@ -1021,31 +988,31 @@
         <v>27</v>
       </c>
       <c r="I8" s="7">
-        <v>46167</v>
+        <v>46202</v>
       </c>
       <c r="J8" s="7">
-        <v>46204</v>
+        <v>46212</v>
       </c>
       <c r="K8" s="7">
-        <v>46167</v>
+        <v>46202</v>
       </c>
       <c r="L8" s="8">
-        <v>110</v>
+        <v>300</v>
       </c>
       <c r="M8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-36</v>
+        <v>-29</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-73</v>
+        <v>-39</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -1056,13 +1023,13 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -1071,7 +1038,7 @@
         <v>25</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G9" s="7">
         <v>46190</v>
@@ -1083,10 +1050,10 @@
         <v>46174</v>
       </c>
       <c r="J9" s="7">
-        <v>46209</v>
+        <v>46216</v>
       </c>
       <c r="K9" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="L9" s="8">
         <v>50</v>
@@ -1095,19 +1062,19 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-31</v>
+        <v>-25</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-15</v>
+        <v>-9</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S9" s="6" t="s">
         <v>24</v>
@@ -1115,13 +1082,13 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>24</v>
@@ -1130,43 +1097,43 @@
         <v>25</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G10" s="7">
+        <v>46198</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="7">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="J10" s="7">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="K10" s="7">
-        <v>46202</v>
+        <v>46216</v>
       </c>
       <c r="L10" s="8">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-28</v>
+        <v>-25</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-38</v>
+        <v>-25</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S10" s="6" t="s">
         <v>24</v>
@@ -1174,13 +1141,13 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>24</v>
@@ -1189,7 +1156,7 @@
         <v>25</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="G11" s="7">
         <v>46190</v>
@@ -1201,10 +1168,10 @@
         <v>46174</v>
       </c>
       <c r="J11" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K11" s="7">
-        <v>46232</v>
+        <v>46239</v>
       </c>
       <c r="L11" s="8">
         <v>50</v>
@@ -1213,19 +1180,19 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-8</v>
+        <v>-2</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S11" s="6" t="s">
         <v>24</v>
@@ -1233,13 +1200,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>24</v>
@@ -1251,40 +1218,40 @@
         <v>26</v>
       </c>
       <c r="G12" s="7">
-        <v>46198</v>
+        <v>46182</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I12" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J12" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="K12" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L12" s="8">
-        <v>600</v>
+        <v>680</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S12" s="6" t="s">
         <v>24</v>
@@ -1292,11 +1259,11 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>40</v>
-      </c>
       <c r="C13" s="6" t="s">
         <v>24</v>
       </c>
@@ -1307,43 +1274,43 @@
         <v>25</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G13" s="7">
-        <v>46182</v>
+        <v>24</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I13" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="J13" s="7">
-        <v>46216</v>
+        <v>46225</v>
       </c>
       <c r="K13" s="7">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="L13" s="8">
-        <v>680</v>
+        <v>480</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-24</v>
+        <v>-16</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-24</v>
+        <v>-18</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S13" s="6" t="s">
         <v>24</v>
@@ -1351,58 +1318,58 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G14" s="7">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="I14" s="7">
-        <v>46216</v>
+        <v>46174</v>
       </c>
       <c r="J14" s="7">
-        <v>46216</v>
+        <v>46230</v>
       </c>
       <c r="K14" s="7">
-        <v>46216</v>
+        <v>46246</v>
       </c>
       <c r="L14" s="8">
-        <v>800</v>
+        <v>50</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-24</v>
+        <v>-11</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q14" s="9">
-        <v>-24</v>
+        <v>5</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S14" s="6" t="s">
         <v>24</v>
@@ -1410,13 +1377,13 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>24</v>
@@ -1425,43 +1392,43 @@
         <v>25</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G15" s="7">
-        <v>46190</v>
+        <v>46232</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I15" s="7">
-        <v>46174</v>
+        <v>46230</v>
       </c>
       <c r="J15" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K15" s="7">
-        <v>46239</v>
+        <v>46230</v>
       </c>
       <c r="L15" s="8">
-        <v>50</v>
+        <v>630</v>
       </c>
       <c r="M15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-1</v>
+        <v>-11</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>24</v>
@@ -1469,10 +1436,10 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>24</v>
@@ -1487,19 +1454,19 @@
         <v>26</v>
       </c>
       <c r="G16" s="7">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I16" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J16" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K16" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L16" s="8">
         <v>630</v>
@@ -1508,19 +1475,19 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S16" s="6" t="s">
         <v>24</v>
@@ -1528,10 +1495,10 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>24</v>
@@ -1546,19 +1513,19 @@
         <v>26</v>
       </c>
       <c r="G17" s="7">
-        <v>46203</v>
+        <v>46225</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I17" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J17" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K17" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L17" s="8">
         <v>630</v>
@@ -1567,19 +1534,19 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S17" s="6" t="s">
         <v>24</v>
@@ -1587,13 +1554,13 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>24</v>
@@ -1605,19 +1572,19 @@
         <v>26</v>
       </c>
       <c r="G18" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I18" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J18" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K18" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L18" s="8">
         <v>650</v>
@@ -1626,19 +1593,19 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S18" s="6" t="s">
         <v>24</v>
@@ -1646,13 +1613,13 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>24</v>
@@ -1664,19 +1631,19 @@
         <v>26</v>
       </c>
       <c r="G19" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I19" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J19" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K19" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L19" s="8">
         <v>650</v>
@@ -1685,19 +1652,19 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S19" s="6" t="s">
         <v>24</v>
@@ -1705,10 +1672,10 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>24</v>
@@ -1723,19 +1690,19 @@
         <v>26</v>
       </c>
       <c r="G20" s="7">
-        <v>46182</v>
+        <v>46232</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I20" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J20" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K20" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L20" s="8">
         <v>680</v>
@@ -1744,19 +1711,19 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S20" s="6" t="s">
         <v>24</v>
@@ -1764,10 +1731,10 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>24</v>
@@ -1776,46 +1743,46 @@
         <v>24</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G21" s="7">
-        <v>46182</v>
+        <v>46232</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="I21" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J21" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K21" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L21" s="8">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S21" s="6" t="s">
         <v>24</v>
@@ -1823,10 +1790,10 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>24</v>
@@ -1838,43 +1805,43 @@
         <v>25</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G22" s="7">
+        <v>46225</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I22" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="J22" s="7">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="K22" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="L22" s="8">
-        <v>480</v>
+        <v>680</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-15</v>
+        <v>-11</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-17</v>
+        <v>-11</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S22" s="6" t="s">
         <v>24</v>
@@ -1882,58 +1849,58 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>33</v>
+        <v>56</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="G23" s="7">
-        <v>46190</v>
+        <v>46232</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="I23" s="7">
-        <v>46174</v>
+        <v>46230</v>
       </c>
       <c r="J23" s="7">
         <v>46230</v>
       </c>
       <c r="K23" s="7">
-        <v>46246</v>
+        <v>46230</v>
       </c>
       <c r="L23" s="8">
-        <v>50</v>
+        <v>750</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P23" s="6" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>6</v>
+        <v>-11</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S23" s="6" t="s">
         <v>24</v>
@@ -1941,10 +1908,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>24</v>
@@ -1956,25 +1923,25 @@
         <v>25</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I24" s="7">
-        <v>46230</v>
+        <v>46188</v>
       </c>
       <c r="J24" s="7">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K24" s="7">
-        <v>46230</v>
+        <v>46188</v>
       </c>
       <c r="L24" s="8">
-        <v>630</v>
+        <v>16.66</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>28</v>
@@ -1983,16 +1950,16 @@
         <v>-10</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-10</v>
+        <v>-53</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="S24" s="6" t="s">
         <v>24</v>
@@ -2000,10 +1967,10 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>24</v>
@@ -2015,10 +1982,10 @@
         <v>25</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>27</v>
@@ -2027,13 +1994,13 @@
         <v>46230</v>
       </c>
       <c r="J25" s="7">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K25" s="7">
         <v>46230</v>
       </c>
       <c r="L25" s="8">
-        <v>630</v>
+        <v>42.03</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>28</v>
@@ -2042,16 +2009,16 @@
         <v>-10</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S25" s="6" t="s">
         <v>24</v>
@@ -2059,10 +2026,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>24</v>
@@ -2074,22 +2041,22 @@
         <v>25</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="7">
-        <v>46212</v>
+        <v>24</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I26" s="7">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="J26" s="7">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="K26" s="7">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="L26" s="8">
         <v>630</v>
@@ -2098,19 +2065,19 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-10</v>
+        <v>-9</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-10</v>
+        <v>-18</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>24</v>
@@ -2118,13 +2085,13 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>24</v>
@@ -2133,43 +2100,43 @@
         <v>25</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G27" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I27" s="7">
-        <v>46230</v>
+        <v>45930</v>
       </c>
       <c r="J27" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="K27" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="L27" s="8">
-        <v>650</v>
+        <v>185.5</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S27" s="6" t="s">
         <v>24</v>
@@ -2177,58 +2144,58 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B28" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H28" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G28" s="7">
+      <c r="I28" s="7">
         <v>46188</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I28" s="7">
-        <v>46230</v>
-      </c>
       <c r="J28" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K28" s="7">
-        <v>46230</v>
+        <v>46188</v>
       </c>
       <c r="L28" s="8">
-        <v>650</v>
+        <v>116.7</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-10</v>
+        <v>-53</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="S28" s="6" t="s">
         <v>24</v>
@@ -2236,25 +2203,25 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>27</v>
@@ -2263,31 +2230,31 @@
         <v>46230</v>
       </c>
       <c r="J29" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K29" s="7">
         <v>46230</v>
       </c>
       <c r="L29" s="8">
-        <v>650</v>
+        <v>560</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S29" s="6" t="s">
         <v>24</v>
@@ -2295,13 +2262,13 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>24</v>
@@ -2313,40 +2280,40 @@
         <v>26</v>
       </c>
       <c r="G30" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I30" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J30" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K30" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L30" s="8">
-        <v>680</v>
+        <v>620</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S30" s="6" t="s">
         <v>24</v>
@@ -2354,10 +2321,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>24</v>
@@ -2372,40 +2339,40 @@
         <v>26</v>
       </c>
       <c r="G31" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I31" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J31" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K31" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L31" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S31" s="6" t="s">
         <v>24</v>
@@ -2413,10 +2380,10 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>24</v>
@@ -2437,34 +2404,34 @@
         <v>27</v>
       </c>
       <c r="I32" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J32" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K32" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L32" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S32" s="6" t="s">
         <v>24</v>
@@ -2472,16 +2439,16 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E33" s="6" t="s">
         <v>25</v>
@@ -2490,40 +2457,40 @@
         <v>26</v>
       </c>
       <c r="G33" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I33" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J33" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K33" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L33" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S33" s="6" t="s">
         <v>24</v>
@@ -2531,58 +2498,58 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="I34" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J34" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K34" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L34" s="8">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S34" s="6" t="s">
         <v>24</v>
@@ -2590,10 +2557,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>24</v>
@@ -2605,43 +2572,43 @@
         <v>25</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G35" s="7">
+        <v>46188</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I35" s="7">
-        <v>46188</v>
+        <v>46237</v>
       </c>
       <c r="J35" s="7">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="K35" s="7">
-        <v>46188</v>
+        <v>46237</v>
       </c>
       <c r="L35" s="8">
-        <v>16.66</v>
+        <v>650</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-52</v>
+        <v>-4</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S35" s="6" t="s">
         <v>24</v>
@@ -2664,43 +2631,43 @@
         <v>25</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G36" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G36" s="7">
+        <v>46210</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I36" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J36" s="7">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="K36" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L36" s="8">
-        <v>42.03</v>
+        <v>650</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-9</v>
+        <v>-4</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>24</v>
@@ -2711,7 +2678,7 @@
         <v>79</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>24</v>
@@ -2723,43 +2690,43 @@
         <v>25</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G37" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G37" s="7">
+        <v>46225</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I37" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J37" s="7">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="K37" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L37" s="8">
-        <v>495.15</v>
+        <v>680</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-10</v>
+        <v>-4</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S37" s="6" t="s">
         <v>24</v>
@@ -2767,11 +2734,11 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="B38" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>69</v>
-      </c>
       <c r="C38" s="6" t="s">
         <v>24</v>
       </c>
@@ -2782,43 +2749,43 @@
         <v>25</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G38" s="7">
+        <v>46225</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I38" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="J38" s="7">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="K38" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="L38" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-8</v>
+        <v>-4</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S38" s="6" t="s">
         <v>24</v>
@@ -2826,10 +2793,10 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="s">
-        <v>24</v>
+        <v>82</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>24</v>
@@ -2841,43 +2808,43 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G39" s="7">
+        <v>46232</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I39" s="7">
-        <v>45930</v>
+        <v>46237</v>
       </c>
       <c r="J39" s="7">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="K39" s="7">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="L39" s="8">
-        <v>185.5</v>
+        <v>680</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S39" s="6" t="s">
         <v>24</v>
@@ -2891,7 +2858,7 @@
         <v>53</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>24</v>
@@ -2900,43 +2867,43 @@
         <v>25</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G40" s="7">
+        <v>46232</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I40" s="7">
-        <v>46216</v>
+        <v>46237</v>
       </c>
       <c r="J40" s="7">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="K40" s="7">
-        <v>46216</v>
+        <v>46237</v>
       </c>
       <c r="L40" s="8">
-        <v>250</v>
+        <v>680</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-24</v>
+        <v>-4</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S40" s="6" t="s">
         <v>24</v>
@@ -2947,55 +2914,55 @@
         <v>84</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E41" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G41" s="7">
+        <v>46232</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I41" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="J41" s="7">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="K41" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="L41" s="8">
-        <v>560</v>
+        <v>680</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-17</v>
+        <v>-4</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S41" s="6" t="s">
         <v>24</v>
@@ -3003,10 +2970,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>24</v>
@@ -3024,37 +2991,37 @@
         <v>24</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="I42" s="7">
-        <v>46188</v>
+        <v>46230</v>
       </c>
       <c r="J42" s="7">
         <v>46237</v>
       </c>
       <c r="K42" s="7">
-        <v>46188</v>
+        <v>46230</v>
       </c>
       <c r="L42" s="8">
-        <v>116.7</v>
+        <v>700</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-52</v>
+        <v>-11</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S42" s="6" t="s">
         <v>24</v>
@@ -3062,16 +3029,16 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="E43" s="6" t="s">
         <v>25</v>
@@ -3080,7 +3047,7 @@
         <v>26</v>
       </c>
       <c r="G43" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>27</v>
@@ -3095,25 +3062,25 @@
         <v>46237</v>
       </c>
       <c r="L43" s="8">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O43" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S43" s="6" t="s">
         <v>24</v>
@@ -3121,19 +3088,19 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
@@ -3142,7 +3109,7 @@
         <v>46232</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I44" s="7">
         <v>46237</v>
@@ -3154,25 +3121,25 @@
         <v>46237</v>
       </c>
       <c r="L44" s="8">
-        <v>620</v>
+        <v>750</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S44" s="6" t="s">
         <v>24</v>
@@ -3180,10 +3147,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>24</v>
@@ -3201,7 +3168,7 @@
         <v>46225</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="I45" s="7">
         <v>46237</v>
@@ -3213,25 +3180,25 @@
         <v>46237</v>
       </c>
       <c r="L45" s="8">
-        <v>630</v>
+        <v>1200</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S45" s="6" t="s">
         <v>24</v>
@@ -3239,10 +3206,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>24</v>
@@ -3254,25 +3221,25 @@
         <v>25</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G46" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H46" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I46" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="J46" s="7">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K46" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="L46" s="8">
-        <v>630</v>
+        <v>215.15</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>28</v>
@@ -3281,16 +3248,16 @@
         <v>-3</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q46" s="9">
-        <v>-3</v>
+        <v>-11</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S46" s="6" t="s">
         <v>24</v>
@@ -3298,10 +3265,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>24</v>
@@ -3313,25 +3280,25 @@
         <v>25</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G47" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I47" s="7">
         <v>46237</v>
       </c>
       <c r="J47" s="7">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K47" s="7">
         <v>46237</v>
       </c>
       <c r="L47" s="8">
-        <v>630</v>
+        <v>300</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>28</v>
@@ -3340,16 +3307,16 @@
         <v>-3</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S47" s="6" t="s">
         <v>24</v>
@@ -3357,13 +3324,13 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>93</v>
+        <v>47</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>24</v>
@@ -3372,25 +3339,25 @@
         <v>25</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G48" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I48" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="J48" s="7">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K48" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="L48" s="8">
-        <v>630</v>
+        <v>450</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>28</v>
@@ -3399,16 +3366,16 @@
         <v>-3</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>-3</v>
+        <v>-18</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S48" s="6" t="s">
         <v>24</v>
@@ -3419,7 +3386,7 @@
         <v>94</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>24</v>
@@ -3431,25 +3398,25 @@
         <v>25</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G49" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I49" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="J49" s="7">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K49" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="L49" s="8">
-        <v>650</v>
+        <v>550</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>28</v>
@@ -3458,16 +3425,16 @@
         <v>-3</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>-3</v>
+        <v>-18</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S49" s="6" t="s">
         <v>24</v>
@@ -3478,7 +3445,7 @@
         <v>95</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>24</v>
@@ -3493,40 +3460,40 @@
         <v>26</v>
       </c>
       <c r="G50" s="7">
-        <v>46188</v>
+        <v>46240</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I50" s="7">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="J50" s="7">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="K50" s="7">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="L50" s="8">
-        <v>650</v>
+        <v>464.29</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S50" s="6" t="s">
         <v>24</v>
@@ -3534,13 +3501,13 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>24</v>
@@ -3549,43 +3516,43 @@
         <v>25</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G51" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G51" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I51" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="J51" s="7">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="K51" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="L51" s="8">
-        <v>650</v>
+        <v>480</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="P51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>-3</v>
+        <v>-18</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="S51" s="6" t="s">
         <v>24</v>
@@ -3593,13 +3560,13 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>24</v>
@@ -3611,40 +3578,40 @@
         <v>26</v>
       </c>
       <c r="G52" s="7">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I52" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J52" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K52" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L52" s="8">
-        <v>650</v>
+        <v>600</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N52" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q52" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S52" s="6" t="s">
         <v>24</v>
@@ -3652,13 +3619,13 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>24</v>
@@ -3670,40 +3637,40 @@
         <v>26</v>
       </c>
       <c r="G53" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I53" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J53" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K53" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L53" s="8">
-        <v>680</v>
+        <v>620</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N53" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q53" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S53" s="6" t="s">
         <v>24</v>
@@ -3711,16 +3678,16 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>25</v>
@@ -3729,40 +3696,40 @@
         <v>26</v>
       </c>
       <c r="G54" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I54" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J54" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K54" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L54" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N54" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q54" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S54" s="6" t="s">
         <v>24</v>
@@ -3770,10 +3737,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>24</v>
@@ -3794,34 +3761,34 @@
         <v>27</v>
       </c>
       <c r="I55" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J55" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K55" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L55" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N55" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q55" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S55" s="6" t="s">
         <v>24</v>
@@ -3829,10 +3796,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>24</v>
@@ -3847,40 +3814,40 @@
         <v>26</v>
       </c>
       <c r="G56" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H56" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I56" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J56" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K56" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L56" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N56" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q56" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S56" s="6" t="s">
         <v>24</v>
@@ -3888,10 +3855,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>24</v>
@@ -3906,40 +3873,40 @@
         <v>26</v>
       </c>
       <c r="G57" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I57" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J57" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K57" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L57" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N57" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q57" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S57" s="6" t="s">
         <v>24</v>
@@ -3947,10 +3914,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>24</v>
@@ -3962,43 +3929,43 @@
         <v>25</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G58" s="7">
+        <v>46225</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="I58" s="7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="J58" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K58" s="7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="L58" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N58" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q58" s="9">
-        <v>-10</v>
+        <v>3</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S58" s="6" t="s">
         <v>24</v>
@@ -4006,7 +3973,7 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>72</v>
@@ -4015,7 +3982,7 @@
         <v>24</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E59" s="6" t="s">
         <v>25</v>
@@ -4024,40 +3991,40 @@
         <v>26</v>
       </c>
       <c r="G59" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H59" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I59" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J59" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K59" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L59" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N59" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q59" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S59" s="6" t="s">
         <v>24</v>
@@ -4065,10 +4032,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
@@ -4083,40 +4050,40 @@
         <v>26</v>
       </c>
       <c r="G60" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I60" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J60" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K60" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L60" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N60" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q60" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S60" s="6" t="s">
         <v>24</v>
@@ -4124,10 +4091,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>24</v>
@@ -4136,46 +4103,46 @@
         <v>24</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="I61" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J61" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K61" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L61" s="8">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N61" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q61" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S61" s="6" t="s">
         <v>24</v>
@@ -4183,13 +4150,13 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>24</v>
@@ -4204,37 +4171,37 @@
         <v>46225</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="I62" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J62" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K62" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L62" s="8">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="N62" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q62" s="9">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S62" s="6" t="s">
         <v>24</v>
@@ -4242,13 +4209,13 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>24</v>
@@ -4260,7 +4227,7 @@
         <v>26</v>
       </c>
       <c r="G63" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H63" s="6" t="s">
         <v>27</v>
@@ -4275,22 +4242,22 @@
         <v>46244</v>
       </c>
       <c r="L63" s="8">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N63" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q63" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>24</v>
@@ -4301,13 +4268,13 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>24</v>
@@ -4319,7 +4286,7 @@
         <v>26</v>
       </c>
       <c r="G64" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H64" s="6" t="s">
         <v>27</v>
@@ -4334,22 +4301,22 @@
         <v>46244</v>
       </c>
       <c r="L64" s="8">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N64" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q64" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R64" s="6" t="s">
         <v>24</v>
@@ -4360,13 +4327,13 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>24</v>
@@ -4381,7 +4348,7 @@
         <v>46232</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I65" s="7">
         <v>46244</v>
@@ -4393,22 +4360,22 @@
         <v>46244</v>
       </c>
       <c r="L65" s="8">
-        <v>620</v>
+        <v>670</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N65" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O65" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q65" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>24</v>
@@ -4419,16 +4386,16 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>117</v>
+        <v>55</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>25</v>
@@ -4437,10 +4404,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I66" s="7">
         <v>46244</v>
@@ -4452,22 +4419,22 @@
         <v>46244</v>
       </c>
       <c r="L66" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N66" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q66" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>24</v>
@@ -4478,10 +4445,10 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>24</v>
@@ -4496,7 +4463,7 @@
         <v>26</v>
       </c>
       <c r="G67" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H67" s="6" t="s">
         <v>27</v>
@@ -4511,22 +4478,22 @@
         <v>46244</v>
       </c>
       <c r="L67" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N67" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q67" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>24</v>
@@ -4537,10 +4504,10 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>24</v>
@@ -4555,7 +4522,7 @@
         <v>26</v>
       </c>
       <c r="G68" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>27</v>
@@ -4570,22 +4537,22 @@
         <v>46244</v>
       </c>
       <c r="L68" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N68" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q68" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>24</v>
@@ -4596,10 +4563,10 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>24</v>
@@ -4629,22 +4596,22 @@
         <v>46244</v>
       </c>
       <c r="L69" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N69" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q69" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>24</v>
@@ -4655,10 +4622,10 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>122</v>
+        <v>63</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>24</v>
@@ -4673,7 +4640,7 @@
         <v>26</v>
       </c>
       <c r="G70" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>27</v>
@@ -4688,22 +4655,22 @@
         <v>46244</v>
       </c>
       <c r="L70" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N70" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q70" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>24</v>
@@ -4714,10 +4681,10 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>24</v>
@@ -4735,7 +4702,7 @@
         <v>46225</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I71" s="7">
         <v>46244</v>
@@ -4747,22 +4714,22 @@
         <v>46244</v>
       </c>
       <c r="L71" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N71" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q71" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>24</v>
@@ -4773,10 +4740,10 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>65</v>
+        <v>127</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>24</v>
@@ -4791,10 +4758,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="7">
-        <v>46232</v>
+        <v>46212</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I72" s="7">
         <v>46244</v>
@@ -4806,22 +4773,22 @@
         <v>46244</v>
       </c>
       <c r="L72" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N72" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q72" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4832,10 +4799,10 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>24</v>
@@ -4850,10 +4817,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="7">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I73" s="7">
         <v>46244</v>
@@ -4865,22 +4832,22 @@
         <v>46244</v>
       </c>
       <c r="L73" s="8">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N73" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q73" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4891,13 +4858,13 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>24</v>
@@ -4909,10 +4876,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I74" s="7">
         <v>46244</v>
@@ -4924,22 +4891,22 @@
         <v>46244</v>
       </c>
       <c r="L74" s="8">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N74" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q74" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -4950,16 +4917,16 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>98</v>
+        <v>67</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="E75" s="6" t="s">
         <v>25</v>
@@ -4968,7 +4935,7 @@
         <v>26</v>
       </c>
       <c r="G75" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>27</v>
@@ -4983,22 +4950,22 @@
         <v>46244</v>
       </c>
       <c r="L75" s="8">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N75" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q75" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -5009,10 +4976,10 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>129</v>
+        <v>57</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>24</v>
@@ -5021,7 +4988,7 @@
         <v>24</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
@@ -5030,7 +4997,7 @@
         <v>46232</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="I76" s="7">
         <v>46244</v>
@@ -5042,22 +5009,22 @@
         <v>46244</v>
       </c>
       <c r="L76" s="8">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N76" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q76" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -5068,10 +5035,10 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>24</v>
@@ -5086,10 +5053,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="I77" s="7">
         <v>46244</v>
@@ -5101,22 +5068,22 @@
         <v>46244</v>
       </c>
       <c r="L77" s="8">
-        <v>670</v>
+        <v>800</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N77" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q77" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5127,10 +5094,10 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>67</v>
+        <v>86</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -5148,7 +5115,7 @@
         <v>46225</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="I78" s="7">
         <v>46244</v>
@@ -5160,22 +5127,22 @@
         <v>46244</v>
       </c>
       <c r="L78" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N78" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q78" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5186,16 +5153,16 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>40</v>
+        <v>137</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="E79" s="6" t="s">
         <v>25</v>
@@ -5204,10 +5171,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="I79" s="7">
         <v>46244</v>
@@ -5219,22 +5186,22 @@
         <v>46244</v>
       </c>
       <c r="L79" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N79" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q79" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5245,16 +5212,16 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>69</v>
+        <v>140</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>25</v>
@@ -5263,10 +5230,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="I80" s="7">
         <v>46244</v>
@@ -5278,22 +5245,22 @@
         <v>46244</v>
       </c>
       <c r="L80" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N80" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q80" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5304,10 +5271,10 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5319,28 +5286,28 @@
         <v>25</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G81" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I81" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="J81" s="7">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K81" s="7">
-        <v>46244</v>
+        <v>46237</v>
       </c>
       <c r="L81" s="8">
-        <v>680</v>
+        <v>316.64</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N81" s="9">
         <v>4</v>
@@ -5349,13 +5316,13 @@
         <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>58</v>
+        <v>28</v>
       </c>
       <c r="Q81" s="9">
-        <v>4</v>
+        <v>-4</v>
       </c>
       <c r="R81" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S81" s="6" t="s">
         <v>24</v>
@@ -5363,13 +5330,13 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>24</v>
@@ -5381,37 +5348,37 @@
         <v>26</v>
       </c>
       <c r="G82" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I82" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J82" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K82" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L82" s="8">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N82" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q82" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5422,13 +5389,13 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>24</v>
@@ -5440,37 +5407,37 @@
         <v>26</v>
       </c>
       <c r="G83" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I83" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J83" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K83" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L83" s="8">
-        <v>680</v>
+        <v>620</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N83" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q83" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5481,16 +5448,16 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>25</v>
@@ -5499,37 +5466,37 @@
         <v>26</v>
       </c>
       <c r="G84" s="7">
-        <v>46212</v>
+        <v>46232</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I84" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J84" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K84" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L84" s="8">
-        <v>680</v>
+        <v>630</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N84" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q84" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5540,10 +5507,10 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>142</v>
+        <v>45</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>24</v>
@@ -5558,37 +5525,37 @@
         <v>26</v>
       </c>
       <c r="G85" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H85" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I85" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J85" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K85" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L85" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N85" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q85" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5599,10 +5566,10 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>76</v>
+        <v>108</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>24</v>
@@ -5617,37 +5584,37 @@
         <v>26</v>
       </c>
       <c r="G86" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I86" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J86" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K86" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L86" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N86" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q86" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5658,16 +5625,16 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>25</v>
@@ -5682,31 +5649,31 @@
         <v>27</v>
       </c>
       <c r="I87" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J87" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K87" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L87" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N87" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q87" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5717,10 +5684,10 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>24</v>
@@ -5729,43 +5696,43 @@
         <v>24</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G88" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="I88" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J88" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K88" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L88" s="8">
-        <v>750</v>
+        <v>630</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N88" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q88" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5776,10 +5743,10 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>24</v>
@@ -5797,34 +5764,34 @@
         <v>46225</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="I89" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J89" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K89" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L89" s="8">
-        <v>800</v>
+        <v>630</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N89" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q89" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5835,16 +5802,16 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>25</v>
@@ -5853,37 +5820,37 @@
         <v>26</v>
       </c>
       <c r="G90" s="7">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="I90" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J90" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K90" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L90" s="8">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N90" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q90" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5897,13 +5864,13 @@
         <v>151</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>25</v>
@@ -5912,37 +5879,37 @@
         <v>26</v>
       </c>
       <c r="G91" s="7">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="I91" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J91" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K91" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L91" s="8">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N91" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q91" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -5953,13 +5920,13 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>24</v>
@@ -5974,34 +5941,34 @@
         <v>46225</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="I92" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J92" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K92" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L92" s="8">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N92" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q92" s="9">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -6012,10 +5979,10 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>136</v>
+        <v>78</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>24</v>
@@ -6027,43 +5994,43 @@
         <v>25</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G93" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G93" s="7">
+        <v>46210</v>
       </c>
       <c r="H93" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I93" s="7">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="J93" s="7">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="K93" s="7">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="L93" s="8">
-        <v>316.64</v>
+        <v>650</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N93" s="9">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="Q93" s="9">
-        <v>-3</v>
+        <v>10</v>
       </c>
       <c r="R93" s="6" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="S93" s="6" t="s">
         <v>24</v>
@@ -6071,13 +6038,13 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>114</v>
+        <v>24</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>24</v>
@@ -6089,7 +6056,7 @@
         <v>26</v>
       </c>
       <c r="G94" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H94" s="6" t="s">
         <v>27</v>
@@ -6104,22 +6071,22 @@
         <v>46251</v>
       </c>
       <c r="L94" s="8">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N94" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q94" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6130,13 +6097,13 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>86</v>
+        <v>24</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>24</v>
@@ -6148,10 +6115,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I95" s="7">
         <v>46251</v>
@@ -6163,22 +6130,22 @@
         <v>46251</v>
       </c>
       <c r="L95" s="8">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N95" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q95" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6189,13 +6156,13 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>24</v>
@@ -6210,7 +6177,7 @@
         <v>46232</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I96" s="7">
         <v>46251</v>
@@ -6222,22 +6189,22 @@
         <v>46251</v>
       </c>
       <c r="L96" s="8">
-        <v>620</v>
+        <v>670</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N96" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q96" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6248,16 +6215,16 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>117</v>
+        <v>37</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>25</v>
@@ -6281,22 +6248,22 @@
         <v>46251</v>
       </c>
       <c r="L97" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N97" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q97" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6307,10 +6274,10 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>24</v>
@@ -6325,7 +6292,7 @@
         <v>26</v>
       </c>
       <c r="G98" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>27</v>
@@ -6340,22 +6307,22 @@
         <v>46251</v>
       </c>
       <c r="L98" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N98" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q98" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6366,10 +6333,10 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>24</v>
@@ -6387,7 +6354,7 @@
         <v>46225</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I99" s="7">
         <v>46251</v>
@@ -6399,22 +6366,22 @@
         <v>46251</v>
       </c>
       <c r="L99" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N99" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q99" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6425,10 +6392,10 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>24</v>
@@ -6458,22 +6425,22 @@
         <v>46251</v>
       </c>
       <c r="L100" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N100" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q100" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6484,10 +6451,10 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>24</v>
@@ -6502,10 +6469,10 @@
         <v>26</v>
       </c>
       <c r="G101" s="7">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I101" s="7">
         <v>46251</v>
@@ -6517,22 +6484,22 @@
         <v>46251</v>
       </c>
       <c r="L101" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M101" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N101" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q101" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6543,10 +6510,10 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>24</v>
@@ -6564,7 +6531,7 @@
         <v>46225</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I102" s="7">
         <v>46251</v>
@@ -6576,22 +6543,22 @@
         <v>46251</v>
       </c>
       <c r="L102" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N102" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q102" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6602,10 +6569,10 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>24</v>
@@ -6635,22 +6602,22 @@
         <v>46251</v>
       </c>
       <c r="L103" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N103" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q103" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6661,10 +6628,10 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>24</v>
@@ -6679,10 +6646,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I104" s="7">
         <v>46251</v>
@@ -6694,22 +6661,22 @@
         <v>46251</v>
       </c>
       <c r="L104" s="8">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N104" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q104" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6720,16 +6687,16 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>25</v>
@@ -6738,7 +6705,7 @@
         <v>26</v>
       </c>
       <c r="G105" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H105" s="6" t="s">
         <v>27</v>
@@ -6753,22 +6720,22 @@
         <v>46251</v>
       </c>
       <c r="L105" s="8">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N105" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q105" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6779,10 +6746,10 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>24</v>
@@ -6797,7 +6764,7 @@
         <v>26</v>
       </c>
       <c r="G106" s="7">
-        <v>46210</v>
+        <v>46238</v>
       </c>
       <c r="H106" s="6" t="s">
         <v>27</v>
@@ -6812,22 +6779,22 @@
         <v>46251</v>
       </c>
       <c r="L106" s="8">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N106" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q106" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>
@@ -6838,10 +6805,10 @@
     </row>
     <row r="107">
       <c r="A107" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>24</v>
@@ -6850,16 +6817,16 @@
         <v>24</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="F107" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H107" s="6" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I107" s="7">
         <v>46251</v>
@@ -6871,22 +6838,22 @@
         <v>46251</v>
       </c>
       <c r="L107" s="8">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N107" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q107" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>24</v>
@@ -6897,10 +6864,10 @@
     </row>
     <row r="108">
       <c r="A108" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>24</v>
@@ -6915,10 +6882,10 @@
         <v>26</v>
       </c>
       <c r="G108" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="I108" s="7">
         <v>46251</v>
@@ -6930,22 +6897,22 @@
         <v>46251</v>
       </c>
       <c r="L108" s="8">
-        <v>670</v>
+        <v>800</v>
       </c>
       <c r="M108" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N108" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q108" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>24</v>
@@ -6956,16 +6923,16 @@
     </row>
     <row r="109">
       <c r="A109" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="E109" s="6" t="s">
         <v>25</v>
@@ -6974,10 +6941,10 @@
         <v>26</v>
       </c>
       <c r="G109" s="7">
-        <v>46212</v>
+        <v>46238</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="I109" s="7">
         <v>46251</v>
@@ -6989,22 +6956,22 @@
         <v>46251</v>
       </c>
       <c r="L109" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N109" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P109" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q109" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R109" s="6" t="s">
         <v>24</v>
@@ -7015,10 +6982,10 @@
     </row>
     <row r="110">
       <c r="A110" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>24</v>
@@ -7033,10 +7000,10 @@
         <v>26</v>
       </c>
       <c r="G110" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="I110" s="7">
         <v>46251</v>
@@ -7048,22 +7015,22 @@
         <v>46251</v>
       </c>
       <c r="L110" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N110" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q110" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R110" s="6" t="s">
         <v>24</v>
@@ -7074,16 +7041,16 @@
     </row>
     <row r="111">
       <c r="A111" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="E111" s="6" t="s">
         <v>25</v>
@@ -7092,10 +7059,10 @@
         <v>26</v>
       </c>
       <c r="G111" s="7">
-        <v>46225</v>
+        <v>46238</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>51</v>
+        <v>87</v>
       </c>
       <c r="I111" s="7">
         <v>46251</v>
@@ -7107,22 +7074,22 @@
         <v>46251</v>
       </c>
       <c r="L111" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M111" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N111" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P111" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q111" s="9">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R111" s="6" t="s">
         <v>24</v>
@@ -7133,10 +7100,10 @@
     </row>
     <row r="112">
       <c r="A112" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>136</v>
+        <v>49</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>24</v>
@@ -7151,37 +7118,37 @@
         <v>26</v>
       </c>
       <c r="G112" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I112" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J112" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K112" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L112" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N112" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q112" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R112" s="6" t="s">
         <v>24</v>
@@ -7192,10 +7159,10 @@
     </row>
     <row r="113">
       <c r="A113" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>40</v>
+        <v>116</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>24</v>
@@ -7216,31 +7183,31 @@
         <v>27</v>
       </c>
       <c r="I113" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J113" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K113" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L113" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N113" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q113" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R113" s="6" t="s">
         <v>24</v>
@@ -7251,10 +7218,10 @@
     </row>
     <row r="114">
       <c r="A114" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>24</v>
@@ -7269,37 +7236,37 @@
         <v>26</v>
       </c>
       <c r="G114" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I114" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J114" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K114" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L114" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N114" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q114" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R114" s="6" t="s">
         <v>24</v>
@@ -7310,10 +7277,10 @@
     </row>
     <row r="115">
       <c r="A115" s="6" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>24</v>
@@ -7328,37 +7295,37 @@
         <v>26</v>
       </c>
       <c r="G115" s="7">
-        <v>46232</v>
+        <v>46240</v>
       </c>
       <c r="H115" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I115" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J115" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K115" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L115" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M115" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N115" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O115" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P115" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q115" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R115" s="6" t="s">
         <v>24</v>
@@ -7369,10 +7336,10 @@
     </row>
     <row r="116">
       <c r="A116" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>76</v>
+        <v>127</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>24</v>
@@ -7387,37 +7354,37 @@
         <v>26</v>
       </c>
       <c r="G116" s="7">
-        <v>46188</v>
+        <v>46212</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="I116" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J116" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K116" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L116" s="8">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="M116" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N116" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q116" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R116" s="6" t="s">
         <v>24</v>
@@ -7428,16 +7395,16 @@
     </row>
     <row r="117">
       <c r="A117" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>73</v>
+        <v>24</v>
       </c>
       <c r="E117" s="6" t="s">
         <v>25</v>
@@ -7446,37 +7413,37 @@
         <v>26</v>
       </c>
       <c r="G117" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H117" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I117" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J117" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K117" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L117" s="8">
         <v>700</v>
       </c>
       <c r="M117" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N117" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O117" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P117" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q117" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R117" s="6" t="s">
         <v>24</v>
@@ -7487,10 +7454,10 @@
     </row>
     <row r="118">
       <c r="A118" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>24</v>
@@ -7511,31 +7478,31 @@
         <v>27</v>
       </c>
       <c r="I118" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J118" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K118" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L118" s="8">
         <v>700</v>
       </c>
       <c r="M118" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N118" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q118" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R118" s="6" t="s">
         <v>24</v>
@@ -7546,10 +7513,10 @@
     </row>
     <row r="119">
       <c r="A119" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>42</v>
+        <v>134</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>24</v>
@@ -7558,43 +7525,43 @@
         <v>24</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="F119" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H119" s="6" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="I119" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J119" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K119" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L119" s="8">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="M119" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N119" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O119" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P119" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q119" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R119" s="6" t="s">
         <v>24</v>
@@ -7605,16 +7572,16 @@
     </row>
     <row r="120">
       <c r="A120" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>25</v>
@@ -7623,37 +7590,37 @@
         <v>26</v>
       </c>
       <c r="G120" s="7">
-        <v>46225</v>
+        <v>46238</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="I120" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J120" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K120" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L120" s="8">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="M120" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N120" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q120" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R120" s="6" t="s">
         <v>24</v>
@@ -7664,16 +7631,16 @@
     </row>
     <row r="121">
       <c r="A121" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>25</v>
@@ -7685,34 +7652,34 @@
         <v>46238</v>
       </c>
       <c r="H121" s="6" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="I121" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J121" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K121" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L121" s="8">
         <v>1200</v>
       </c>
       <c r="M121" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N121" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="O121" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P121" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q121" s="9">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="R121" s="6" t="s">
         <v>24</v>
@@ -7723,10 +7690,10 @@
     </row>
     <row r="122">
       <c r="A122" s="6" t="s">
-        <v>183</v>
+        <v>24</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>106</v>
+        <v>65</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>24</v>
@@ -7738,40 +7705,40 @@
         <v>25</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G122" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G122" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>107</v>
+        <v>24</v>
       </c>
       <c r="I122" s="7">
-        <v>46251</v>
+        <v>45930</v>
       </c>
       <c r="J122" s="7">
-        <v>46251</v>
+        <v>46264</v>
       </c>
       <c r="K122" s="7">
-        <v>46251</v>
+        <v>46264</v>
       </c>
       <c r="L122" s="8">
-        <v>1200</v>
+        <v>185.5</v>
       </c>
       <c r="M122" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N122" s="9">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q122" s="9">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="R122" s="6" t="s">
         <v>24</v>
@@ -7782,16 +7749,16 @@
     </row>
     <row r="123">
       <c r="A123" s="6" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>149</v>
+        <v>96</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="E123" s="6" t="s">
         <v>25</v>
@@ -7800,37 +7767,37 @@
         <v>26</v>
       </c>
       <c r="G123" s="7">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="H123" s="6" t="s">
-        <v>107</v>
+        <v>27</v>
       </c>
       <c r="I123" s="7">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="J123" s="7">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="K123" s="7">
-        <v>46251</v>
+        <v>46265</v>
       </c>
       <c r="L123" s="8">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="M123" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N123" s="9">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="O123" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P123" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q123" s="9">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="R123" s="6" t="s">
         <v>24</v>
@@ -7841,10 +7808,10 @@
     </row>
     <row r="124">
       <c r="A124" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>24</v>
@@ -7859,37 +7826,37 @@
         <v>26</v>
       </c>
       <c r="G124" s="7">
-        <v>46188</v>
+        <v>46210</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I124" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J124" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K124" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L124" s="8">
         <v>650</v>
       </c>
       <c r="M124" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N124" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O124" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q124" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R124" s="6" t="s">
         <v>24</v>
@@ -7900,10 +7867,10 @@
     </row>
     <row r="125">
       <c r="A125" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>24</v>
@@ -7924,31 +7891,31 @@
         <v>27</v>
       </c>
       <c r="I125" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J125" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K125" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L125" s="8">
         <v>650</v>
       </c>
       <c r="M125" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N125" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O125" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P125" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q125" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R125" s="6" t="s">
         <v>24</v>
@@ -7959,10 +7926,10 @@
     </row>
     <row r="126">
       <c r="A126" s="6" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>98</v>
+        <v>127</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>24</v>
@@ -7977,37 +7944,37 @@
         <v>26</v>
       </c>
       <c r="G126" s="7">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I126" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J126" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K126" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L126" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M126" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N126" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O126" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q126" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R126" s="6" t="s">
         <v>24</v>
@@ -8018,10 +7985,10 @@
     </row>
     <row r="127">
       <c r="A127" s="6" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>24</v>
@@ -8036,37 +8003,37 @@
         <v>26</v>
       </c>
       <c r="G127" s="7">
-        <v>46212</v>
+        <v>46238</v>
       </c>
       <c r="H127" s="6" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="I127" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J127" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K127" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L127" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M127" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N127" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O127" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P127" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q127" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R127" s="6" t="s">
         <v>24</v>
@@ -8077,10 +8044,10 @@
     </row>
     <row r="128">
       <c r="A128" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>76</v>
+        <v>134</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>24</v>
@@ -8095,37 +8062,37 @@
         <v>26</v>
       </c>
       <c r="G128" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="I128" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J128" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K128" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L128" s="8">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="M128" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N128" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O128" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q128" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R128" s="6" t="s">
         <v>24</v>
@@ -8136,16 +8103,16 @@
     </row>
     <row r="129">
       <c r="A129" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="E129" s="6" t="s">
         <v>25</v>
@@ -8157,34 +8124,34 @@
         <v>46238</v>
       </c>
       <c r="H129" s="6" t="s">
-        <v>27</v>
+        <v>87</v>
       </c>
       <c r="I129" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J129" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K129" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L129" s="8">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="M129" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N129" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O129" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P129" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q129" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R129" s="6" t="s">
         <v>24</v>
@@ -8195,16 +8162,16 @@
     </row>
     <row r="130">
       <c r="A130" s="6" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>25</v>
@@ -8213,37 +8180,37 @@
         <v>26</v>
       </c>
       <c r="G130" s="7">
-        <v>46225</v>
+        <v>46238</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>44</v>
+        <v>87</v>
       </c>
       <c r="I130" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J130" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K130" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L130" s="8">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="M130" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="N130" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="Q130" s="9">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="R130" s="6" t="s">
         <v>24</v>
@@ -8252,618 +8219,28 @@
         <v>24</v>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="B131" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C131" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D131" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E131" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F131" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G131" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H131" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="I131" s="7">
-        <v>46258</v>
-      </c>
-      <c r="J131" s="7">
-        <v>46258</v>
-      </c>
-      <c r="K131" s="7">
-        <v>46258</v>
-      </c>
-      <c r="L131" s="8">
-        <v>1200</v>
-      </c>
-      <c r="M131" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N131" s="9">
-        <v>18</v>
-      </c>
-      <c r="O131" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P131" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q131" s="9">
-        <v>18</v>
-      </c>
-      <c r="R131" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S131" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="B132" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E132" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G132" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H132" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="I132" s="7">
-        <v>46258</v>
-      </c>
-      <c r="J132" s="7">
-        <v>46258</v>
-      </c>
-      <c r="K132" s="7">
-        <v>46258</v>
-      </c>
-      <c r="L132" s="8">
-        <v>1200</v>
-      </c>
-      <c r="M132" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N132" s="9">
-        <v>18</v>
-      </c>
-      <c r="O132" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P132" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q132" s="9">
-        <v>18</v>
-      </c>
-      <c r="R132" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S132" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B133" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D133" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E133" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F133" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G133" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H133" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="I133" s="7">
-        <v>45930</v>
-      </c>
-      <c r="J133" s="7">
-        <v>46264</v>
-      </c>
-      <c r="K133" s="7">
-        <v>46264</v>
-      </c>
-      <c r="L133" s="8">
-        <v>185.5</v>
-      </c>
-      <c r="M133" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N133" s="9">
-        <v>24</v>
-      </c>
-      <c r="O133" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P133" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q133" s="9">
-        <v>24</v>
-      </c>
-      <c r="R133" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S133" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="B134" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E134" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F134" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G134" s="7">
-        <v>46232</v>
-      </c>
-      <c r="H134" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I134" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J134" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K134" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L134" s="8">
-        <v>650</v>
-      </c>
-      <c r="M134" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N134" s="9">
-        <v>25</v>
-      </c>
-      <c r="O134" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P134" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q134" s="9">
-        <v>25</v>
-      </c>
-      <c r="R134" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S134" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="B135" s="6" t="s">
-        <v>98</v>
-      </c>
-      <c r="C135" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D135" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E135" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G135" s="7">
-        <v>46210</v>
-      </c>
-      <c r="H135" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I135" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J135" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K135" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L135" s="8">
-        <v>650</v>
-      </c>
-      <c r="M135" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N135" s="9">
-        <v>25</v>
-      </c>
-      <c r="O135" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P135" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q135" s="9">
-        <v>25</v>
-      </c>
-      <c r="R135" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S135" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="C136" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D136" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E136" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F136" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G136" s="7">
-        <v>46212</v>
-      </c>
-      <c r="H136" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I136" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J136" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K136" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L136" s="8">
-        <v>680</v>
-      </c>
-      <c r="M136" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N136" s="9">
-        <v>25</v>
-      </c>
-      <c r="O136" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P136" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q136" s="9">
-        <v>25</v>
-      </c>
-      <c r="R136" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S136" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D137" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E137" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F137" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G137" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H137" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I137" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J137" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K137" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L137" s="8">
-        <v>700</v>
-      </c>
-      <c r="M137" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N137" s="9">
-        <v>25</v>
-      </c>
-      <c r="O137" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P137" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q137" s="9">
-        <v>25</v>
-      </c>
-      <c r="R137" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S137" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B138" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D138" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E138" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G138" s="7">
-        <v>46225</v>
-      </c>
-      <c r="H138" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="I138" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J138" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K138" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L138" s="8">
-        <v>800</v>
-      </c>
-      <c r="M138" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N138" s="9">
-        <v>25</v>
-      </c>
-      <c r="O138" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P138" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q138" s="9">
-        <v>25</v>
-      </c>
-      <c r="R138" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S138" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="B139" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C139" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D139" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E139" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G139" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H139" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="I139" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J139" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K139" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L139" s="8">
-        <v>1200</v>
-      </c>
-      <c r="M139" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N139" s="9">
-        <v>25</v>
-      </c>
-      <c r="O139" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P139" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q139" s="9">
-        <v>25</v>
-      </c>
-      <c r="R139" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S139" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="B140" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="C140" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D140" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E140" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F140" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G140" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H140" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="I140" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J140" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K140" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L140" s="8">
-        <v>1200</v>
-      </c>
-      <c r="M140" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="N140" s="9">
-        <v>25</v>
-      </c>
-      <c r="O140" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P140" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="Q140" s="9">
-        <v>25</v>
-      </c>
-      <c r="R140" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S140" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="141" ht="23" customHeight="1">
-      <c r="A141" s="10"/>
-      <c r="B141" s="10"/>
-      <c r="C141" s="10"/>
-      <c r="D141" s="10"/>
-      <c r="E141" s="10"/>
-      <c r="F141" s="10"/>
-      <c r="G141" s="11"/>
-      <c r="H141" s="10"/>
-      <c r="I141" s="11"/>
-      <c r="J141" s="11"/>
-      <c r="K141" s="11"/>
-      <c r="L141" s="12">
-        <f>SUM(L6:L140)</f>
-      </c>
-      <c r="M141" s="10"/>
-      <c r="N141" s="13"/>
-      <c r="O141" s="10"/>
-      <c r="P141" s="10"/>
-      <c r="Q141" s="13"/>
-      <c r="R141" s="10"/>
-      <c r="S141" s="10"/>
+    <row r="131" ht="23" customHeight="1">
+      <c r="A131" s="10"/>
+      <c r="B131" s="10"/>
+      <c r="C131" s="10"/>
+      <c r="D131" s="10"/>
+      <c r="E131" s="10"/>
+      <c r="F131" s="10"/>
+      <c r="G131" s="11"/>
+      <c r="H131" s="10"/>
+      <c r="I131" s="11"/>
+      <c r="J131" s="11"/>
+      <c r="K131" s="11"/>
+      <c r="L131" s="12">
+        <f>SUM(L6:L130)</f>
+      </c>
+      <c r="M131" s="10"/>
+      <c r="N131" s="13"/>
+      <c r="O131" s="10"/>
+      <c r="P131" s="10"/>
+      <c r="Q131" s="13"/>
+      <c r="R131" s="10"/>
+      <c r="S131" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:S5"/>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sábado, 8 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em domingo, 9 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -861,7 +861,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -870,7 +870,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -920,7 +920,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -929,7 +929,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>33</v>
@@ -979,16 +979,16 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="O8" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="P8" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -1038,7 +1038,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>33</v>
@@ -1047,7 +1047,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>33</v>
@@ -1097,7 +1097,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>33</v>
@@ -1106,7 +1106,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>33</v>
@@ -1156,7 +1156,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>33</v>
@@ -1165,7 +1165,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1215,7 +1215,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>33</v>
@@ -1224,7 +1224,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>33</v>
@@ -1274,7 +1274,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>33</v>
@@ -1283,7 +1283,7 @@
         <v>38</v>
       </c>
       <c r="Q13" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>24</v>
@@ -1333,7 +1333,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>33</v>
@@ -1342,7 +1342,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>33</v>
@@ -1392,7 +1392,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>33</v>
@@ -1401,7 +1401,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>33</v>
@@ -1451,7 +1451,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>33</v>
@@ -1460,7 +1460,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>33</v>
@@ -1510,7 +1510,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>33</v>
@@ -1519,7 +1519,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>33</v>
@@ -1569,7 +1569,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>33</v>
@@ -1578,7 +1578,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>33</v>
@@ -1628,7 +1628,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>33</v>
@@ -1637,7 +1637,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>33</v>
@@ -1687,7 +1687,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>33</v>
@@ -1696,7 +1696,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>33</v>
@@ -1746,7 +1746,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>33</v>
@@ -1755,7 +1755,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>29</v>
@@ -1805,7 +1805,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>33</v>
@@ -1814,7 +1814,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>33</v>
@@ -1864,7 +1864,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>33</v>
@@ -1873,7 +1873,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>33</v>
@@ -1923,7 +1923,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>33</v>
@@ -1932,7 +1932,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>29</v>
@@ -1982,7 +1982,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>33</v>
@@ -1991,7 +1991,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>33</v>
@@ -2041,7 +2041,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>33</v>
@@ -2050,7 +2050,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>33</v>
@@ -2100,7 +2100,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>33</v>
@@ -2109,7 +2109,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>33</v>
@@ -2159,7 +2159,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>33</v>
@@ -2168,7 +2168,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>33</v>
@@ -2218,7 +2218,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>33</v>
@@ -2227,7 +2227,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>33</v>
@@ -2277,7 +2277,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>33</v>
@@ -2286,7 +2286,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>33</v>
@@ -2336,7 +2336,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>33</v>
@@ -2345,7 +2345,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>33</v>
@@ -2395,7 +2395,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>33</v>
@@ -2404,7 +2404,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>33</v>
@@ -2454,7 +2454,7 @@
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>33</v>
@@ -2463,7 +2463,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>33</v>
@@ -2513,7 +2513,7 @@
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>33</v>
@@ -2522,7 +2522,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>33</v>
@@ -2572,7 +2572,7 @@
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>33</v>
@@ -2581,7 +2581,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>33</v>
@@ -2631,7 +2631,7 @@
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>33</v>
@@ -2640,7 +2640,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>33</v>
@@ -2690,7 +2690,7 @@
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>33</v>
@@ -2699,7 +2699,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>33</v>
@@ -2749,7 +2749,7 @@
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>33</v>
@@ -2758,7 +2758,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>33</v>
@@ -2808,7 +2808,7 @@
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>33</v>
@@ -2817,7 +2817,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>33</v>
@@ -2867,7 +2867,7 @@
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>33</v>
@@ -2876,7 +2876,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>33</v>
@@ -2926,7 +2926,7 @@
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>33</v>
@@ -2935,7 +2935,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>33</v>
@@ -2985,7 +2985,7 @@
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>33</v>
@@ -2994,7 +2994,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>33</v>
@@ -3044,7 +3044,7 @@
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>33</v>
@@ -3053,7 +3053,7 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>33</v>
@@ -3103,7 +3103,7 @@
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>33</v>
@@ -3112,7 +3112,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>33</v>
@@ -3162,7 +3162,7 @@
         <v>38</v>
       </c>
       <c r="N45" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>24</v>
@@ -3171,7 +3171,7 @@
         <v>38</v>
       </c>
       <c r="Q45" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>24</v>
@@ -3221,7 +3221,7 @@
         <v>38</v>
       </c>
       <c r="N46" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>24</v>
@@ -3230,7 +3230,7 @@
         <v>38</v>
       </c>
       <c r="Q46" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>24</v>
@@ -3280,7 +3280,7 @@
         <v>38</v>
       </c>
       <c r="N47" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>24</v>
@@ -3289,7 +3289,7 @@
         <v>38</v>
       </c>
       <c r="Q47" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>24</v>
@@ -3339,7 +3339,7 @@
         <v>38</v>
       </c>
       <c r="N48" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>24</v>
@@ -3348,7 +3348,7 @@
         <v>38</v>
       </c>
       <c r="Q48" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>24</v>
@@ -3398,7 +3398,7 @@
         <v>38</v>
       </c>
       <c r="N49" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>24</v>
@@ -3407,7 +3407,7 @@
         <v>38</v>
       </c>
       <c r="Q49" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>24</v>
@@ -3457,7 +3457,7 @@
         <v>38</v>
       </c>
       <c r="N50" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>24</v>
@@ -3466,7 +3466,7 @@
         <v>38</v>
       </c>
       <c r="Q50" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>24</v>
@@ -3516,7 +3516,7 @@
         <v>38</v>
       </c>
       <c r="N51" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O51" s="6" t="s">
         <v>24</v>
@@ -3525,7 +3525,7 @@
         <v>38</v>
       </c>
       <c r="Q51" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>24</v>
@@ -3575,7 +3575,7 @@
         <v>38</v>
       </c>
       <c r="N52" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>24</v>
@@ -3584,7 +3584,7 @@
         <v>38</v>
       </c>
       <c r="Q52" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>24</v>
@@ -3634,7 +3634,7 @@
         <v>38</v>
       </c>
       <c r="N53" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>24</v>
@@ -3643,7 +3643,7 @@
         <v>38</v>
       </c>
       <c r="Q53" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>24</v>
@@ -3693,7 +3693,7 @@
         <v>38</v>
       </c>
       <c r="N54" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>24</v>
@@ -3702,7 +3702,7 @@
         <v>38</v>
       </c>
       <c r="Q54" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>24</v>
@@ -3752,7 +3752,7 @@
         <v>38</v>
       </c>
       <c r="N55" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>24</v>
@@ -3761,7 +3761,7 @@
         <v>38</v>
       </c>
       <c r="Q55" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>24</v>
@@ -3811,7 +3811,7 @@
         <v>38</v>
       </c>
       <c r="N56" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>24</v>
@@ -3820,7 +3820,7 @@
         <v>38</v>
       </c>
       <c r="Q56" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>24</v>
@@ -3870,7 +3870,7 @@
         <v>38</v>
       </c>
       <c r="N57" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O57" s="6" t="s">
         <v>24</v>
@@ -3879,7 +3879,7 @@
         <v>38</v>
       </c>
       <c r="Q57" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>24</v>
@@ -3929,7 +3929,7 @@
         <v>38</v>
       </c>
       <c r="N58" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>24</v>
@@ -3938,7 +3938,7 @@
         <v>38</v>
       </c>
       <c r="Q58" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>24</v>
@@ -3988,7 +3988,7 @@
         <v>38</v>
       </c>
       <c r="N59" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O59" s="6" t="s">
         <v>24</v>
@@ -3997,7 +3997,7 @@
         <v>38</v>
       </c>
       <c r="Q59" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>24</v>
@@ -4047,7 +4047,7 @@
         <v>38</v>
       </c>
       <c r="N60" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>24</v>
@@ -4056,7 +4056,7 @@
         <v>38</v>
       </c>
       <c r="Q60" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>24</v>
@@ -4106,7 +4106,7 @@
         <v>38</v>
       </c>
       <c r="N61" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O61" s="6" t="s">
         <v>24</v>
@@ -4115,7 +4115,7 @@
         <v>38</v>
       </c>
       <c r="Q61" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>24</v>
@@ -4165,7 +4165,7 @@
         <v>38</v>
       </c>
       <c r="N62" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>24</v>
@@ -4174,7 +4174,7 @@
         <v>38</v>
       </c>
       <c r="Q62" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>24</v>
@@ -4224,7 +4224,7 @@
         <v>38</v>
       </c>
       <c r="N63" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O63" s="6" t="s">
         <v>24</v>
@@ -4233,7 +4233,7 @@
         <v>38</v>
       </c>
       <c r="Q63" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>24</v>
@@ -4283,7 +4283,7 @@
         <v>38</v>
       </c>
       <c r="N64" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>24</v>
@@ -4292,7 +4292,7 @@
         <v>38</v>
       </c>
       <c r="Q64" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R64" s="6" t="s">
         <v>24</v>
@@ -4342,7 +4342,7 @@
         <v>38</v>
       </c>
       <c r="N65" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O65" s="6" t="s">
         <v>24</v>
@@ -4351,7 +4351,7 @@
         <v>38</v>
       </c>
       <c r="Q65" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>24</v>
@@ -4401,7 +4401,7 @@
         <v>38</v>
       </c>
       <c r="N66" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>24</v>
@@ -4410,7 +4410,7 @@
         <v>38</v>
       </c>
       <c r="Q66" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>24</v>
@@ -4460,7 +4460,7 @@
         <v>38</v>
       </c>
       <c r="N67" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>24</v>
@@ -4469,7 +4469,7 @@
         <v>38</v>
       </c>
       <c r="Q67" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>24</v>
@@ -4519,7 +4519,7 @@
         <v>38</v>
       </c>
       <c r="N68" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>24</v>
@@ -4528,7 +4528,7 @@
         <v>38</v>
       </c>
       <c r="Q68" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>24</v>
@@ -4578,7 +4578,7 @@
         <v>38</v>
       </c>
       <c r="N69" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>24</v>
@@ -4587,7 +4587,7 @@
         <v>38</v>
       </c>
       <c r="Q69" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>24</v>
@@ -4637,7 +4637,7 @@
         <v>38</v>
       </c>
       <c r="N70" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>24</v>
@@ -4646,7 +4646,7 @@
         <v>38</v>
       </c>
       <c r="Q70" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>24</v>
@@ -4696,7 +4696,7 @@
         <v>38</v>
       </c>
       <c r="N71" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
@@ -4705,7 +4705,7 @@
         <v>38</v>
       </c>
       <c r="Q71" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>24</v>
@@ -4755,7 +4755,7 @@
         <v>38</v>
       </c>
       <c r="N72" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
@@ -4764,7 +4764,7 @@
         <v>38</v>
       </c>
       <c r="Q72" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4814,7 +4814,7 @@
         <v>38</v>
       </c>
       <c r="N73" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
@@ -4823,7 +4823,7 @@
         <v>38</v>
       </c>
       <c r="Q73" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4873,7 +4873,7 @@
         <v>38</v>
       </c>
       <c r="N74" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
@@ -4882,7 +4882,7 @@
         <v>38</v>
       </c>
       <c r="Q74" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -4932,7 +4932,7 @@
         <v>38</v>
       </c>
       <c r="N75" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
@@ -4941,7 +4941,7 @@
         <v>38</v>
       </c>
       <c r="Q75" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -4991,7 +4991,7 @@
         <v>38</v>
       </c>
       <c r="N76" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
@@ -5000,7 +5000,7 @@
         <v>38</v>
       </c>
       <c r="Q76" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -5050,7 +5050,7 @@
         <v>38</v>
       </c>
       <c r="N77" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
@@ -5059,7 +5059,7 @@
         <v>38</v>
       </c>
       <c r="Q77" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5109,7 +5109,7 @@
         <v>38</v>
       </c>
       <c r="N78" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
@@ -5118,7 +5118,7 @@
         <v>38</v>
       </c>
       <c r="Q78" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5168,7 +5168,7 @@
         <v>38</v>
       </c>
       <c r="N79" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
@@ -5177,7 +5177,7 @@
         <v>38</v>
       </c>
       <c r="Q79" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5227,7 +5227,7 @@
         <v>38</v>
       </c>
       <c r="N80" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
@@ -5236,7 +5236,7 @@
         <v>38</v>
       </c>
       <c r="Q80" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5286,7 +5286,7 @@
         <v>38</v>
       </c>
       <c r="N81" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
@@ -5295,7 +5295,7 @@
         <v>38</v>
       </c>
       <c r="Q81" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5345,7 +5345,7 @@
         <v>38</v>
       </c>
       <c r="N82" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
@@ -5354,7 +5354,7 @@
         <v>38</v>
       </c>
       <c r="Q82" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5404,7 +5404,7 @@
         <v>38</v>
       </c>
       <c r="N83" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
@@ -5413,7 +5413,7 @@
         <v>38</v>
       </c>
       <c r="Q83" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5463,7 +5463,7 @@
         <v>38</v>
       </c>
       <c r="N84" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
@@ -5472,7 +5472,7 @@
         <v>38</v>
       </c>
       <c r="Q84" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5522,7 +5522,7 @@
         <v>38</v>
       </c>
       <c r="N85" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
@@ -5531,7 +5531,7 @@
         <v>38</v>
       </c>
       <c r="Q85" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5581,7 +5581,7 @@
         <v>38</v>
       </c>
       <c r="N86" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
@@ -5590,7 +5590,7 @@
         <v>38</v>
       </c>
       <c r="Q86" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5640,7 +5640,7 @@
         <v>38</v>
       </c>
       <c r="N87" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
@@ -5649,7 +5649,7 @@
         <v>38</v>
       </c>
       <c r="Q87" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5699,7 +5699,7 @@
         <v>38</v>
       </c>
       <c r="N88" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
@@ -5708,7 +5708,7 @@
         <v>38</v>
       </c>
       <c r="Q88" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5758,7 +5758,7 @@
         <v>38</v>
       </c>
       <c r="N89" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
@@ -5767,7 +5767,7 @@
         <v>38</v>
       </c>
       <c r="Q89" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5817,7 +5817,7 @@
         <v>38</v>
       </c>
       <c r="N90" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
@@ -5826,7 +5826,7 @@
         <v>38</v>
       </c>
       <c r="Q90" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5876,7 +5876,7 @@
         <v>38</v>
       </c>
       <c r="N91" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
@@ -5885,7 +5885,7 @@
         <v>38</v>
       </c>
       <c r="Q91" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -5935,7 +5935,7 @@
         <v>38</v>
       </c>
       <c r="N92" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
@@ -5944,7 +5944,7 @@
         <v>38</v>
       </c>
       <c r="Q92" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -5994,7 +5994,7 @@
         <v>38</v>
       </c>
       <c r="N93" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
@@ -6003,7 +6003,7 @@
         <v>38</v>
       </c>
       <c r="Q93" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -6053,7 +6053,7 @@
         <v>38</v>
       </c>
       <c r="N94" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
@@ -6062,7 +6062,7 @@
         <v>38</v>
       </c>
       <c r="Q94" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6112,7 +6112,7 @@
         <v>38</v>
       </c>
       <c r="N95" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
@@ -6121,7 +6121,7 @@
         <v>38</v>
       </c>
       <c r="Q95" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6171,7 +6171,7 @@
         <v>38</v>
       </c>
       <c r="N96" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
@@ -6180,7 +6180,7 @@
         <v>38</v>
       </c>
       <c r="Q96" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6230,7 +6230,7 @@
         <v>38</v>
       </c>
       <c r="N97" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
@@ -6239,7 +6239,7 @@
         <v>38</v>
       </c>
       <c r="Q97" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6289,7 +6289,7 @@
         <v>38</v>
       </c>
       <c r="N98" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
@@ -6298,7 +6298,7 @@
         <v>38</v>
       </c>
       <c r="Q98" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6348,7 +6348,7 @@
         <v>38</v>
       </c>
       <c r="N99" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
@@ -6357,7 +6357,7 @@
         <v>38</v>
       </c>
       <c r="Q99" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6407,7 +6407,7 @@
         <v>38</v>
       </c>
       <c r="N100" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
@@ -6416,7 +6416,7 @@
         <v>38</v>
       </c>
       <c r="Q100" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6466,7 +6466,7 @@
         <v>38</v>
       </c>
       <c r="N101" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
@@ -6475,7 +6475,7 @@
         <v>38</v>
       </c>
       <c r="Q101" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6525,7 +6525,7 @@
         <v>38</v>
       </c>
       <c r="N102" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
@@ -6534,7 +6534,7 @@
         <v>38</v>
       </c>
       <c r="Q102" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6584,7 +6584,7 @@
         <v>38</v>
       </c>
       <c r="N103" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
@@ -6593,7 +6593,7 @@
         <v>38</v>
       </c>
       <c r="Q103" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6643,7 +6643,7 @@
         <v>38</v>
       </c>
       <c r="N104" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
@@ -6652,7 +6652,7 @@
         <v>38</v>
       </c>
       <c r="Q104" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6702,7 +6702,7 @@
         <v>38</v>
       </c>
       <c r="N105" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
@@ -6711,7 +6711,7 @@
         <v>38</v>
       </c>
       <c r="Q105" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6761,7 +6761,7 @@
         <v>38</v>
       </c>
       <c r="N106" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
@@ -6770,7 +6770,7 @@
         <v>38</v>
       </c>
       <c r="Q106" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>
@@ -6820,7 +6820,7 @@
         <v>38</v>
       </c>
       <c r="N107" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>24</v>
@@ -6829,7 +6829,7 @@
         <v>38</v>
       </c>
       <c r="Q107" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>24</v>
@@ -6879,7 +6879,7 @@
         <v>38</v>
       </c>
       <c r="N108" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>24</v>
@@ -6888,7 +6888,7 @@
         <v>38</v>
       </c>
       <c r="Q108" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>24</v>
@@ -6938,7 +6938,7 @@
         <v>38</v>
       </c>
       <c r="N109" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>24</v>
@@ -6947,7 +6947,7 @@
         <v>38</v>
       </c>
       <c r="Q109" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R109" s="6" t="s">
         <v>24</v>
@@ -6997,7 +6997,7 @@
         <v>38</v>
       </c>
       <c r="N110" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>24</v>
@@ -7006,7 +7006,7 @@
         <v>38</v>
       </c>
       <c r="Q110" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R110" s="6" t="s">
         <v>24</v>
@@ -7056,7 +7056,7 @@
         <v>38</v>
       </c>
       <c r="N111" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>24</v>
@@ -7065,7 +7065,7 @@
         <v>38</v>
       </c>
       <c r="Q111" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R111" s="6" t="s">
         <v>24</v>
@@ -7115,7 +7115,7 @@
         <v>38</v>
       </c>
       <c r="N112" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>24</v>
@@ -7124,7 +7124,7 @@
         <v>38</v>
       </c>
       <c r="Q112" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R112" s="6" t="s">
         <v>24</v>
@@ -7174,7 +7174,7 @@
         <v>38</v>
       </c>
       <c r="N113" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>24</v>
@@ -7183,7 +7183,7 @@
         <v>38</v>
       </c>
       <c r="Q113" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R113" s="6" t="s">
         <v>24</v>
@@ -7233,7 +7233,7 @@
         <v>38</v>
       </c>
       <c r="N114" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>24</v>
@@ -7242,7 +7242,7 @@
         <v>38</v>
       </c>
       <c r="Q114" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R114" s="6" t="s">
         <v>24</v>
@@ -7292,7 +7292,7 @@
         <v>38</v>
       </c>
       <c r="N115" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O115" s="6" t="s">
         <v>24</v>
@@ -7301,7 +7301,7 @@
         <v>38</v>
       </c>
       <c r="Q115" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R115" s="6" t="s">
         <v>24</v>
@@ -7351,7 +7351,7 @@
         <v>38</v>
       </c>
       <c r="N116" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>24</v>
@@ -7360,7 +7360,7 @@
         <v>38</v>
       </c>
       <c r="Q116" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R116" s="6" t="s">
         <v>24</v>
@@ -7410,7 +7410,7 @@
         <v>38</v>
       </c>
       <c r="N117" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O117" s="6" t="s">
         <v>24</v>
@@ -7419,7 +7419,7 @@
         <v>38</v>
       </c>
       <c r="Q117" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R117" s="6" t="s">
         <v>24</v>
@@ -7469,7 +7469,7 @@
         <v>38</v>
       </c>
       <c r="N118" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>24</v>
@@ -7478,7 +7478,7 @@
         <v>38</v>
       </c>
       <c r="Q118" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R118" s="6" t="s">
         <v>24</v>
@@ -7528,7 +7528,7 @@
         <v>38</v>
       </c>
       <c r="N119" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O119" s="6" t="s">
         <v>24</v>
@@ -7537,7 +7537,7 @@
         <v>38</v>
       </c>
       <c r="Q119" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R119" s="6" t="s">
         <v>24</v>
@@ -7587,7 +7587,7 @@
         <v>38</v>
       </c>
       <c r="N120" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>24</v>
@@ -7596,7 +7596,7 @@
         <v>38</v>
       </c>
       <c r="Q120" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R120" s="6" t="s">
         <v>24</v>
@@ -7646,7 +7646,7 @@
         <v>38</v>
       </c>
       <c r="N121" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O121" s="6" t="s">
         <v>24</v>
@@ -7655,7 +7655,7 @@
         <v>38</v>
       </c>
       <c r="Q121" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R121" s="6" t="s">
         <v>24</v>
@@ -7705,7 +7705,7 @@
         <v>38</v>
       </c>
       <c r="N122" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>24</v>
@@ -7714,7 +7714,7 @@
         <v>38</v>
       </c>
       <c r="Q122" s="9">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R122" s="6" t="s">
         <v>24</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em domingo, 9 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em segunda-feira, 10 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -172,21 +172,21 @@
     <t>AZ EMPREENDIMENTOS</t>
   </si>
   <si>
+    <t>FA-12017</t>
+  </si>
+  <si>
+    <t>FA-12019</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
     <t>FA-11962</t>
   </si>
   <si>
     <t>RAMON TALLES BARBALHO DE FRANÇA</t>
   </si>
   <si>
-    <t>FA-12019</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-12017</t>
-  </si>
-  <si>
     <t>FA-12016</t>
   </si>
   <si>
@@ -307,6 +307,9 @@
     <t>ROBERTO MURATORI</t>
   </si>
   <si>
+    <t>HOJE</t>
+  </si>
+  <si>
     <t>FA-12055</t>
   </si>
   <si>
@@ -319,18 +322,18 @@
     <t>ROSSILY PEREIRA DA SILVA</t>
   </si>
   <si>
+    <t>FA-12037</t>
+  </si>
+  <si>
+    <t>FA-11979</t>
+  </si>
+  <si>
     <t>FA-12000</t>
   </si>
   <si>
     <t>JONILSON JOSEMAR DO NASCIMENTO</t>
   </si>
   <si>
-    <t>FA-11979</t>
-  </si>
-  <si>
-    <t>FA-12037</t>
-  </si>
-  <si>
     <t>FA-11982</t>
   </si>
   <si>
@@ -463,16 +466,16 @@
     <t>FA-11984</t>
   </si>
   <si>
+    <t>FA-12109</t>
+  </si>
+  <si>
+    <t>FA-12064</t>
+  </si>
+  <si>
+    <t>FA-11923</t>
+  </si>
+  <si>
     <t>FA-12058</t>
-  </si>
-  <si>
-    <t>FA-12064</t>
-  </si>
-  <si>
-    <t>FA-11923</t>
-  </si>
-  <si>
-    <t>FA-12109</t>
   </si>
   <si>
     <t>FA-11862</t>
@@ -861,7 +864,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -870,7 +873,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -920,7 +923,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -929,7 +932,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>33</v>
@@ -979,7 +982,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-31</v>
+        <v>-32</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -988,7 +991,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -1038,7 +1041,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>33</v>
@@ -1047,7 +1050,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>33</v>
@@ -1097,7 +1100,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>33</v>
@@ -1106,7 +1109,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>33</v>
@@ -1156,7 +1159,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>33</v>
@@ -1165,7 +1168,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1215,7 +1218,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>33</v>
@@ -1224,7 +1227,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>33</v>
@@ -1274,7 +1277,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>33</v>
@@ -1283,7 +1286,7 @@
         <v>38</v>
       </c>
       <c r="Q13" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>24</v>
@@ -1333,7 +1336,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>33</v>
@@ -1342,7 +1345,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>33</v>
@@ -1392,7 +1395,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>33</v>
@@ -1401,7 +1404,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>33</v>
@@ -1451,7 +1454,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>33</v>
@@ -1460,7 +1463,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>33</v>
@@ -1474,7 +1477,7 @@
         <v>46</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>24</v>
@@ -1489,10 +1492,10 @@
         <v>26</v>
       </c>
       <c r="G17" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I17" s="7">
         <v>46230</v>
@@ -1510,7 +1513,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>33</v>
@@ -1519,7 +1522,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>33</v>
@@ -1530,10 +1533,10 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>24</v>
@@ -1569,7 +1572,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>33</v>
@@ -1578,7 +1581,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>33</v>
@@ -1589,11 +1592,11 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>37</v>
-      </c>
       <c r="C19" s="6" t="s">
         <v>24</v>
       </c>
@@ -1607,10 +1610,10 @@
         <v>26</v>
       </c>
       <c r="G19" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="I19" s="7">
         <v>46230</v>
@@ -1628,7 +1631,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>33</v>
@@ -1637,7 +1640,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>33</v>
@@ -1687,7 +1690,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>33</v>
@@ -1696,7 +1699,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>33</v>
@@ -1746,7 +1749,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>33</v>
@@ -1755,7 +1758,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>29</v>
@@ -1805,7 +1808,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>33</v>
@@ -1814,7 +1817,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>33</v>
@@ -1864,7 +1867,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>33</v>
@@ -1873,7 +1876,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>33</v>
@@ -1923,7 +1926,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>33</v>
@@ -1932,7 +1935,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>29</v>
@@ -1982,7 +1985,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>33</v>
@@ -1991,7 +1994,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>33</v>
@@ -2005,7 +2008,7 @@
         <v>63</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>24</v>
@@ -2041,7 +2044,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>33</v>
@@ -2050,7 +2053,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>33</v>
@@ -2100,7 +2103,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>33</v>
@@ -2109,7 +2112,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>33</v>
@@ -2159,7 +2162,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>33</v>
@@ -2168,7 +2171,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>33</v>
@@ -2218,7 +2221,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>33</v>
@@ -2227,7 +2230,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>33</v>
@@ -2277,7 +2280,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>33</v>
@@ -2286,7 +2289,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>33</v>
@@ -2336,7 +2339,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>33</v>
@@ -2345,7 +2348,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>33</v>
@@ -2395,7 +2398,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>33</v>
@@ -2404,7 +2407,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>33</v>
@@ -2418,7 +2421,7 @@
         <v>74</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>24</v>
@@ -2454,7 +2457,7 @@
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>33</v>
@@ -2463,7 +2466,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>33</v>
@@ -2477,7 +2480,7 @@
         <v>75</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>24</v>
@@ -2513,7 +2516,7 @@
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>33</v>
@@ -2522,7 +2525,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>33</v>
@@ -2572,7 +2575,7 @@
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>33</v>
@@ -2581,7 +2584,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>33</v>
@@ -2631,7 +2634,7 @@
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>33</v>
@@ -2640,7 +2643,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>33</v>
@@ -2690,7 +2693,7 @@
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>33</v>
@@ -2699,7 +2702,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>33</v>
@@ -2749,7 +2752,7 @@
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>33</v>
@@ -2758,7 +2761,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>33</v>
@@ -2808,7 +2811,7 @@
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>33</v>
@@ -2817,7 +2820,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>33</v>
@@ -2867,7 +2870,7 @@
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>33</v>
@@ -2876,7 +2879,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>33</v>
@@ -2926,7 +2929,7 @@
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>33</v>
@@ -2935,7 +2938,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>33</v>
@@ -2985,7 +2988,7 @@
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>33</v>
@@ -2994,7 +2997,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>33</v>
@@ -3044,7 +3047,7 @@
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>33</v>
@@ -3053,7 +3056,7 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>33</v>
@@ -3103,7 +3106,7 @@
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>33</v>
@@ -3112,7 +3115,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>33</v>
@@ -3159,19 +3162,19 @@
         <v>600</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N45" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q45" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>24</v>
@@ -3182,13 +3185,13 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>24</v>
@@ -3218,19 +3221,19 @@
         <v>620</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N46" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q46" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>24</v>
@@ -3241,10 +3244,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>24</v>
@@ -3277,19 +3280,19 @@
         <v>630</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N47" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q47" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>24</v>
@@ -3300,10 +3303,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>24</v>
@@ -3318,7 +3321,7 @@
         <v>26</v>
       </c>
       <c r="G48" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>27</v>
@@ -3336,19 +3339,19 @@
         <v>630</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N48" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q48" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>24</v>
@@ -3395,19 +3398,19 @@
         <v>630</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N49" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q49" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>24</v>
@@ -3421,7 +3424,7 @@
         <v>98</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>40</v>
+        <v>99</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>24</v>
@@ -3436,7 +3439,7 @@
         <v>26</v>
       </c>
       <c r="G50" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>27</v>
@@ -3454,19 +3457,19 @@
         <v>630</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N50" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q50" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>24</v>
@@ -3477,10 +3480,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>24</v>
@@ -3513,19 +3516,19 @@
         <v>630</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N51" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q51" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>24</v>
@@ -3536,7 +3539,7 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>83</v>
@@ -3572,19 +3575,19 @@
         <v>630</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N52" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q52" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>24</v>
@@ -3595,10 +3598,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>24</v>
@@ -3631,19 +3634,19 @@
         <v>650</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N53" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q53" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>24</v>
@@ -3654,7 +3657,7 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>44</v>
@@ -3690,19 +3693,19 @@
         <v>650</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N54" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q54" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>24</v>
@@ -3713,7 +3716,7 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>42</v>
@@ -3749,19 +3752,19 @@
         <v>650</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N55" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q55" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>24</v>
@@ -3772,10 +3775,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>24</v>
@@ -3808,19 +3811,19 @@
         <v>650</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N56" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q56" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>24</v>
@@ -3831,10 +3834,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>24</v>
@@ -3867,19 +3870,19 @@
         <v>650</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N57" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q57" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>24</v>
@@ -3890,10 +3893,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>24</v>
@@ -3926,19 +3929,19 @@
         <v>670</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N58" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q58" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>24</v>
@@ -3949,10 +3952,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>24</v>
@@ -3985,19 +3988,19 @@
         <v>680</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N59" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q59" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>24</v>
@@ -4008,7 +4011,7 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>37</v>
@@ -4044,19 +4047,19 @@
         <v>680</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N60" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q60" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>24</v>
@@ -4067,10 +4070,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>24</v>
@@ -4103,19 +4106,19 @@
         <v>680</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N61" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q61" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>24</v>
@@ -4126,10 +4129,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4162,19 +4165,19 @@
         <v>680</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N62" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q62" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>24</v>
@@ -4185,7 +4188,7 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>58</v>
@@ -4221,19 +4224,19 @@
         <v>680</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N63" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q63" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>24</v>
@@ -4244,7 +4247,7 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>73</v>
@@ -4280,19 +4283,19 @@
         <v>680</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N64" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q64" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64" s="6" t="s">
         <v>24</v>
@@ -4303,10 +4306,10 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>24</v>
@@ -4339,19 +4342,19 @@
         <v>680</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N65" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q65" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>24</v>
@@ -4362,10 +4365,10 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>24</v>
@@ -4398,19 +4401,19 @@
         <v>700</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N66" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q66" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>24</v>
@@ -4421,7 +4424,7 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>56</v>
@@ -4457,19 +4460,19 @@
         <v>700</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N67" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q67" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>24</v>
@@ -4480,7 +4483,7 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>65</v>
@@ -4516,19 +4519,19 @@
         <v>700</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N68" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q68" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>24</v>
@@ -4539,7 +4542,7 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>52</v>
@@ -4575,19 +4578,19 @@
         <v>750</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N69" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q69" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>24</v>
@@ -4598,10 +4601,10 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>24</v>
@@ -4634,19 +4637,19 @@
         <v>800</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N70" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q70" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>24</v>
@@ -4657,7 +4660,7 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>61</v>
@@ -4693,19 +4696,19 @@
         <v>1200</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N71" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q71" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>24</v>
@@ -4716,16 +4719,16 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>25</v>
@@ -4752,19 +4755,19 @@
         <v>1200</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N72" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q72" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4775,16 +4778,16 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B73" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C73" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D73" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="C73" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D73" s="6" t="s">
-        <v>131</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>25</v>
@@ -4811,19 +4814,19 @@
         <v>1200</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="N73" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>38</v>
+        <v>91</v>
       </c>
       <c r="Q73" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4834,7 +4837,7 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>90</v>
@@ -4873,7 +4876,7 @@
         <v>38</v>
       </c>
       <c r="N74" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
@@ -4882,7 +4885,7 @@
         <v>38</v>
       </c>
       <c r="Q74" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -4893,13 +4896,13 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>24</v>
@@ -4932,7 +4935,7 @@
         <v>38</v>
       </c>
       <c r="N75" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
@@ -4941,7 +4944,7 @@
         <v>38</v>
       </c>
       <c r="Q75" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -4952,10 +4955,10 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>24</v>
@@ -4991,7 +4994,7 @@
         <v>38</v>
       </c>
       <c r="N76" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
@@ -5000,7 +5003,7 @@
         <v>38</v>
       </c>
       <c r="Q76" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -5011,7 +5014,7 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>68</v>
@@ -5050,7 +5053,7 @@
         <v>38</v>
       </c>
       <c r="N77" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
@@ -5059,7 +5062,7 @@
         <v>38</v>
       </c>
       <c r="Q77" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5070,10 +5073,10 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -5109,7 +5112,7 @@
         <v>38</v>
       </c>
       <c r="N78" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
@@ -5118,7 +5121,7 @@
         <v>38</v>
       </c>
       <c r="Q78" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5129,7 +5132,7 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>40</v>
@@ -5168,7 +5171,7 @@
         <v>38</v>
       </c>
       <c r="N79" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
@@ -5177,7 +5180,7 @@
         <v>38</v>
       </c>
       <c r="Q79" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5188,7 +5191,7 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>83</v>
@@ -5227,7 +5230,7 @@
         <v>38</v>
       </c>
       <c r="N80" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
@@ -5236,7 +5239,7 @@
         <v>38</v>
       </c>
       <c r="Q80" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5247,10 +5250,10 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5286,7 +5289,7 @@
         <v>38</v>
       </c>
       <c r="N81" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
@@ -5295,7 +5298,7 @@
         <v>38</v>
       </c>
       <c r="Q81" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5306,7 +5309,7 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>42</v>
@@ -5345,7 +5348,7 @@
         <v>38</v>
       </c>
       <c r="N82" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
@@ -5354,7 +5357,7 @@
         <v>38</v>
       </c>
       <c r="Q82" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5365,10 +5368,10 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>24</v>
@@ -5383,7 +5386,7 @@
         <v>26</v>
       </c>
       <c r="G83" s="7">
-        <v>46232</v>
+        <v>46240</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>27</v>
@@ -5404,7 +5407,7 @@
         <v>38</v>
       </c>
       <c r="N83" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
@@ -5413,7 +5416,7 @@
         <v>38</v>
       </c>
       <c r="Q83" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5424,10 +5427,10 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>24</v>
@@ -5463,7 +5466,7 @@
         <v>38</v>
       </c>
       <c r="N84" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
@@ -5472,7 +5475,7 @@
         <v>38</v>
       </c>
       <c r="Q84" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5483,10 +5486,10 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>24</v>
@@ -5522,7 +5525,7 @@
         <v>38</v>
       </c>
       <c r="N85" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
@@ -5531,7 +5534,7 @@
         <v>38</v>
       </c>
       <c r="Q85" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5542,10 +5545,10 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>24</v>
@@ -5560,7 +5563,7 @@
         <v>26</v>
       </c>
       <c r="G86" s="7">
-        <v>46240</v>
+        <v>46232</v>
       </c>
       <c r="H86" s="6" t="s">
         <v>27</v>
@@ -5581,7 +5584,7 @@
         <v>38</v>
       </c>
       <c r="N86" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
@@ -5590,7 +5593,7 @@
         <v>38</v>
       </c>
       <c r="Q86" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5601,7 +5604,7 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>44</v>
@@ -5640,7 +5643,7 @@
         <v>38</v>
       </c>
       <c r="N87" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
@@ -5649,7 +5652,7 @@
         <v>38</v>
       </c>
       <c r="Q87" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5660,10 +5663,10 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>24</v>
@@ -5699,7 +5702,7 @@
         <v>38</v>
       </c>
       <c r="N88" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
@@ -5708,7 +5711,7 @@
         <v>38</v>
       </c>
       <c r="Q88" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5719,7 +5722,7 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>37</v>
@@ -5758,7 +5761,7 @@
         <v>38</v>
       </c>
       <c r="N89" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
@@ -5767,7 +5770,7 @@
         <v>38</v>
       </c>
       <c r="Q89" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5778,10 +5781,10 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>24</v>
@@ -5817,7 +5820,7 @@
         <v>38</v>
       </c>
       <c r="N90" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
@@ -5826,7 +5829,7 @@
         <v>38</v>
       </c>
       <c r="Q90" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5837,7 +5840,7 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>73</v>
@@ -5876,7 +5879,7 @@
         <v>38</v>
       </c>
       <c r="N91" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
@@ -5885,7 +5888,7 @@
         <v>38</v>
       </c>
       <c r="Q91" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -5896,10 +5899,10 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>24</v>
@@ -5935,7 +5938,7 @@
         <v>38</v>
       </c>
       <c r="N92" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
@@ -5944,7 +5947,7 @@
         <v>38</v>
       </c>
       <c r="Q92" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -5955,10 +5958,10 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>24</v>
@@ -5994,7 +5997,7 @@
         <v>38</v>
       </c>
       <c r="N93" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
@@ -6003,7 +6006,7 @@
         <v>38</v>
       </c>
       <c r="Q93" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -6014,10 +6017,10 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>24</v>
@@ -6053,7 +6056,7 @@
         <v>38</v>
       </c>
       <c r="N94" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
@@ -6062,7 +6065,7 @@
         <v>38</v>
       </c>
       <c r="Q94" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6073,7 +6076,7 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>58</v>
@@ -6112,7 +6115,7 @@
         <v>38</v>
       </c>
       <c r="N95" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
@@ -6121,7 +6124,7 @@
         <v>38</v>
       </c>
       <c r="Q95" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6132,7 +6135,7 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>56</v>
@@ -6171,7 +6174,7 @@
         <v>38</v>
       </c>
       <c r="N96" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
@@ -6180,7 +6183,7 @@
         <v>38</v>
       </c>
       <c r="Q96" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6191,7 +6194,7 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>65</v>
@@ -6230,7 +6233,7 @@
         <v>38</v>
       </c>
       <c r="N97" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
@@ -6239,7 +6242,7 @@
         <v>38</v>
       </c>
       <c r="Q97" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6250,10 +6253,10 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>24</v>
@@ -6289,7 +6292,7 @@
         <v>38</v>
       </c>
       <c r="N98" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
@@ -6298,7 +6301,7 @@
         <v>38</v>
       </c>
       <c r="Q98" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6309,7 +6312,7 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>52</v>
@@ -6348,7 +6351,7 @@
         <v>38</v>
       </c>
       <c r="N99" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
@@ -6357,7 +6360,7 @@
         <v>38</v>
       </c>
       <c r="Q99" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6368,10 +6371,10 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>24</v>
@@ -6407,7 +6410,7 @@
         <v>38</v>
       </c>
       <c r="N100" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
@@ -6416,7 +6419,7 @@
         <v>38</v>
       </c>
       <c r="Q100" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6427,16 +6430,16 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>25</v>
@@ -6466,7 +6469,7 @@
         <v>38</v>
       </c>
       <c r="N101" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
@@ -6475,7 +6478,7 @@
         <v>38</v>
       </c>
       <c r="Q101" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6486,7 +6489,7 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>61</v>
@@ -6525,7 +6528,7 @@
         <v>38</v>
       </c>
       <c r="N102" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
@@ -6534,7 +6537,7 @@
         <v>38</v>
       </c>
       <c r="Q102" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6545,16 +6548,16 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>25</v>
@@ -6584,7 +6587,7 @@
         <v>38</v>
       </c>
       <c r="N103" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
@@ -6593,7 +6596,7 @@
         <v>38</v>
       </c>
       <c r="Q103" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6604,7 +6607,7 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>44</v>
@@ -6643,7 +6646,7 @@
         <v>38</v>
       </c>
       <c r="N104" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
@@ -6652,7 +6655,7 @@
         <v>38</v>
       </c>
       <c r="Q104" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6663,10 +6666,10 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>24</v>
@@ -6702,7 +6705,7 @@
         <v>38</v>
       </c>
       <c r="N105" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
@@ -6711,7 +6714,7 @@
         <v>38</v>
       </c>
       <c r="Q105" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6722,10 +6725,10 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>24</v>
@@ -6761,7 +6764,7 @@
         <v>38</v>
       </c>
       <c r="N106" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
@@ -6770,7 +6773,7 @@
         <v>38</v>
       </c>
       <c r="Q106" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>
@@ -6781,7 +6784,7 @@
     </row>
     <row r="107">
       <c r="A107" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>87</v>
@@ -6820,7 +6823,7 @@
         <v>38</v>
       </c>
       <c r="N107" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>24</v>
@@ -6829,7 +6832,7 @@
         <v>38</v>
       </c>
       <c r="Q107" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>24</v>
@@ -6840,10 +6843,10 @@
     </row>
     <row r="108">
       <c r="A108" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>24</v>
@@ -6879,7 +6882,7 @@
         <v>38</v>
       </c>
       <c r="N108" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>24</v>
@@ -6888,7 +6891,7 @@
         <v>38</v>
       </c>
       <c r="Q108" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>24</v>
@@ -6899,7 +6902,7 @@
     </row>
     <row r="109">
       <c r="A109" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>56</v>
@@ -6938,7 +6941,7 @@
         <v>38</v>
       </c>
       <c r="N109" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>24</v>
@@ -6947,7 +6950,7 @@
         <v>38</v>
       </c>
       <c r="Q109" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R109" s="6" t="s">
         <v>24</v>
@@ -6958,10 +6961,10 @@
     </row>
     <row r="110">
       <c r="A110" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>24</v>
@@ -6997,7 +7000,7 @@
         <v>38</v>
       </c>
       <c r="N110" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>24</v>
@@ -7006,7 +7009,7 @@
         <v>38</v>
       </c>
       <c r="Q110" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R110" s="6" t="s">
         <v>24</v>
@@ -7017,10 +7020,10 @@
     </row>
     <row r="111">
       <c r="A111" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>24</v>
@@ -7056,7 +7059,7 @@
         <v>38</v>
       </c>
       <c r="N111" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>24</v>
@@ -7065,7 +7068,7 @@
         <v>38</v>
       </c>
       <c r="Q111" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R111" s="6" t="s">
         <v>24</v>
@@ -7076,16 +7079,16 @@
     </row>
     <row r="112">
       <c r="A112" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>25</v>
@@ -7115,7 +7118,7 @@
         <v>38</v>
       </c>
       <c r="N112" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>24</v>
@@ -7124,7 +7127,7 @@
         <v>38</v>
       </c>
       <c r="Q112" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R112" s="6" t="s">
         <v>24</v>
@@ -7135,16 +7138,16 @@
     </row>
     <row r="113">
       <c r="A113" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>25</v>
@@ -7174,7 +7177,7 @@
         <v>38</v>
       </c>
       <c r="N113" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>24</v>
@@ -7183,7 +7186,7 @@
         <v>38</v>
       </c>
       <c r="Q113" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R113" s="6" t="s">
         <v>24</v>
@@ -7233,7 +7236,7 @@
         <v>38</v>
       </c>
       <c r="N114" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="O114" s="6" t="s">
         <v>24</v>
@@ -7242,7 +7245,7 @@
         <v>38</v>
       </c>
       <c r="Q114" s="9">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="R114" s="6" t="s">
         <v>24</v>
@@ -7253,7 +7256,7 @@
     </row>
     <row r="115">
       <c r="A115" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>87</v>
@@ -7292,7 +7295,7 @@
         <v>38</v>
       </c>
       <c r="N115" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O115" s="6" t="s">
         <v>24</v>
@@ -7301,7 +7304,7 @@
         <v>38</v>
       </c>
       <c r="Q115" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R115" s="6" t="s">
         <v>24</v>
@@ -7312,10 +7315,10 @@
     </row>
     <row r="116">
       <c r="A116" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>24</v>
@@ -7351,7 +7354,7 @@
         <v>38</v>
       </c>
       <c r="N116" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O116" s="6" t="s">
         <v>24</v>
@@ -7360,7 +7363,7 @@
         <v>38</v>
       </c>
       <c r="Q116" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R116" s="6" t="s">
         <v>24</v>
@@ -7371,10 +7374,10 @@
     </row>
     <row r="117">
       <c r="A117" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>24</v>
@@ -7410,7 +7413,7 @@
         <v>38</v>
       </c>
       <c r="N117" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O117" s="6" t="s">
         <v>24</v>
@@ -7419,7 +7422,7 @@
         <v>38</v>
       </c>
       <c r="Q117" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R117" s="6" t="s">
         <v>24</v>
@@ -7430,10 +7433,10 @@
     </row>
     <row r="118">
       <c r="A118" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>24</v>
@@ -7469,7 +7472,7 @@
         <v>38</v>
       </c>
       <c r="N118" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O118" s="6" t="s">
         <v>24</v>
@@ -7478,7 +7481,7 @@
         <v>38</v>
       </c>
       <c r="Q118" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R118" s="6" t="s">
         <v>24</v>
@@ -7489,10 +7492,10 @@
     </row>
     <row r="119">
       <c r="A119" s="6" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>24</v>
@@ -7528,7 +7531,7 @@
         <v>38</v>
       </c>
       <c r="N119" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O119" s="6" t="s">
         <v>24</v>
@@ -7537,7 +7540,7 @@
         <v>38</v>
       </c>
       <c r="Q119" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R119" s="6" t="s">
         <v>24</v>
@@ -7548,10 +7551,10 @@
     </row>
     <row r="120">
       <c r="A120" s="6" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>24</v>
@@ -7587,7 +7590,7 @@
         <v>38</v>
       </c>
       <c r="N120" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>24</v>
@@ -7596,7 +7599,7 @@
         <v>38</v>
       </c>
       <c r="Q120" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R120" s="6" t="s">
         <v>24</v>
@@ -7607,16 +7610,16 @@
     </row>
     <row r="121">
       <c r="A121" s="6" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E121" s="6" t="s">
         <v>25</v>
@@ -7646,7 +7649,7 @@
         <v>38</v>
       </c>
       <c r="N121" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O121" s="6" t="s">
         <v>24</v>
@@ -7655,7 +7658,7 @@
         <v>38</v>
       </c>
       <c r="Q121" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R121" s="6" t="s">
         <v>24</v>
@@ -7666,16 +7669,16 @@
     </row>
     <row r="122">
       <c r="A122" s="6" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>25</v>
@@ -7705,7 +7708,7 @@
         <v>38</v>
       </c>
       <c r="N122" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="O122" s="6" t="s">
         <v>24</v>
@@ -7714,7 +7717,7 @@
         <v>38</v>
       </c>
       <c r="Q122" s="9">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="R122" s="6" t="s">
         <v>24</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$123</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$115</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em segunda-feira, 10 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em terça-feira, 11 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -142,342 +142,318 @@
     <t>FA-11884</t>
   </si>
   <si>
-    <t>FA-11838</t>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-12031</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11972</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11857</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-12019</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-12016</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-12030</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>FA-11839</t>
+  </si>
+  <si>
+    <t>FA-12046</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-12034</t>
+  </si>
+  <si>
+    <t>FA-11976</t>
+  </si>
+  <si>
+    <t>FA-11858</t>
+  </si>
+  <si>
+    <t>FA-11998</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11963</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-12022</t>
+  </si>
+  <si>
+    <t>FA-12021</t>
   </si>
   <si>
     <t>LEONARDO GOMES DO NASCIMENTO</t>
   </si>
   <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-12031</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11972</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11857</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
+    <t>FA-12050</t>
+  </si>
+  <si>
+    <t>FA-12020</t>
+  </si>
+  <si>
+    <t>FA-11996</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11995</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>1.3 UBER SUPPLIER</t>
+  </si>
+  <si>
+    <t>FA-12107</t>
+  </si>
+  <si>
+    <t>EDCARLOS MARTINS DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11969</t>
+  </si>
+  <si>
+    <t>FA-11915</t>
+  </si>
+  <si>
+    <t>FA-11856</t>
+  </si>
+  <si>
+    <t>FA-12055</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
   </si>
   <si>
     <t>FA-12017</t>
   </si>
   <si>
-    <t>FA-12019</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-11962</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-12016</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-11849</t>
+    <t>FA-12010</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-12053</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12037</t>
+  </si>
+  <si>
+    <t>FA-12001</t>
+  </si>
+  <si>
+    <t>FA-12000</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11979</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-11982</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-12054</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11860</t>
+  </si>
+  <si>
+    <t>FA-11980</t>
+  </si>
+  <si>
+    <t>FA-11922</t>
+  </si>
+  <si>
+    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
+  </si>
+  <si>
+    <t>FA-12039</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12025</t>
+  </si>
+  <si>
+    <t>FA-12024</t>
+  </si>
+  <si>
+    <t>FA-11964</t>
+  </si>
+  <si>
+    <t>FA-12033</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-12038</t>
+  </si>
+  <si>
+    <t>FA-12002</t>
+  </si>
+  <si>
+    <t>FA-11934</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-12078</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-11867</t>
   </si>
   <si>
     <t>MAICON LOPES SILVA</t>
   </si>
   <si>
-    <t>FA-12030</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>FA-11991</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11839</t>
-  </si>
-  <si>
-    <t>FA-12046</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-11975</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-12034</t>
-  </si>
-  <si>
-    <t>FA-11976</t>
-  </si>
-  <si>
-    <t>FA-11858</t>
-  </si>
-  <si>
-    <t>FA-11998</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11963</t>
-  </si>
-  <si>
-    <t>FA-12022</t>
-  </si>
-  <si>
-    <t>FA-12021</t>
-  </si>
-  <si>
-    <t>FA-12050</t>
-  </si>
-  <si>
-    <t>FA-12020</t>
-  </si>
-  <si>
-    <t>FA-11996</t>
-  </si>
-  <si>
-    <t>FA-11866</t>
-  </si>
-  <si>
-    <t>FA-11969</t>
-  </si>
-  <si>
-    <t>FA-11995</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>1.3 UBER SUPPLIER</t>
-  </si>
-  <si>
-    <t>FA-11856</t>
-  </si>
-  <si>
-    <t>FA-12107</t>
-  </si>
-  <si>
-    <t>EDCARLOS MARTINS DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11915</t>
-  </si>
-  <si>
-    <t>FA-12010</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>FA-12055</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-12053</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12037</t>
-  </si>
-  <si>
-    <t>FA-11979</t>
-  </si>
-  <si>
-    <t>FA-12000</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11982</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-12001</t>
-  </si>
-  <si>
-    <t>FA-12054</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11860</t>
-  </si>
-  <si>
-    <t>FA-11980</t>
-  </si>
-  <si>
-    <t>FA-11922</t>
-  </si>
-  <si>
-    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
-  </si>
-  <si>
-    <t>FA-12063</t>
+    <t>FA-12051</t>
+  </si>
+  <si>
+    <t>FA-12023</t>
+  </si>
+  <si>
+    <t>FA-11952</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11999</t>
+  </si>
+  <si>
+    <t>FA-12076</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-12077</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12011</t>
+  </si>
+  <si>
+    <t>FA-12059</t>
+  </si>
+  <si>
+    <t>FA-12057</t>
+  </si>
+  <si>
+    <t>FA-11983</t>
+  </si>
+  <si>
+    <t>FA-11986</t>
+  </si>
+  <si>
+    <t>FA-12040</t>
+  </si>
+  <si>
+    <t>FA-12004</t>
+  </si>
+  <si>
+    <t>FA-12008</t>
+  </si>
+  <si>
+    <t>FA-11984</t>
+  </si>
+  <si>
+    <t>FA-12058</t>
+  </si>
+  <si>
+    <t>FA-12064</t>
   </si>
   <si>
     <t>WILSON COUTINHO BEZERRA</t>
   </si>
   <si>
-    <t>FA-12039</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11964</t>
-  </si>
-  <si>
-    <t>FA-12024</t>
-  </si>
-  <si>
-    <t>FA-12025</t>
-  </si>
-  <si>
-    <t>FA-12033</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-12038</t>
-  </si>
-  <si>
-    <t>FA-12002</t>
-  </si>
-  <si>
-    <t>FA-11934</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-12078</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
-    <t>FA-11867</t>
-  </si>
-  <si>
-    <t>FA-12051</t>
-  </si>
-  <si>
-    <t>FA-12023</t>
-  </si>
-  <si>
-    <t>FA-11952</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11999</t>
-  </si>
-  <si>
-    <t>FA-12076</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-12077</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12011</t>
-  </si>
-  <si>
-    <t>FA-12059</t>
-  </si>
-  <si>
-    <t>FA-12057</t>
-  </si>
-  <si>
-    <t>FA-11983</t>
-  </si>
-  <si>
-    <t>FA-11986</t>
-  </si>
-  <si>
-    <t>FA-12040</t>
-  </si>
-  <si>
-    <t>FA-12004</t>
-  </si>
-  <si>
-    <t>FA-12008</t>
-  </si>
-  <si>
-    <t>FA-11984</t>
+    <t>FA-11923</t>
   </si>
   <si>
     <t>FA-12109</t>
   </si>
   <si>
-    <t>FA-12064</t>
-  </si>
-  <si>
-    <t>FA-11923</t>
-  </si>
-  <si>
-    <t>FA-12058</t>
-  </si>
-  <si>
     <t>FA-11862</t>
   </si>
   <si>
@@ -508,10 +484,10 @@
     <t>FA-11868</t>
   </si>
   <si>
+    <t>FA-12081</t>
+  </si>
+  <si>
     <t>FA-12056</t>
-  </si>
-  <si>
-    <t>FA-12081</t>
   </si>
   <si>
     <t>FA-12026</t>
@@ -723,7 +699,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S123"/>
+  <dimension ref="A1:S115"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1" style="1"/>
@@ -864,7 +840,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -873,7 +849,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -923,7 +899,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -932,7 +908,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>33</v>
@@ -982,7 +958,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -991,7 +967,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -1041,7 +1017,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>33</v>
@@ -1050,7 +1026,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>33</v>
@@ -1100,7 +1076,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>33</v>
@@ -1109,7 +1085,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>33</v>
@@ -1159,7 +1135,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>33</v>
@@ -1168,7 +1144,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1179,13 +1155,13 @@
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>24</v>
@@ -1194,43 +1170,43 @@
         <v>25</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G12" s="7">
-        <v>46182</v>
+        <v>46190</v>
       </c>
       <c r="H12" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I12" s="7">
-        <v>46223</v>
+        <v>46174</v>
       </c>
       <c r="J12" s="7">
-        <v>46223</v>
+        <v>46230</v>
       </c>
       <c r="K12" s="7">
-        <v>46223</v>
+        <v>46246</v>
       </c>
       <c r="L12" s="8">
-        <v>680</v>
+        <v>50</v>
       </c>
       <c r="M12" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-21</v>
+        <v>-15</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>33</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="Q12" s="9">
-        <v>-21</v>
+        <v>1</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S12" s="6" t="s">
         <v>24</v>
@@ -1238,13 +1214,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>24</v>
@@ -1253,43 +1229,43 @@
         <v>25</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G13" s="7">
-        <v>46190</v>
+        <v>46232</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I13" s="7">
-        <v>46174</v>
+        <v>46230</v>
       </c>
       <c r="J13" s="7">
         <v>46230</v>
       </c>
       <c r="K13" s="7">
-        <v>46246</v>
+        <v>46230</v>
       </c>
       <c r="L13" s="8">
-        <v>50</v>
+        <v>630</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>33</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>2</v>
+        <v>-15</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S13" s="6" t="s">
         <v>24</v>
@@ -1303,7 +1279,7 @@
         <v>40</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>24</v>
@@ -1315,7 +1291,7 @@
         <v>26</v>
       </c>
       <c r="G14" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>27</v>
@@ -1330,13 +1306,13 @@
         <v>46230</v>
       </c>
       <c r="L14" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>33</v>
@@ -1345,7 +1321,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>33</v>
@@ -1362,7 +1338,7 @@
         <v>42</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>24</v>
@@ -1374,10 +1350,10 @@
         <v>26</v>
       </c>
       <c r="G15" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I15" s="7">
         <v>46230</v>
@@ -1395,7 +1371,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>33</v>
@@ -1404,7 +1380,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>33</v>
@@ -1415,10 +1391,10 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>24</v>
@@ -1433,10 +1409,10 @@
         <v>26</v>
       </c>
       <c r="G16" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I16" s="7">
         <v>46230</v>
@@ -1448,13 +1424,13 @@
         <v>46230</v>
       </c>
       <c r="L16" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>33</v>
@@ -1463,7 +1439,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>33</v>
@@ -1477,7 +1453,7 @@
         <v>46</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>24</v>
@@ -1486,7 +1462,7 @@
         <v>24</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>26</v>
@@ -1495,7 +1471,7 @@
         <v>46232</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="I17" s="7">
         <v>46230</v>
@@ -1507,13 +1483,13 @@
         <v>46230</v>
       </c>
       <c r="L17" s="8">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>33</v>
@@ -1522,7 +1498,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>33</v>
@@ -1533,10 +1509,10 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>24</v>
@@ -1548,10 +1524,10 @@
         <v>25</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G18" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>27</v>
@@ -1560,13 +1536,13 @@
         <v>46230</v>
       </c>
       <c r="J18" s="7">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K18" s="7">
         <v>46230</v>
       </c>
       <c r="L18" s="8">
-        <v>680</v>
+        <v>42.03</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>28</v>
@@ -1581,7 +1557,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>33</v>
@@ -1592,10 +1568,10 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>24</v>
@@ -1607,31 +1583,31 @@
         <v>25</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G19" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="I19" s="7">
-        <v>46230</v>
+        <v>45930</v>
       </c>
       <c r="J19" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="K19" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="L19" s="8">
-        <v>680</v>
+        <v>185.5</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>33</v>
@@ -1640,7 +1616,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>33</v>
@@ -1651,10 +1627,10 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>24</v>
@@ -1663,34 +1639,34 @@
         <v>24</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G20" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="I20" s="7">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="J20" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="K20" s="7">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="L20" s="8">
-        <v>750</v>
+        <v>355</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>33</v>
@@ -1699,7 +1675,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>33</v>
@@ -1710,17 +1686,17 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B21" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="C21" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="C21" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="E21" s="6" t="s">
         <v>25</v>
       </c>
@@ -1731,25 +1707,25 @@
         <v>24</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I21" s="7">
-        <v>46188</v>
+        <v>46230</v>
       </c>
       <c r="J21" s="7">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="K21" s="7">
-        <v>46188</v>
+        <v>46230</v>
       </c>
       <c r="L21" s="8">
-        <v>16.66</v>
+        <v>560</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-13</v>
+        <v>-8</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>33</v>
@@ -1758,10 +1734,10 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-56</v>
+        <v>-15</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S21" s="6" t="s">
         <v>24</v>
@@ -1772,7 +1748,7 @@
         <v>57</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>24</v>
@@ -1784,31 +1760,31 @@
         <v>25</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G22" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G22" s="7">
+        <v>46232</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I22" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J22" s="7">
-        <v>46231</v>
+        <v>46237</v>
       </c>
       <c r="K22" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L22" s="8">
-        <v>42.03</v>
+        <v>630</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-13</v>
+        <v>-8</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>33</v>
@@ -1817,7 +1793,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>33</v>
@@ -1828,13 +1804,13 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>24</v>
@@ -1843,31 +1819,31 @@
         <v>25</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G23" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G23" s="7">
+        <v>46225</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I23" s="7">
-        <v>45930</v>
+        <v>46237</v>
       </c>
       <c r="J23" s="7">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="K23" s="7">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="L23" s="8">
-        <v>185.5</v>
+        <v>650</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>33</v>
@@ -1876,7 +1852,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>33</v>
@@ -1887,10 +1863,10 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>24</v>
@@ -1902,31 +1878,31 @@
         <v>25</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G24" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G24" s="7">
+        <v>46188</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I24" s="7">
-        <v>46188</v>
+        <v>46237</v>
       </c>
       <c r="J24" s="7">
         <v>46237</v>
       </c>
       <c r="K24" s="7">
-        <v>46188</v>
+        <v>46237</v>
       </c>
       <c r="L24" s="8">
-        <v>116.7</v>
+        <v>650</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>33</v>
@@ -1935,10 +1911,10 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-56</v>
+        <v>-8</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S24" s="6" t="s">
         <v>24</v>
@@ -1961,31 +1937,31 @@
         <v>25</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G25" s="7">
+        <v>46225</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="I25" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J25" s="7">
         <v>46237</v>
       </c>
       <c r="K25" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L25" s="8">
-        <v>320</v>
+        <v>680</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>33</v>
@@ -1994,7 +1970,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>33</v>
@@ -2005,11 +1981,11 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>48</v>
-      </c>
       <c r="C26" s="6" t="s">
         <v>24</v>
       </c>
@@ -2020,31 +1996,31 @@
         <v>25</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G26" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G26" s="7">
+        <v>46225</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I26" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="J26" s="7">
         <v>46237</v>
       </c>
       <c r="K26" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="L26" s="8">
-        <v>355</v>
+        <v>680</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>33</v>
@@ -2053,7 +2029,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-21</v>
+        <v>-8</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>33</v>
@@ -2067,43 +2043,43 @@
         <v>64</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E27" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G27" s="7">
+        <v>46232</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I27" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J27" s="7">
         <v>46237</v>
       </c>
       <c r="K27" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L27" s="8">
-        <v>560</v>
+        <v>680</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>33</v>
@@ -2112,7 +2088,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>33</v>
@@ -2123,10 +2099,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>24</v>
@@ -2141,7 +2117,7 @@
         <v>26</v>
       </c>
       <c r="G28" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>27</v>
@@ -2156,13 +2132,13 @@
         <v>46237</v>
       </c>
       <c r="L28" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>33</v>
@@ -2171,7 +2147,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>33</v>
@@ -2182,16 +2158,16 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>25</v>
@@ -2215,13 +2191,13 @@
         <v>46237</v>
       </c>
       <c r="L29" s="8">
-        <v>630</v>
+        <v>700</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>33</v>
@@ -2230,7 +2206,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>33</v>
@@ -2241,28 +2217,28 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="I30" s="7">
         <v>46237</v>
@@ -2274,13 +2250,13 @@
         <v>46237</v>
       </c>
       <c r="L30" s="8">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>33</v>
@@ -2289,7 +2265,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>33</v>
@@ -2300,28 +2276,28 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F31" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G31" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H31" s="6" t="s">
         <v>71</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E31" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F31" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G31" s="7">
-        <v>46188</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>45</v>
       </c>
       <c r="I31" s="7">
         <v>46237</v>
@@ -2333,13 +2309,13 @@
         <v>46237</v>
       </c>
       <c r="L31" s="8">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>33</v>
@@ -2348,7 +2324,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>33</v>
@@ -2371,28 +2347,28 @@
         <v>24</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>25</v>
+        <v>74</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G32" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I32" s="7">
         <v>46237</v>
       </c>
       <c r="J32" s="7">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="K32" s="7">
         <v>46237</v>
       </c>
       <c r="L32" s="8">
-        <v>680</v>
+        <v>392.05</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>28</v>
@@ -2407,7 +2383,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>33</v>
@@ -2418,10 +2394,10 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>24</v>
@@ -2436,28 +2412,28 @@
         <v>26</v>
       </c>
       <c r="G33" s="7">
-        <v>46225</v>
+        <v>46240</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I33" s="7">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="J33" s="7">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="K33" s="7">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="L33" s="8">
-        <v>680</v>
+        <v>464.29</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>33</v>
@@ -2466,7 +2442,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>33</v>
@@ -2477,13 +2453,13 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>24</v>
@@ -2492,31 +2468,31 @@
         <v>25</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G34" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H34" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I34" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="J34" s="7">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="K34" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="L34" s="8">
-        <v>680</v>
+        <v>190</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>33</v>
@@ -2525,7 +2501,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-7</v>
+        <v>-22</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>33</v>
@@ -2536,10 +2512,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>24</v>
@@ -2551,31 +2527,31 @@
         <v>25</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G35" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I35" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="J35" s="7">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="K35" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="L35" s="8">
-        <v>680</v>
+        <v>330</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>33</v>
@@ -2584,7 +2560,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-7</v>
+        <v>-22</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>33</v>
@@ -2595,46 +2571,46 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G36" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G36" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I36" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="J36" s="7">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="K36" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="L36" s="8">
-        <v>700</v>
+        <v>450</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>33</v>
@@ -2643,7 +2619,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-7</v>
+        <v>-22</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>33</v>
@@ -2654,46 +2630,46 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>52</v>
+        <v>81</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G37" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="I37" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J37" s="7">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="K37" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L37" s="8">
-        <v>750</v>
+        <v>320</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>33</v>
@@ -2702,7 +2678,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>33</v>
@@ -2713,10 +2689,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>24</v>
@@ -2728,31 +2704,31 @@
         <v>25</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G38" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G38" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I38" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="J38" s="7">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="K38" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="L38" s="8">
-        <v>1200</v>
+        <v>582</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-7</v>
+        <v>-4</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>33</v>
@@ -2761,7 +2737,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-7</v>
+        <v>-15</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>33</v>
@@ -2772,13 +2748,13 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>24</v>
@@ -2787,31 +2763,31 @@
         <v>25</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G39" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G39" s="7">
+        <v>46225</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I39" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J39" s="7">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="K39" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L39" s="8">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>33</v>
@@ -2820,7 +2796,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>33</v>
@@ -2831,46 +2807,46 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G40" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G40" s="7">
+        <v>46232</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I40" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="J40" s="7">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="K40" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="L40" s="8">
-        <v>390</v>
+        <v>630</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>33</v>
@@ -2879,7 +2855,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-21</v>
+        <v>-1</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>33</v>
@@ -2890,10 +2866,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>83</v>
+        <v>38</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>24</v>
@@ -2902,34 +2878,34 @@
         <v>24</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>84</v>
+        <v>25</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G41" s="7">
+        <v>46232</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I41" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J41" s="7">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="K41" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="L41" s="8">
-        <v>392.05</v>
+        <v>630</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>33</v>
@@ -2938,7 +2914,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>33</v>
@@ -2949,10 +2925,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>24</v>
@@ -2964,31 +2940,31 @@
         <v>25</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G42" s="7">
+        <v>46225</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I42" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="J42" s="7">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="K42" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="L42" s="8">
-        <v>550</v>
+        <v>630</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>33</v>
@@ -2997,7 +2973,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-21</v>
+        <v>-1</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>33</v>
@@ -3008,10 +2984,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>24</v>
@@ -3026,28 +3002,28 @@
         <v>26</v>
       </c>
       <c r="G43" s="7">
-        <v>46240</v>
+        <v>46225</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I43" s="7">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="J43" s="7">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="K43" s="7">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="L43" s="8">
-        <v>464.29</v>
+        <v>630</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>33</v>
@@ -3056,7 +3032,7 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>33</v>
@@ -3067,10 +3043,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>40</v>
+        <v>92</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>24</v>
@@ -3082,31 +3058,31 @@
         <v>25</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G44" s="7">
+        <v>46225</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I44" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="J44" s="7">
-        <v>46239</v>
+        <v>46244</v>
       </c>
       <c r="K44" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="L44" s="8">
-        <v>480</v>
+        <v>630</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-5</v>
+        <v>-1</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>33</v>
@@ -3115,7 +3091,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-21</v>
+        <v>-1</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>33</v>
@@ -3126,13 +3102,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>24</v>
@@ -3159,25 +3135,25 @@
         <v>46244</v>
       </c>
       <c r="L45" s="8">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P45" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S45" s="6" t="s">
         <v>24</v>
@@ -3185,13 +3161,13 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>24</v>
@@ -3206,7 +3182,7 @@
         <v>46232</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I46" s="7">
         <v>46244</v>
@@ -3218,25 +3194,25 @@
         <v>46244</v>
       </c>
       <c r="L46" s="8">
-        <v>620</v>
+        <v>650</v>
       </c>
       <c r="M46" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q46" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S46" s="6" t="s">
         <v>24</v>
@@ -3244,16 +3220,16 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>25</v>
@@ -3262,10 +3238,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I47" s="7">
         <v>46244</v>
@@ -3277,25 +3253,25 @@
         <v>46244</v>
       </c>
       <c r="L47" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S47" s="6" t="s">
         <v>24</v>
@@ -3303,13 +3279,13 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>40</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>24</v>
@@ -3321,7 +3297,7 @@
         <v>26</v>
       </c>
       <c r="G48" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>27</v>
@@ -3336,25 +3312,25 @@
         <v>46244</v>
       </c>
       <c r="L48" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S48" s="6" t="s">
         <v>24</v>
@@ -3362,10 +3338,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>24</v>
@@ -3380,7 +3356,7 @@
         <v>26</v>
       </c>
       <c r="G49" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>27</v>
@@ -3395,25 +3371,25 @@
         <v>46244</v>
       </c>
       <c r="L49" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S49" s="6" t="s">
         <v>24</v>
@@ -3421,10 +3397,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>24</v>
@@ -3439,7 +3415,7 @@
         <v>26</v>
       </c>
       <c r="G50" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>27</v>
@@ -3454,25 +3430,25 @@
         <v>46244</v>
       </c>
       <c r="L50" s="8">
-        <v>630</v>
+        <v>670</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S50" s="6" t="s">
         <v>24</v>
@@ -3480,10 +3456,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>101</v>
+        <v>45</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>24</v>
@@ -3498,7 +3474,7 @@
         <v>26</v>
       </c>
       <c r="G51" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H51" s="6" t="s">
         <v>27</v>
@@ -3513,25 +3489,25 @@
         <v>46244</v>
       </c>
       <c r="L51" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S51" s="6" t="s">
         <v>24</v>
@@ -3539,10 +3515,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>83</v>
+        <v>66</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>24</v>
@@ -3557,7 +3533,7 @@
         <v>26</v>
       </c>
       <c r="G52" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>27</v>
@@ -3572,25 +3548,25 @@
         <v>46244</v>
       </c>
       <c r="L52" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S52" s="6" t="s">
         <v>24</v>
@@ -3598,10 +3574,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>24</v>
@@ -3616,10 +3592,10 @@
         <v>26</v>
       </c>
       <c r="G53" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I53" s="7">
         <v>46244</v>
@@ -3631,25 +3607,25 @@
         <v>46244</v>
       </c>
       <c r="L53" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S53" s="6" t="s">
         <v>24</v>
@@ -3657,10 +3633,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>24</v>
@@ -3675,10 +3651,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I54" s="7">
         <v>46244</v>
@@ -3690,25 +3666,25 @@
         <v>46244</v>
       </c>
       <c r="L54" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S54" s="6" t="s">
         <v>24</v>
@@ -3716,13 +3692,13 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>24</v>
@@ -3734,7 +3710,7 @@
         <v>26</v>
       </c>
       <c r="G55" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>27</v>
@@ -3749,25 +3725,25 @@
         <v>46244</v>
       </c>
       <c r="L55" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S55" s="6" t="s">
         <v>24</v>
@@ -3775,10 +3751,10 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>24</v>
@@ -3793,10 +3769,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="7">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I56" s="7">
         <v>46244</v>
@@ -3808,25 +3784,25 @@
         <v>46244</v>
       </c>
       <c r="L56" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S56" s="6" t="s">
         <v>24</v>
@@ -3834,10 +3810,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>24</v>
@@ -3852,10 +3828,10 @@
         <v>26</v>
       </c>
       <c r="G57" s="7">
-        <v>46232</v>
+        <v>46212</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I57" s="7">
         <v>46244</v>
@@ -3867,25 +3843,25 @@
         <v>46244</v>
       </c>
       <c r="L57" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N57" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S57" s="6" t="s">
         <v>24</v>
@@ -3893,10 +3869,10 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>24</v>
@@ -3911,7 +3887,7 @@
         <v>26</v>
       </c>
       <c r="G58" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>27</v>
@@ -3926,25 +3902,25 @@
         <v>46244</v>
       </c>
       <c r="L58" s="8">
-        <v>670</v>
+        <v>700</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N58" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q58" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S58" s="6" t="s">
         <v>24</v>
@@ -3952,10 +3928,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>24</v>
@@ -3970,10 +3946,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I59" s="7">
         <v>46244</v>
@@ -3985,25 +3961,25 @@
         <v>46244</v>
       </c>
       <c r="L59" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N59" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q59" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S59" s="6" t="s">
         <v>24</v>
@@ -4011,16 +3987,16 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>25</v>
@@ -4044,25 +4020,25 @@
         <v>46244</v>
       </c>
       <c r="L60" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N60" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q60" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S60" s="6" t="s">
         <v>24</v>
@@ -4070,19 +4046,19 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B61" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E61" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="C61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E61" s="6" t="s">
-        <v>25</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>26</v>
@@ -4091,7 +4067,7 @@
         <v>46232</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="I61" s="7">
         <v>46244</v>
@@ -4103,25 +4079,25 @@
         <v>46244</v>
       </c>
       <c r="L61" s="8">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N61" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q61" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S61" s="6" t="s">
         <v>24</v>
@@ -4129,10 +4105,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4147,10 +4123,10 @@
         <v>26</v>
       </c>
       <c r="G62" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="I62" s="7">
         <v>46244</v>
@@ -4162,25 +4138,25 @@
         <v>46244</v>
       </c>
       <c r="L62" s="8">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N62" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q62" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S62" s="6" t="s">
         <v>24</v>
@@ -4188,10 +4164,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>24</v>
@@ -4206,10 +4182,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I63" s="7">
         <v>46244</v>
@@ -4221,25 +4197,25 @@
         <v>46244</v>
       </c>
       <c r="L63" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N63" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q63" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S63" s="6" t="s">
         <v>24</v>
@@ -4247,16 +4223,16 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>25</v>
@@ -4265,10 +4241,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="7">
-        <v>46225</v>
+        <v>46238</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="I64" s="7">
         <v>46244</v>
@@ -4280,25 +4256,25 @@
         <v>46244</v>
       </c>
       <c r="L64" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N64" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q64" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S64" s="6" t="s">
         <v>24</v>
@@ -4306,16 +4282,16 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>25</v>
@@ -4324,10 +4300,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="7">
-        <v>46212</v>
+        <v>46238</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="I65" s="7">
         <v>46244</v>
@@ -4339,25 +4315,25 @@
         <v>46244</v>
       </c>
       <c r="L65" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="N65" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>91</v>
+        <v>28</v>
       </c>
       <c r="Q65" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S65" s="6" t="s">
         <v>24</v>
@@ -4365,13 +4341,13 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>123</v>
+        <v>84</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>24</v>
+        <v>84</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>24</v>
@@ -4383,37 +4359,37 @@
         <v>26</v>
       </c>
       <c r="G66" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H66" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I66" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J66" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K66" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L66" s="8">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="N66" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="Q66" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>24</v>
@@ -4424,13 +4400,13 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>24</v>
+        <v>81</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>24</v>
@@ -4442,37 +4418,37 @@
         <v>26</v>
       </c>
       <c r="G67" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I67" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J67" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K67" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L67" s="8">
-        <v>700</v>
+        <v>620</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="N67" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="Q67" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>24</v>
@@ -4483,16 +4459,16 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>65</v>
+        <v>86</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>25</v>
@@ -4507,31 +4483,31 @@
         <v>27</v>
       </c>
       <c r="I68" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J68" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K68" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L68" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="N68" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="Q68" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>24</v>
@@ -4542,10 +4518,10 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>52</v>
+        <v>92</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>24</v>
@@ -4554,43 +4530,43 @@
         <v>24</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F69" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="I69" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J69" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K69" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L69" s="8">
-        <v>750</v>
+        <v>630</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="N69" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="Q69" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>24</v>
@@ -4601,10 +4577,10 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>128</v>
+        <v>94</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>24</v>
@@ -4622,34 +4598,34 @@
         <v>46225</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="I70" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J70" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K70" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L70" s="8">
-        <v>800</v>
+        <v>630</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="N70" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="Q70" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>24</v>
@@ -4660,10 +4636,10 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>24</v>
@@ -4678,37 +4654,37 @@
         <v>26</v>
       </c>
       <c r="G71" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I71" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J71" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K71" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L71" s="8">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="N71" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="Q71" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>24</v>
@@ -4719,16 +4695,16 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>25</v>
@@ -4737,37 +4713,37 @@
         <v>26</v>
       </c>
       <c r="G72" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I72" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J72" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K72" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L72" s="8">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="N72" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="Q72" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4781,13 +4757,13 @@
         <v>133</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>134</v>
+        <v>90</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>25</v>
@@ -4796,37 +4772,37 @@
         <v>26</v>
       </c>
       <c r="G73" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I73" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J73" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K73" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L73" s="8">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="N73" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>91</v>
+        <v>36</v>
       </c>
       <c r="Q73" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4837,13 +4813,13 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>90</v>
+        <v>40</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>24</v>
@@ -4870,22 +4846,22 @@
         <v>46251</v>
       </c>
       <c r="L74" s="8">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N74" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q74" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -4896,13 +4872,13 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>93</v>
+        <v>24</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>24</v>
@@ -4917,7 +4893,7 @@
         <v>46232</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I75" s="7">
         <v>46251</v>
@@ -4929,22 +4905,22 @@
         <v>46251</v>
       </c>
       <c r="L75" s="8">
-        <v>620</v>
+        <v>650</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N75" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q75" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -4955,16 +4931,16 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="B76" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B76" s="6" t="s">
-        <v>95</v>
-      </c>
       <c r="C76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>25</v>
@@ -4988,22 +4964,22 @@
         <v>46251</v>
       </c>
       <c r="L76" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N76" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q76" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -5017,7 +4993,7 @@
         <v>138</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>24</v>
@@ -5032,7 +5008,7 @@
         <v>26</v>
       </c>
       <c r="G77" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>27</v>
@@ -5047,22 +5023,22 @@
         <v>46251</v>
       </c>
       <c r="L77" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N77" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q77" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5076,7 +5052,7 @@
         <v>139</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>101</v>
+        <v>76</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -5091,7 +5067,7 @@
         <v>26</v>
       </c>
       <c r="G78" s="7">
-        <v>46225</v>
+        <v>46240</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>27</v>
@@ -5106,22 +5082,22 @@
         <v>46251</v>
       </c>
       <c r="L78" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N78" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q78" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5135,7 +5111,7 @@
         <v>140</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
@@ -5150,10 +5126,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I79" s="7">
         <v>46251</v>
@@ -5165,22 +5141,22 @@
         <v>46251</v>
       </c>
       <c r="L79" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N79" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q79" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5194,7 +5170,7 @@
         <v>141</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
@@ -5209,7 +5185,7 @@
         <v>26</v>
       </c>
       <c r="G80" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H80" s="6" t="s">
         <v>27</v>
@@ -5224,22 +5200,22 @@
         <v>46251</v>
       </c>
       <c r="L80" s="8">
-        <v>630</v>
+        <v>670</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N80" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q80" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5253,7 +5229,7 @@
         <v>142</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5268,7 +5244,7 @@
         <v>26</v>
       </c>
       <c r="G81" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H81" s="6" t="s">
         <v>27</v>
@@ -5283,22 +5259,22 @@
         <v>46251</v>
       </c>
       <c r="L81" s="8">
-        <v>630</v>
+        <v>680</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N81" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q81" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5312,10 +5288,10 @@
         <v>143</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D82" s="6" t="s">
         <v>24</v>
@@ -5327,7 +5303,7 @@
         <v>26</v>
       </c>
       <c r="G82" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>27</v>
@@ -5342,22 +5318,22 @@
         <v>46251</v>
       </c>
       <c r="L82" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N82" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q82" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5371,7 +5347,7 @@
         <v>144</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>24</v>
@@ -5386,10 +5362,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="7">
-        <v>46240</v>
+        <v>46225</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I83" s="7">
         <v>46251</v>
@@ -5401,22 +5377,22 @@
         <v>46251</v>
       </c>
       <c r="L83" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N83" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q83" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5430,7 +5406,7 @@
         <v>145</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>24</v>
@@ -5460,22 +5436,22 @@
         <v>46251</v>
       </c>
       <c r="L84" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N84" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q84" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5489,7 +5465,7 @@
         <v>146</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>24</v>
@@ -5504,10 +5480,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="7">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I85" s="7">
         <v>46251</v>
@@ -5519,22 +5495,22 @@
         <v>46251</v>
       </c>
       <c r="L85" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N85" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q85" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5548,7 +5524,7 @@
         <v>147</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>104</v>
+        <v>63</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>24</v>
@@ -5563,10 +5539,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I86" s="7">
         <v>46251</v>
@@ -5578,22 +5554,22 @@
         <v>46251</v>
       </c>
       <c r="L86" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N86" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q86" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5607,7 +5583,7 @@
         <v>148</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>24</v>
@@ -5622,10 +5598,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I87" s="7">
         <v>46251</v>
@@ -5637,22 +5613,22 @@
         <v>46251</v>
       </c>
       <c r="L87" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N87" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q87" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5666,7 +5642,7 @@
         <v>149</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>24</v>
@@ -5681,10 +5657,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I88" s="7">
         <v>46251</v>
@@ -5696,22 +5672,22 @@
         <v>46251</v>
       </c>
       <c r="L88" s="8">
-        <v>670</v>
+        <v>700</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N88" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q88" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5725,7 +5701,7 @@
         <v>150</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>37</v>
+        <v>113</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>24</v>
@@ -5740,7 +5716,7 @@
         <v>26</v>
       </c>
       <c r="G89" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>27</v>
@@ -5755,22 +5731,22 @@
         <v>46251</v>
       </c>
       <c r="L89" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N89" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q89" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5784,13 +5760,13 @@
         <v>151</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>25</v>
@@ -5814,22 +5790,22 @@
         <v>46251</v>
       </c>
       <c r="L90" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N90" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q90" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5843,7 +5819,7 @@
         <v>152</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>24</v>
@@ -5852,16 +5828,16 @@
         <v>24</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="I91" s="7">
         <v>46251</v>
@@ -5873,22 +5849,22 @@
         <v>46251</v>
       </c>
       <c r="L91" s="8">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N91" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q91" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -5902,7 +5878,7 @@
         <v>153</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>24</v>
@@ -5917,10 +5893,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="I92" s="7">
         <v>46251</v>
@@ -5932,22 +5908,22 @@
         <v>46251</v>
       </c>
       <c r="L92" s="8">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N92" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q92" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -5961,13 +5937,13 @@
         <v>154</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>25</v>
@@ -5976,10 +5952,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="7">
-        <v>46212</v>
+        <v>46238</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="I93" s="7">
         <v>46251</v>
@@ -5991,22 +5967,22 @@
         <v>46251</v>
       </c>
       <c r="L93" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N93" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q93" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -6020,7 +5996,7 @@
         <v>155</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>24</v>
@@ -6038,7 +6014,7 @@
         <v>46225</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="I94" s="7">
         <v>46251</v>
@@ -6050,22 +6026,22 @@
         <v>46251</v>
       </c>
       <c r="L94" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N94" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q94" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6079,13 +6055,13 @@
         <v>156</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>58</v>
+        <v>125</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>25</v>
@@ -6094,10 +6070,10 @@
         <v>26</v>
       </c>
       <c r="G95" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I95" s="7">
         <v>46251</v>
@@ -6109,22 +6085,22 @@
         <v>46251</v>
       </c>
       <c r="L95" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N95" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q95" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6138,7 +6114,7 @@
         <v>157</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>24</v>
@@ -6156,34 +6132,34 @@
         <v>46188</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="I96" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J96" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K96" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L96" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N96" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q96" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6197,13 +6173,13 @@
         <v>158</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>65</v>
+        <v>137</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>25</v>
@@ -6218,31 +6194,31 @@
         <v>27</v>
       </c>
       <c r="I97" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J97" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K97" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L97" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N97" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q97" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6256,7 +6232,7 @@
         <v>159</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>123</v>
+        <v>100</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>24</v>
@@ -6271,37 +6247,37 @@
         <v>26</v>
       </c>
       <c r="G98" s="7">
-        <v>46238</v>
+        <v>46210</v>
       </c>
       <c r="H98" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I98" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J98" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K98" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L98" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N98" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q98" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6315,7 +6291,7 @@
         <v>160</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>24</v>
@@ -6324,43 +6300,43 @@
         <v>24</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="F99" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="7">
-        <v>46232</v>
+        <v>46240</v>
       </c>
       <c r="H99" s="6" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="I99" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J99" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K99" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L99" s="8">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N99" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q99" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6374,7 +6350,7 @@
         <v>161</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>128</v>
+        <v>111</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>24</v>
@@ -6389,37 +6365,37 @@
         <v>26</v>
       </c>
       <c r="G100" s="7">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="I100" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J100" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K100" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L100" s="8">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N100" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q100" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6433,13 +6409,13 @@
         <v>162</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="E101" s="6" t="s">
         <v>25</v>
@@ -6448,37 +6424,37 @@
         <v>26</v>
       </c>
       <c r="G101" s="7">
-        <v>46238</v>
+        <v>46188</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>62</v>
+        <v>43</v>
       </c>
       <c r="I101" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J101" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K101" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L101" s="8">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="M101" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N101" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q101" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6492,7 +6468,7 @@
         <v>163</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>61</v>
+        <v>113</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>24</v>
@@ -6507,37 +6483,37 @@
         <v>26</v>
       </c>
       <c r="G102" s="7">
-        <v>46225</v>
+        <v>46238</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="I102" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J102" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K102" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L102" s="8">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N102" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q102" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6551,13 +6527,13 @@
         <v>164</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="E103" s="6" t="s">
         <v>25</v>
@@ -6566,37 +6542,37 @@
         <v>26</v>
       </c>
       <c r="G103" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="I103" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J103" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K103" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L103" s="8">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N103" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q103" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6610,13 +6586,13 @@
         <v>165</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>44</v>
+        <v>122</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>25</v>
@@ -6625,10 +6601,10 @@
         <v>26</v>
       </c>
       <c r="G104" s="7">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="I104" s="7">
         <v>46258</v>
@@ -6640,22 +6616,22 @@
         <v>46258</v>
       </c>
       <c r="L104" s="8">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N104" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q104" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6669,13 +6645,13 @@
         <v>166</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>25</v>
@@ -6684,10 +6660,10 @@
         <v>26</v>
       </c>
       <c r="G105" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="I105" s="7">
         <v>46258</v>
@@ -6699,22 +6675,22 @@
         <v>46258</v>
       </c>
       <c r="L105" s="8">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N105" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q105" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6725,10 +6701,10 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="s">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>108</v>
+        <v>52</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>24</v>
@@ -6740,40 +6716,40 @@
         <v>25</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G106" s="7">
-        <v>46210</v>
+        <v>24</v>
+      </c>
+      <c r="G106" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I106" s="7">
-        <v>46258</v>
+        <v>45930</v>
       </c>
       <c r="J106" s="7">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="K106" s="7">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="L106" s="8">
-        <v>650</v>
+        <v>185.5</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N106" s="9">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q106" s="9">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>
@@ -6784,10 +6760,10 @@
     </row>
     <row r="107">
       <c r="A107" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>24</v>
@@ -6808,31 +6784,31 @@
         <v>27</v>
       </c>
       <c r="I107" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J107" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K107" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L107" s="8">
         <v>650</v>
       </c>
       <c r="M107" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N107" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O107" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P107" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q107" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R107" s="6" t="s">
         <v>24</v>
@@ -6843,10 +6819,10 @@
     </row>
     <row r="108">
       <c r="A108" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>121</v>
+        <v>100</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>24</v>
@@ -6861,37 +6837,37 @@
         <v>26</v>
       </c>
       <c r="G108" s="7">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I108" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J108" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K108" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L108" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M108" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N108" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O108" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q108" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R108" s="6" t="s">
         <v>24</v>
@@ -6902,10 +6878,10 @@
     </row>
     <row r="109">
       <c r="A109" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>56</v>
+        <v>137</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>24</v>
@@ -6920,37 +6896,37 @@
         <v>26</v>
       </c>
       <c r="G109" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H109" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I109" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J109" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K109" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L109" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M109" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N109" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O109" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P109" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q109" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R109" s="6" t="s">
         <v>24</v>
@@ -6961,10 +6937,10 @@
     </row>
     <row r="110">
       <c r="A110" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>24</v>
@@ -6979,37 +6955,37 @@
         <v>26</v>
       </c>
       <c r="G110" s="7">
-        <v>46238</v>
+        <v>46212</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I110" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J110" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K110" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L110" s="8">
-        <v>700</v>
+        <v>680</v>
       </c>
       <c r="M110" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N110" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O110" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q110" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R110" s="6" t="s">
         <v>24</v>
@@ -7020,10 +6996,10 @@
     </row>
     <row r="111">
       <c r="A111" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>128</v>
+        <v>113</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>24</v>
@@ -7038,37 +7014,37 @@
         <v>26</v>
       </c>
       <c r="G111" s="7">
-        <v>46225</v>
+        <v>46238</v>
       </c>
       <c r="H111" s="6" t="s">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="I111" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J111" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K111" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L111" s="8">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="M111" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N111" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O111" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P111" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q111" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R111" s="6" t="s">
         <v>24</v>
@@ -7079,16 +7055,16 @@
     </row>
     <row r="112">
       <c r="A112" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>132</v>
+        <v>24</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>25</v>
@@ -7097,37 +7073,37 @@
         <v>26</v>
       </c>
       <c r="G112" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="I112" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J112" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K112" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L112" s="8">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="M112" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N112" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O112" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q112" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R112" s="6" t="s">
         <v>24</v>
@@ -7138,16 +7114,16 @@
     </row>
     <row r="113">
       <c r="A113" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>134</v>
+        <v>125</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="E113" s="6" t="s">
         <v>25</v>
@@ -7159,34 +7135,34 @@
         <v>46238</v>
       </c>
       <c r="H113" s="6" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="I113" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J113" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K113" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L113" s="8">
         <v>1200</v>
       </c>
       <c r="M113" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N113" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="O113" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P113" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q113" s="9">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="R113" s="6" t="s">
         <v>24</v>
@@ -7197,43 +7173,43 @@
     </row>
     <row r="114">
       <c r="A114" s="6" t="s">
-        <v>24</v>
+        <v>174</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>59</v>
+        <v>122</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>24</v>
+        <v>123</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G114" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G114" s="7">
+        <v>46238</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>24</v>
+        <v>71</v>
       </c>
       <c r="I114" s="7">
-        <v>45930</v>
+        <v>46265</v>
       </c>
       <c r="J114" s="7">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="K114" s="7">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="L114" s="8">
-        <v>185.5</v>
+        <v>1200</v>
       </c>
       <c r="M114" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="N114" s="9">
         <v>20</v>
@@ -7242,7 +7218,7 @@
         <v>24</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="Q114" s="9">
         <v>20</v>
@@ -7254,500 +7230,28 @@
         <v>24</v>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="C115" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D115" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E115" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F115" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G115" s="7">
-        <v>46240</v>
-      </c>
-      <c r="H115" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I115" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J115" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K115" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L115" s="8">
-        <v>650</v>
-      </c>
-      <c r="M115" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N115" s="9">
-        <v>21</v>
-      </c>
-      <c r="O115" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P115" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q115" s="9">
-        <v>21</v>
-      </c>
-      <c r="R115" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S115" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E116" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G116" s="7">
-        <v>46210</v>
-      </c>
-      <c r="H116" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I116" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J116" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K116" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L116" s="8">
-        <v>650</v>
-      </c>
-      <c r="M116" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N116" s="9">
-        <v>21</v>
-      </c>
-      <c r="O116" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P116" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q116" s="9">
-        <v>21</v>
-      </c>
-      <c r="R116" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S116" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D117" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E117" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F117" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G117" s="7">
-        <v>46232</v>
-      </c>
-      <c r="H117" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I117" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J117" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K117" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L117" s="8">
-        <v>650</v>
-      </c>
-      <c r="M117" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N117" s="9">
-        <v>21</v>
-      </c>
-      <c r="O117" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P117" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q117" s="9">
-        <v>21</v>
-      </c>
-      <c r="R117" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S117" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="B118" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="C118" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D118" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E118" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G118" s="7">
-        <v>46212</v>
-      </c>
-      <c r="H118" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="I118" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J118" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K118" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L118" s="8">
-        <v>680</v>
-      </c>
-      <c r="M118" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N118" s="9">
-        <v>21</v>
-      </c>
-      <c r="O118" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P118" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q118" s="9">
-        <v>21</v>
-      </c>
-      <c r="R118" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S118" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D119" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E119" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F119" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G119" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H119" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I119" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J119" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K119" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L119" s="8">
-        <v>700</v>
-      </c>
-      <c r="M119" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N119" s="9">
-        <v>21</v>
-      </c>
-      <c r="O119" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P119" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q119" s="9">
-        <v>21</v>
-      </c>
-      <c r="R119" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S119" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D120" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E120" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G120" s="7">
-        <v>46225</v>
-      </c>
-      <c r="H120" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I120" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J120" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K120" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L120" s="8">
-        <v>800</v>
-      </c>
-      <c r="M120" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N120" s="9">
-        <v>21</v>
-      </c>
-      <c r="O120" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P120" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q120" s="9">
-        <v>21</v>
-      </c>
-      <c r="R120" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S120" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D121" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E121" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F121" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G121" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H121" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I121" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J121" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K121" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L121" s="8">
-        <v>1200</v>
-      </c>
-      <c r="M121" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N121" s="9">
-        <v>21</v>
-      </c>
-      <c r="O121" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P121" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q121" s="9">
-        <v>21</v>
-      </c>
-      <c r="R121" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S121" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B122" s="6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="E122" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F122" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G122" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H122" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="I122" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J122" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K122" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L122" s="8">
-        <v>1200</v>
-      </c>
-      <c r="M122" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N122" s="9">
-        <v>21</v>
-      </c>
-      <c r="O122" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P122" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q122" s="9">
-        <v>21</v>
-      </c>
-      <c r="R122" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S122" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="123" ht="23" customHeight="1">
-      <c r="A123" s="10"/>
-      <c r="B123" s="10"/>
-      <c r="C123" s="10"/>
-      <c r="D123" s="10"/>
-      <c r="E123" s="10"/>
-      <c r="F123" s="10"/>
-      <c r="G123" s="11"/>
-      <c r="H123" s="10"/>
-      <c r="I123" s="11"/>
-      <c r="J123" s="11"/>
-      <c r="K123" s="11"/>
-      <c r="L123" s="12">
-        <f>SUM(L6:L122)</f>
-      </c>
-      <c r="M123" s="10"/>
-      <c r="N123" s="13"/>
-      <c r="O123" s="10"/>
-      <c r="P123" s="10"/>
-      <c r="Q123" s="13"/>
-      <c r="R123" s="10"/>
-      <c r="S123" s="10"/>
+    <row r="115" ht="23" customHeight="1">
+      <c r="A115" s="10"/>
+      <c r="B115" s="10"/>
+      <c r="C115" s="10"/>
+      <c r="D115" s="10"/>
+      <c r="E115" s="10"/>
+      <c r="F115" s="10"/>
+      <c r="G115" s="11"/>
+      <c r="H115" s="10"/>
+      <c r="I115" s="11"/>
+      <c r="J115" s="11"/>
+      <c r="K115" s="11"/>
+      <c r="L115" s="12">
+        <f>SUM(L6:L114)</f>
+      </c>
+      <c r="M115" s="10"/>
+      <c r="N115" s="13"/>
+      <c r="O115" s="10"/>
+      <c r="P115" s="10"/>
+      <c r="Q115" s="13"/>
+      <c r="R115" s="10"/>
+      <c r="S115" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:S5"/>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$115</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$107</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em terça-feira, 11 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em quarta-feira, 12 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -139,354 +139,336 @@
     <t>FA-11876</t>
   </si>
   <si>
+    <t>GILENO CACHINA</t>
+  </si>
+  <si>
     <t>FA-11884</t>
   </si>
   <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>FA-12031</t>
+  </si>
+  <si>
+    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11972</t>
+  </si>
+  <si>
+    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
+  </si>
+  <si>
+    <t>FA-11857</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-12019</t>
+  </si>
+  <si>
+    <t>OLIZIEL DA SILVA CARDOSO</t>
+  </si>
+  <si>
+    <t>FA-12016</t>
+  </si>
+  <si>
+    <t>ELIONILSON CORDEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
+  </si>
+  <si>
+    <t>JOÃO PAULO CONSÓRCIOS</t>
+  </si>
+  <si>
+    <t>FA-12030</t>
+  </si>
+  <si>
+    <t>LUCAS NAJA MOURA RODRIGUES</t>
+  </si>
+  <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>FA-11839</t>
+  </si>
+  <si>
+    <t>FA-12046</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-12034</t>
+  </si>
+  <si>
+    <t>FA-11976</t>
+  </si>
+  <si>
+    <t>FA-11858</t>
+  </si>
+  <si>
+    <t>FA-12022</t>
+  </si>
+  <si>
+    <t>FA-11963</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-12021</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-12050</t>
+  </si>
+  <si>
+    <t>FA-12020</t>
+  </si>
+  <si>
+    <t>FA-11996</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-11995</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>1.3 UBER SUPPLIER</t>
+  </si>
+  <si>
+    <t>FA-11969</t>
+  </si>
+  <si>
+    <t>FA-11915</t>
+  </si>
+  <si>
+    <t>FA-11856</t>
+  </si>
+  <si>
+    <t>FA-12055</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-12017</t>
+  </si>
+  <si>
+    <t>FA-12037</t>
+  </si>
+  <si>
+    <t>FA-12001</t>
+  </si>
+  <si>
+    <t>FA-12000</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11979</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-12054</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11860</t>
+  </si>
+  <si>
+    <t>FA-11980</t>
+  </si>
+  <si>
+    <t>FA-11922</t>
+  </si>
+  <si>
+    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
+  </si>
+  <si>
+    <t>FA-12025</t>
+  </si>
+  <si>
+    <t>FA-12024</t>
+  </si>
+  <si>
+    <t>FA-11964</t>
+  </si>
+  <si>
+    <t>FA-12002</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12038</t>
+  </si>
+  <si>
+    <t>FA-11867</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>FA-12051</t>
+  </si>
+  <si>
+    <t>FA-12023</t>
+  </si>
+  <si>
+    <t>FA-11952</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11999</t>
+  </si>
+  <si>
+    <t>FA-12077</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-12033</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-12011</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
     <t>A VENCER</t>
   </si>
   <si>
-    <t>FA-12031</t>
-  </si>
-  <si>
-    <t>LUCAS SANTOS REVOREDO DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11972</t>
-  </si>
-  <si>
-    <t>DERICK PEDRO BEZERRA DA ROCHA</t>
-  </si>
-  <si>
-    <t>FA-11857</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>FA-12019</t>
-  </si>
-  <si>
-    <t>OLIZIEL DA SILVA CARDOSO</t>
-  </si>
-  <si>
-    <t>FA-12016</t>
-  </si>
-  <si>
-    <t>ELIONILSON CORDEIRO BARBOSA</t>
-  </si>
-  <si>
-    <t>Z. FROTA INVESTIDORES - JOÃO PAULO</t>
-  </si>
-  <si>
-    <t>JOÃO PAULO CONSÓRCIOS</t>
-  </si>
-  <si>
-    <t>FA-12030</t>
-  </si>
-  <si>
-    <t>LUCAS NAJA MOURA RODRIGUES</t>
-  </si>
-  <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>FA-11839</t>
-  </si>
-  <si>
-    <t>FA-12046</t>
-  </si>
-  <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-12034</t>
-  </si>
-  <si>
-    <t>FA-11976</t>
-  </si>
-  <si>
-    <t>FA-11858</t>
-  </si>
-  <si>
-    <t>FA-11998</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11963</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-12022</t>
-  </si>
-  <si>
-    <t>FA-12021</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-12050</t>
-  </si>
-  <si>
-    <t>FA-12020</t>
-  </si>
-  <si>
-    <t>FA-11996</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-11995</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>1.3 UBER SUPPLIER</t>
-  </si>
-  <si>
-    <t>FA-12107</t>
+    <t>FA-12059</t>
+  </si>
+  <si>
+    <t>FA-12057</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11983</t>
+  </si>
+  <si>
+    <t>FA-11986</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-12040</t>
+  </si>
+  <si>
+    <t>FA-12004</t>
+  </si>
+  <si>
+    <t>FA-12008</t>
+  </si>
+  <si>
+    <t>FA-11984</t>
+  </si>
+  <si>
+    <t>FA-12109</t>
   </si>
   <si>
     <t>EDCARLOS MARTINS DA SILVA</t>
   </si>
   <si>
-    <t>FA-11969</t>
-  </si>
-  <si>
-    <t>FA-11915</t>
-  </si>
-  <si>
-    <t>FA-11856</t>
-  </si>
-  <si>
-    <t>FA-12055</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-12017</t>
-  </si>
-  <si>
-    <t>FA-12010</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>FA-12053</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12037</t>
-  </si>
-  <si>
-    <t>FA-12001</t>
-  </si>
-  <si>
-    <t>FA-12000</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11979</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-11982</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-12054</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11860</t>
-  </si>
-  <si>
-    <t>FA-11980</t>
-  </si>
-  <si>
-    <t>FA-11922</t>
-  </si>
-  <si>
-    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
-  </si>
-  <si>
-    <t>FA-12039</t>
+    <t>FA-12121</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11923</t>
+  </si>
+  <si>
+    <t>FA-12064</t>
+  </si>
+  <si>
+    <t>WILSON COUTINHO BEZERRA</t>
+  </si>
+  <si>
+    <t>FA-12058</t>
+  </si>
+  <si>
+    <t>FA-11862</t>
+  </si>
+  <si>
+    <t>FA-12041</t>
   </si>
   <si>
     <t>RAYANE ROBERTA DA SILVA</t>
   </si>
   <si>
-    <t>FA-12025</t>
-  </si>
-  <si>
-    <t>FA-12024</t>
-  </si>
-  <si>
-    <t>FA-11964</t>
-  </si>
-  <si>
-    <t>FA-12033</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-12038</t>
-  </si>
-  <si>
-    <t>FA-12002</t>
-  </si>
-  <si>
-    <t>FA-11934</t>
+    <t>FA-12028</t>
+  </si>
+  <si>
+    <t>FA-12027</t>
+  </si>
+  <si>
+    <t>FA-12005</t>
+  </si>
+  <si>
+    <t>FA-12043</t>
+  </si>
+  <si>
+    <t>FA-11935</t>
   </si>
   <si>
     <t>WESCLY JEAN DE MEDEIROS</t>
   </si>
   <si>
-    <t>FA-12078</t>
+    <t>FA-11965</t>
+  </si>
+  <si>
+    <t>FA-12042</t>
+  </si>
+  <si>
+    <t>FA-11868</t>
+  </si>
+  <si>
+    <t>FA-12081</t>
   </si>
   <si>
     <t>LUCA ZOLI</t>
   </si>
   <si>
-    <t>FA-11867</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-12051</t>
-  </si>
-  <si>
-    <t>FA-12023</t>
-  </si>
-  <si>
-    <t>FA-11952</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11999</t>
-  </si>
-  <si>
-    <t>FA-12076</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-12077</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12011</t>
-  </si>
-  <si>
-    <t>FA-12059</t>
-  </si>
-  <si>
-    <t>FA-12057</t>
-  </si>
-  <si>
-    <t>FA-11983</t>
-  </si>
-  <si>
-    <t>FA-11986</t>
-  </si>
-  <si>
-    <t>FA-12040</t>
-  </si>
-  <si>
-    <t>FA-12004</t>
-  </si>
-  <si>
-    <t>FA-12008</t>
-  </si>
-  <si>
-    <t>FA-11984</t>
-  </si>
-  <si>
-    <t>FA-12058</t>
-  </si>
-  <si>
-    <t>FA-12064</t>
-  </si>
-  <si>
-    <t>WILSON COUTINHO BEZERRA</t>
-  </si>
-  <si>
-    <t>FA-11923</t>
-  </si>
-  <si>
-    <t>FA-12109</t>
-  </si>
-  <si>
-    <t>FA-11862</t>
-  </si>
-  <si>
-    <t>FA-12041</t>
-  </si>
-  <si>
-    <t>FA-12028</t>
-  </si>
-  <si>
-    <t>FA-12027</t>
-  </si>
-  <si>
-    <t>FA-12005</t>
-  </si>
-  <si>
-    <t>FA-12043</t>
-  </si>
-  <si>
-    <t>FA-11935</t>
-  </si>
-  <si>
-    <t>FA-11965</t>
-  </si>
-  <si>
-    <t>FA-12042</t>
-  </si>
-  <si>
-    <t>FA-11868</t>
-  </si>
-  <si>
-    <t>FA-12081</t>
-  </si>
-  <si>
     <t>FA-12056</t>
   </si>
   <si>
@@ -496,9 +478,6 @@
     <t>FA-11953</t>
   </si>
   <si>
-    <t>FA-12080</t>
-  </si>
-  <si>
     <t>FA-12003</t>
   </si>
   <si>
@@ -511,12 +490,15 @@
     <t>FA-12065</t>
   </si>
   <si>
+    <t>FA-12122</t>
+  </si>
+  <si>
+    <t>FA-12110</t>
+  </si>
+  <si>
     <t>FA-11924</t>
   </si>
   <si>
-    <t>FA-12110</t>
-  </si>
-  <si>
     <t>FA-11936</t>
   </si>
   <si>
@@ -529,9 +511,6 @@
     <t>FA-11954</t>
   </si>
   <si>
-    <t>FA-12084</t>
-  </si>
-  <si>
     <t>FA-12082</t>
   </si>
   <si>
@@ -544,6 +523,9 @@
     <t>FA-12066</t>
   </si>
   <si>
+    <t>FA-12123</t>
+  </si>
+  <si>
     <t>FA-11937</t>
   </si>
   <si>
@@ -554,9 +536,6 @@
   </si>
   <si>
     <t>FA-12085</t>
-  </si>
-  <si>
-    <t>FA-12086</t>
   </si>
 </sst>
 </file>
@@ -699,7 +678,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S115"/>
+  <dimension ref="A1:S107"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1" style="1"/>
@@ -840,7 +819,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -849,7 +828,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-50</v>
+        <v>-51</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -899,7 +878,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -908,7 +887,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>33</v>
@@ -958,7 +937,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -967,7 +946,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-43</v>
+        <v>-44</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -978,13 +957,13 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>24</v>
@@ -993,43 +972,43 @@
         <v>25</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G9" s="7">
-        <v>46190</v>
+        <v>24</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I9" s="7">
-        <v>46174</v>
+        <v>46213</v>
       </c>
       <c r="J9" s="7">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="K9" s="7">
-        <v>46232</v>
+        <v>46213</v>
       </c>
       <c r="L9" s="8">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="M9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-29</v>
+        <v>-33</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="P9" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-13</v>
+        <v>-33</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S9" s="6" t="s">
         <v>24</v>
@@ -1037,7 +1016,7 @@
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>31</v>
@@ -1052,31 +1031,31 @@
         <v>25</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G10" s="7">
-        <v>46198</v>
+        <v>46190</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="7">
-        <v>46216</v>
+        <v>46174</v>
       </c>
       <c r="J10" s="7">
         <v>46216</v>
       </c>
       <c r="K10" s="7">
-        <v>46216</v>
+        <v>46232</v>
       </c>
       <c r="L10" s="8">
-        <v>600</v>
+        <v>50</v>
       </c>
       <c r="M10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-29</v>
+        <v>-30</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>33</v>
@@ -1085,7 +1064,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-29</v>
+        <v>-14</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>33</v>
@@ -1096,7 +1075,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>31</v>
@@ -1111,31 +1090,31 @@
         <v>25</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="G11" s="7">
-        <v>46190</v>
+        <v>46198</v>
       </c>
       <c r="H11" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I11" s="7">
-        <v>46174</v>
+        <v>46216</v>
       </c>
       <c r="J11" s="7">
-        <v>46223</v>
+        <v>46216</v>
       </c>
       <c r="K11" s="7">
-        <v>46239</v>
+        <v>46216</v>
       </c>
       <c r="L11" s="8">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="M11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-22</v>
+        <v>-30</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>33</v>
@@ -1144,7 +1123,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-6</v>
+        <v>-30</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1182,10 +1161,10 @@
         <v>46174</v>
       </c>
       <c r="J12" s="7">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="K12" s="7">
-        <v>46246</v>
+        <v>46239</v>
       </c>
       <c r="L12" s="8">
         <v>50</v>
@@ -1194,19 +1173,19 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-15</v>
+        <v>-23</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>33</v>
       </c>
       <c r="P12" s="6" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>1</v>
+        <v>-7</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S12" s="6" t="s">
         <v>24</v>
@@ -1214,13 +1193,13 @@
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>24</v>
@@ -1229,43 +1208,43 @@
         <v>25</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="G13" s="7">
-        <v>46232</v>
+        <v>46190</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I13" s="7">
-        <v>46230</v>
+        <v>46174</v>
       </c>
       <c r="J13" s="7">
         <v>46230</v>
       </c>
       <c r="K13" s="7">
-        <v>46230</v>
+        <v>46246</v>
       </c>
       <c r="L13" s="8">
-        <v>630</v>
+        <v>50</v>
       </c>
       <c r="M13" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>33</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="Q13" s="9">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S13" s="6" t="s">
         <v>24</v>
@@ -1273,13 +1252,13 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>40</v>
-      </c>
       <c r="C14" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>24</v>
@@ -1291,7 +1270,7 @@
         <v>26</v>
       </c>
       <c r="G14" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>27</v>
@@ -1306,13 +1285,13 @@
         <v>46230</v>
       </c>
       <c r="L14" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="M14" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>33</v>
@@ -1321,7 +1300,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>33</v>
@@ -1332,13 +1311,13 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>42</v>
-      </c>
       <c r="C15" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>24</v>
@@ -1350,10 +1329,10 @@
         <v>26</v>
       </c>
       <c r="G15" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I15" s="7">
         <v>46230</v>
@@ -1371,7 +1350,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>33</v>
@@ -1380,7 +1359,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>33</v>
@@ -1391,28 +1370,28 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="7">
+        <v>46188</v>
+      </c>
+      <c r="H16" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="7">
-        <v>46232</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="I16" s="7">
         <v>46230</v>
@@ -1424,13 +1403,13 @@
         <v>46230</v>
       </c>
       <c r="L16" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>33</v>
@@ -1439,7 +1418,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>33</v>
@@ -1450,11 +1429,11 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>47</v>
-      </c>
       <c r="C17" s="6" t="s">
         <v>24</v>
       </c>
@@ -1462,7 +1441,7 @@
         <v>24</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F17" s="6" t="s">
         <v>26</v>
@@ -1471,7 +1450,7 @@
         <v>46232</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="I17" s="7">
         <v>46230</v>
@@ -1483,13 +1462,13 @@
         <v>46230</v>
       </c>
       <c r="L17" s="8">
-        <v>750</v>
+        <v>680</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>33</v>
@@ -1498,7 +1477,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>33</v>
@@ -1509,46 +1488,46 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G18" s="7">
+        <v>46232</v>
+      </c>
+      <c r="H18" s="6" t="s">
         <v>50</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="I18" s="7">
         <v>46230</v>
       </c>
       <c r="J18" s="7">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="K18" s="7">
         <v>46230</v>
       </c>
       <c r="L18" s="8">
-        <v>42.03</v>
+        <v>750</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-14</v>
+        <v>-16</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>33</v>
@@ -1557,7 +1536,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>33</v>
@@ -1568,7 +1547,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>52</v>
@@ -1589,25 +1568,25 @@
         <v>24</v>
       </c>
       <c r="H19" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I19" s="7">
-        <v>45930</v>
+        <v>46230</v>
       </c>
       <c r="J19" s="7">
-        <v>46233</v>
+        <v>46231</v>
       </c>
       <c r="K19" s="7">
-        <v>46233</v>
+        <v>46230</v>
       </c>
       <c r="L19" s="8">
-        <v>185.5</v>
+        <v>42.03</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-12</v>
+        <v>-15</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>33</v>
@@ -1616,7 +1595,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-12</v>
+        <v>-16</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>33</v>
@@ -1627,11 +1606,11 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>45</v>
-      </c>
       <c r="C20" s="6" t="s">
         <v>24</v>
       </c>
@@ -1648,25 +1627,25 @@
         <v>24</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I20" s="7">
-        <v>46223</v>
+        <v>45930</v>
       </c>
       <c r="J20" s="7">
-        <v>46237</v>
+        <v>46233</v>
       </c>
       <c r="K20" s="7">
-        <v>46223</v>
+        <v>46233</v>
       </c>
       <c r="L20" s="8">
-        <v>355</v>
+        <v>185.5</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-8</v>
+        <v>-13</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>33</v>
@@ -1675,7 +1654,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-22</v>
+        <v>-13</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>33</v>
@@ -1689,13 +1668,13 @@
         <v>54</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="E21" s="6" t="s">
         <v>25</v>
@@ -1710,22 +1689,22 @@
         <v>27</v>
       </c>
       <c r="I21" s="7">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="J21" s="7">
         <v>46237</v>
       </c>
       <c r="K21" s="7">
-        <v>46230</v>
+        <v>46223</v>
       </c>
       <c r="L21" s="8">
-        <v>560</v>
+        <v>355</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>33</v>
@@ -1734,7 +1713,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-15</v>
+        <v>-23</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>33</v>
@@ -1745,46 +1724,46 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="E22" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G22" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I22" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="J22" s="7">
         <v>46237</v>
       </c>
       <c r="K22" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="L22" s="8">
-        <v>630</v>
+        <v>560</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>33</v>
@@ -1793,7 +1772,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-8</v>
+        <v>-16</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>33</v>
@@ -1807,10 +1786,10 @@
         <v>58</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>24</v>
@@ -1822,7 +1801,7 @@
         <v>26</v>
       </c>
       <c r="G23" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H23" s="6" t="s">
         <v>27</v>
@@ -1837,13 +1816,13 @@
         <v>46237</v>
       </c>
       <c r="L23" s="8">
-        <v>650</v>
+        <v>630</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>33</v>
@@ -1852,7 +1831,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>33</v>
@@ -1866,10 +1845,10 @@
         <v>59</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>24</v>
@@ -1881,10 +1860,10 @@
         <v>26</v>
       </c>
       <c r="G24" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I24" s="7">
         <v>46237</v>
@@ -1902,7 +1881,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>33</v>
@@ -1911,7 +1890,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>33</v>
@@ -1925,7 +1904,7 @@
         <v>60</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>24</v>
@@ -1940,10 +1919,10 @@
         <v>26</v>
       </c>
       <c r="G25" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I25" s="7">
         <v>46237</v>
@@ -1955,13 +1934,13 @@
         <v>46237</v>
       </c>
       <c r="L25" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>33</v>
@@ -1970,7 +1949,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>33</v>
@@ -1981,10 +1960,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>24</v>
@@ -1999,10 +1978,10 @@
         <v>26</v>
       </c>
       <c r="G26" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I26" s="7">
         <v>46237</v>
@@ -2020,7 +1999,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>33</v>
@@ -2029,7 +2008,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>33</v>
@@ -2040,10 +2019,10 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>24</v>
@@ -2058,10 +2037,10 @@
         <v>26</v>
       </c>
       <c r="G27" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I27" s="7">
         <v>46237</v>
@@ -2079,7 +2058,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>33</v>
@@ -2088,7 +2067,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>33</v>
@@ -2099,10 +2078,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>65</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>66</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>24</v>
@@ -2138,7 +2117,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>33</v>
@@ -2147,7 +2126,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>33</v>
@@ -2158,16 +2137,16 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>25</v>
@@ -2197,7 +2176,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>33</v>
@@ -2206,7 +2185,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>33</v>
@@ -2217,10 +2196,10 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>24</v>
@@ -2229,7 +2208,7 @@
         <v>24</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -2238,7 +2217,7 @@
         <v>46232</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="I30" s="7">
         <v>46237</v>
@@ -2256,7 +2235,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>33</v>
@@ -2265,7 +2244,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>33</v>
@@ -2276,10 +2255,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>24</v>
@@ -2297,7 +2276,7 @@
         <v>46225</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="I31" s="7">
         <v>46237</v>
@@ -2315,7 +2294,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>33</v>
@@ -2324,7 +2303,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>33</v>
@@ -2335,19 +2314,19 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="C32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>73</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>74</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>24</v>
@@ -2374,7 +2353,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>33</v>
@@ -2383,7 +2362,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>33</v>
@@ -2394,13 +2373,13 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>24</v>
@@ -2409,25 +2388,25 @@
         <v>25</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="7">
-        <v>46240</v>
+        <v>24</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I33" s="7">
-        <v>46239</v>
+        <v>46223</v>
       </c>
       <c r="J33" s="7">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="K33" s="7">
-        <v>46239</v>
+        <v>46223</v>
       </c>
       <c r="L33" s="8">
-        <v>464.29</v>
+        <v>190</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>28</v>
@@ -2442,7 +2421,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-6</v>
+        <v>-23</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>33</v>
@@ -2453,13 +2432,13 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>24</v>
@@ -2486,13 +2465,13 @@
         <v>46223</v>
       </c>
       <c r="L34" s="8">
-        <v>190</v>
+        <v>330</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>33</v>
@@ -2501,7 +2480,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>33</v>
@@ -2512,10 +2491,10 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>24</v>
@@ -2533,7 +2512,7 @@
         <v>24</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I35" s="7">
         <v>46223</v>
@@ -2545,13 +2524,13 @@
         <v>46223</v>
       </c>
       <c r="L35" s="8">
-        <v>330</v>
+        <v>450</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>33</v>
@@ -2560,7 +2539,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-22</v>
+        <v>-23</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>33</v>
@@ -2571,13 +2550,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>42</v>
+        <v>78</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>24</v>
@@ -2592,19 +2571,19 @@
         <v>24</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I36" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="J36" s="7">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="K36" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="L36" s="8">
-        <v>450</v>
+        <v>320</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>28</v>
@@ -2619,7 +2598,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-22</v>
+        <v>-2</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>33</v>
@@ -2630,13 +2609,13 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>24</v>
@@ -2651,25 +2630,25 @@
         <v>24</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I37" s="7">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="J37" s="7">
         <v>46241</v>
       </c>
       <c r="K37" s="7">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="L37" s="8">
-        <v>320</v>
+        <v>582</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>33</v>
@@ -2678,7 +2657,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-1</v>
+        <v>-16</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>33</v>
@@ -2689,10 +2668,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>24</v>
@@ -2704,31 +2683,31 @@
         <v>25</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G38" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G38" s="7">
+        <v>46232</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I38" s="7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="J38" s="7">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K38" s="7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="L38" s="8">
-        <v>582</v>
+        <v>630</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-4</v>
+        <v>-2</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>33</v>
@@ -2737,7 +2716,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-15</v>
+        <v>-2</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>33</v>
@@ -2748,13 +2727,13 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>84</v>
+        <v>24</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>24</v>
@@ -2781,13 +2760,13 @@
         <v>46244</v>
       </c>
       <c r="L39" s="8">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>33</v>
@@ -2796,7 +2775,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>33</v>
@@ -2807,16 +2786,16 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>25</v>
@@ -2825,7 +2804,7 @@
         <v>26</v>
       </c>
       <c r="G40" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>27</v>
@@ -2846,7 +2825,7 @@
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>33</v>
@@ -2855,7 +2834,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>33</v>
@@ -2866,10 +2845,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>24</v>
@@ -2884,7 +2863,7 @@
         <v>26</v>
       </c>
       <c r="G41" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>27</v>
@@ -2905,7 +2884,7 @@
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>33</v>
@@ -2914,7 +2893,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>33</v>
@@ -2925,10 +2904,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>24</v>
@@ -2943,7 +2922,7 @@
         <v>26</v>
       </c>
       <c r="G42" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>27</v>
@@ -2958,13 +2937,13 @@
         <v>46244</v>
       </c>
       <c r="L42" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>33</v>
@@ -2973,7 +2952,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>33</v>
@@ -2984,10 +2963,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>24</v>
@@ -3002,10 +2981,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I43" s="7">
         <v>46244</v>
@@ -3017,13 +2996,13 @@
         <v>46244</v>
       </c>
       <c r="L43" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>33</v>
@@ -3032,7 +3011,7 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>33</v>
@@ -3043,13 +3022,13 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>92</v>
+        <v>41</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>24</v>
@@ -3076,13 +3055,13 @@
         <v>46244</v>
       </c>
       <c r="L44" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>33</v>
@@ -3091,7 +3070,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>33</v>
@@ -3102,10 +3081,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>24</v>
@@ -3120,7 +3099,7 @@
         <v>26</v>
       </c>
       <c r="G45" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>27</v>
@@ -3135,13 +3114,13 @@
         <v>46244</v>
       </c>
       <c r="L45" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>33</v>
@@ -3150,7 +3129,7 @@
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>33</v>
@@ -3161,10 +3140,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>24</v>
@@ -3194,13 +3173,13 @@
         <v>46244</v>
       </c>
       <c r="L46" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>33</v>
@@ -3209,7 +3188,7 @@
         <v>28</v>
       </c>
       <c r="Q46" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>33</v>
@@ -3220,10 +3199,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>24</v>
@@ -3238,10 +3217,10 @@
         <v>26</v>
       </c>
       <c r="G47" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I47" s="7">
         <v>46244</v>
@@ -3253,13 +3232,13 @@
         <v>46244</v>
       </c>
       <c r="L47" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>33</v>
@@ -3268,7 +3247,7 @@
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>33</v>
@@ -3279,13 +3258,13 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>24</v>
@@ -3300,7 +3279,7 @@
         <v>46225</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I48" s="7">
         <v>46244</v>
@@ -3312,13 +3291,13 @@
         <v>46244</v>
       </c>
       <c r="L48" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M48" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>33</v>
@@ -3327,7 +3306,7 @@
         <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>33</v>
@@ -3338,10 +3317,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>24</v>
@@ -3356,10 +3335,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="7">
-        <v>46210</v>
+        <v>46225</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I49" s="7">
         <v>46244</v>
@@ -3371,13 +3350,13 @@
         <v>46244</v>
       </c>
       <c r="L49" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M49" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>33</v>
@@ -3386,7 +3365,7 @@
         <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>33</v>
@@ -3397,10 +3376,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>24</v>
@@ -3430,13 +3409,13 @@
         <v>46244</v>
       </c>
       <c r="L50" s="8">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="M50" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>33</v>
@@ -3445,7 +3424,7 @@
         <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>33</v>
@@ -3456,10 +3435,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>45</v>
+        <v>99</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>24</v>
@@ -3474,10 +3453,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I51" s="7">
         <v>46244</v>
@@ -3489,13 +3468,13 @@
         <v>46244</v>
       </c>
       <c r="L51" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M51" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O51" s="6" t="s">
         <v>33</v>
@@ -3504,7 +3483,7 @@
         <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>33</v>
@@ -3515,16 +3494,16 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>25</v>
@@ -3548,13 +3527,13 @@
         <v>46244</v>
       </c>
       <c r="L52" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M52" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>33</v>
@@ -3563,7 +3542,7 @@
         <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>33</v>
@@ -3574,10 +3553,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>24</v>
@@ -3586,16 +3565,16 @@
         <v>24</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I53" s="7">
         <v>46244</v>
@@ -3607,13 +3586,13 @@
         <v>46244</v>
       </c>
       <c r="L53" s="8">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="M53" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>33</v>
@@ -3622,7 +3601,7 @@
         <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>33</v>
@@ -3633,10 +3612,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>24</v>
@@ -3651,10 +3630,10 @@
         <v>26</v>
       </c>
       <c r="G54" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I54" s="7">
         <v>46244</v>
@@ -3666,13 +3645,13 @@
         <v>46244</v>
       </c>
       <c r="L54" s="8">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="M54" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>33</v>
@@ -3681,7 +3660,7 @@
         <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>33</v>
@@ -3692,10 +3671,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>24</v>
@@ -3710,10 +3689,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I55" s="7">
         <v>46244</v>
@@ -3725,13 +3704,13 @@
         <v>46244</v>
       </c>
       <c r="L55" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M55" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>33</v>
@@ -3740,7 +3719,7 @@
         <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>33</v>
@@ -3751,16 +3730,16 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>25</v>
@@ -3769,10 +3748,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="7">
-        <v>46225</v>
+        <v>46238</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="I56" s="7">
         <v>46244</v>
@@ -3784,13 +3763,13 @@
         <v>46244</v>
       </c>
       <c r="L56" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M56" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>33</v>
@@ -3799,7 +3778,7 @@
         <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>33</v>
@@ -3810,10 +3789,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>24</v>
@@ -3825,25 +3804,25 @@
         <v>25</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G57" s="7">
-        <v>46212</v>
+        <v>24</v>
+      </c>
+      <c r="G57" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H57" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I57" s="7">
         <v>46244</v>
       </c>
       <c r="J57" s="7">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K57" s="7">
         <v>46244</v>
       </c>
       <c r="L57" s="8">
-        <v>680</v>
+        <v>197.7</v>
       </c>
       <c r="M57" s="6" t="s">
         <v>28</v>
@@ -3858,7 +3837,7 @@
         <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>33</v>
@@ -3869,13 +3848,13 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>24</v>
+        <v>111</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>24</v>
@@ -3887,40 +3866,40 @@
         <v>26</v>
       </c>
       <c r="G58" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H58" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I58" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J58" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K58" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L58" s="8">
-        <v>700</v>
+        <v>600</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="N58" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="Q58" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S58" s="6" t="s">
         <v>24</v>
@@ -3928,13 +3907,13 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>24</v>
@@ -3946,40 +3925,40 @@
         <v>26</v>
       </c>
       <c r="G59" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I59" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J59" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K59" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L59" s="8">
-        <v>700</v>
+        <v>620</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="N59" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="Q59" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S59" s="6" t="s">
         <v>24</v>
@@ -3987,16 +3966,16 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>55</v>
+        <v>115</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>25</v>
@@ -4011,34 +3990,34 @@
         <v>27</v>
       </c>
       <c r="I60" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J60" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K60" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L60" s="8">
-        <v>700</v>
+        <v>630</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="N60" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="Q60" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S60" s="6" t="s">
         <v>24</v>
@@ -4046,10 +4025,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>24</v>
@@ -4058,46 +4037,46 @@
         <v>24</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F61" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H61" s="6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="I61" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J61" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K61" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L61" s="8">
-        <v>750</v>
+        <v>630</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="N61" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="Q61" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S61" s="6" t="s">
         <v>24</v>
@@ -4105,10 +4084,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>118</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>119</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4126,37 +4105,37 @@
         <v>46225</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="I62" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J62" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K62" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L62" s="8">
-        <v>800</v>
+        <v>630</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="N62" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="Q62" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S62" s="6" t="s">
         <v>24</v>
@@ -4164,10 +4143,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>24</v>
@@ -4182,40 +4161,40 @@
         <v>26</v>
       </c>
       <c r="G63" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I63" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J63" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K63" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L63" s="8">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="N63" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="Q63" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S63" s="6" t="s">
         <v>24</v>
@@ -4223,16 +4202,16 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>122</v>
+        <v>72</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>25</v>
@@ -4241,40 +4220,40 @@
         <v>26</v>
       </c>
       <c r="G64" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I64" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J64" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K64" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L64" s="8">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="N64" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="Q64" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S64" s="6" t="s">
         <v>24</v>
@@ -4282,16 +4261,16 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="E65" s="6" t="s">
         <v>25</v>
@@ -4300,40 +4279,40 @@
         <v>26</v>
       </c>
       <c r="G65" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I65" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J65" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="K65" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L65" s="8">
-        <v>1200</v>
+        <v>630</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="N65" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="Q65" s="9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S65" s="6" t="s">
         <v>24</v>
@@ -4341,13 +4320,13 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>24</v>
@@ -4374,22 +4353,22 @@
         <v>46251</v>
       </c>
       <c r="L66" s="8">
-        <v>600</v>
+        <v>650</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N66" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q66" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>24</v>
@@ -4400,13 +4379,13 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>81</v>
+        <v>24</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>24</v>
@@ -4418,10 +4397,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="7">
-        <v>46232</v>
+        <v>46240</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I67" s="7">
         <v>46251</v>
@@ -4433,22 +4412,22 @@
         <v>46251</v>
       </c>
       <c r="L67" s="8">
-        <v>620</v>
+        <v>650</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N67" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q67" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>24</v>
@@ -4459,16 +4438,16 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>25</v>
@@ -4477,10 +4456,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="7">
-        <v>46232</v>
+        <v>46245</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I68" s="7">
         <v>46251</v>
@@ -4492,22 +4471,22 @@
         <v>46251</v>
       </c>
       <c r="L68" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N68" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q68" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>24</v>
@@ -4518,10 +4497,10 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>24</v>
@@ -4536,7 +4515,7 @@
         <v>26</v>
       </c>
       <c r="G69" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H69" s="6" t="s">
         <v>27</v>
@@ -4551,22 +4530,22 @@
         <v>46251</v>
       </c>
       <c r="L69" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N69" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q69" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>24</v>
@@ -4577,10 +4556,10 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>94</v>
+        <v>129</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>24</v>
@@ -4595,7 +4574,7 @@
         <v>26</v>
       </c>
       <c r="G70" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>27</v>
@@ -4610,22 +4589,22 @@
         <v>46251</v>
       </c>
       <c r="L70" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N70" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q70" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>24</v>
@@ -4636,10 +4615,10 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>38</v>
+        <v>87</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>24</v>
@@ -4669,22 +4648,22 @@
         <v>46251</v>
       </c>
       <c r="L71" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N71" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q71" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>24</v>
@@ -4695,10 +4674,10 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>24</v>
@@ -4713,10 +4692,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I72" s="7">
         <v>46251</v>
@@ -4728,22 +4707,22 @@
         <v>46251</v>
       </c>
       <c r="L72" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N72" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q72" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4754,11 +4733,11 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B73" s="6" t="s">
-        <v>90</v>
-      </c>
       <c r="C73" s="6" t="s">
         <v>24</v>
       </c>
@@ -4772,7 +4751,7 @@
         <v>26</v>
       </c>
       <c r="G73" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>27</v>
@@ -4787,22 +4766,22 @@
         <v>46251</v>
       </c>
       <c r="L73" s="8">
-        <v>630</v>
+        <v>670</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N73" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q73" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4816,10 +4795,10 @@
         <v>134</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>24</v>
@@ -4831,7 +4810,7 @@
         <v>26</v>
       </c>
       <c r="G74" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H74" s="6" t="s">
         <v>27</v>
@@ -4846,22 +4825,22 @@
         <v>46251</v>
       </c>
       <c r="L74" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N74" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q74" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -4875,7 +4854,7 @@
         <v>135</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>96</v>
+        <v>46</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>24</v>
@@ -4905,22 +4884,22 @@
         <v>46251</v>
       </c>
       <c r="L75" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N75" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q75" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -4934,7 +4913,7 @@
         <v>136</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>24</v>
@@ -4949,10 +4928,10 @@
         <v>26</v>
       </c>
       <c r="G76" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I76" s="7">
         <v>46251</v>
@@ -4964,22 +4943,22 @@
         <v>46251</v>
       </c>
       <c r="L76" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N76" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q76" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -4990,10 +4969,10 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>24</v>
@@ -5008,7 +4987,7 @@
         <v>26</v>
       </c>
       <c r="G77" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H77" s="6" t="s">
         <v>27</v>
@@ -5023,22 +5002,22 @@
         <v>46251</v>
       </c>
       <c r="L77" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N77" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q77" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5049,11 +5028,11 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B78" s="6" t="s">
-        <v>76</v>
-      </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
       </c>
@@ -5067,10 +5046,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="7">
-        <v>46240</v>
+        <v>46212</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I78" s="7">
         <v>46251</v>
@@ -5082,22 +5061,22 @@
         <v>46251</v>
       </c>
       <c r="L78" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N78" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q78" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5111,7 +5090,7 @@
         <v>140</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
@@ -5126,10 +5105,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I79" s="7">
         <v>46251</v>
@@ -5141,22 +5120,22 @@
         <v>46251</v>
       </c>
       <c r="L79" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N79" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q79" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5170,7 +5149,7 @@
         <v>141</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>102</v>
+        <v>52</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
@@ -5200,22 +5179,22 @@
         <v>46251</v>
       </c>
       <c r="L80" s="8">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N80" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q80" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5229,7 +5208,7 @@
         <v>142</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5244,10 +5223,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="I81" s="7">
         <v>46251</v>
@@ -5259,22 +5238,22 @@
         <v>46251</v>
       </c>
       <c r="L81" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N81" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q81" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5288,7 +5267,7 @@
         <v>143</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>24</v>
@@ -5303,7 +5282,7 @@
         <v>26</v>
       </c>
       <c r="G82" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H82" s="6" t="s">
         <v>27</v>
@@ -5318,22 +5297,22 @@
         <v>46251</v>
       </c>
       <c r="L82" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N82" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q82" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5344,16 +5323,16 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>25</v>
@@ -5362,10 +5341,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I83" s="7">
         <v>46251</v>
@@ -5377,22 +5356,22 @@
         <v>46251</v>
       </c>
       <c r="L83" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N83" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q83" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5403,10 +5382,10 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>107</v>
+        <v>48</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>24</v>
@@ -5415,7 +5394,7 @@
         <v>24</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -5424,7 +5403,7 @@
         <v>46232</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="I84" s="7">
         <v>46251</v>
@@ -5436,22 +5415,22 @@
         <v>46251</v>
       </c>
       <c r="L84" s="8">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N84" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q84" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5462,10 +5441,10 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>24</v>
@@ -5480,10 +5459,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="7">
-        <v>46212</v>
+        <v>46225</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I85" s="7">
         <v>46251</v>
@@ -5495,22 +5474,22 @@
         <v>46251</v>
       </c>
       <c r="L85" s="8">
-        <v>680</v>
+        <v>800</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N85" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q85" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5521,10 +5500,10 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>24</v>
@@ -5542,7 +5521,7 @@
         <v>46225</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="I86" s="7">
         <v>46251</v>
@@ -5554,22 +5533,22 @@
         <v>46251</v>
       </c>
       <c r="L86" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N86" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q86" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5580,16 +5559,16 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>25</v>
@@ -5598,10 +5577,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I87" s="7">
         <v>46251</v>
@@ -5613,22 +5592,22 @@
         <v>46251</v>
       </c>
       <c r="L87" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N87" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q87" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5639,10 +5618,10 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>115</v>
+        <v>43</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>24</v>
@@ -5660,34 +5639,34 @@
         <v>46188</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I88" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J88" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K88" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L88" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N88" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q88" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5698,10 +5677,10 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>113</v>
+        <v>129</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>24</v>
@@ -5716,37 +5695,37 @@
         <v>26</v>
       </c>
       <c r="G89" s="7">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="H89" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I89" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J89" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K89" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L89" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N89" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q89" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5757,16 +5736,16 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>56</v>
+        <v>107</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>25</v>
@@ -5775,37 +5754,37 @@
         <v>26</v>
       </c>
       <c r="G90" s="7">
-        <v>46232</v>
+        <v>46245</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I90" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J90" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K90" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L90" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N90" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q90" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5816,10 +5795,10 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>47</v>
+        <v>124</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>24</v>
@@ -5828,43 +5807,43 @@
         <v>24</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="F91" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="7">
-        <v>46232</v>
+        <v>46240</v>
       </c>
       <c r="H91" s="6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="I91" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J91" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K91" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L91" s="8">
-        <v>750</v>
+        <v>650</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N91" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q91" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -5875,10 +5854,10 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>24</v>
@@ -5893,37 +5872,37 @@
         <v>26</v>
       </c>
       <c r="G92" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="I92" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J92" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K92" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L92" s="8">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N92" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q92" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -5934,16 +5913,16 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>25</v>
@@ -5952,37 +5931,37 @@
         <v>26</v>
       </c>
       <c r="G93" s="7">
-        <v>46238</v>
+        <v>46212</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="I93" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J93" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K93" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L93" s="8">
-        <v>1200</v>
+        <v>680</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N93" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q93" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -5993,10 +5972,10 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>24</v>
@@ -6011,37 +5990,37 @@
         <v>26</v>
       </c>
       <c r="G94" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="I94" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J94" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K94" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L94" s="8">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N94" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q94" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6052,16 +6031,16 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>125</v>
+        <v>144</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="E95" s="6" t="s">
         <v>25</v>
@@ -6073,34 +6052,34 @@
         <v>46238</v>
       </c>
       <c r="H95" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I95" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J95" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K95" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L95" s="8">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N95" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q95" s="9">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6111,10 +6090,10 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>24</v>
@@ -6129,10 +6108,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I96" s="7">
         <v>46258</v>
@@ -6144,22 +6123,22 @@
         <v>46258</v>
       </c>
       <c r="L96" s="8">
-        <v>650</v>
+        <v>800</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N96" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q96" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6170,16 +6149,16 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>25</v>
@@ -6188,10 +6167,10 @@
         <v>26</v>
       </c>
       <c r="G97" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I97" s="7">
         <v>46258</v>
@@ -6203,22 +6182,22 @@
         <v>46258</v>
       </c>
       <c r="L97" s="8">
-        <v>650</v>
+        <v>1200</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N97" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q97" s="9">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6229,10 +6208,10 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
-        <v>159</v>
+        <v>24</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>100</v>
+        <v>53</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>24</v>
@@ -6244,40 +6223,40 @@
         <v>25</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G98" s="7">
-        <v>46210</v>
+        <v>24</v>
+      </c>
+      <c r="G98" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I98" s="7">
-        <v>46258</v>
+        <v>45930</v>
       </c>
       <c r="J98" s="7">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="K98" s="7">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="L98" s="8">
-        <v>650</v>
+        <v>185.5</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N98" s="9">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q98" s="9">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6291,7 +6270,7 @@
         <v>160</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>24</v>
@@ -6312,31 +6291,31 @@
         <v>27</v>
       </c>
       <c r="I99" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J99" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K99" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L99" s="8">
         <v>650</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N99" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q99" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6350,7 +6329,7 @@
         <v>161</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>24</v>
@@ -6365,37 +6344,37 @@
         <v>26</v>
       </c>
       <c r="G100" s="7">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I100" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J100" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K100" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L100" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N100" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q100" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6409,7 +6388,7 @@
         <v>162</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>24</v>
@@ -6424,37 +6403,37 @@
         <v>26</v>
       </c>
       <c r="G101" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H101" s="6" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="I101" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J101" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K101" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L101" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M101" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N101" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q101" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6468,13 +6447,13 @@
         <v>163</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>25</v>
@@ -6483,37 +6462,37 @@
         <v>26</v>
       </c>
       <c r="G102" s="7">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="I102" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J102" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K102" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L102" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N102" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q102" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6527,7 +6506,7 @@
         <v>164</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>24</v>
@@ -6542,37 +6521,37 @@
         <v>26</v>
       </c>
       <c r="G103" s="7">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="I103" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J103" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K103" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L103" s="8">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N103" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q103" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6586,13 +6565,13 @@
         <v>165</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>25</v>
@@ -6604,34 +6583,34 @@
         <v>46238</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="I104" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J104" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K104" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L104" s="8">
-        <v>1200</v>
+        <v>700</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N104" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q104" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6645,13 +6624,13 @@
         <v>166</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>123</v>
+        <v>24</v>
       </c>
       <c r="E105" s="6" t="s">
         <v>25</v>
@@ -6660,37 +6639,37 @@
         <v>26</v>
       </c>
       <c r="G105" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="I105" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J105" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K105" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L105" s="8">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N105" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q105" s="9">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6701,43 +6680,43 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="s">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>52</v>
+        <v>106</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G106" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G106" s="7">
+        <v>46238</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="I106" s="7">
-        <v>45930</v>
+        <v>46265</v>
       </c>
       <c r="J106" s="7">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="K106" s="7">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="L106" s="8">
-        <v>185.5</v>
+        <v>1200</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="N106" s="9">
         <v>19</v>
@@ -6746,7 +6725,7 @@
         <v>24</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="Q106" s="9">
         <v>19</v>
@@ -6758,500 +6737,28 @@
         <v>24</v>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="B107" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D107" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E107" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F107" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G107" s="7">
-        <v>46240</v>
-      </c>
-      <c r="H107" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I107" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J107" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K107" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L107" s="8">
-        <v>650</v>
-      </c>
-      <c r="M107" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N107" s="9">
-        <v>20</v>
-      </c>
-      <c r="O107" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P107" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q107" s="9">
-        <v>20</v>
-      </c>
-      <c r="R107" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S107" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="B108" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E108" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F108" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G108" s="7">
-        <v>46210</v>
-      </c>
-      <c r="H108" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I108" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J108" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K108" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L108" s="8">
-        <v>650</v>
-      </c>
-      <c r="M108" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N108" s="9">
-        <v>20</v>
-      </c>
-      <c r="O108" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P108" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q108" s="9">
-        <v>20</v>
-      </c>
-      <c r="R108" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S108" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="B109" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E109" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F109" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G109" s="7">
-        <v>46232</v>
-      </c>
-      <c r="H109" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I109" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J109" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K109" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L109" s="8">
-        <v>650</v>
-      </c>
-      <c r="M109" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N109" s="9">
-        <v>20</v>
-      </c>
-      <c r="O109" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P109" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q109" s="9">
-        <v>20</v>
-      </c>
-      <c r="R109" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S109" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="B110" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E110" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F110" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G110" s="7">
-        <v>46212</v>
-      </c>
-      <c r="H110" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="I110" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J110" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K110" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L110" s="8">
-        <v>680</v>
-      </c>
-      <c r="M110" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N110" s="9">
-        <v>20</v>
-      </c>
-      <c r="O110" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P110" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q110" s="9">
-        <v>20</v>
-      </c>
-      <c r="R110" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S110" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="B111" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D111" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E111" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F111" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G111" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H111" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I111" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J111" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K111" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L111" s="8">
-        <v>700</v>
-      </c>
-      <c r="M111" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N111" s="9">
-        <v>20</v>
-      </c>
-      <c r="O111" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P111" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q111" s="9">
-        <v>20</v>
-      </c>
-      <c r="R111" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S111" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="B112" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D112" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E112" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F112" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G112" s="7">
-        <v>46225</v>
-      </c>
-      <c r="H112" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I112" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J112" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K112" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L112" s="8">
-        <v>800</v>
-      </c>
-      <c r="M112" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N112" s="9">
-        <v>20</v>
-      </c>
-      <c r="O112" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P112" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q112" s="9">
-        <v>20</v>
-      </c>
-      <c r="R112" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S112" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="6" t="s">
-        <v>173</v>
-      </c>
-      <c r="B113" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="C113" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D113" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E113" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F113" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G113" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H113" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I113" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J113" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K113" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L113" s="8">
-        <v>1200</v>
-      </c>
-      <c r="M113" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N113" s="9">
-        <v>20</v>
-      </c>
-      <c r="O113" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P113" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q113" s="9">
-        <v>20</v>
-      </c>
-      <c r="R113" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S113" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="B114" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D114" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="E114" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G114" s="7">
-        <v>46238</v>
-      </c>
-      <c r="H114" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="I114" s="7">
-        <v>46265</v>
-      </c>
-      <c r="J114" s="7">
-        <v>46265</v>
-      </c>
-      <c r="K114" s="7">
-        <v>46265</v>
-      </c>
-      <c r="L114" s="8">
-        <v>1200</v>
-      </c>
-      <c r="M114" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N114" s="9">
-        <v>20</v>
-      </c>
-      <c r="O114" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P114" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q114" s="9">
-        <v>20</v>
-      </c>
-      <c r="R114" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S114" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="115" ht="23" customHeight="1">
-      <c r="A115" s="10"/>
-      <c r="B115" s="10"/>
-      <c r="C115" s="10"/>
-      <c r="D115" s="10"/>
-      <c r="E115" s="10"/>
-      <c r="F115" s="10"/>
-      <c r="G115" s="11"/>
-      <c r="H115" s="10"/>
-      <c r="I115" s="11"/>
-      <c r="J115" s="11"/>
-      <c r="K115" s="11"/>
-      <c r="L115" s="12">
-        <f>SUM(L6:L114)</f>
-      </c>
-      <c r="M115" s="10"/>
-      <c r="N115" s="13"/>
-      <c r="O115" s="10"/>
-      <c r="P115" s="10"/>
-      <c r="Q115" s="13"/>
-      <c r="R115" s="10"/>
-      <c r="S115" s="10"/>
+    <row r="107" ht="23" customHeight="1">
+      <c r="A107" s="10"/>
+      <c r="B107" s="10"/>
+      <c r="C107" s="10"/>
+      <c r="D107" s="10"/>
+      <c r="E107" s="10"/>
+      <c r="F107" s="10"/>
+      <c r="G107" s="11"/>
+      <c r="H107" s="10"/>
+      <c r="I107" s="11"/>
+      <c r="J107" s="11"/>
+      <c r="K107" s="11"/>
+      <c r="L107" s="12">
+        <f>SUM(L6:L106)</f>
+      </c>
+      <c r="M107" s="10"/>
+      <c r="N107" s="13"/>
+      <c r="O107" s="10"/>
+      <c r="P107" s="10"/>
+      <c r="Q107" s="13"/>
+      <c r="R107" s="10"/>
+      <c r="S107" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:S5"/>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="167">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em quarta-feira, 12 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em quinta-feira, 13 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -143,9 +143,6 @@
   </si>
   <si>
     <t>FA-11884</t>
-  </si>
-  <si>
-    <t>HOJE</t>
   </si>
   <si>
     <t>FA-12031</t>
@@ -819,7 +816,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -828,7 +825,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-51</v>
+        <v>-52</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -878,7 +875,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -887,7 +884,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>33</v>
@@ -937,7 +934,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -946,7 +943,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-44</v>
+        <v>-45</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -996,7 +993,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -1005,7 +1002,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>29</v>
@@ -1055,16 +1052,16 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>33</v>
@@ -1114,19 +1111,19 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-30</v>
+        <v>-31</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S11" s="6" t="s">
         <v>24</v>
@@ -1173,7 +1170,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>33</v>
@@ -1182,7 +1179,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>33</v>
@@ -1232,19 +1229,19 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>33</v>
       </c>
       <c r="P13" s="6" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S13" s="6" t="s">
         <v>24</v>
@@ -1252,10 +1249,10 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>38</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>39</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>24</v>
@@ -1291,7 +1288,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>33</v>
@@ -1300,7 +1297,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>33</v>
@@ -1311,13 +1308,13 @@
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="C15" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>24</v>
@@ -1350,7 +1347,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>33</v>
@@ -1359,7 +1356,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>33</v>
@@ -1370,10 +1367,10 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>42</v>
-      </c>
-      <c r="B16" s="6" t="s">
-        <v>43</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>24</v>
@@ -1391,7 +1388,7 @@
         <v>46188</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I16" s="7">
         <v>46230</v>
@@ -1409,7 +1406,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>33</v>
@@ -1418,7 +1415,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>33</v>
@@ -1429,10 +1426,10 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>46</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>24</v>
@@ -1468,7 +1465,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>33</v>
@@ -1477,7 +1474,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>33</v>
@@ -1488,19 +1485,19 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="C18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E18" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -1509,7 +1506,7 @@
         <v>46232</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I18" s="7">
         <v>46230</v>
@@ -1527,7 +1524,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>33</v>
@@ -1536,7 +1533,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>33</v>
@@ -1547,10 +1544,10 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>24</v>
@@ -1586,7 +1583,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>33</v>
@@ -1595,7 +1592,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>33</v>
@@ -1609,7 +1606,7 @@
         <v>24</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>24</v>
@@ -1645,7 +1642,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>33</v>
@@ -1654,7 +1651,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>33</v>
@@ -1665,10 +1662,10 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>24</v>
@@ -1704,7 +1701,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>33</v>
@@ -1713,7 +1710,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>33</v>
@@ -1724,16 +1721,16 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="C22" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D22" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>25</v>
@@ -1763,7 +1760,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>33</v>
@@ -1772,7 +1769,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>33</v>
@@ -1783,10 +1780,10 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>24</v>
@@ -1822,7 +1819,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>33</v>
@@ -1831,7 +1828,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>33</v>
@@ -1842,13 +1839,13 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>24</v>
@@ -1881,7 +1878,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>33</v>
@@ -1890,7 +1887,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>33</v>
@@ -1901,10 +1898,10 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>24</v>
@@ -1922,7 +1919,7 @@
         <v>46188</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I25" s="7">
         <v>46237</v>
@@ -1940,7 +1937,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>33</v>
@@ -1949,7 +1946,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>33</v>
@@ -1960,10 +1957,10 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>24</v>
@@ -1999,7 +1996,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>33</v>
@@ -2008,7 +2005,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>33</v>
@@ -2019,10 +2016,10 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B27" s="6" t="s">
         <v>62</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>63</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>24</v>
@@ -2040,7 +2037,7 @@
         <v>46225</v>
       </c>
       <c r="H27" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I27" s="7">
         <v>46237</v>
@@ -2058,7 +2055,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>33</v>
@@ -2067,7 +2064,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>33</v>
@@ -2078,10 +2075,10 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>64</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>65</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>24</v>
@@ -2117,7 +2114,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>33</v>
@@ -2126,7 +2123,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>33</v>
@@ -2137,16 +2134,16 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="E29" s="6" t="s">
         <v>25</v>
@@ -2176,7 +2173,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>33</v>
@@ -2185,7 +2182,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>33</v>
@@ -2196,19 +2193,19 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B30" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E30" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E30" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -2217,7 +2214,7 @@
         <v>46232</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I30" s="7">
         <v>46237</v>
@@ -2235,7 +2232,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>33</v>
@@ -2244,7 +2241,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>33</v>
@@ -2255,10 +2252,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B31" s="6" t="s">
         <v>68</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>69</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>24</v>
@@ -2276,7 +2273,7 @@
         <v>46225</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I31" s="7">
         <v>46237</v>
@@ -2294,7 +2291,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>33</v>
@@ -2303,7 +2300,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>33</v>
@@ -2314,19 +2311,19 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="C32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D32" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E32" s="6" t="s">
         <v>72</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>73</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>24</v>
@@ -2353,7 +2350,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>33</v>
@@ -2362,7 +2359,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>33</v>
@@ -2373,13 +2370,13 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>24</v>
@@ -2412,7 +2409,7 @@
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>33</v>
@@ -2421,7 +2418,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>33</v>
@@ -2432,10 +2429,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>24</v>
@@ -2471,7 +2468,7 @@
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>33</v>
@@ -2480,7 +2477,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>33</v>
@@ -2491,28 +2488,28 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B35" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="H35" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="C35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H35" s="6" t="s">
-        <v>44</v>
       </c>
       <c r="I35" s="7">
         <v>46223</v>
@@ -2530,7 +2527,7 @@
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>33</v>
@@ -2539,7 +2536,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>33</v>
@@ -2550,13 +2547,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="C36" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>24</v>
@@ -2571,7 +2568,7 @@
         <v>24</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I36" s="7">
         <v>46244</v>
@@ -2589,7 +2586,7 @@
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>33</v>
@@ -2598,7 +2595,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>33</v>
@@ -2609,10 +2606,10 @@
     </row>
     <row r="37">
       <c r="A37" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>24</v>
@@ -2648,7 +2645,7 @@
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>33</v>
@@ -2657,7 +2654,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>33</v>
@@ -2668,10 +2665,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>24</v>
@@ -2707,7 +2704,7 @@
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>33</v>
@@ -2716,7 +2713,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>33</v>
@@ -2727,10 +2724,10 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>24</v>
@@ -2766,7 +2763,7 @@
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>33</v>
@@ -2775,7 +2772,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>33</v>
@@ -2786,10 +2783,10 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B40" s="6" t="s">
         <v>82</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>83</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>24</v>
@@ -2825,7 +2822,7 @@
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>33</v>
@@ -2834,7 +2831,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>33</v>
@@ -2845,10 +2842,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>85</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>24</v>
@@ -2884,7 +2881,7 @@
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>33</v>
@@ -2893,7 +2890,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>33</v>
@@ -2904,10 +2901,10 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B42" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>87</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>24</v>
@@ -2943,7 +2940,7 @@
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>33</v>
@@ -2952,7 +2949,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>33</v>
@@ -2963,10 +2960,10 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>24</v>
@@ -2984,7 +2981,7 @@
         <v>46188</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I43" s="7">
         <v>46244</v>
@@ -3002,7 +2999,7 @@
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>33</v>
@@ -3011,7 +3008,7 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>33</v>
@@ -3022,13 +3019,13 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>24</v>
@@ -3061,7 +3058,7 @@
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>33</v>
@@ -3070,7 +3067,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>33</v>
@@ -3081,10 +3078,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B45" s="6" t="s">
         <v>90</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>91</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>24</v>
@@ -3120,7 +3117,7 @@
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>33</v>
@@ -3129,7 +3126,7 @@
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>33</v>
@@ -3140,10 +3137,10 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="6" t="s">
         <v>24</v>
@@ -3179,7 +3176,7 @@
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>33</v>
@@ -3188,7 +3185,7 @@
         <v>28</v>
       </c>
       <c r="Q46" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>33</v>
@@ -3199,10 +3196,10 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>24</v>
@@ -3238,7 +3235,7 @@
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>33</v>
@@ -3247,7 +3244,7 @@
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>33</v>
@@ -3258,10 +3255,10 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C48" s="6" t="s">
         <v>24</v>
@@ -3279,7 +3276,7 @@
         <v>46225</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I48" s="7">
         <v>46244</v>
@@ -3297,7 +3294,7 @@
         <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>33</v>
@@ -3306,7 +3303,7 @@
         <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>33</v>
@@ -3317,10 +3314,10 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>95</v>
-      </c>
-      <c r="B49" s="6" t="s">
-        <v>96</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>24</v>
@@ -3338,7 +3335,7 @@
         <v>46225</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I49" s="7">
         <v>46244</v>
@@ -3356,7 +3353,7 @@
         <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>33</v>
@@ -3365,7 +3362,7 @@
         <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>33</v>
@@ -3376,10 +3373,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>24</v>
@@ -3415,7 +3412,7 @@
         <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>33</v>
@@ -3424,7 +3421,7 @@
         <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>33</v>
@@ -3435,10 +3432,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" s="6" t="s">
         <v>98</v>
-      </c>
-      <c r="B51" s="6" t="s">
-        <v>99</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>24</v>
@@ -3456,7 +3453,7 @@
         <v>46188</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I51" s="7">
         <v>46244</v>
@@ -3474,7 +3471,7 @@
         <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O51" s="6" t="s">
         <v>33</v>
@@ -3483,7 +3480,7 @@
         <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>33</v>
@@ -3494,16 +3491,16 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B52" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D52" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="C52" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>25</v>
@@ -3533,7 +3530,7 @@
         <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>33</v>
@@ -3542,7 +3539,7 @@
         <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>33</v>
@@ -3553,19 +3550,19 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B53" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E53" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="C53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E53" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="F53" s="6" t="s">
         <v>26</v>
@@ -3574,7 +3571,7 @@
         <v>46232</v>
       </c>
       <c r="H53" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I53" s="7">
         <v>46244</v>
@@ -3592,7 +3589,7 @@
         <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>33</v>
@@ -3601,7 +3598,7 @@
         <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>33</v>
@@ -3612,10 +3609,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B54" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="B54" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>24</v>
@@ -3633,7 +3630,7 @@
         <v>46225</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I54" s="7">
         <v>46244</v>
@@ -3651,7 +3648,7 @@
         <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>33</v>
@@ -3660,7 +3657,7 @@
         <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>33</v>
@@ -3671,10 +3668,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>24</v>
@@ -3692,7 +3689,7 @@
         <v>46225</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I55" s="7">
         <v>46244</v>
@@ -3710,7 +3707,7 @@
         <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>33</v>
@@ -3719,7 +3716,7 @@
         <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>33</v>
@@ -3730,16 +3727,16 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="B56" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="C56" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D56" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>25</v>
@@ -3751,7 +3748,7 @@
         <v>46238</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I56" s="7">
         <v>46244</v>
@@ -3769,7 +3766,7 @@
         <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>33</v>
@@ -3778,7 +3775,7 @@
         <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>33</v>
@@ -3789,10 +3786,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" s="6" t="s">
         <v>108</v>
-      </c>
-      <c r="B57" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>24</v>
@@ -3828,7 +3825,7 @@
         <v>28</v>
       </c>
       <c r="N57" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O57" s="6" t="s">
         <v>33</v>
@@ -3837,7 +3834,7 @@
         <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>33</v>
@@ -3848,13 +3845,13 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="B58" s="6" t="s">
-        <v>111</v>
-      </c>
       <c r="C58" s="6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>24</v>
@@ -3884,19 +3881,19 @@
         <v>600</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N58" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q58" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>24</v>
@@ -3907,13 +3904,13 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>24</v>
@@ -3928,7 +3925,7 @@
         <v>46232</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I59" s="7">
         <v>46251</v>
@@ -3943,19 +3940,19 @@
         <v>620</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N59" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O59" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q59" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>24</v>
@@ -3966,16 +3963,16 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B60" s="6" t="s">
-        <v>115</v>
-      </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>25</v>
@@ -4002,19 +3999,19 @@
         <v>630</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N60" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q60" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>24</v>
@@ -4025,10 +4022,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>24</v>
@@ -4061,19 +4058,19 @@
         <v>630</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N61" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O61" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q61" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>24</v>
@@ -4084,10 +4081,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>117</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>118</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4120,19 +4117,19 @@
         <v>630</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N62" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q62" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>24</v>
@@ -4143,10 +4140,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>24</v>
@@ -4179,19 +4176,19 @@
         <v>630</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N63" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q63" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>24</v>
@@ -4202,10 +4199,10 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>24</v>
@@ -4238,19 +4235,19 @@
         <v>630</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N64" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q64" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R64" s="6" t="s">
         <v>24</v>
@@ -4261,10 +4258,10 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>24</v>
@@ -4297,19 +4294,19 @@
         <v>630</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N65" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O65" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q65" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>24</v>
@@ -4320,13 +4317,13 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>24</v>
@@ -4356,19 +4353,19 @@
         <v>650</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N66" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q66" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>24</v>
@@ -4379,10 +4376,10 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B67" s="6" t="s">
         <v>123</v>
-      </c>
-      <c r="B67" s="6" t="s">
-        <v>124</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>24</v>
@@ -4415,19 +4412,19 @@
         <v>650</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N67" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q67" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>24</v>
@@ -4438,16 +4435,16 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="B68" s="6" t="s">
-        <v>126</v>
-      </c>
       <c r="C68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>25</v>
@@ -4459,7 +4456,7 @@
         <v>46245</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I68" s="7">
         <v>46251</v>
@@ -4474,19 +4471,19 @@
         <v>650</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N68" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q68" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>24</v>
@@ -4497,10 +4494,10 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>24</v>
@@ -4533,19 +4530,19 @@
         <v>650</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N69" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q69" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>24</v>
@@ -4556,10 +4553,10 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>128</v>
-      </c>
-      <c r="B70" s="6" t="s">
-        <v>129</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>24</v>
@@ -4592,19 +4589,19 @@
         <v>650</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N70" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q70" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>24</v>
@@ -4615,10 +4612,10 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>24</v>
@@ -4651,19 +4648,19 @@
         <v>650</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N71" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q71" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>24</v>
@@ -4674,10 +4671,10 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>24</v>
@@ -4695,7 +4692,7 @@
         <v>46188</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I72" s="7">
         <v>46251</v>
@@ -4710,19 +4707,19 @@
         <v>650</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N72" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q72" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4733,10 +4730,10 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>24</v>
@@ -4769,19 +4766,19 @@
         <v>670</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N73" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q73" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4792,10 +4789,10 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>24</v>
@@ -4828,19 +4825,19 @@
         <v>680</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N74" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q74" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -4851,10 +4848,10 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>24</v>
@@ -4887,19 +4884,19 @@
         <v>680</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N75" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q75" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -4910,10 +4907,10 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>24</v>
@@ -4931,7 +4928,7 @@
         <v>46225</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I76" s="7">
         <v>46251</v>
@@ -4946,19 +4943,19 @@
         <v>680</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N76" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q76" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -4969,10 +4966,10 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>24</v>
@@ -5005,19 +5002,19 @@
         <v>680</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N77" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q77" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5028,10 +5025,10 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B78" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="B78" s="6" t="s">
-        <v>139</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -5049,7 +5046,7 @@
         <v>46212</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I78" s="7">
         <v>46251</v>
@@ -5064,19 +5061,19 @@
         <v>680</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N78" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q78" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5087,10 +5084,10 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
@@ -5108,7 +5105,7 @@
         <v>46225</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I79" s="7">
         <v>46251</v>
@@ -5123,19 +5120,19 @@
         <v>680</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N79" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q79" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5146,10 +5143,10 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
@@ -5182,19 +5179,19 @@
         <v>680</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N80" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q80" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5205,10 +5202,10 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5226,7 +5223,7 @@
         <v>46188</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I81" s="7">
         <v>46251</v>
@@ -5241,19 +5238,19 @@
         <v>700</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N81" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q81" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5264,10 +5261,10 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B82" s="6" t="s">
         <v>143</v>
-      </c>
-      <c r="B82" s="6" t="s">
-        <v>144</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>24</v>
@@ -5300,19 +5297,19 @@
         <v>700</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N82" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q82" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5323,16 +5320,16 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B83" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D83" s="6" t="s">
         <v>56</v>
-      </c>
-      <c r="C83" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D83" s="6" t="s">
-        <v>57</v>
       </c>
       <c r="E83" s="6" t="s">
         <v>25</v>
@@ -5359,19 +5356,19 @@
         <v>700</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N83" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q83" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5382,19 +5379,19 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B84" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C84" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D84" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E84" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -5403,7 +5400,7 @@
         <v>46232</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I84" s="7">
         <v>46251</v>
@@ -5418,19 +5415,19 @@
         <v>750</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N84" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q84" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5441,10 +5438,10 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>24</v>
@@ -5462,7 +5459,7 @@
         <v>46225</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I85" s="7">
         <v>46251</v>
@@ -5477,19 +5474,19 @@
         <v>800</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N85" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q85" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5500,10 +5497,10 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>24</v>
@@ -5521,7 +5518,7 @@
         <v>46225</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I86" s="7">
         <v>46251</v>
@@ -5536,19 +5533,19 @@
         <v>1200</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N86" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q86" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5559,16 +5556,16 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B87" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D87" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="C87" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D87" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="E87" s="6" t="s">
         <v>25</v>
@@ -5580,7 +5577,7 @@
         <v>46238</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I87" s="7">
         <v>46251</v>
@@ -5595,19 +5592,19 @@
         <v>1200</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N87" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q87" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5618,10 +5615,10 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>24</v>
@@ -5639,7 +5636,7 @@
         <v>46188</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I88" s="7">
         <v>46258</v>
@@ -5654,19 +5651,19 @@
         <v>650</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N88" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q88" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5677,10 +5674,10 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>24</v>
@@ -5713,19 +5710,19 @@
         <v>650</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N89" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q89" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5736,16 +5733,16 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>25</v>
@@ -5757,7 +5754,7 @@
         <v>46245</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I90" s="7">
         <v>46258</v>
@@ -5772,19 +5769,19 @@
         <v>650</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N90" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q90" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5795,10 +5792,10 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>24</v>
@@ -5831,19 +5828,19 @@
         <v>650</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N91" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q91" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -5854,10 +5851,10 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>24</v>
@@ -5890,19 +5887,19 @@
         <v>650</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N92" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q92" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -5913,10 +5910,10 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>24</v>
@@ -5934,7 +5931,7 @@
         <v>46212</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I93" s="7">
         <v>46258</v>
@@ -5949,19 +5946,19 @@
         <v>680</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N93" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q93" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -5972,10 +5969,10 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>24</v>
@@ -5993,7 +5990,7 @@
         <v>46188</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I94" s="7">
         <v>46258</v>
@@ -6008,19 +6005,19 @@
         <v>700</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N94" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q94" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6031,10 +6028,10 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>24</v>
@@ -6067,19 +6064,19 @@
         <v>700</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N95" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q95" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6090,10 +6087,10 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>24</v>
@@ -6111,7 +6108,7 @@
         <v>46225</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I96" s="7">
         <v>46258</v>
@@ -6126,19 +6123,19 @@
         <v>800</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N96" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q96" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6149,16 +6146,16 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B97" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C97" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D97" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>25</v>
@@ -6170,7 +6167,7 @@
         <v>46238</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I97" s="7">
         <v>46258</v>
@@ -6185,19 +6182,19 @@
         <v>1200</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N97" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q97" s="9">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6211,7 +6208,7 @@
         <v>24</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>24</v>
@@ -6244,19 +6241,19 @@
         <v>185.5</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N98" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q98" s="9">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6267,10 +6264,10 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>24</v>
@@ -6303,19 +6300,19 @@
         <v>650</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N99" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q99" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6326,10 +6323,10 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>24</v>
@@ -6362,19 +6359,19 @@
         <v>650</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N100" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q100" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>
@@ -6385,10 +6382,10 @@
     </row>
     <row r="101">
       <c r="A101" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>24</v>
@@ -6421,19 +6418,19 @@
         <v>650</v>
       </c>
       <c r="M101" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N101" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O101" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P101" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q101" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R101" s="6" t="s">
         <v>24</v>
@@ -6444,16 +6441,16 @@
     </row>
     <row r="102">
       <c r="A102" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>25</v>
@@ -6465,7 +6462,7 @@
         <v>46245</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I102" s="7">
         <v>46265</v>
@@ -6480,19 +6477,19 @@
         <v>650</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N102" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q102" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R102" s="6" t="s">
         <v>24</v>
@@ -6503,10 +6500,10 @@
     </row>
     <row r="103">
       <c r="A103" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>24</v>
@@ -6524,7 +6521,7 @@
         <v>46212</v>
       </c>
       <c r="H103" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I103" s="7">
         <v>46265</v>
@@ -6539,19 +6536,19 @@
         <v>680</v>
       </c>
       <c r="M103" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N103" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O103" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P103" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q103" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R103" s="6" t="s">
         <v>24</v>
@@ -6562,10 +6559,10 @@
     </row>
     <row r="104">
       <c r="A104" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>24</v>
@@ -6598,19 +6595,19 @@
         <v>700</v>
       </c>
       <c r="M104" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N104" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O104" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q104" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R104" s="6" t="s">
         <v>24</v>
@@ -6621,10 +6618,10 @@
     </row>
     <row r="105">
       <c r="A105" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>24</v>
@@ -6642,7 +6639,7 @@
         <v>46225</v>
       </c>
       <c r="H105" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="I105" s="7">
         <v>46265</v>
@@ -6657,19 +6654,19 @@
         <v>800</v>
       </c>
       <c r="M105" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N105" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O105" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P105" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q105" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R105" s="6" t="s">
         <v>24</v>
@@ -6680,16 +6677,16 @@
     </row>
     <row r="106">
       <c r="A106" s="6" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B106" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D106" s="6" t="s">
         <v>106</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>107</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>25</v>
@@ -6701,7 +6698,7 @@
         <v>46238</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="I106" s="7">
         <v>46265</v>
@@ -6716,19 +6713,19 @@
         <v>1200</v>
       </c>
       <c r="M106" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="N106" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O106" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="Q106" s="9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="R106" s="6" t="s">
         <v>24</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$98</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$101</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sexta-feira, 14 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em sábado, 15 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -223,183 +223,180 @@
     <t>FA-11915</t>
   </si>
   <si>
-    <t>FA-12055</t>
+    <t>FA-12017</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-12001</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-12037</t>
+  </si>
+  <si>
+    <t>FA-11979</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-12054</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11860</t>
+  </si>
+  <si>
+    <t>FA-11980</t>
+  </si>
+  <si>
+    <t>FA-12002</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12025</t>
+  </si>
+  <si>
+    <t>FA-12024</t>
+  </si>
+  <si>
+    <t>FA-11964</t>
+  </si>
+  <si>
+    <t>FA-12051</t>
+  </si>
+  <si>
+    <t>FA-12023</t>
+  </si>
+  <si>
+    <t>FA-11952</t>
+  </si>
+  <si>
+    <t>ANNY KATARINA ACIOLE DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11999</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-12033</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11867</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
+  </si>
+  <si>
+    <t>JOAO PAULO CONSORCIOS</t>
+  </si>
+  <si>
+    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
+  </si>
+  <si>
+    <t>FA-12147</t>
+  </si>
+  <si>
+    <t>CARLOS FERNANDO GARCIA DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>FA-12011</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>A VENCER</t>
+  </si>
+  <si>
+    <t>FA-12059</t>
   </si>
   <si>
     <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
   </si>
   <si>
-    <t>FA-12017</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-12037</t>
-  </si>
-  <si>
-    <t>FA-12001</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-11979</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-12054</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11860</t>
-  </si>
-  <si>
-    <t>FA-11980</t>
-  </si>
-  <si>
-    <t>FA-11922</t>
+    <t>FA-12057</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11983</t>
+  </si>
+  <si>
+    <t>FA-11986</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-12040</t>
+  </si>
+  <si>
+    <t>FA-12004</t>
+  </si>
+  <si>
+    <t>FA-12008</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11984</t>
+  </si>
+  <si>
+    <t>FA-12109</t>
+  </si>
+  <si>
+    <t>EDCARLOS MARTINS DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12121</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-11862</t>
+  </si>
+  <si>
+    <t>FA-12064</t>
+  </si>
+  <si>
+    <t>WILSON COUTINHO BEZERRA</t>
+  </si>
+  <si>
+    <t>FA-12058</t>
+  </si>
+  <si>
+    <t>FA-11923</t>
   </si>
   <si>
     <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
   </si>
   <si>
-    <t>FA-12025</t>
-  </si>
-  <si>
-    <t>FA-12002</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11964</t>
-  </si>
-  <si>
-    <t>FA-12024</t>
-  </si>
-  <si>
-    <t>FA-12051</t>
-  </si>
-  <si>
-    <t>FA-12023</t>
-  </si>
-  <si>
-    <t>FA-11952</t>
-  </si>
-  <si>
-    <t>ANNY KATARINA ACIOLE DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11999</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-12033</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11867</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>FA-11995</t>
-  </si>
-  <si>
-    <t>1.3 UBER SUPPLIER</t>
-  </si>
-  <si>
-    <t>JOAO PAULO CONSORCIOS</t>
-  </si>
-  <si>
-    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
-  </si>
-  <si>
-    <t>FA-12011</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>A VENCER</t>
-  </si>
-  <si>
-    <t>FA-12059</t>
-  </si>
-  <si>
-    <t>FA-12057</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11983</t>
-  </si>
-  <si>
-    <t>FA-11986</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-12040</t>
-  </si>
-  <si>
-    <t>FA-12004</t>
-  </si>
-  <si>
-    <t>FA-12008</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11984</t>
-  </si>
-  <si>
-    <t>FA-12109</t>
-  </si>
-  <si>
-    <t>EDCARLOS MARTINS DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12121</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11923</t>
-  </si>
-  <si>
-    <t>FA-12064</t>
-  </si>
-  <si>
-    <t>WILSON COUTINHO BEZERRA</t>
-  </si>
-  <si>
-    <t>FA-12058</t>
-  </si>
-  <si>
-    <t>FA-11862</t>
-  </si>
-  <si>
     <t>FA-12041</t>
   </si>
   <si>
@@ -439,6 +436,12 @@
     <t>LUCA ZOLI</t>
   </si>
   <si>
+    <t>FA-12138</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
     <t>FA-12026</t>
   </si>
   <si>
@@ -454,24 +457,30 @@
     <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
   </si>
   <si>
+    <t>FA-11924</t>
+  </si>
+  <si>
+    <t>FA-12065</t>
+  </si>
+  <si>
+    <t>FA-12122</t>
+  </si>
+  <si>
+    <t>FA-12110</t>
+  </si>
+  <si>
     <t>FA-11864</t>
   </si>
   <si>
-    <t>FA-12065</t>
-  </si>
-  <si>
-    <t>FA-12122</t>
-  </si>
-  <si>
-    <t>FA-12110</t>
-  </si>
-  <si>
-    <t>FA-11924</t>
+    <t>FA-12149</t>
   </si>
   <si>
     <t>FA-11936</t>
   </si>
   <si>
+    <t>FA-12139</t>
+  </si>
+  <si>
     <t>FA-11869</t>
   </si>
   <si>
@@ -484,6 +493,12 @@
     <t>FA-12082</t>
   </si>
   <si>
+    <t>FA-12150</t>
+  </si>
+  <si>
+    <t>FA-12123</t>
+  </si>
+  <si>
     <t>FA-12111</t>
   </si>
   <si>
@@ -493,13 +508,13 @@
     <t>FA-12066</t>
   </si>
   <si>
-    <t>FA-12123</t>
-  </si>
-  <si>
     <t>FA-11937</t>
   </si>
   <si>
     <t>FA-12087</t>
+  </si>
+  <si>
+    <t>FA-12140</t>
   </si>
   <si>
     <t>FA-11955</t>
@@ -648,7 +663,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S98"/>
+  <dimension ref="A1:S101"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1" style="1"/>
@@ -789,7 +804,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -798,7 +813,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-53</v>
+        <v>-54</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -848,7 +863,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -857,7 +872,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-23</v>
+        <v>-24</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>33</v>
@@ -907,7 +922,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-36</v>
+        <v>-37</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -916,7 +931,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-46</v>
+        <v>-47</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -966,7 +981,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -975,7 +990,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>33</v>
@@ -1025,7 +1040,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -1034,7 +1049,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-32</v>
+        <v>-33</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -1084,7 +1099,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>33</v>
@@ -1093,7 +1108,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1143,7 +1158,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>33</v>
@@ -1152,7 +1167,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>33</v>
@@ -1202,7 +1217,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>33</v>
@@ -1211,7 +1226,7 @@
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>33</v>
@@ -1261,7 +1276,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>33</v>
@@ -1270,7 +1285,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>33</v>
@@ -1320,7 +1335,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>33</v>
@@ -1329,7 +1344,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>33</v>
@@ -1379,7 +1394,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>33</v>
@@ -1388,7 +1403,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>33</v>
@@ -1438,7 +1453,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>33</v>
@@ -1447,7 +1462,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-15</v>
+        <v>-16</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>33</v>
@@ -1497,7 +1512,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>33</v>
@@ -1506,7 +1521,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>33</v>
@@ -1556,7 +1571,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>33</v>
@@ -1565,7 +1580,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>33</v>
@@ -1615,7 +1630,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>33</v>
@@ -1624,7 +1639,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>33</v>
@@ -1674,7 +1689,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>33</v>
@@ -1683,7 +1698,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>33</v>
@@ -1733,7 +1748,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>33</v>
@@ -1742,7 +1757,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>33</v>
@@ -1792,7 +1807,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>33</v>
@@ -1801,7 +1816,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>33</v>
@@ -1851,7 +1866,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>33</v>
@@ -1860,7 +1875,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>33</v>
@@ -1910,7 +1925,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>33</v>
@@ -1919,7 +1934,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>33</v>
@@ -1969,7 +1984,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>33</v>
@@ -1978,7 +1993,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>33</v>
@@ -2028,7 +2043,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>33</v>
@@ -2037,7 +2052,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>33</v>
@@ -2087,7 +2102,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>33</v>
@@ -2096,7 +2111,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>33</v>
@@ -2113,7 +2128,7 @@
         <v>64</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>24</v>
@@ -2128,25 +2143,25 @@
         <v>24</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I29" s="7">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="J29" s="7">
         <v>46241</v>
       </c>
       <c r="K29" s="7">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="L29" s="8">
-        <v>320</v>
+        <v>582</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>33</v>
@@ -2155,7 +2170,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-4</v>
+        <v>-19</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>33</v>
@@ -2190,22 +2205,22 @@
         <v>27</v>
       </c>
       <c r="I30" s="7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="J30" s="7">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K30" s="7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="L30" s="8">
-        <v>582</v>
+        <v>502.31</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>33</v>
@@ -2214,7 +2229,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-18</v>
+        <v>-5</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>33</v>
@@ -2264,7 +2279,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>33</v>
@@ -2273,7 +2288,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>33</v>
@@ -2323,7 +2338,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>33</v>
@@ -2332,7 +2347,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>33</v>
@@ -2361,7 +2376,7 @@
         <v>26</v>
       </c>
       <c r="G33" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H33" s="6" t="s">
         <v>27</v>
@@ -2376,13 +2391,13 @@
         <v>46244</v>
       </c>
       <c r="L33" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>33</v>
@@ -2391,7 +2406,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>33</v>
@@ -2405,7 +2420,7 @@
         <v>72</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>24</v>
@@ -2420,10 +2435,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="I34" s="7">
         <v>46244</v>
@@ -2441,7 +2456,7 @@
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>33</v>
@@ -2450,7 +2465,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>33</v>
@@ -2461,13 +2476,13 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>24</v>
@@ -2479,10 +2494,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I35" s="7">
         <v>46244</v>
@@ -2500,7 +2515,7 @@
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>33</v>
@@ -2509,7 +2524,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>33</v>
@@ -2520,13 +2535,13 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>39</v>
-      </c>
       <c r="C36" s="6" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>24</v>
@@ -2541,7 +2556,7 @@
         <v>46225</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="I36" s="7">
         <v>46244</v>
@@ -2553,13 +2568,13 @@
         <v>46244</v>
       </c>
       <c r="L36" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>33</v>
@@ -2568,7 +2583,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>33</v>
@@ -2582,7 +2597,7 @@
         <v>76</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>77</v>
+        <v>41</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>24</v>
@@ -2597,7 +2612,7 @@
         <v>26</v>
       </c>
       <c r="G37" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>27</v>
@@ -2612,13 +2627,13 @@
         <v>46244</v>
       </c>
       <c r="L37" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>33</v>
@@ -2627,7 +2642,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>33</v>
@@ -2638,10 +2653,10 @@
     </row>
     <row r="38">
       <c r="A38" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>24</v>
@@ -2677,7 +2692,7 @@
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>33</v>
@@ -2686,7 +2701,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>33</v>
@@ -2697,10 +2712,10 @@
     </row>
     <row r="39">
       <c r="A39" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>24</v>
@@ -2736,7 +2751,7 @@
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>33</v>
@@ -2745,7 +2760,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>33</v>
@@ -2756,16 +2771,16 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>25</v>
@@ -2774,10 +2789,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I40" s="7">
         <v>46244</v>
@@ -2789,13 +2804,13 @@
         <v>46244</v>
       </c>
       <c r="L40" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>33</v>
@@ -2804,7 +2819,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>33</v>
@@ -2815,10 +2830,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>24</v>
@@ -2827,7 +2842,7 @@
         <v>24</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F41" s="6" t="s">
         <v>26</v>
@@ -2836,7 +2851,7 @@
         <v>46232</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="I41" s="7">
         <v>46244</v>
@@ -2848,13 +2863,13 @@
         <v>46244</v>
       </c>
       <c r="L41" s="8">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>33</v>
@@ -2863,7 +2878,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>33</v>
@@ -2874,16 +2889,16 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>25</v>
@@ -2892,10 +2907,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="I42" s="7">
         <v>46244</v>
@@ -2907,13 +2922,13 @@
         <v>46244</v>
       </c>
       <c r="L42" s="8">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>33</v>
@@ -2922,7 +2937,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>33</v>
@@ -2933,11 +2948,11 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="C43" s="6" t="s">
         <v>24</v>
       </c>
@@ -2945,16 +2960,16 @@
         <v>24</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F43" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="I43" s="7">
         <v>46244</v>
@@ -2966,13 +2981,13 @@
         <v>46244</v>
       </c>
       <c r="L43" s="8">
-        <v>750</v>
+        <v>1200</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>33</v>
@@ -2981,7 +2996,7 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>33</v>
@@ -2992,10 +3007,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>24</v>
@@ -3007,25 +3022,25 @@
         <v>25</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G44" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I44" s="7">
         <v>46244</v>
       </c>
       <c r="J44" s="7">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K44" s="7">
         <v>46244</v>
       </c>
       <c r="L44" s="8">
-        <v>800</v>
+        <v>70.49</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>28</v>
@@ -3040,7 +3055,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>33</v>
@@ -3051,10 +3066,10 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>24</v>
@@ -3066,25 +3081,25 @@
         <v>25</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G45" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="I45" s="7">
         <v>46244</v>
       </c>
       <c r="J45" s="7">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K45" s="7">
         <v>46244</v>
       </c>
       <c r="L45" s="8">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>28</v>
@@ -3099,7 +3114,7 @@
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>33</v>
@@ -3110,14 +3125,14 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="C46" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="C46" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="D46" s="6" t="s">
         <v>24</v>
       </c>
@@ -3131,25 +3146,25 @@
         <v>24</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I46" s="7">
-        <v>46244</v>
+        <v>46209</v>
       </c>
       <c r="J46" s="7">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="K46" s="7">
-        <v>46244</v>
+        <v>46209</v>
       </c>
       <c r="L46" s="8">
-        <v>197.7</v>
+        <v>112.5</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>33</v>
@@ -3158,10 +3173,10 @@
         <v>28</v>
       </c>
       <c r="Q46" s="9">
-        <v>-4</v>
+        <v>-40</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S46" s="6" t="s">
         <v>24</v>
@@ -3184,43 +3199,43 @@
         <v>25</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G47" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G47" s="7">
+        <v>46248</v>
       </c>
       <c r="H47" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I47" s="7">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="J47" s="7">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="K47" s="7">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="L47" s="8">
-        <v>300</v>
+        <v>185.71</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="N47" s="9">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="Q47" s="9">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S47" s="6" t="s">
         <v>24</v>
@@ -3228,58 +3243,58 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>24</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>95</v>
+        <v>25</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G48" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G48" s="7">
+        <v>46225</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I48" s="7">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="J48" s="7">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="K48" s="7">
-        <v>46237</v>
+        <v>46251</v>
       </c>
       <c r="L48" s="8">
-        <v>222.31</v>
+        <v>600</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="N48" s="9">
-        <v>-2</v>
+        <v>2</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="Q48" s="9">
-        <v>-11</v>
+        <v>2</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="S48" s="6" t="s">
         <v>24</v>
@@ -3287,13 +3302,13 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>24</v>
@@ -3302,43 +3317,43 @@
         <v>25</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G49" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G49" s="7">
+        <v>46232</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="I49" s="7">
-        <v>46209</v>
+        <v>46251</v>
       </c>
       <c r="J49" s="7">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="K49" s="7">
-        <v>46209</v>
+        <v>46251</v>
       </c>
       <c r="L49" s="8">
-        <v>112.5</v>
+        <v>620</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="N49" s="9">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>28</v>
+        <v>97</v>
       </c>
       <c r="Q49" s="9">
-        <v>-39</v>
+        <v>2</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="S49" s="6" t="s">
         <v>24</v>
@@ -3346,16 +3361,16 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>25</v>
@@ -3364,7 +3379,7 @@
         <v>26</v>
       </c>
       <c r="G50" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>27</v>
@@ -3379,22 +3394,22 @@
         <v>46251</v>
       </c>
       <c r="L50" s="8">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N50" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q50" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>24</v>
@@ -3405,13 +3420,13 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>64</v>
+        <v>24</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>24</v>
@@ -3423,10 +3438,10 @@
         <v>26</v>
       </c>
       <c r="G51" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H51" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I51" s="7">
         <v>46251</v>
@@ -3438,22 +3453,22 @@
         <v>46251</v>
       </c>
       <c r="L51" s="8">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N51" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O51" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q51" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>24</v>
@@ -3464,16 +3479,16 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>25</v>
@@ -3482,7 +3497,7 @@
         <v>26</v>
       </c>
       <c r="G52" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H52" s="6" t="s">
         <v>27</v>
@@ -3500,19 +3515,19 @@
         <v>630</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N52" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q52" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>24</v>
@@ -3523,10 +3538,10 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>71</v>
+        <v>37</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>24</v>
@@ -3541,7 +3556,7 @@
         <v>26</v>
       </c>
       <c r="G53" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>27</v>
@@ -3559,19 +3574,19 @@
         <v>630</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N53" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q53" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>24</v>
@@ -3582,10 +3597,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>106</v>
+        <v>66</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>24</v>
@@ -3618,19 +3633,19 @@
         <v>630</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N54" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q54" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>24</v>
@@ -3644,7 +3659,7 @@
         <v>107</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>24</v>
@@ -3659,7 +3674,7 @@
         <v>26</v>
       </c>
       <c r="G55" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H55" s="6" t="s">
         <v>27</v>
@@ -3677,19 +3692,19 @@
         <v>630</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N55" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q55" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>24</v>
@@ -3700,13 +3715,13 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>24</v>
@@ -3733,22 +3748,22 @@
         <v>46251</v>
       </c>
       <c r="L56" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N56" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q56" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>24</v>
@@ -3759,10 +3774,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>24</v>
@@ -3777,7 +3792,7 @@
         <v>26</v>
       </c>
       <c r="G57" s="7">
-        <v>46225</v>
+        <v>46240</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>27</v>
@@ -3792,22 +3807,22 @@
         <v>46251</v>
       </c>
       <c r="L57" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N57" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O57" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q57" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>24</v>
@@ -3818,16 +3833,16 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>25</v>
@@ -3836,10 +3851,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="7">
-        <v>46225</v>
+        <v>46245</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="I58" s="7">
         <v>46251</v>
@@ -3854,19 +3869,19 @@
         <v>650</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N58" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q58" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>24</v>
@@ -3877,10 +3892,10 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>24</v>
@@ -3895,10 +3910,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="7">
-        <v>46240</v>
+        <v>46188</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="I59" s="7">
         <v>46251</v>
@@ -3913,19 +3928,19 @@
         <v>650</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N59" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O59" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q59" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>24</v>
@@ -3936,16 +3951,16 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>25</v>
@@ -3954,10 +3969,10 @@
         <v>26</v>
       </c>
       <c r="G60" s="7">
-        <v>46245</v>
+        <v>46232</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="I60" s="7">
         <v>46251</v>
@@ -3972,19 +3987,19 @@
         <v>650</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N60" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q60" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>24</v>
@@ -3995,10 +4010,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>24</v>
@@ -4013,7 +4028,7 @@
         <v>26</v>
       </c>
       <c r="G61" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>27</v>
@@ -4031,19 +4046,19 @@
         <v>650</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N61" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O61" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q61" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>24</v>
@@ -4054,10 +4069,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4072,7 +4087,7 @@
         <v>26</v>
       </c>
       <c r="G62" s="7">
-        <v>46232</v>
+        <v>46210</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>27</v>
@@ -4090,19 +4105,19 @@
         <v>650</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N62" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q62" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>24</v>
@@ -4113,10 +4128,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>73</v>
+        <v>122</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>24</v>
@@ -4146,22 +4161,22 @@
         <v>46251</v>
       </c>
       <c r="L63" s="8">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N63" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q63" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>24</v>
@@ -4172,10 +4187,10 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>24</v>
@@ -4190,10 +4205,10 @@
         <v>26</v>
       </c>
       <c r="G64" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I64" s="7">
         <v>46251</v>
@@ -4205,22 +4220,22 @@
         <v>46251</v>
       </c>
       <c r="L64" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N64" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q64" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R64" s="6" t="s">
         <v>24</v>
@@ -4231,10 +4246,10 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>123</v>
+        <v>41</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>24</v>
@@ -4264,22 +4279,22 @@
         <v>46251</v>
       </c>
       <c r="L65" s="8">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N65" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O65" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q65" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>24</v>
@@ -4290,10 +4305,10 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>24</v>
@@ -4308,10 +4323,10 @@
         <v>26</v>
       </c>
       <c r="G66" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="I66" s="7">
         <v>46251</v>
@@ -4326,19 +4341,19 @@
         <v>680</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N66" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q66" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>24</v>
@@ -4349,10 +4364,10 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>24</v>
@@ -4385,19 +4400,19 @@
         <v>680</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N67" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q67" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>24</v>
@@ -4408,10 +4423,10 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>24</v>
@@ -4426,7 +4441,7 @@
         <v>26</v>
       </c>
       <c r="G68" s="7">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="H68" s="6" t="s">
         <v>55</v>
@@ -4444,19 +4459,19 @@
         <v>680</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N68" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q68" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>24</v>
@@ -4467,10 +4482,10 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>91</v>
+        <v>58</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>24</v>
@@ -4485,10 +4500,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="I69" s="7">
         <v>46251</v>
@@ -4503,19 +4518,19 @@
         <v>680</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N69" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q69" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>24</v>
@@ -4526,10 +4541,10 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>24</v>
@@ -4544,7 +4559,7 @@
         <v>26</v>
       </c>
       <c r="G70" s="7">
-        <v>46212</v>
+        <v>46188</v>
       </c>
       <c r="H70" s="6" t="s">
         <v>55</v>
@@ -4559,22 +4574,22 @@
         <v>46251</v>
       </c>
       <c r="L70" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N70" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q70" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>24</v>
@@ -4585,16 +4600,16 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="E71" s="6" t="s">
         <v>25</v>
@@ -4603,10 +4618,10 @@
         <v>26</v>
       </c>
       <c r="G71" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I71" s="7">
         <v>46251</v>
@@ -4618,22 +4633,22 @@
         <v>46251</v>
       </c>
       <c r="L71" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N71" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q71" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>24</v>
@@ -4644,10 +4659,10 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>24</v>
@@ -4662,10 +4677,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="7">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I72" s="7">
         <v>46251</v>
@@ -4680,19 +4695,19 @@
         <v>700</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N72" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q72" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4703,16 +4718,16 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>49</v>
+        <v>135</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E73" s="6" t="s">
         <v>25</v>
@@ -4721,7 +4736,7 @@
         <v>26</v>
       </c>
       <c r="G73" s="7">
-        <v>46232</v>
+        <v>46248</v>
       </c>
       <c r="H73" s="6" t="s">
         <v>27</v>
@@ -4739,19 +4754,19 @@
         <v>700</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N73" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q73" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4762,10 +4777,10 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>134</v>
+        <v>43</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>24</v>
@@ -4774,16 +4789,16 @@
         <v>24</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>25</v>
+        <v>44</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="7">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="I74" s="7">
         <v>46251</v>
@@ -4795,22 +4810,22 @@
         <v>46251</v>
       </c>
       <c r="L74" s="8">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N74" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q74" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -4821,10 +4836,10 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>24</v>
@@ -4833,13 +4848,13 @@
         <v>24</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F75" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H75" s="6" t="s">
         <v>45</v>
@@ -4854,22 +4869,22 @@
         <v>46251</v>
       </c>
       <c r="L75" s="8">
-        <v>750</v>
+        <v>800</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N75" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q75" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -4880,10 +4895,10 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>24</v>
@@ -4901,7 +4916,7 @@
         <v>46225</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>45</v>
+        <v>85</v>
       </c>
       <c r="I76" s="7">
         <v>46251</v>
@@ -4913,22 +4928,22 @@
         <v>46251</v>
       </c>
       <c r="L76" s="8">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N76" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q76" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -4939,16 +4954,16 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>88</v>
+        <v>140</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>25</v>
@@ -4957,10 +4972,10 @@
         <v>26</v>
       </c>
       <c r="G77" s="7">
-        <v>46225</v>
+        <v>46238</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I77" s="7">
         <v>46251</v>
@@ -4975,19 +4990,19 @@
         <v>1200</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N77" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q77" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -4998,16 +5013,16 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>139</v>
+        <v>120</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>25</v>
@@ -5016,37 +5031,37 @@
         <v>26</v>
       </c>
       <c r="G78" s="7">
-        <v>46238</v>
+        <v>46210</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="I78" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J78" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K78" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L78" s="8">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N78" s="9">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q78" s="9">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5057,10 +5072,10 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>54</v>
+        <v>117</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
@@ -5075,10 +5090,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I79" s="7">
         <v>46258</v>
@@ -5093,19 +5108,19 @@
         <v>650</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N79" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q79" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5116,16 +5131,16 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>25</v>
@@ -5134,10 +5149,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="7">
-        <v>46232</v>
+        <v>46245</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="I80" s="7">
         <v>46258</v>
@@ -5152,19 +5167,19 @@
         <v>650</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N80" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q80" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5175,16 +5190,16 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="E81" s="6" t="s">
         <v>25</v>
@@ -5193,10 +5208,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="7">
-        <v>46245</v>
+        <v>46240</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="I81" s="7">
         <v>46258</v>
@@ -5211,19 +5226,19 @@
         <v>650</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N81" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q81" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5234,10 +5249,10 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>24</v>
@@ -5252,10 +5267,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="7">
-        <v>46240</v>
+        <v>46188</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="I82" s="7">
         <v>46258</v>
@@ -5270,19 +5285,19 @@
         <v>650</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N82" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q82" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5293,10 +5308,10 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>24</v>
@@ -5311,7 +5326,7 @@
         <v>26</v>
       </c>
       <c r="G83" s="7">
-        <v>46210</v>
+        <v>46248</v>
       </c>
       <c r="H83" s="6" t="s">
         <v>27</v>
@@ -5329,19 +5344,19 @@
         <v>650</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N83" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q83" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5352,10 +5367,10 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>24</v>
@@ -5388,19 +5403,19 @@
         <v>680</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N84" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q84" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5411,10 +5426,10 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>93</v>
+        <v>135</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>24</v>
@@ -5429,10 +5444,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="7">
-        <v>46188</v>
+        <v>46248</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I85" s="7">
         <v>46258</v>
@@ -5447,19 +5462,19 @@
         <v>700</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N85" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q85" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5470,10 +5485,10 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>24</v>
@@ -5488,10 +5503,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="7">
-        <v>46238</v>
+        <v>46188</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="I86" s="7">
         <v>46258</v>
@@ -5506,19 +5521,19 @@
         <v>700</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N86" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q86" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5529,10 +5544,10 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>24</v>
@@ -5547,10 +5562,10 @@
         <v>26</v>
       </c>
       <c r="G87" s="7">
-        <v>46225</v>
+        <v>46238</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I87" s="7">
         <v>46258</v>
@@ -5562,22 +5577,22 @@
         <v>46258</v>
       </c>
       <c r="L87" s="8">
-        <v>800</v>
+        <v>700</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N87" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q87" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5588,16 +5603,16 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>139</v>
+        <v>82</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>25</v>
@@ -5606,10 +5621,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>89</v>
+        <v>45</v>
       </c>
       <c r="I88" s="7">
         <v>46258</v>
@@ -5621,22 +5636,22 @@
         <v>46258</v>
       </c>
       <c r="L88" s="8">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N88" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q88" s="9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5647,55 +5662,55 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>24</v>
+        <v>152</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>46</v>
+        <v>140</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F89" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G89" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G89" s="7">
+        <v>46238</v>
       </c>
       <c r="H89" s="6" t="s">
-        <v>24</v>
+        <v>85</v>
       </c>
       <c r="I89" s="7">
-        <v>45930</v>
+        <v>46258</v>
       </c>
       <c r="J89" s="7">
-        <v>46264</v>
+        <v>46258</v>
       </c>
       <c r="K89" s="7">
-        <v>46264</v>
+        <v>46258</v>
       </c>
       <c r="L89" s="8">
-        <v>185.5</v>
+        <v>1200</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N89" s="9">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q89" s="9">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5706,10 +5721,10 @@
     </row>
     <row r="90">
       <c r="A90" s="6" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>24</v>
@@ -5721,40 +5736,40 @@
         <v>25</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G90" s="7">
-        <v>46240</v>
+        <v>24</v>
+      </c>
+      <c r="G90" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I90" s="7">
-        <v>46265</v>
+        <v>45930</v>
       </c>
       <c r="J90" s="7">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="K90" s="7">
-        <v>46265</v>
+        <v>46264</v>
       </c>
       <c r="L90" s="8">
-        <v>650</v>
+        <v>185.5</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N90" s="9">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q90" s="9">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5765,10 +5780,10 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>77</v>
+        <v>93</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>24</v>
@@ -5783,7 +5798,7 @@
         <v>26</v>
       </c>
       <c r="G91" s="7">
-        <v>46210</v>
+        <v>46248</v>
       </c>
       <c r="H91" s="6" t="s">
         <v>27</v>
@@ -5801,19 +5816,19 @@
         <v>650</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N91" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q91" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -5824,16 +5839,16 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>24</v>
+        <v>114</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>25</v>
@@ -5842,10 +5857,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="7">
-        <v>46232</v>
+        <v>46245</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="I92" s="7">
         <v>46265</v>
@@ -5860,19 +5875,19 @@
         <v>650</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N92" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q92" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -5883,16 +5898,16 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>25</v>
@@ -5901,10 +5916,10 @@
         <v>26</v>
       </c>
       <c r="G93" s="7">
-        <v>46245</v>
+        <v>46240</v>
       </c>
       <c r="H93" s="6" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="I93" s="7">
         <v>46265</v>
@@ -5919,19 +5934,19 @@
         <v>650</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N93" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q93" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -5942,10 +5957,10 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>24</v>
@@ -5960,10 +5975,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="7">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I94" s="7">
         <v>46265</v>
@@ -5975,22 +5990,22 @@
         <v>46265</v>
       </c>
       <c r="L94" s="8">
-        <v>680</v>
+        <v>650</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N94" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q94" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6001,10 +6016,10 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>134</v>
+        <v>117</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>24</v>
@@ -6019,7 +6034,7 @@
         <v>26</v>
       </c>
       <c r="G95" s="7">
-        <v>46238</v>
+        <v>46232</v>
       </c>
       <c r="H95" s="6" t="s">
         <v>27</v>
@@ -6034,22 +6049,22 @@
         <v>46265</v>
       </c>
       <c r="L95" s="8">
-        <v>700</v>
+        <v>650</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N95" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q95" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6060,10 +6075,10 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>86</v>
+        <v>128</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>24</v>
@@ -6078,10 +6093,10 @@
         <v>26</v>
       </c>
       <c r="G96" s="7">
-        <v>46225</v>
+        <v>46212</v>
       </c>
       <c r="H96" s="6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="I96" s="7">
         <v>46265</v>
@@ -6093,22 +6108,22 @@
         <v>46265</v>
       </c>
       <c r="L96" s="8">
-        <v>800</v>
+        <v>680</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="N96" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="Q96" s="9">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6119,16 +6134,16 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>116</v>
+        <v>24</v>
       </c>
       <c r="E97" s="6" t="s">
         <v>25</v>
@@ -6140,7 +6155,7 @@
         <v>46238</v>
       </c>
       <c r="H97" s="6" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="I97" s="7">
         <v>46265</v>
@@ -6152,52 +6167,229 @@
         <v>46265</v>
       </c>
       <c r="L97" s="8">
+        <v>700</v>
+      </c>
+      <c r="M97" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="N97" s="9">
+        <v>16</v>
+      </c>
+      <c r="O97" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P97" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q97" s="9">
+        <v>16</v>
+      </c>
+      <c r="R97" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S97" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="B98" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="C98" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D98" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E98" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G98" s="7">
+        <v>46248</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I98" s="7">
+        <v>46265</v>
+      </c>
+      <c r="J98" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K98" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L98" s="8">
+        <v>700</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="N98" s="9">
+        <v>16</v>
+      </c>
+      <c r="O98" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P98" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q98" s="9">
+        <v>16</v>
+      </c>
+      <c r="R98" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S98" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B99" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C99" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F99" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G99" s="7">
+        <v>46225</v>
+      </c>
+      <c r="H99" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="I99" s="7">
+        <v>46265</v>
+      </c>
+      <c r="J99" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K99" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L99" s="8">
+        <v>800</v>
+      </c>
+      <c r="M99" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="N99" s="9">
+        <v>16</v>
+      </c>
+      <c r="O99" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P99" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q99" s="9">
+        <v>16</v>
+      </c>
+      <c r="R99" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S99" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="B100" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="E100" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F100" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G100" s="7">
+        <v>46238</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="I100" s="7">
+        <v>46265</v>
+      </c>
+      <c r="J100" s="7">
+        <v>46265</v>
+      </c>
+      <c r="K100" s="7">
+        <v>46265</v>
+      </c>
+      <c r="L100" s="8">
         <v>1200</v>
       </c>
-      <c r="M97" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="N97" s="9">
-        <v>17</v>
-      </c>
-      <c r="O97" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="P97" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q97" s="9">
-        <v>17</v>
-      </c>
-      <c r="R97" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="S97" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="98" ht="23" customHeight="1">
-      <c r="A98" s="10"/>
-      <c r="B98" s="10"/>
-      <c r="C98" s="10"/>
-      <c r="D98" s="10"/>
-      <c r="E98" s="10"/>
-      <c r="F98" s="10"/>
-      <c r="G98" s="11"/>
-      <c r="H98" s="10"/>
-      <c r="I98" s="11"/>
-      <c r="J98" s="11"/>
-      <c r="K98" s="11"/>
-      <c r="L98" s="12">
-        <f>SUM(L6:L97)</f>
-      </c>
-      <c r="M98" s="10"/>
-      <c r="N98" s="13"/>
-      <c r="O98" s="10"/>
-      <c r="P98" s="10"/>
-      <c r="Q98" s="13"/>
-      <c r="R98" s="10"/>
-      <c r="S98" s="10"/>
+      <c r="M100" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="N100" s="9">
+        <v>16</v>
+      </c>
+      <c r="O100" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="P100" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q100" s="9">
+        <v>16</v>
+      </c>
+      <c r="R100" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="S100" s="6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" ht="23" customHeight="1">
+      <c r="A101" s="10"/>
+      <c r="B101" s="10"/>
+      <c r="C101" s="10"/>
+      <c r="D101" s="10"/>
+      <c r="E101" s="10"/>
+      <c r="F101" s="10"/>
+      <c r="G101" s="11"/>
+      <c r="H101" s="10"/>
+      <c r="I101" s="11"/>
+      <c r="J101" s="11"/>
+      <c r="K101" s="11"/>
+      <c r="L101" s="12">
+        <f>SUM(L6:L100)</f>
+      </c>
+      <c r="M101" s="10"/>
+      <c r="N101" s="13"/>
+      <c r="O101" s="10"/>
+      <c r="P101" s="10"/>
+      <c r="Q101" s="13"/>
+      <c r="R101" s="10"/>
+      <c r="S101" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="A5:S5"/>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em sábado, 15 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em domingo, 16 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -316,9 +316,6 @@
     <t>CARLOS FERNANDO GARCIA DE MEDEIROS</t>
   </si>
   <si>
-    <t>HOJE</t>
-  </si>
-  <si>
     <t>FA-12011</t>
   </si>
   <si>
@@ -364,31 +361,31 @@
     <t>FA-11984</t>
   </si>
   <si>
+    <t>FA-12058</t>
+  </si>
+  <si>
+    <t>FA-12121</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-11862</t>
+  </si>
+  <si>
+    <t>FA-12064</t>
+  </si>
+  <si>
+    <t>WILSON COUTINHO BEZERRA</t>
+  </si>
+  <si>
     <t>FA-12109</t>
   </si>
   <si>
     <t>EDCARLOS MARTINS DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12121</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11862</t>
-  </si>
-  <si>
-    <t>FA-12064</t>
-  </si>
-  <si>
-    <t>WILSON COUTINHO BEZERRA</t>
-  </si>
-  <si>
-    <t>FA-12058</t>
   </si>
   <si>
     <t>FA-11923</t>
@@ -804,7 +801,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -813,7 +810,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-54</v>
+        <v>-55</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -863,7 +860,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -872,7 +869,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-24</v>
+        <v>-25</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>33</v>
@@ -922,7 +919,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-37</v>
+        <v>-38</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -931,7 +928,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -981,7 +978,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -990,7 +987,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>33</v>
@@ -1040,7 +1037,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -1049,7 +1046,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-33</v>
+        <v>-34</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -1099,7 +1096,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>33</v>
@@ -1108,7 +1105,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1158,7 +1155,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>33</v>
@@ -1167,7 +1164,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>33</v>
@@ -1217,7 +1214,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>33</v>
@@ -1226,7 +1223,7 @@
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>33</v>
@@ -1276,7 +1273,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>33</v>
@@ -1285,7 +1282,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>33</v>
@@ -1335,7 +1332,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>33</v>
@@ -1344,7 +1341,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>33</v>
@@ -1394,7 +1391,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>33</v>
@@ -1403,7 +1400,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>33</v>
@@ -1453,7 +1450,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>33</v>
@@ -1462,7 +1459,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-16</v>
+        <v>-17</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>33</v>
@@ -1512,7 +1509,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>33</v>
@@ -1521,7 +1518,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>33</v>
@@ -1571,7 +1568,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>33</v>
@@ -1580,7 +1577,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>33</v>
@@ -1630,7 +1627,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>33</v>
@@ -1639,7 +1636,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>33</v>
@@ -1689,7 +1686,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>33</v>
@@ -1698,7 +1695,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>33</v>
@@ -1748,7 +1745,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>33</v>
@@ -1757,7 +1754,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>33</v>
@@ -1807,7 +1804,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>33</v>
@@ -1816,7 +1813,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>33</v>
@@ -1866,7 +1863,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>33</v>
@@ -1875,7 +1872,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>33</v>
@@ -1925,7 +1922,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>33</v>
@@ -1934,7 +1931,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>33</v>
@@ -1984,7 +1981,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>33</v>
@@ -1993,7 +1990,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>33</v>
@@ -2043,7 +2040,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>33</v>
@@ -2052,7 +2049,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>33</v>
@@ -2102,7 +2099,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>33</v>
@@ -2111,7 +2108,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>33</v>
@@ -2161,7 +2158,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-8</v>
+        <v>-9</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>33</v>
@@ -2170,7 +2167,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>33</v>
@@ -2220,7 +2217,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>33</v>
@@ -2229,7 +2226,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>33</v>
@@ -2279,7 +2276,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>33</v>
@@ -2288,7 +2285,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>33</v>
@@ -2338,7 +2335,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>33</v>
@@ -2347,7 +2344,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>33</v>
@@ -2397,7 +2394,7 @@
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>33</v>
@@ -2406,7 +2403,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>33</v>
@@ -2456,7 +2453,7 @@
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>33</v>
@@ -2465,7 +2462,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>33</v>
@@ -2515,7 +2512,7 @@
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>33</v>
@@ -2524,7 +2521,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>33</v>
@@ -2574,7 +2571,7 @@
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>33</v>
@@ -2583,7 +2580,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>33</v>
@@ -2633,7 +2630,7 @@
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>33</v>
@@ -2642,7 +2639,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>33</v>
@@ -2692,7 +2689,7 @@
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>33</v>
@@ -2701,7 +2698,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>33</v>
@@ -2751,7 +2748,7 @@
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>33</v>
@@ -2760,7 +2757,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>33</v>
@@ -2810,7 +2807,7 @@
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>33</v>
@@ -2819,7 +2816,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>33</v>
@@ -2869,7 +2866,7 @@
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>33</v>
@@ -2878,7 +2875,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>33</v>
@@ -2928,7 +2925,7 @@
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>33</v>
@@ -2937,7 +2934,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>33</v>
@@ -2987,7 +2984,7 @@
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>33</v>
@@ -2996,7 +2993,7 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>33</v>
@@ -3046,7 +3043,7 @@
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>33</v>
@@ -3055,7 +3052,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>33</v>
@@ -3105,7 +3102,7 @@
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>33</v>
@@ -3114,7 +3111,7 @@
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>33</v>
@@ -3164,7 +3161,7 @@
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-2</v>
+        <v>-3</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>33</v>
@@ -3173,7 +3170,7 @@
         <v>28</v>
       </c>
       <c r="Q46" s="9">
-        <v>-40</v>
+        <v>-41</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>29</v>
@@ -3220,22 +3217,22 @@
         <v>185.71</v>
       </c>
       <c r="M47" s="6" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O47" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P47" s="6" t="s">
-        <v>94</v>
+        <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R47" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S47" s="6" t="s">
         <v>24</v>
@@ -3243,13 +3240,13 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="C48" s="6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>24</v>
@@ -3279,19 +3276,19 @@
         <v>600</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N48" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q48" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>24</v>
@@ -3302,13 +3299,13 @@
     </row>
     <row r="49">
       <c r="A49" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="B49" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>99</v>
-      </c>
       <c r="C49" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>24</v>
@@ -3338,19 +3335,19 @@
         <v>620</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N49" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q49" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>24</v>
@@ -3361,10 +3358,10 @@
     </row>
     <row r="50">
       <c r="A50" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B50" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="B50" s="6" t="s">
-        <v>101</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>24</v>
@@ -3397,19 +3394,19 @@
         <v>630</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N50" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q50" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>24</v>
@@ -3420,7 +3417,7 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>69</v>
@@ -3456,19 +3453,19 @@
         <v>630</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N51" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O51" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q51" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>24</v>
@@ -3479,10 +3476,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>103</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>104</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>24</v>
@@ -3515,19 +3512,19 @@
         <v>630</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N52" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q52" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>24</v>
@@ -3538,7 +3535,7 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>37</v>
@@ -3574,19 +3571,19 @@
         <v>630</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N53" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q53" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>24</v>
@@ -3597,7 +3594,7 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>66</v>
@@ -3633,19 +3630,19 @@
         <v>630</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N54" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q54" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>24</v>
@@ -3656,10 +3653,10 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>107</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>108</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>24</v>
@@ -3692,19 +3689,19 @@
         <v>630</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N55" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q55" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>24</v>
@@ -3715,7 +3712,7 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>39</v>
@@ -3751,19 +3748,19 @@
         <v>650</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N56" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q56" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>24</v>
@@ -3774,10 +3771,10 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>24</v>
@@ -3792,7 +3789,7 @@
         <v>26</v>
       </c>
       <c r="G57" s="7">
-        <v>46240</v>
+        <v>46232</v>
       </c>
       <c r="H57" s="6" t="s">
         <v>27</v>
@@ -3810,19 +3807,19 @@
         <v>650</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N57" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O57" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q57" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>24</v>
@@ -3833,16 +3830,16 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D58" s="6" t="s">
         <v>112</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="C58" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>114</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>25</v>
@@ -3869,19 +3866,19 @@
         <v>650</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N58" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q58" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>24</v>
@@ -3892,7 +3889,7 @@
     </row>
     <row r="59">
       <c r="A59" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>54</v>
@@ -3928,19 +3925,19 @@
         <v>650</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N59" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O59" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q59" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>24</v>
@@ -3951,10 +3948,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
@@ -3987,19 +3984,19 @@
         <v>650</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N60" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q60" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>24</v>
@@ -4010,10 +4007,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>24</v>
@@ -4028,7 +4025,7 @@
         <v>26</v>
       </c>
       <c r="G61" s="7">
-        <v>46232</v>
+        <v>46240</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>27</v>
@@ -4046,19 +4043,19 @@
         <v>650</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N61" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O61" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q61" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>24</v>
@@ -4069,10 +4066,10 @@
     </row>
     <row r="62">
       <c r="A62" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B62" s="6" t="s">
         <v>119</v>
-      </c>
-      <c r="B62" s="6" t="s">
-        <v>120</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4105,19 +4102,19 @@
         <v>650</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N62" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q62" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>24</v>
@@ -4128,10 +4125,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B63" s="6" t="s">
         <v>121</v>
-      </c>
-      <c r="B63" s="6" t="s">
-        <v>122</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>24</v>
@@ -4164,19 +4161,19 @@
         <v>670</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N63" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O63" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q63" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>24</v>
@@ -4187,7 +4184,7 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>64</v>
@@ -4223,19 +4220,19 @@
         <v>680</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N64" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q64" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R64" s="6" t="s">
         <v>24</v>
@@ -4246,7 +4243,7 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>41</v>
@@ -4282,19 +4279,19 @@
         <v>680</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N65" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O65" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q65" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>24</v>
@@ -4305,7 +4302,7 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>75</v>
@@ -4341,19 +4338,19 @@
         <v>680</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N66" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q66" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>24</v>
@@ -4364,7 +4361,7 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>87</v>
@@ -4400,19 +4397,19 @@
         <v>680</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N67" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q67" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>24</v>
@@ -4423,10 +4420,10 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="B68" s="6" t="s">
         <v>127</v>
-      </c>
-      <c r="B68" s="6" t="s">
-        <v>128</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>24</v>
@@ -4459,19 +4456,19 @@
         <v>680</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N68" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q68" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>24</v>
@@ -4482,7 +4479,7 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>58</v>
@@ -4518,19 +4515,19 @@
         <v>680</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N69" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q69" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>24</v>
@@ -4541,7 +4538,7 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>89</v>
@@ -4577,19 +4574,19 @@
         <v>700</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N70" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q70" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>24</v>
@@ -4600,7 +4597,7 @@
     </row>
     <row r="71">
       <c r="A71" s="6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>49</v>
@@ -4636,19 +4633,19 @@
         <v>700</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N71" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q71" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>24</v>
@@ -4659,10 +4656,10 @@
     </row>
     <row r="72">
       <c r="A72" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="B72" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="B72" s="6" t="s">
-        <v>133</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>24</v>
@@ -4695,19 +4692,19 @@
         <v>700</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N72" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q72" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4718,10 +4715,10 @@
     </row>
     <row r="73">
       <c r="A73" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B73" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="B73" s="6" t="s">
-        <v>135</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>24</v>
@@ -4754,19 +4751,19 @@
         <v>700</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N73" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q73" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4777,7 +4774,7 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>43</v>
@@ -4813,19 +4810,19 @@
         <v>750</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N74" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q74" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -4836,7 +4833,7 @@
     </row>
     <row r="75">
       <c r="A75" s="6" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>82</v>
@@ -4872,19 +4869,19 @@
         <v>800</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N75" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q75" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -4895,7 +4892,7 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>84</v>
@@ -4931,19 +4928,19 @@
         <v>1200</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N76" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q76" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -4954,16 +4951,16 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B77" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B77" s="6" t="s">
-        <v>140</v>
-      </c>
       <c r="C77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>25</v>
@@ -4990,19 +4987,19 @@
         <v>1200</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N77" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q77" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5013,10 +5010,10 @@
     </row>
     <row r="78">
       <c r="A78" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -5049,19 +5046,19 @@
         <v>650</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N78" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q78" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5072,10 +5069,10 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
@@ -5108,19 +5105,19 @@
         <v>650</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N79" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q79" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5131,16 +5128,16 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>25</v>
@@ -5167,19 +5164,19 @@
         <v>650</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N80" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q80" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5190,10 +5187,10 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5226,19 +5223,19 @@
         <v>650</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N81" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q81" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5249,7 +5246,7 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>54</v>
@@ -5285,19 +5282,19 @@
         <v>650</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N82" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q82" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5308,7 +5305,7 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>93</v>
@@ -5344,19 +5341,19 @@
         <v>650</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N83" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q83" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5367,10 +5364,10 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>24</v>
@@ -5403,19 +5400,19 @@
         <v>680</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N84" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q84" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5426,10 +5423,10 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>24</v>
@@ -5462,19 +5459,19 @@
         <v>700</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N85" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q85" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5485,7 +5482,7 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>89</v>
@@ -5521,19 +5518,19 @@
         <v>700</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N86" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q86" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5544,10 +5541,10 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>24</v>
@@ -5580,19 +5577,19 @@
         <v>700</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N87" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q87" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5603,7 +5600,7 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>82</v>
@@ -5639,19 +5636,19 @@
         <v>800</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N88" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q88" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5662,16 +5659,16 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E89" s="6" t="s">
         <v>25</v>
@@ -5698,19 +5695,19 @@
         <v>1200</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N89" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q89" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5757,19 +5754,19 @@
         <v>185.5</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N90" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q90" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5780,7 +5777,7 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>93</v>
@@ -5816,19 +5813,19 @@
         <v>650</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N91" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q91" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -5839,16 +5836,16 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>25</v>
@@ -5875,19 +5872,19 @@
         <v>650</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N92" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q92" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -5898,10 +5895,10 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>24</v>
@@ -5934,19 +5931,19 @@
         <v>650</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N93" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q93" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -5957,10 +5954,10 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>24</v>
@@ -5993,19 +5990,19 @@
         <v>650</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N94" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q94" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6016,10 +6013,10 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>24</v>
@@ -6052,19 +6049,19 @@
         <v>650</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N95" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q95" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6075,10 +6072,10 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>24</v>
@@ -6111,19 +6108,19 @@
         <v>680</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N96" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q96" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6134,10 +6131,10 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>24</v>
@@ -6170,19 +6167,19 @@
         <v>700</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N97" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q97" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6193,10 +6190,10 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>24</v>
@@ -6229,19 +6226,19 @@
         <v>700</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N98" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q98" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6252,7 +6249,7 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>82</v>
@@ -6288,19 +6285,19 @@
         <v>800</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N99" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q99" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6311,16 +6308,16 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>25</v>
@@ -6347,19 +6344,19 @@
         <v>1200</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N100" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q100" s="9">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em domingo, 16 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em segunda-feira, 17 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -322,141 +322,144 @@
     <t>ROBERTO MURATORI</t>
   </si>
   <si>
+    <t>HOJE</t>
+  </si>
+  <si>
+    <t>FA-12059</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-12057</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11983</t>
+  </si>
+  <si>
+    <t>FA-11986</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-12040</t>
+  </si>
+  <si>
+    <t>FA-12004</t>
+  </si>
+  <si>
+    <t>FA-12008</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11984</t>
+  </si>
+  <si>
+    <t>FA-12058</t>
+  </si>
+  <si>
+    <t>FA-12121</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-11862</t>
+  </si>
+  <si>
+    <t>FA-12064</t>
+  </si>
+  <si>
+    <t>WILSON COUTINHO BEZERRA</t>
+  </si>
+  <si>
+    <t>FA-12109</t>
+  </si>
+  <si>
+    <t>EDCARLOS MARTINS DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11923</t>
+  </si>
+  <si>
+    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
+  </si>
+  <si>
+    <t>FA-12041</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12028</t>
+  </si>
+  <si>
+    <t>FA-12027</t>
+  </si>
+  <si>
+    <t>FA-12005</t>
+  </si>
+  <si>
+    <t>FA-12043</t>
+  </si>
+  <si>
+    <t>FA-11935</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11965</t>
+  </si>
+  <si>
+    <t>FA-11868</t>
+  </si>
+  <si>
+    <t>FA-12056</t>
+  </si>
+  <si>
+    <t>FA-12081</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-12138</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-12026</t>
+  </si>
+  <si>
+    <t>FA-11953</t>
+  </si>
+  <si>
+    <t>FA-12003</t>
+  </si>
+  <si>
+    <t>FA-12079</t>
+  </si>
+  <si>
+    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11924</t>
+  </si>
+  <si>
     <t>A VENCER</t>
   </si>
   <si>
-    <t>FA-12059</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-12057</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11983</t>
-  </si>
-  <si>
-    <t>FA-11986</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-12040</t>
-  </si>
-  <si>
-    <t>FA-12004</t>
-  </si>
-  <si>
-    <t>FA-12008</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11984</t>
-  </si>
-  <si>
-    <t>FA-12058</t>
-  </si>
-  <si>
-    <t>FA-12121</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11862</t>
-  </si>
-  <si>
-    <t>FA-12064</t>
-  </si>
-  <si>
-    <t>WILSON COUTINHO BEZERRA</t>
-  </si>
-  <si>
-    <t>FA-12109</t>
-  </si>
-  <si>
-    <t>EDCARLOS MARTINS DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11923</t>
-  </si>
-  <si>
-    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
-  </si>
-  <si>
-    <t>FA-12041</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12028</t>
-  </si>
-  <si>
-    <t>FA-12027</t>
-  </si>
-  <si>
-    <t>FA-12005</t>
-  </si>
-  <si>
-    <t>FA-12043</t>
-  </si>
-  <si>
-    <t>FA-11935</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11965</t>
-  </si>
-  <si>
-    <t>FA-11868</t>
-  </si>
-  <si>
-    <t>FA-12056</t>
-  </si>
-  <si>
-    <t>FA-12081</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
-    <t>FA-12138</t>
-  </si>
-  <si>
-    <t>GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t>FA-12026</t>
-  </si>
-  <si>
-    <t>FA-11953</t>
-  </si>
-  <si>
-    <t>FA-12003</t>
-  </si>
-  <si>
-    <t>FA-12079</t>
-  </si>
-  <si>
-    <t>MARCIANO EZEQUIEL VALDEVINO DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11924</t>
-  </si>
-  <si>
     <t>FA-12065</t>
   </si>
   <si>
@@ -493,13 +496,13 @@
     <t>FA-12150</t>
   </si>
   <si>
+    <t>FA-11925</t>
+  </si>
+  <si>
+    <t>FA-12111</t>
+  </si>
+  <si>
     <t>FA-12123</t>
-  </si>
-  <si>
-    <t>FA-12111</t>
-  </si>
-  <si>
-    <t>FA-11925</t>
   </si>
   <si>
     <t>FA-12066</t>
@@ -801,7 +804,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -810,7 +813,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-55</v>
+        <v>-56</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -860,7 +863,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -869,7 +872,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-25</v>
+        <v>-26</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>33</v>
@@ -919,7 +922,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-38</v>
+        <v>-39</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -928,7 +931,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-48</v>
+        <v>-49</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -978,7 +981,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -987,7 +990,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-18</v>
+        <v>-19</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>33</v>
@@ -1037,7 +1040,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -1046,7 +1049,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-34</v>
+        <v>-35</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -1096,7 +1099,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>33</v>
@@ -1105,7 +1108,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-11</v>
+        <v>-12</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1155,7 +1158,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>33</v>
@@ -1164,7 +1167,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-4</v>
+        <v>-5</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>33</v>
@@ -1214,7 +1217,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>33</v>
@@ -1223,7 +1226,7 @@
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>33</v>
@@ -1273,7 +1276,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>33</v>
@@ -1282,7 +1285,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>33</v>
@@ -1332,7 +1335,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>33</v>
@@ -1341,7 +1344,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>33</v>
@@ -1391,7 +1394,7 @@
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>33</v>
@@ -1400,7 +1403,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>33</v>
@@ -1450,7 +1453,7 @@
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>33</v>
@@ -1459,7 +1462,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-17</v>
+        <v>-18</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>33</v>
@@ -1509,7 +1512,7 @@
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>33</v>
@@ -1518,7 +1521,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>33</v>
@@ -1568,7 +1571,7 @@
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>33</v>
@@ -1577,7 +1580,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>33</v>
@@ -1627,7 +1630,7 @@
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>33</v>
@@ -1636,7 +1639,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>33</v>
@@ -1686,7 +1689,7 @@
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>33</v>
@@ -1695,7 +1698,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>33</v>
@@ -1745,7 +1748,7 @@
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>33</v>
@@ -1754,7 +1757,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>33</v>
@@ -1804,7 +1807,7 @@
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>33</v>
@@ -1813,7 +1816,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>33</v>
@@ -1863,7 +1866,7 @@
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>33</v>
@@ -1872,7 +1875,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>33</v>
@@ -1922,7 +1925,7 @@
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>33</v>
@@ -1931,7 +1934,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>33</v>
@@ -1981,7 +1984,7 @@
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>33</v>
@@ -1990,7 +1993,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-13</v>
+        <v>-14</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>33</v>
@@ -2040,7 +2043,7 @@
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>33</v>
@@ -2049,7 +2052,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>33</v>
@@ -2099,7 +2102,7 @@
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>33</v>
@@ -2108,7 +2111,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-27</v>
+        <v>-28</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>33</v>
@@ -2158,7 +2161,7 @@
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>33</v>
@@ -2167,7 +2170,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-20</v>
+        <v>-21</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>33</v>
@@ -2217,7 +2220,7 @@
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>33</v>
@@ -2226,7 +2229,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>33</v>
@@ -2276,7 +2279,7 @@
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>33</v>
@@ -2285,7 +2288,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>33</v>
@@ -2335,7 +2338,7 @@
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>33</v>
@@ -2344,7 +2347,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>33</v>
@@ -2394,7 +2397,7 @@
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>33</v>
@@ -2403,7 +2406,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>33</v>
@@ -2453,7 +2456,7 @@
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>33</v>
@@ -2462,7 +2465,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>33</v>
@@ -2512,7 +2515,7 @@
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>33</v>
@@ -2521,7 +2524,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>33</v>
@@ -2571,7 +2574,7 @@
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>33</v>
@@ -2580,7 +2583,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>33</v>
@@ -2630,7 +2633,7 @@
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>33</v>
@@ -2639,7 +2642,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>33</v>
@@ -2689,7 +2692,7 @@
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>33</v>
@@ -2698,7 +2701,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>33</v>
@@ -2748,7 +2751,7 @@
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>33</v>
@@ -2757,7 +2760,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>33</v>
@@ -2807,7 +2810,7 @@
         <v>28</v>
       </c>
       <c r="N40" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>33</v>
@@ -2816,7 +2819,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>33</v>
@@ -2866,7 +2869,7 @@
         <v>28</v>
       </c>
       <c r="N41" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O41" s="6" t="s">
         <v>33</v>
@@ -2875,7 +2878,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>33</v>
@@ -2925,7 +2928,7 @@
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>33</v>
@@ -2934,7 +2937,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>33</v>
@@ -2984,7 +2987,7 @@
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>33</v>
@@ -2993,7 +2996,7 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R43" s="6" t="s">
         <v>33</v>
@@ -3043,7 +3046,7 @@
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>33</v>
@@ -3052,7 +3055,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>33</v>
@@ -3102,7 +3105,7 @@
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>33</v>
@@ -3111,7 +3114,7 @@
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-6</v>
+        <v>-7</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>33</v>
@@ -3161,7 +3164,7 @@
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>33</v>
@@ -3170,7 +3173,7 @@
         <v>28</v>
       </c>
       <c r="Q46" s="9">
-        <v>-41</v>
+        <v>-42</v>
       </c>
       <c r="R46" s="6" t="s">
         <v>29</v>
@@ -3220,7 +3223,7 @@
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>33</v>
@@ -3229,7 +3232,7 @@
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>33</v>
@@ -3279,7 +3282,7 @@
         <v>96</v>
       </c>
       <c r="N48" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" s="6" t="s">
         <v>24</v>
@@ -3288,7 +3291,7 @@
         <v>96</v>
       </c>
       <c r="Q48" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" s="6" t="s">
         <v>24</v>
@@ -3338,7 +3341,7 @@
         <v>96</v>
       </c>
       <c r="N49" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O49" s="6" t="s">
         <v>24</v>
@@ -3347,7 +3350,7 @@
         <v>96</v>
       </c>
       <c r="Q49" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R49" s="6" t="s">
         <v>24</v>
@@ -3397,7 +3400,7 @@
         <v>96</v>
       </c>
       <c r="N50" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" s="6" t="s">
         <v>24</v>
@@ -3406,7 +3409,7 @@
         <v>96</v>
       </c>
       <c r="Q50" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R50" s="6" t="s">
         <v>24</v>
@@ -3456,7 +3459,7 @@
         <v>96</v>
       </c>
       <c r="N51" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O51" s="6" t="s">
         <v>24</v>
@@ -3465,7 +3468,7 @@
         <v>96</v>
       </c>
       <c r="Q51" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" s="6" t="s">
         <v>24</v>
@@ -3515,7 +3518,7 @@
         <v>96</v>
       </c>
       <c r="N52" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>24</v>
@@ -3524,7 +3527,7 @@
         <v>96</v>
       </c>
       <c r="Q52" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R52" s="6" t="s">
         <v>24</v>
@@ -3574,7 +3577,7 @@
         <v>96</v>
       </c>
       <c r="N53" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O53" s="6" t="s">
         <v>24</v>
@@ -3583,7 +3586,7 @@
         <v>96</v>
       </c>
       <c r="Q53" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" s="6" t="s">
         <v>24</v>
@@ -3633,7 +3636,7 @@
         <v>96</v>
       </c>
       <c r="N54" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="6" t="s">
         <v>24</v>
@@ -3642,7 +3645,7 @@
         <v>96</v>
       </c>
       <c r="Q54" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R54" s="6" t="s">
         <v>24</v>
@@ -3692,7 +3695,7 @@
         <v>96</v>
       </c>
       <c r="N55" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" s="6" t="s">
         <v>24</v>
@@ -3701,7 +3704,7 @@
         <v>96</v>
       </c>
       <c r="Q55" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R55" s="6" t="s">
         <v>24</v>
@@ -3751,7 +3754,7 @@
         <v>96</v>
       </c>
       <c r="N56" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" s="6" t="s">
         <v>24</v>
@@ -3760,7 +3763,7 @@
         <v>96</v>
       </c>
       <c r="Q56" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R56" s="6" t="s">
         <v>24</v>
@@ -3810,7 +3813,7 @@
         <v>96</v>
       </c>
       <c r="N57" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" s="6" t="s">
         <v>24</v>
@@ -3819,7 +3822,7 @@
         <v>96</v>
       </c>
       <c r="Q57" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" s="6" t="s">
         <v>24</v>
@@ -3869,7 +3872,7 @@
         <v>96</v>
       </c>
       <c r="N58" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O58" s="6" t="s">
         <v>24</v>
@@ -3878,7 +3881,7 @@
         <v>96</v>
       </c>
       <c r="Q58" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" s="6" t="s">
         <v>24</v>
@@ -3928,7 +3931,7 @@
         <v>96</v>
       </c>
       <c r="N59" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" s="6" t="s">
         <v>24</v>
@@ -3937,7 +3940,7 @@
         <v>96</v>
       </c>
       <c r="Q59" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R59" s="6" t="s">
         <v>24</v>
@@ -3987,7 +3990,7 @@
         <v>96</v>
       </c>
       <c r="N60" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" s="6" t="s">
         <v>24</v>
@@ -3996,7 +3999,7 @@
         <v>96</v>
       </c>
       <c r="Q60" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>24</v>
@@ -4046,7 +4049,7 @@
         <v>96</v>
       </c>
       <c r="N61" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" s="6" t="s">
         <v>24</v>
@@ -4055,7 +4058,7 @@
         <v>96</v>
       </c>
       <c r="Q61" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" s="6" t="s">
         <v>24</v>
@@ -4105,7 +4108,7 @@
         <v>96</v>
       </c>
       <c r="N62" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O62" s="6" t="s">
         <v>24</v>
@@ -4114,7 +4117,7 @@
         <v>96</v>
       </c>
       <c r="Q62" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62" s="6" t="s">
         <v>24</v>
@@ -4164,7 +4167,7 @@
         <v>96</v>
       </c>
       <c r="N63" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O63" s="6" t="s">
         <v>24</v>
@@ -4173,7 +4176,7 @@
         <v>96</v>
       </c>
       <c r="Q63" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63" s="6" t="s">
         <v>24</v>
@@ -4223,7 +4226,7 @@
         <v>96</v>
       </c>
       <c r="N64" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O64" s="6" t="s">
         <v>24</v>
@@ -4232,7 +4235,7 @@
         <v>96</v>
       </c>
       <c r="Q64" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64" s="6" t="s">
         <v>24</v>
@@ -4282,7 +4285,7 @@
         <v>96</v>
       </c>
       <c r="N65" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" s="6" t="s">
         <v>24</v>
@@ -4291,7 +4294,7 @@
         <v>96</v>
       </c>
       <c r="Q65" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65" s="6" t="s">
         <v>24</v>
@@ -4341,7 +4344,7 @@
         <v>96</v>
       </c>
       <c r="N66" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O66" s="6" t="s">
         <v>24</v>
@@ -4350,7 +4353,7 @@
         <v>96</v>
       </c>
       <c r="Q66" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R66" s="6" t="s">
         <v>24</v>
@@ -4400,7 +4403,7 @@
         <v>96</v>
       </c>
       <c r="N67" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" s="6" t="s">
         <v>24</v>
@@ -4409,7 +4412,7 @@
         <v>96</v>
       </c>
       <c r="Q67" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R67" s="6" t="s">
         <v>24</v>
@@ -4459,7 +4462,7 @@
         <v>96</v>
       </c>
       <c r="N68" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" s="6" t="s">
         <v>24</v>
@@ -4468,7 +4471,7 @@
         <v>96</v>
       </c>
       <c r="Q68" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R68" s="6" t="s">
         <v>24</v>
@@ -4518,7 +4521,7 @@
         <v>96</v>
       </c>
       <c r="N69" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" s="6" t="s">
         <v>24</v>
@@ -4527,7 +4530,7 @@
         <v>96</v>
       </c>
       <c r="Q69" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R69" s="6" t="s">
         <v>24</v>
@@ -4577,7 +4580,7 @@
         <v>96</v>
       </c>
       <c r="N70" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O70" s="6" t="s">
         <v>24</v>
@@ -4586,7 +4589,7 @@
         <v>96</v>
       </c>
       <c r="Q70" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R70" s="6" t="s">
         <v>24</v>
@@ -4636,7 +4639,7 @@
         <v>96</v>
       </c>
       <c r="N71" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O71" s="6" t="s">
         <v>24</v>
@@ -4645,7 +4648,7 @@
         <v>96</v>
       </c>
       <c r="Q71" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R71" s="6" t="s">
         <v>24</v>
@@ -4695,7 +4698,7 @@
         <v>96</v>
       </c>
       <c r="N72" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" s="6" t="s">
         <v>24</v>
@@ -4704,7 +4707,7 @@
         <v>96</v>
       </c>
       <c r="Q72" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R72" s="6" t="s">
         <v>24</v>
@@ -4754,7 +4757,7 @@
         <v>96</v>
       </c>
       <c r="N73" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" s="6" t="s">
         <v>24</v>
@@ -4763,7 +4766,7 @@
         <v>96</v>
       </c>
       <c r="Q73" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R73" s="6" t="s">
         <v>24</v>
@@ -4813,7 +4816,7 @@
         <v>96</v>
       </c>
       <c r="N74" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" s="6" t="s">
         <v>24</v>
@@ -4822,7 +4825,7 @@
         <v>96</v>
       </c>
       <c r="Q74" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R74" s="6" t="s">
         <v>24</v>
@@ -4872,7 +4875,7 @@
         <v>96</v>
       </c>
       <c r="N75" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
@@ -4881,7 +4884,7 @@
         <v>96</v>
       </c>
       <c r="Q75" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -4931,7 +4934,7 @@
         <v>96</v>
       </c>
       <c r="N76" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
@@ -4940,7 +4943,7 @@
         <v>96</v>
       </c>
       <c r="Q76" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -4990,7 +4993,7 @@
         <v>96</v>
       </c>
       <c r="N77" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
@@ -4999,7 +5002,7 @@
         <v>96</v>
       </c>
       <c r="Q77" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5046,19 +5049,19 @@
         <v>650</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N78" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q78" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5069,7 +5072,7 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>115</v>
@@ -5105,19 +5108,19 @@
         <v>650</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N79" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q79" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5128,7 +5131,7 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B80" s="6" t="s">
         <v>111</v>
@@ -5164,19 +5167,19 @@
         <v>650</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N80" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q80" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5187,7 +5190,7 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>117</v>
@@ -5223,19 +5226,19 @@
         <v>650</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N81" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q81" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5246,7 +5249,7 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>54</v>
@@ -5282,19 +5285,19 @@
         <v>650</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N82" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q82" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5305,7 +5308,7 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>93</v>
@@ -5341,19 +5344,19 @@
         <v>650</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N83" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q83" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5364,7 +5367,7 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>127</v>
@@ -5400,19 +5403,19 @@
         <v>680</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N84" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q84" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5423,7 +5426,7 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>134</v>
@@ -5459,19 +5462,19 @@
         <v>700</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N85" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q85" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5482,7 +5485,7 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>89</v>
@@ -5518,19 +5521,19 @@
         <v>700</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N86" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q86" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5541,7 +5544,7 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B87" s="6" t="s">
         <v>132</v>
@@ -5577,19 +5580,19 @@
         <v>700</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N87" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q87" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5600,7 +5603,7 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>82</v>
@@ -5636,19 +5639,19 @@
         <v>800</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N88" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q88" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5659,7 +5662,7 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>139</v>
@@ -5695,19 +5698,19 @@
         <v>1200</v>
       </c>
       <c r="M89" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N89" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P89" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q89" s="9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R89" s="6" t="s">
         <v>24</v>
@@ -5754,19 +5757,19 @@
         <v>185.5</v>
       </c>
       <c r="M90" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N90" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q90" s="9">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="R90" s="6" t="s">
         <v>24</v>
@@ -5777,7 +5780,7 @@
     </row>
     <row r="91">
       <c r="A91" s="6" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>93</v>
@@ -5813,19 +5816,19 @@
         <v>650</v>
       </c>
       <c r="M91" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N91" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O91" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P91" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q91" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R91" s="6" t="s">
         <v>24</v>
@@ -5836,16 +5839,16 @@
     </row>
     <row r="92">
       <c r="A92" s="6" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>25</v>
@@ -5854,10 +5857,10 @@
         <v>26</v>
       </c>
       <c r="G92" s="7">
-        <v>46245</v>
+        <v>46210</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="I92" s="7">
         <v>46265</v>
@@ -5872,19 +5875,19 @@
         <v>650</v>
       </c>
       <c r="M92" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N92" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O92" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q92" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R92" s="6" t="s">
         <v>24</v>
@@ -5895,7 +5898,7 @@
     </row>
     <row r="93">
       <c r="A93" s="6" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>117</v>
@@ -5931,19 +5934,19 @@
         <v>650</v>
       </c>
       <c r="M93" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N93" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O93" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P93" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q93" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R93" s="6" t="s">
         <v>24</v>
@@ -5954,16 +5957,16 @@
     </row>
     <row r="94">
       <c r="A94" s="6" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>25</v>
@@ -5972,10 +5975,10 @@
         <v>26</v>
       </c>
       <c r="G94" s="7">
-        <v>46210</v>
+        <v>46245</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="I94" s="7">
         <v>46265</v>
@@ -5990,19 +5993,19 @@
         <v>650</v>
       </c>
       <c r="M94" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N94" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O94" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q94" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R94" s="6" t="s">
         <v>24</v>
@@ -6013,7 +6016,7 @@
     </row>
     <row r="95">
       <c r="A95" s="6" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>115</v>
@@ -6049,19 +6052,19 @@
         <v>650</v>
       </c>
       <c r="M95" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N95" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O95" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P95" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q95" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R95" s="6" t="s">
         <v>24</v>
@@ -6072,7 +6075,7 @@
     </row>
     <row r="96">
       <c r="A96" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>127</v>
@@ -6108,19 +6111,19 @@
         <v>680</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N96" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O96" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q96" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R96" s="6" t="s">
         <v>24</v>
@@ -6131,7 +6134,7 @@
     </row>
     <row r="97">
       <c r="A97" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>132</v>
@@ -6167,19 +6170,19 @@
         <v>700</v>
       </c>
       <c r="M97" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N97" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O97" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P97" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q97" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R97" s="6" t="s">
         <v>24</v>
@@ -6190,7 +6193,7 @@
     </row>
     <row r="98">
       <c r="A98" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>134</v>
@@ -6226,19 +6229,19 @@
         <v>700</v>
       </c>
       <c r="M98" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N98" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q98" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R98" s="6" t="s">
         <v>24</v>
@@ -6249,7 +6252,7 @@
     </row>
     <row r="99">
       <c r="A99" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>82</v>
@@ -6285,19 +6288,19 @@
         <v>800</v>
       </c>
       <c r="M99" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N99" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O99" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P99" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q99" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R99" s="6" t="s">
         <v>24</v>
@@ -6308,7 +6311,7 @@
     </row>
     <row r="100">
       <c r="A100" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>139</v>
@@ -6344,19 +6347,19 @@
         <v>1200</v>
       </c>
       <c r="M100" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="N100" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>96</v>
+        <v>141</v>
       </c>
       <c r="Q100" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="R100" s="6" t="s">
         <v>24</v>

--- a/planilhas/CONTAS-A-RECEBER.xlsx
+++ b/planilhas/CONTAS-A-RECEBER.xlsx
@@ -9,14 +9,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Relatório!$A$5:$S$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$101</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Relatório!$A$1:$S$98</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1" fullPrecision="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t>Contas a Receber em aberto</t>
   </si>
@@ -40,7 +40,7 @@
     </r>
   </si>
   <si>
-    <t>Relatório exportado em segunda-feira, 17 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
+    <t>Relatório exportado em terça-feira, 18 de agosto de 2026 por LUZ DIVINA - FROTA 2</t>
   </si>
   <si>
     <t>Número do Documento</t>
@@ -160,6 +160,54 @@
     <t>OLIZIEL DA SILVA CARDOSO</t>
   </si>
   <si>
+    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>FA-11839</t>
+  </si>
+  <si>
+    <t>FA-12034</t>
+  </si>
+  <si>
+    <t>FA-11976</t>
+  </si>
+  <si>
+    <t>FA-11858</t>
+  </si>
+  <si>
+    <t>ANDRE CAVALCANTI DA FE</t>
+  </si>
+  <si>
+    <t>AZ EMPREENDIMENTOS</t>
+  </si>
+  <si>
+    <t>FA-12022</t>
+  </si>
+  <si>
+    <t>FA-11963</t>
+  </si>
+  <si>
+    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
+  </si>
+  <si>
+    <t>FA-12050</t>
+  </si>
+  <si>
+    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>PRIVADO</t>
+  </si>
+  <si>
+    <t>FA-11969</t>
+  </si>
+  <si>
+    <t>FA-12017</t>
+  </si>
+  <si>
+    <t>LEONARDO GOMES DO NASCIMENTO</t>
+  </si>
+  <si>
     <t>FA-12016</t>
   </si>
   <si>
@@ -172,279 +220,219 @@
     <t>JOÃO PAULO CONSÓRCIOS</t>
   </si>
   <si>
-    <t>ANA CONCEIÇÃO CARNEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>FA-11839</t>
+    <t>FA-12001</t>
+  </si>
+  <si>
+    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
+  </si>
+  <si>
+    <t>FA-12037</t>
+  </si>
+  <si>
+    <t>FA-11979</t>
+  </si>
+  <si>
+    <t>ADRIANO SANTOS DE CARVALHO</t>
+  </si>
+  <si>
+    <t>FA-12054</t>
+  </si>
+  <si>
+    <t>DANILO DE ALMEIDA TORRES</t>
+  </si>
+  <si>
+    <t>FA-11860</t>
+  </si>
+  <si>
+    <t>FA-11980</t>
+  </si>
+  <si>
+    <t>FA-12002</t>
+  </si>
+  <si>
+    <t>ELSON VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12025</t>
+  </si>
+  <si>
+    <t>FA-12024</t>
+  </si>
+  <si>
+    <t>FA-11964</t>
+  </si>
+  <si>
+    <t>FA-12051</t>
+  </si>
+  <si>
+    <t>FA-12023</t>
+  </si>
+  <si>
+    <t>FA-11999</t>
+  </si>
+  <si>
+    <t>JACKSON CASSIANO VERISSIMO</t>
+  </si>
+  <si>
+    <t>LUZ DIVINA LTDA</t>
+  </si>
+  <si>
+    <t>FA-12033</t>
+  </si>
+  <si>
+    <t>ANDERSON QUEIROZ PINHEIRO</t>
+  </si>
+  <si>
+    <t>FA-11867</t>
+  </si>
+  <si>
+    <t>MAICON LOPES SILVA</t>
   </si>
   <si>
     <t>FA-12046</t>
   </si>
   <si>
-    <t>FERNANDO RODRIGUES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>PRIVADO</t>
-  </si>
-  <si>
-    <t>FA-12034</t>
-  </si>
-  <si>
-    <t>FA-11976</t>
-  </si>
-  <si>
-    <t>FA-11858</t>
-  </si>
-  <si>
-    <t>ANDRE CAVALCANTI DA FE</t>
-  </si>
-  <si>
-    <t>AZ EMPREENDIMENTOS</t>
-  </si>
-  <si>
-    <t>FA-12022</t>
-  </si>
-  <si>
-    <t>FA-11963</t>
-  </si>
-  <si>
-    <t>RAMON TALLES BARBALHO DE FRANÇA</t>
-  </si>
-  <si>
-    <t>FA-12050</t>
-  </si>
-  <si>
-    <t>FA-12020</t>
-  </si>
-  <si>
-    <t>FA-11969</t>
-  </si>
-  <si>
-    <t>FA-11915</t>
-  </si>
-  <si>
-    <t>FA-12017</t>
-  </si>
-  <si>
-    <t>LEONARDO GOMES DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-12001</t>
-  </si>
-  <si>
-    <t>MARIO EWERTON CANDIDO DE SOUZA</t>
-  </si>
-  <si>
-    <t>FA-12037</t>
-  </si>
-  <si>
-    <t>FA-11979</t>
-  </si>
-  <si>
-    <t>ADRIANO SANTOS DE CARVALHO</t>
-  </si>
-  <si>
-    <t>FA-12054</t>
-  </si>
-  <si>
-    <t>DANILO DE ALMEIDA TORRES</t>
-  </si>
-  <si>
-    <t>FA-11860</t>
-  </si>
-  <si>
-    <t>FA-11980</t>
-  </si>
-  <si>
-    <t>FA-12002</t>
-  </si>
-  <si>
-    <t>ELSON VIEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12025</t>
-  </si>
-  <si>
-    <t>FA-12024</t>
-  </si>
-  <si>
-    <t>FA-11964</t>
-  </si>
-  <si>
-    <t>FA-12051</t>
-  </si>
-  <si>
-    <t>FA-12023</t>
-  </si>
-  <si>
-    <t>FA-11952</t>
+    <t>JOAO PAULO CONSORCIOS</t>
+  </si>
+  <si>
+    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
+  </si>
+  <si>
+    <t>FA-12147</t>
+  </si>
+  <si>
+    <t>CARLOS FERNANDO GARCIA DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-12011</t>
+  </si>
+  <si>
+    <t>ROBERTO MURATORI</t>
+  </si>
+  <si>
+    <t>FA-12059</t>
+  </si>
+  <si>
+    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
+  </si>
+  <si>
+    <t>FA-12057</t>
+  </si>
+  <si>
+    <t>ROSSILY PEREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11983</t>
+  </si>
+  <si>
+    <t>FA-11986</t>
+  </si>
+  <si>
+    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
+  </si>
+  <si>
+    <t>FA-12040</t>
+  </si>
+  <si>
+    <t>FA-12004</t>
+  </si>
+  <si>
+    <t>FA-12008</t>
+  </si>
+  <si>
+    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>FA-11984</t>
+  </si>
+  <si>
+    <t>FA-12058</t>
+  </si>
+  <si>
+    <t>FA-12121</t>
+  </si>
+  <si>
+    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
+  </si>
+  <si>
+    <t>PÚBLICO</t>
+  </si>
+  <si>
+    <t>FA-11862</t>
+  </si>
+  <si>
+    <t>FA-12064</t>
+  </si>
+  <si>
+    <t>WILSON COUTINHO BEZERRA</t>
+  </si>
+  <si>
+    <t>FA-12109</t>
+  </si>
+  <si>
+    <t>EDCARLOS MARTINS DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-11923</t>
+  </si>
+  <si>
+    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
+  </si>
+  <si>
+    <t>FA-12041</t>
+  </si>
+  <si>
+    <t>RAYANE ROBERTA DA SILVA</t>
+  </si>
+  <si>
+    <t>FA-12028</t>
+  </si>
+  <si>
+    <t>FA-12027</t>
+  </si>
+  <si>
+    <t>FA-12005</t>
+  </si>
+  <si>
+    <t>FA-12043</t>
+  </si>
+  <si>
+    <t>FA-11935</t>
+  </si>
+  <si>
+    <t>WESCLY JEAN DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>FA-11965</t>
+  </si>
+  <si>
+    <t>FA-11868</t>
+  </si>
+  <si>
+    <t>FA-12056</t>
+  </si>
+  <si>
+    <t>FA-12081</t>
+  </si>
+  <si>
+    <t>LUCA ZOLI</t>
+  </si>
+  <si>
+    <t>FA-12138</t>
+  </si>
+  <si>
+    <t>GILVAN RODRIGUES MACHADO</t>
+  </si>
+  <si>
+    <t>FA-12026</t>
+  </si>
+  <si>
+    <t>FA-11953</t>
   </si>
   <si>
     <t>ANNY KATARINA ACIOLE DA SILVA</t>
   </si>
   <si>
-    <t>FA-11999</t>
-  </si>
-  <si>
-    <t>JACKSON CASSIANO VERISSIMO</t>
-  </si>
-  <si>
-    <t>LUZ DIVINA LTDA</t>
-  </si>
-  <si>
-    <t>FA-12033</t>
-  </si>
-  <si>
-    <t>ANDERSON QUEIROZ PINHEIRO</t>
-  </si>
-  <si>
-    <t>FA-11867</t>
-  </si>
-  <si>
-    <t>MAICON LOPES SILVA</t>
-  </si>
-  <si>
-    <t>JOAO PAULO CONSORCIOS</t>
-  </si>
-  <si>
-    <t>JOAO PAULO SERVICOS DE CONSULTORIA EM CONSORCIOS LTDA</t>
-  </si>
-  <si>
-    <t>FA-12147</t>
-  </si>
-  <si>
-    <t>CARLOS FERNANDO GARCIA DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-12011</t>
-  </si>
-  <si>
-    <t>ROBERTO MURATORI</t>
-  </si>
-  <si>
-    <t>HOJE</t>
-  </si>
-  <si>
-    <t>FA-12059</t>
-  </si>
-  <si>
-    <t>RAFAEL CAVALCANTI BARROS FERREIRA</t>
-  </si>
-  <si>
-    <t>FA-12057</t>
-  </si>
-  <si>
-    <t>ROSSILY PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11983</t>
-  </si>
-  <si>
-    <t>FA-11986</t>
-  </si>
-  <si>
-    <t>ANA FLORIPES CARVALHO DA CUNHA</t>
-  </si>
-  <si>
-    <t>FA-12040</t>
-  </si>
-  <si>
-    <t>FA-12004</t>
-  </si>
-  <si>
-    <t>FA-12008</t>
-  </si>
-  <si>
-    <t>JONILSON JOSEMAR DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>FA-11984</t>
-  </si>
-  <si>
-    <t>FA-12058</t>
-  </si>
-  <si>
-    <t>FA-12121</t>
-  </si>
-  <si>
-    <t>TANIELLE GLAUCIANA SOUZA DA SILVA</t>
-  </si>
-  <si>
-    <t>PÚBLICO</t>
-  </si>
-  <si>
-    <t>FA-11862</t>
-  </si>
-  <si>
-    <t>FA-12064</t>
-  </si>
-  <si>
-    <t>WILSON COUTINHO BEZERRA</t>
-  </si>
-  <si>
-    <t>FA-12109</t>
-  </si>
-  <si>
-    <t>EDCARLOS MARTINS DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-11923</t>
-  </si>
-  <si>
-    <t>MATHEUS MATIAS CORTEZ TRIGUEIRO</t>
-  </si>
-  <si>
-    <t>FA-12041</t>
-  </si>
-  <si>
-    <t>RAYANE ROBERTA DA SILVA</t>
-  </si>
-  <si>
-    <t>FA-12028</t>
-  </si>
-  <si>
-    <t>FA-12027</t>
-  </si>
-  <si>
-    <t>FA-12005</t>
-  </si>
-  <si>
-    <t>FA-12043</t>
-  </si>
-  <si>
-    <t>FA-11935</t>
-  </si>
-  <si>
-    <t>WESCLY JEAN DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>FA-11965</t>
-  </si>
-  <si>
-    <t>FA-11868</t>
-  </si>
-  <si>
-    <t>FA-12056</t>
-  </si>
-  <si>
-    <t>FA-12081</t>
-  </si>
-  <si>
-    <t>LUCA ZOLI</t>
-  </si>
-  <si>
-    <t>FA-12138</t>
-  </si>
-  <si>
-    <t>GILVAN RODRIGUES MACHADO</t>
-  </si>
-  <si>
-    <t>FA-12026</t>
-  </si>
-  <si>
-    <t>FA-11953</t>
-  </si>
-  <si>
     <t>FA-12003</t>
   </si>
   <si>
@@ -460,15 +448,15 @@
     <t>A VENCER</t>
   </si>
   <si>
+    <t>FA-12110</t>
+  </si>
+  <si>
+    <t>FA-12122</t>
+  </si>
+  <si>
     <t>FA-12065</t>
   </si>
   <si>
-    <t>FA-12122</t>
-  </si>
-  <si>
-    <t>FA-12110</t>
-  </si>
-  <si>
     <t>FA-11864</t>
   </si>
   <si>
@@ -499,13 +487,13 @@
     <t>FA-11925</t>
   </si>
   <si>
+    <t>FA-12066</t>
+  </si>
+  <si>
+    <t>FA-12123</t>
+  </si>
+  <si>
     <t>FA-12111</t>
-  </si>
-  <si>
-    <t>FA-12123</t>
-  </si>
-  <si>
-    <t>FA-12066</t>
   </si>
   <si>
     <t>FA-11937</t>
@@ -663,7 +651,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr codeName=""/>
-  <dimension ref="A1:S101"/>
+  <dimension ref="A1:S98"/>
   <sheetFormatPr defaultRowHeight="23" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1" style="1"/>
@@ -804,7 +792,7 @@
         <v>28</v>
       </c>
       <c r="N6" s="9">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="O6" s="6" t="s">
         <v>29</v>
@@ -813,7 +801,7 @@
         <v>28</v>
       </c>
       <c r="Q6" s="9">
-        <v>-56</v>
+        <v>-57</v>
       </c>
       <c r="R6" s="6" t="s">
         <v>29</v>
@@ -863,7 +851,7 @@
         <v>28</v>
       </c>
       <c r="N7" s="9">
-        <v>-42</v>
+        <v>-43</v>
       </c>
       <c r="O7" s="6" t="s">
         <v>29</v>
@@ -872,7 +860,7 @@
         <v>28</v>
       </c>
       <c r="Q7" s="9">
-        <v>-26</v>
+        <v>-27</v>
       </c>
       <c r="R7" s="6" t="s">
         <v>33</v>
@@ -922,7 +910,7 @@
         <v>28</v>
       </c>
       <c r="N8" s="9">
-        <v>-39</v>
+        <v>-40</v>
       </c>
       <c r="O8" s="6" t="s">
         <v>29</v>
@@ -931,7 +919,7 @@
         <v>28</v>
       </c>
       <c r="Q8" s="9">
-        <v>-49</v>
+        <v>-50</v>
       </c>
       <c r="R8" s="6" t="s">
         <v>29</v>
@@ -981,7 +969,7 @@
         <v>28</v>
       </c>
       <c r="N9" s="9">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="O9" s="6" t="s">
         <v>29</v>
@@ -990,7 +978,7 @@
         <v>28</v>
       </c>
       <c r="Q9" s="9">
-        <v>-19</v>
+        <v>-20</v>
       </c>
       <c r="R9" s="6" t="s">
         <v>33</v>
@@ -1040,7 +1028,7 @@
         <v>28</v>
       </c>
       <c r="N10" s="9">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="O10" s="6" t="s">
         <v>29</v>
@@ -1049,7 +1037,7 @@
         <v>28</v>
       </c>
       <c r="Q10" s="9">
-        <v>-35</v>
+        <v>-36</v>
       </c>
       <c r="R10" s="6" t="s">
         <v>29</v>
@@ -1099,7 +1087,7 @@
         <v>28</v>
       </c>
       <c r="N11" s="9">
-        <v>-28</v>
+        <v>-29</v>
       </c>
       <c r="O11" s="6" t="s">
         <v>33</v>
@@ -1108,7 +1096,7 @@
         <v>28</v>
       </c>
       <c r="Q11" s="9">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="R11" s="6" t="s">
         <v>33</v>
@@ -1158,7 +1146,7 @@
         <v>28</v>
       </c>
       <c r="N12" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O12" s="6" t="s">
         <v>33</v>
@@ -1167,7 +1155,7 @@
         <v>28</v>
       </c>
       <c r="Q12" s="9">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="R12" s="6" t="s">
         <v>33</v>
@@ -1217,7 +1205,7 @@
         <v>28</v>
       </c>
       <c r="N13" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O13" s="6" t="s">
         <v>33</v>
@@ -1226,7 +1214,7 @@
         <v>28</v>
       </c>
       <c r="Q13" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R13" s="6" t="s">
         <v>33</v>
@@ -1276,7 +1264,7 @@
         <v>28</v>
       </c>
       <c r="N14" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O14" s="6" t="s">
         <v>33</v>
@@ -1285,7 +1273,7 @@
         <v>28</v>
       </c>
       <c r="Q14" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R14" s="6" t="s">
         <v>33</v>
@@ -1335,7 +1323,7 @@
         <v>28</v>
       </c>
       <c r="N15" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="O15" s="6" t="s">
         <v>33</v>
@@ -1344,7 +1332,7 @@
         <v>28</v>
       </c>
       <c r="Q15" s="9">
-        <v>-21</v>
+        <v>-22</v>
       </c>
       <c r="R15" s="6" t="s">
         <v>33</v>
@@ -1355,11 +1343,11 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="C16" s="6" t="s">
         <v>24</v>
       </c>
@@ -1367,34 +1355,34 @@
         <v>24</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G16" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="I16" s="7">
-        <v>46230</v>
+        <v>45930</v>
       </c>
       <c r="J16" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="K16" s="7">
-        <v>46230</v>
+        <v>46233</v>
       </c>
       <c r="L16" s="8">
-        <v>750</v>
+        <v>185.5</v>
       </c>
       <c r="M16" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N16" s="9">
-        <v>-21</v>
+        <v>-19</v>
       </c>
       <c r="O16" s="6" t="s">
         <v>33</v>
@@ -1403,7 +1391,7 @@
         <v>28</v>
       </c>
       <c r="Q16" s="9">
-        <v>-21</v>
+        <v>-19</v>
       </c>
       <c r="R16" s="6" t="s">
         <v>33</v>
@@ -1414,10 +1402,10 @@
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>24</v>
@@ -1435,25 +1423,25 @@
         <v>24</v>
       </c>
       <c r="H17" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="I17" s="7">
-        <v>45930</v>
+        <v>46223</v>
       </c>
       <c r="J17" s="7">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="K17" s="7">
-        <v>46233</v>
+        <v>46223</v>
       </c>
       <c r="L17" s="8">
-        <v>185.5</v>
+        <v>355</v>
       </c>
       <c r="M17" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N17" s="9">
-        <v>-18</v>
+        <v>-15</v>
       </c>
       <c r="O17" s="6" t="s">
         <v>33</v>
@@ -1462,7 +1450,7 @@
         <v>28</v>
       </c>
       <c r="Q17" s="9">
-        <v>-18</v>
+        <v>-29</v>
       </c>
       <c r="R17" s="6" t="s">
         <v>33</v>
@@ -1473,10 +1461,10 @@
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C18" s="6" t="s">
         <v>24</v>
@@ -1488,31 +1476,31 @@
         <v>25</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G18" s="7">
+        <v>46232</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I18" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="J18" s="7">
         <v>46237</v>
       </c>
       <c r="K18" s="7">
-        <v>46223</v>
+        <v>46237</v>
       </c>
       <c r="L18" s="8">
-        <v>355</v>
+        <v>630</v>
       </c>
       <c r="M18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N18" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>33</v>
@@ -1521,7 +1509,7 @@
         <v>28</v>
       </c>
       <c r="Q18" s="9">
-        <v>-28</v>
+        <v>-15</v>
       </c>
       <c r="R18" s="6" t="s">
         <v>33</v>
@@ -1532,46 +1520,46 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E19" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G19" s="7">
+        <v>46225</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="J19" s="7">
         <v>46237</v>
       </c>
       <c r="K19" s="7">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="L19" s="8">
-        <v>560</v>
+        <v>650</v>
       </c>
       <c r="M19" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N19" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O19" s="6" t="s">
         <v>33</v>
@@ -1580,7 +1568,7 @@
         <v>28</v>
       </c>
       <c r="Q19" s="9">
-        <v>-21</v>
+        <v>-15</v>
       </c>
       <c r="R19" s="6" t="s">
         <v>33</v>
@@ -1591,10 +1579,10 @@
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>24</v>
@@ -1609,10 +1597,10 @@
         <v>26</v>
       </c>
       <c r="G20" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I20" s="7">
         <v>46237</v>
@@ -1624,13 +1612,13 @@
         <v>46237</v>
       </c>
       <c r="L20" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M20" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N20" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>33</v>
@@ -1639,7 +1627,7 @@
         <v>28</v>
       </c>
       <c r="Q20" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R20" s="6" t="s">
         <v>33</v>
@@ -1650,13 +1638,13 @@
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>24</v>
@@ -1668,7 +1656,7 @@
         <v>26</v>
       </c>
       <c r="G21" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>27</v>
@@ -1683,13 +1671,13 @@
         <v>46237</v>
       </c>
       <c r="L21" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M21" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N21" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O21" s="6" t="s">
         <v>33</v>
@@ -1698,7 +1686,7 @@
         <v>28</v>
       </c>
       <c r="Q21" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R21" s="6" t="s">
         <v>33</v>
@@ -1709,10 +1697,10 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>24</v>
@@ -1727,10 +1715,10 @@
         <v>26</v>
       </c>
       <c r="G22" s="7">
-        <v>46188</v>
+        <v>46225</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I22" s="7">
         <v>46237</v>
@@ -1742,13 +1730,13 @@
         <v>46237</v>
       </c>
       <c r="L22" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M22" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N22" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O22" s="6" t="s">
         <v>33</v>
@@ -1757,7 +1745,7 @@
         <v>28</v>
       </c>
       <c r="Q22" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R22" s="6" t="s">
         <v>33</v>
@@ -1768,16 +1756,16 @@
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E23" s="6" t="s">
         <v>25</v>
@@ -1801,13 +1789,13 @@
         <v>46237</v>
       </c>
       <c r="L23" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M23" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N23" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="O23" s="6" t="s">
         <v>33</v>
@@ -1816,7 +1804,7 @@
         <v>28</v>
       </c>
       <c r="Q23" s="9">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="R23" s="6" t="s">
         <v>33</v>
@@ -1827,13 +1815,13 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>58</v>
+        <v>39</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>24</v>
@@ -1842,31 +1830,31 @@
         <v>25</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G24" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I24" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="J24" s="7">
-        <v>46237</v>
+        <v>46240</v>
       </c>
       <c r="K24" s="7">
-        <v>46237</v>
+        <v>46223</v>
       </c>
       <c r="L24" s="8">
-        <v>680</v>
+        <v>190</v>
       </c>
       <c r="M24" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N24" s="9">
-        <v>-14</v>
+        <v>-12</v>
       </c>
       <c r="O24" s="6" t="s">
         <v>33</v>
@@ -1875,7 +1863,7 @@
         <v>28</v>
       </c>
       <c r="Q24" s="9">
-        <v>-14</v>
+        <v>-29</v>
       </c>
       <c r="R24" s="6" t="s">
         <v>33</v>
@@ -1886,46 +1874,46 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E25" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G25" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I25" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="J25" s="7">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="K25" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="L25" s="8">
-        <v>700</v>
+        <v>582</v>
       </c>
       <c r="M25" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N25" s="9">
-        <v>-14</v>
+        <v>-11</v>
       </c>
       <c r="O25" s="6" t="s">
         <v>33</v>
@@ -1934,7 +1922,7 @@
         <v>28</v>
       </c>
       <c r="Q25" s="9">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="R25" s="6" t="s">
         <v>33</v>
@@ -1945,46 +1933,46 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>44</v>
-      </c>
       <c r="F26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G26" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>45</v>
+        <v>61</v>
       </c>
       <c r="I26" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="J26" s="7">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="K26" s="7">
-        <v>46237</v>
+        <v>46230</v>
       </c>
       <c r="L26" s="8">
-        <v>750</v>
+        <v>150</v>
       </c>
       <c r="M26" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N26" s="9">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="O26" s="6" t="s">
         <v>33</v>
@@ -1993,7 +1981,7 @@
         <v>28</v>
       </c>
       <c r="Q26" s="9">
-        <v>-14</v>
+        <v>-22</v>
       </c>
       <c r="R26" s="6" t="s">
         <v>33</v>
@@ -2004,13 +1992,13 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>24</v>
@@ -2028,22 +2016,22 @@
         <v>27</v>
       </c>
       <c r="I27" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="J27" s="7">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="K27" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="L27" s="8">
-        <v>190</v>
+        <v>502.31</v>
       </c>
       <c r="M27" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N27" s="9">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="O27" s="6" t="s">
         <v>33</v>
@@ -2052,7 +2040,7 @@
         <v>28</v>
       </c>
       <c r="Q27" s="9">
-        <v>-28</v>
+        <v>-8</v>
       </c>
       <c r="R27" s="6" t="s">
         <v>33</v>
@@ -2063,7 +2051,7 @@
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>37</v>
@@ -2078,31 +2066,31 @@
         <v>25</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G28" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G28" s="7">
+        <v>46232</v>
       </c>
       <c r="H28" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I28" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="J28" s="7">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="K28" s="7">
-        <v>46223</v>
+        <v>46244</v>
       </c>
       <c r="L28" s="8">
-        <v>330</v>
+        <v>630</v>
       </c>
       <c r="M28" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N28" s="9">
-        <v>-11</v>
+        <v>-8</v>
       </c>
       <c r="O28" s="6" t="s">
         <v>33</v>
@@ -2111,7 +2099,7 @@
         <v>28</v>
       </c>
       <c r="Q28" s="9">
-        <v>-28</v>
+        <v>-8</v>
       </c>
       <c r="R28" s="6" t="s">
         <v>33</v>
@@ -2122,10 +2110,10 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>24</v>
@@ -2137,31 +2125,31 @@
         <v>25</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G29" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G29" s="7">
+        <v>46225</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I29" s="7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="J29" s="7">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="K29" s="7">
-        <v>46230</v>
+        <v>46244</v>
       </c>
       <c r="L29" s="8">
-        <v>582</v>
+        <v>630</v>
       </c>
       <c r="M29" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N29" s="9">
-        <v>-10</v>
+        <v>-8</v>
       </c>
       <c r="O29" s="6" t="s">
         <v>33</v>
@@ -2170,7 +2158,7 @@
         <v>28</v>
       </c>
       <c r="Q29" s="9">
-        <v>-21</v>
+        <v>-8</v>
       </c>
       <c r="R29" s="6" t="s">
         <v>33</v>
@@ -2181,10 +2169,10 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C30" s="6" t="s">
         <v>24</v>
@@ -2196,10 +2184,10 @@
         <v>25</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G30" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G30" s="7">
+        <v>46232</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>27</v>
@@ -2214,13 +2202,13 @@
         <v>46244</v>
       </c>
       <c r="L30" s="8">
-        <v>502.31</v>
+        <v>650</v>
       </c>
       <c r="M30" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N30" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O30" s="6" t="s">
         <v>33</v>
@@ -2229,7 +2217,7 @@
         <v>28</v>
       </c>
       <c r="Q30" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R30" s="6" t="s">
         <v>33</v>
@@ -2240,10 +2228,10 @@
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>24</v>
@@ -2258,10 +2246,10 @@
         <v>26</v>
       </c>
       <c r="G31" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I31" s="7">
         <v>46244</v>
@@ -2273,13 +2261,13 @@
         <v>46244</v>
       </c>
       <c r="L31" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M31" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N31" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O31" s="6" t="s">
         <v>33</v>
@@ -2288,7 +2276,7 @@
         <v>28</v>
       </c>
       <c r="Q31" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R31" s="6" t="s">
         <v>33</v>
@@ -2299,13 +2287,13 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>69</v>
+        <v>39</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>24</v>
@@ -2332,13 +2320,13 @@
         <v>46244</v>
       </c>
       <c r="L32" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M32" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N32" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O32" s="6" t="s">
         <v>33</v>
@@ -2347,7 +2335,7 @@
         <v>28</v>
       </c>
       <c r="Q32" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R32" s="6" t="s">
         <v>33</v>
@@ -2358,10 +2346,10 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>24</v>
@@ -2376,10 +2364,10 @@
         <v>26</v>
       </c>
       <c r="G33" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I33" s="7">
         <v>46244</v>
@@ -2391,13 +2379,13 @@
         <v>46244</v>
       </c>
       <c r="L33" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M33" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N33" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O33" s="6" t="s">
         <v>33</v>
@@ -2406,7 +2394,7 @@
         <v>28</v>
       </c>
       <c r="Q33" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R33" s="6" t="s">
         <v>33</v>
@@ -2417,10 +2405,10 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C34" s="6" t="s">
         <v>24</v>
@@ -2435,10 +2423,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="7">
-        <v>46188</v>
+        <v>46232</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I34" s="7">
         <v>46244</v>
@@ -2450,13 +2438,13 @@
         <v>46244</v>
       </c>
       <c r="L34" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M34" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N34" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>33</v>
@@ -2465,7 +2453,7 @@
         <v>28</v>
       </c>
       <c r="Q34" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R34" s="6" t="s">
         <v>33</v>
@@ -2476,13 +2464,13 @@
     </row>
     <row r="35">
       <c r="A35" s="6" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>24</v>
@@ -2494,7 +2482,7 @@
         <v>26</v>
       </c>
       <c r="G35" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H35" s="6" t="s">
         <v>27</v>
@@ -2509,13 +2497,13 @@
         <v>46244</v>
       </c>
       <c r="L35" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M35" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N35" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O35" s="6" t="s">
         <v>33</v>
@@ -2524,7 +2512,7 @@
         <v>28</v>
       </c>
       <c r="Q35" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R35" s="6" t="s">
         <v>33</v>
@@ -2535,10 +2523,10 @@
     </row>
     <row r="36">
       <c r="A36" s="6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="C36" s="6" t="s">
         <v>24</v>
@@ -2556,7 +2544,7 @@
         <v>46225</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I36" s="7">
         <v>46244</v>
@@ -2574,7 +2562,7 @@
         <v>28</v>
       </c>
       <c r="N36" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>33</v>
@@ -2583,7 +2571,7 @@
         <v>28</v>
       </c>
       <c r="Q36" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R36" s="6" t="s">
         <v>33</v>
@@ -2597,13 +2585,13 @@
         <v>76</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C37" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E37" s="6" t="s">
         <v>25</v>
@@ -2627,13 +2615,13 @@
         <v>46244</v>
       </c>
       <c r="L37" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N37" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O37" s="6" t="s">
         <v>33</v>
@@ -2642,7 +2630,7 @@
         <v>28</v>
       </c>
       <c r="Q37" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R37" s="6" t="s">
         <v>33</v>
@@ -2656,7 +2644,7 @@
         <v>77</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>24</v>
@@ -2665,7 +2653,7 @@
         <v>24</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
@@ -2674,7 +2662,7 @@
         <v>46232</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="I38" s="7">
         <v>46244</v>
@@ -2686,13 +2674,13 @@
         <v>46244</v>
       </c>
       <c r="L38" s="8">
-        <v>680</v>
+        <v>750</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N38" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O38" s="6" t="s">
         <v>33</v>
@@ -2701,7 +2689,7 @@
         <v>28</v>
       </c>
       <c r="Q38" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R38" s="6" t="s">
         <v>33</v>
@@ -2715,7 +2703,7 @@
         <v>78</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>24</v>
@@ -2733,7 +2721,7 @@
         <v>46225</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="I39" s="7">
         <v>46244</v>
@@ -2745,13 +2733,13 @@
         <v>46244</v>
       </c>
       <c r="L39" s="8">
-        <v>680</v>
+        <v>1200</v>
       </c>
       <c r="M39" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N39" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="O39" s="6" t="s">
         <v>33</v>
@@ -2760,7 +2748,7 @@
         <v>28</v>
       </c>
       <c r="Q39" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R39" s="6" t="s">
         <v>33</v>
@@ -2771,25 +2759,25 @@
     </row>
     <row r="40">
       <c r="A40" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>49</v>
+        <v>82</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G40" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>27</v>
@@ -2798,13 +2786,13 @@
         <v>46244</v>
       </c>
       <c r="J40" s="7">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K40" s="7">
         <v>46244</v>
       </c>
       <c r="L40" s="8">
-        <v>700</v>
+        <v>70.49</v>
       </c>
       <c r="M40" s="6" t="s">
         <v>28</v>
@@ -2819,7 +2807,7 @@
         <v>28</v>
       </c>
       <c r="Q40" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R40" s="6" t="s">
         <v>33</v>
@@ -2830,10 +2818,10 @@
     </row>
     <row r="41">
       <c r="A41" s="6" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C41" s="6" t="s">
         <v>24</v>
@@ -2842,28 +2830,28 @@
         <v>24</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G41" s="7">
-        <v>46232</v>
+        <v>24</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I41" s="7">
         <v>46244</v>
       </c>
       <c r="J41" s="7">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="K41" s="7">
         <v>46244</v>
       </c>
       <c r="L41" s="8">
-        <v>750</v>
+        <v>300</v>
       </c>
       <c r="M41" s="6" t="s">
         <v>28</v>
@@ -2878,7 +2866,7 @@
         <v>28</v>
       </c>
       <c r="Q41" s="9">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="R41" s="6" t="s">
         <v>33</v>
@@ -2889,46 +2877,46 @@
     </row>
     <row r="42">
       <c r="A42" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>25</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G42" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G42" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I42" s="7">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="J42" s="7">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="K42" s="7">
-        <v>46244</v>
+        <v>46230</v>
       </c>
       <c r="L42" s="8">
-        <v>800</v>
+        <v>60</v>
       </c>
       <c r="M42" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N42" s="9">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="O42" s="6" t="s">
         <v>33</v>
@@ -2937,7 +2925,7 @@
         <v>28</v>
       </c>
       <c r="Q42" s="9">
-        <v>-7</v>
+        <v>-22</v>
       </c>
       <c r="R42" s="6" t="s">
         <v>33</v>
@@ -2948,13 +2936,13 @@
     </row>
     <row r="43">
       <c r="A43" s="6" t="s">
-        <v>83</v>
+        <v>24</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>24</v>
@@ -2963,31 +2951,31 @@
         <v>25</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G43" s="7">
-        <v>46225</v>
+        <v>24</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>85</v>
+        <v>24</v>
       </c>
       <c r="I43" s="7">
-        <v>46244</v>
+        <v>46209</v>
       </c>
       <c r="J43" s="7">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="K43" s="7">
-        <v>46244</v>
+        <v>46209</v>
       </c>
       <c r="L43" s="8">
-        <v>1200</v>
+        <v>112.5</v>
       </c>
       <c r="M43" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N43" s="9">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="O43" s="6" t="s">
         <v>33</v>
@@ -2996,10 +2984,10 @@
         <v>28</v>
       </c>
       <c r="Q43" s="9">
-        <v>-7</v>
+        <v>-43</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="S43" s="6" t="s">
         <v>24</v>
@@ -3007,10 +2995,10 @@
     </row>
     <row r="44">
       <c r="A44" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>24</v>
@@ -3022,31 +3010,31 @@
         <v>25</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G44" s="7">
+        <v>46248</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I44" s="7">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="J44" s="7">
-        <v>46245</v>
+        <v>46249</v>
       </c>
       <c r="K44" s="7">
-        <v>46244</v>
+        <v>46249</v>
       </c>
       <c r="L44" s="8">
-        <v>70.49</v>
+        <v>185.71</v>
       </c>
       <c r="M44" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N44" s="9">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="O44" s="6" t="s">
         <v>33</v>
@@ -3055,7 +3043,7 @@
         <v>28</v>
       </c>
       <c r="Q44" s="9">
-        <v>-7</v>
+        <v>-3</v>
       </c>
       <c r="R44" s="6" t="s">
         <v>33</v>
@@ -3066,13 +3054,13 @@
     </row>
     <row r="45">
       <c r="A45" s="6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>24</v>
@@ -3081,31 +3069,31 @@
         <v>25</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G45" s="7">
+        <v>46225</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I45" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="J45" s="7">
-        <v>46245</v>
+        <v>46251</v>
       </c>
       <c r="K45" s="7">
-        <v>46244</v>
+        <v>46251</v>
       </c>
       <c r="L45" s="8">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="M45" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N45" s="9">
-        <v>-6</v>
+        <v>-1</v>
       </c>
       <c r="O45" s="6" t="s">
         <v>33</v>
@@ -3114,7 +3102,7 @@
         <v>28</v>
       </c>
       <c r="Q45" s="9">
-        <v>-7</v>
+        <v>-1</v>
       </c>
       <c r="R45" s="6" t="s">
         <v>33</v>
@@ -3125,13 +3113,13 @@
     </row>
     <row r="46">
       <c r="A46" s="6" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>24</v>
@@ -3140,31 +3128,31 @@
         <v>25</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
+      </c>
+      <c r="G46" s="7">
+        <v>46232</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="I46" s="7">
-        <v>46209</v>
+        <v>46251</v>
       </c>
       <c r="J46" s="7">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="K46" s="7">
-        <v>46209</v>
+        <v>46251</v>
       </c>
       <c r="L46" s="8">
-        <v>112.5</v>
+        <v>620</v>
       </c>
       <c r="M46" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N46" s="9">
-        <v>-4</v>
+        <v>-1</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>33</v>
@@ -3173,10 +3161,10 @@
         <v>28</v>
       </c>
       <c r="Q46" s="9">
-        <v>-42</v>
+        <v>-1</v>
       </c>
       <c r="R46" s="6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="S46" s="6" t="s">
         <v>24</v>
@@ -3184,16 +3172,16 @@
     </row>
     <row r="47">
       <c r="A47" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B47" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C47" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E47" s="6" t="s">
         <v>25</v>
@@ -3202,28 +3190,28 @@
         <v>26</v>
       </c>
       <c r="G47" s="7">
-        <v>46248</v>
+        <v>46232</v>
       </c>
       <c r="H47" s="6" t="s">
         <v>27</v>
       </c>
       <c r="I47" s="7">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="J47" s="7">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="K47" s="7">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="L47" s="8">
-        <v>185.71</v>
+        <v>630</v>
       </c>
       <c r="M47" s="6" t="s">
         <v>28</v>
       </c>
       <c r="N47" s="9">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="O47" s="6" t="s">
         <v>33</v>
@@ -3232,7 +3220,7 @@
         <v>28</v>
       </c>
       <c r="Q47" s="9">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="R47" s="6" t="s">
         <v>33</v>
@@ -3243,13 +3231,13 @@
     </row>
     <row r="48">
       <c r="A48" s="6" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B48" s="6" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>95</v>
+        <v>24</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>24</v>
@@ -3276,25 +3264,25 @@
         <v>46251</v>
       </c>
       <c r="L48" s="8">
-        <v>600</v>
+        <v>630</v>
       </c>
       <c r="M48" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N48" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q48" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R48" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S48" s="6" t="s">
         <v>24</v>
@@ -3308,7 +3296,7 @@
         <v>98</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>24</v>
@@ -3320,10 +3308,10 @@
         <v>26</v>
       </c>
       <c r="G49" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I49" s="7">
         <v>46251</v>
@@ -3335,25 +3323,25 @@
         <v>46251</v>
       </c>
       <c r="L49" s="8">
-        <v>620</v>
+        <v>630</v>
       </c>
       <c r="M49" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N49" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O49" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P49" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q49" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R49" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S49" s="6" t="s">
         <v>24</v>
@@ -3364,13 +3352,13 @@
         <v>99</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="C50" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>25</v>
@@ -3397,22 +3385,22 @@
         <v>630</v>
       </c>
       <c r="M50" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N50" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q50" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R50" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S50" s="6" t="s">
         <v>24</v>
@@ -3420,10 +3408,10 @@
     </row>
     <row r="51">
       <c r="A51" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="C51" s="6" t="s">
         <v>24</v>
@@ -3456,22 +3444,22 @@
         <v>630</v>
       </c>
       <c r="M51" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N51" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O51" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P51" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q51" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R51" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S51" s="6" t="s">
         <v>24</v>
@@ -3479,10 +3467,10 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="6" t="s">
         <v>102</v>
-      </c>
-      <c r="B52" s="6" t="s">
-        <v>103</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>24</v>
@@ -3515,22 +3503,22 @@
         <v>630</v>
       </c>
       <c r="M52" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N52" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P52" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q52" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R52" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S52" s="6" t="s">
         <v>24</v>
@@ -3538,13 +3526,13 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>24</v>
@@ -3556,7 +3544,7 @@
         <v>26</v>
       </c>
       <c r="G53" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H53" s="6" t="s">
         <v>27</v>
@@ -3571,25 +3559,25 @@
         <v>46251</v>
       </c>
       <c r="L53" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M53" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N53" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O53" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P53" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q53" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R53" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S53" s="6" t="s">
         <v>24</v>
@@ -3597,10 +3585,10 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>24</v>
@@ -3615,7 +3603,7 @@
         <v>26</v>
       </c>
       <c r="G54" s="7">
-        <v>46225</v>
+        <v>46232</v>
       </c>
       <c r="H54" s="6" t="s">
         <v>27</v>
@@ -3630,25 +3618,25 @@
         <v>46251</v>
       </c>
       <c r="L54" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M54" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N54" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q54" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R54" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S54" s="6" t="s">
         <v>24</v>
@@ -3656,17 +3644,17 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="C55" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D55" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C55" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="E55" s="6" t="s">
         <v>25</v>
       </c>
@@ -3674,10 +3662,10 @@
         <v>26</v>
       </c>
       <c r="G55" s="7">
-        <v>46225</v>
+        <v>46245</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="I55" s="7">
         <v>46251</v>
@@ -3689,25 +3677,25 @@
         <v>46251</v>
       </c>
       <c r="L55" s="8">
-        <v>630</v>
+        <v>650</v>
       </c>
       <c r="M55" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N55" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O55" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P55" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q55" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R55" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S55" s="6" t="s">
         <v>24</v>
@@ -3718,10 +3706,10 @@
         <v>108</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>24</v>
@@ -3733,10 +3721,10 @@
         <v>26</v>
       </c>
       <c r="G56" s="7">
-        <v>46225</v>
+        <v>46188</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I56" s="7">
         <v>46251</v>
@@ -3751,22 +3739,22 @@
         <v>650</v>
       </c>
       <c r="M56" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N56" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q56" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R56" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S56" s="6" t="s">
         <v>24</v>
@@ -3777,7 +3765,7 @@
         <v>109</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>24</v>
@@ -3810,22 +3798,22 @@
         <v>650</v>
       </c>
       <c r="M57" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N57" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O57" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P57" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q57" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R57" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S57" s="6" t="s">
         <v>24</v>
@@ -3833,16 +3821,16 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>25</v>
@@ -3851,10 +3839,10 @@
         <v>26</v>
       </c>
       <c r="G58" s="7">
-        <v>46245</v>
+        <v>46240</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="I58" s="7">
         <v>46251</v>
@@ -3869,22 +3857,22 @@
         <v>650</v>
       </c>
       <c r="M58" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N58" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q58" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R58" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S58" s="6" t="s">
         <v>24</v>
@@ -3895,7 +3883,7 @@
         <v>113</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>54</v>
+        <v>114</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>24</v>
@@ -3910,10 +3898,10 @@
         <v>26</v>
       </c>
       <c r="G59" s="7">
-        <v>46188</v>
+        <v>46210</v>
       </c>
       <c r="H59" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I59" s="7">
         <v>46251</v>
@@ -3928,22 +3916,22 @@
         <v>650</v>
       </c>
       <c r="M59" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N59" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O59" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P59" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q59" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R59" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S59" s="6" t="s">
         <v>24</v>
@@ -3951,10 +3939,10 @@
     </row>
     <row r="60">
       <c r="A60" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>24</v>
@@ -3984,25 +3972,25 @@
         <v>46251</v>
       </c>
       <c r="L60" s="8">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N60" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q60" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R60" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S60" s="6" t="s">
         <v>24</v>
@@ -4010,10 +3998,10 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>117</v>
+        <v>57</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>24</v>
@@ -4028,7 +4016,7 @@
         <v>26</v>
       </c>
       <c r="G61" s="7">
-        <v>46240</v>
+        <v>46232</v>
       </c>
       <c r="H61" s="6" t="s">
         <v>27</v>
@@ -4043,25 +4031,25 @@
         <v>46251</v>
       </c>
       <c r="L61" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M61" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N61" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O61" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P61" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q61" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R61" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S61" s="6" t="s">
         <v>24</v>
@@ -4072,7 +4060,7 @@
         <v>118</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>119</v>
+        <v>41</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>24</v>
@@ -4087,7 +4075,7 @@
         <v>26</v>
       </c>
       <c r="G62" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H62" s="6" t="s">
         <v>27</v>
@@ -4102,25 +4090,25 @@
         <v>46251</v>
       </c>
       <c r="L62" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M62" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N62" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q62" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R62" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S62" s="6" t="s">
         <v>24</v>
@@ -4128,10 +4116,10 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>121</v>
+        <v>72</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>24</v>
@@ -4146,10 +4134,10 @@
         <v>26</v>
       </c>
       <c r="G63" s="7">
-        <v>46232</v>
+        <v>46225</v>
       </c>
       <c r="H63" s="6" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I63" s="7">
         <v>46251</v>
@@ -4161,25 +4149,25 @@
         <v>46251</v>
       </c>
       <c r="L63" s="8">
-        <v>670</v>
+        <v>680</v>
       </c>
       <c r="M63" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N63" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O63" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P63" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q63" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R63" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S63" s="6" t="s">
         <v>24</v>
@@ -4187,10 +4175,10 @@
     </row>
     <row r="64">
       <c r="A64" s="6" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>24</v>
@@ -4223,22 +4211,22 @@
         <v>680</v>
       </c>
       <c r="M64" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N64" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q64" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R64" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S64" s="6" t="s">
         <v>24</v>
@@ -4246,10 +4234,10 @@
     </row>
     <row r="65">
       <c r="A65" s="6" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>41</v>
+        <v>122</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>24</v>
@@ -4264,10 +4252,10 @@
         <v>26</v>
       </c>
       <c r="G65" s="7">
-        <v>46232</v>
+        <v>46212</v>
       </c>
       <c r="H65" s="6" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I65" s="7">
         <v>46251</v>
@@ -4282,22 +4270,22 @@
         <v>680</v>
       </c>
       <c r="M65" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N65" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O65" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P65" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q65" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R65" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S65" s="6" t="s">
         <v>24</v>
@@ -4305,10 +4293,10 @@
     </row>
     <row r="66">
       <c r="A66" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>75</v>
+        <v>51</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>24</v>
@@ -4326,7 +4314,7 @@
         <v>46225</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="I66" s="7">
         <v>46251</v>
@@ -4341,22 +4329,22 @@
         <v>680</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N66" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q66" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R66" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S66" s="6" t="s">
         <v>24</v>
@@ -4364,10 +4352,10 @@
     </row>
     <row r="67">
       <c r="A67" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>24</v>
@@ -4382,10 +4370,10 @@
         <v>26</v>
       </c>
       <c r="G67" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H67" s="6" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I67" s="7">
         <v>46251</v>
@@ -4397,25 +4385,25 @@
         <v>46251</v>
       </c>
       <c r="L67" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M67" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N67" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O67" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P67" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q67" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R67" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S67" s="6" t="s">
         <v>24</v>
@@ -4423,16 +4411,16 @@
     </row>
     <row r="68">
       <c r="A68" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>127</v>
+        <v>53</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>25</v>
@@ -4441,10 +4429,10 @@
         <v>26</v>
       </c>
       <c r="G68" s="7">
-        <v>46212</v>
+        <v>46232</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I68" s="7">
         <v>46251</v>
@@ -4456,25 +4444,25 @@
         <v>46251</v>
       </c>
       <c r="L68" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M68" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N68" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q68" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R68" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S68" s="6" t="s">
         <v>24</v>
@@ -4482,10 +4470,10 @@
     </row>
     <row r="69">
       <c r="A69" s="6" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>58</v>
+        <v>127</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>24</v>
@@ -4500,10 +4488,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="7">
-        <v>46225</v>
+        <v>46238</v>
       </c>
       <c r="H69" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I69" s="7">
         <v>46251</v>
@@ -4515,25 +4503,25 @@
         <v>46251</v>
       </c>
       <c r="L69" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M69" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N69" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O69" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P69" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q69" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R69" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S69" s="6" t="s">
         <v>24</v>
@@ -4541,11 +4529,11 @@
     </row>
     <row r="70">
       <c r="A70" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B70" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="B70" s="6" t="s">
-        <v>89</v>
-      </c>
       <c r="C70" s="6" t="s">
         <v>24</v>
       </c>
@@ -4559,10 +4547,10 @@
         <v>26</v>
       </c>
       <c r="G70" s="7">
-        <v>46188</v>
+        <v>46248</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I70" s="7">
         <v>46251</v>
@@ -4577,22 +4565,22 @@
         <v>700</v>
       </c>
       <c r="M70" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N70" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q70" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R70" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S70" s="6" t="s">
         <v>24</v>
@@ -4603,16 +4591,16 @@
         <v>130</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>50</v>
+        <v>24</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="F71" s="6" t="s">
         <v>26</v>
@@ -4621,7 +4609,7 @@
         <v>46232</v>
       </c>
       <c r="H71" s="6" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="I71" s="7">
         <v>46251</v>
@@ -4633,25 +4621,25 @@
         <v>46251</v>
       </c>
       <c r="L71" s="8">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="M71" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N71" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O71" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P71" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q71" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R71" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S71" s="6" t="s">
         <v>24</v>
@@ -4677,10 +4665,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="7">
-        <v>46238</v>
+        <v>46225</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="I72" s="7">
         <v>46251</v>
@@ -4692,25 +4680,25 @@
         <v>46251</v>
       </c>
       <c r="L72" s="8">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="M72" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N72" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q72" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R72" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S72" s="6" t="s">
         <v>24</v>
@@ -4721,7 +4709,7 @@
         <v>133</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>24</v>
@@ -4736,10 +4724,10 @@
         <v>26</v>
       </c>
       <c r="G73" s="7">
-        <v>46248</v>
+        <v>46225</v>
       </c>
       <c r="H73" s="6" t="s">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="I73" s="7">
         <v>46251</v>
@@ -4751,25 +4739,25 @@
         <v>46251</v>
       </c>
       <c r="L73" s="8">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="M73" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N73" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O73" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P73" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q73" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R73" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S73" s="6" t="s">
         <v>24</v>
@@ -4777,28 +4765,28 @@
     </row>
     <row r="74">
       <c r="A74" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B74" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="B74" s="6" t="s">
-        <v>43</v>
-      </c>
       <c r="C74" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="7">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>45</v>
+        <v>80</v>
       </c>
       <c r="I74" s="7">
         <v>46251</v>
@@ -4810,25 +4798,25 @@
         <v>46251</v>
       </c>
       <c r="L74" s="8">
-        <v>750</v>
+        <v>1200</v>
       </c>
       <c r="M74" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="N74" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="Q74" s="9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R74" s="6" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S74" s="6" t="s">
         <v>24</v>
@@ -4839,7 +4827,7 @@
         <v>136</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>24</v>
@@ -4854,37 +4842,37 @@
         <v>26</v>
       </c>
       <c r="G75" s="7">
-        <v>46225</v>
+        <v>46210</v>
       </c>
       <c r="H75" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I75" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J75" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K75" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L75" s="8">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="M75" s="6" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="N75" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O75" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P75" s="6" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="Q75" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R75" s="6" t="s">
         <v>24</v>
@@ -4895,55 +4883,55 @@
     </row>
     <row r="76">
       <c r="A76" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="B76" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D76" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E76" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="7">
+        <v>46240</v>
+      </c>
+      <c r="H76" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I76" s="7">
+        <v>46258</v>
+      </c>
+      <c r="J76" s="7">
+        <v>46258</v>
+      </c>
+      <c r="K76" s="7">
+        <v>46258</v>
+      </c>
+      <c r="L76" s="8">
+        <v>650</v>
+      </c>
+      <c r="M76" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B76" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="C76" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D76" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E76" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" s="7">
-        <v>46225</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="I76" s="7">
-        <v>46251</v>
-      </c>
-      <c r="J76" s="7">
-        <v>46251</v>
-      </c>
-      <c r="K76" s="7">
-        <v>46251</v>
-      </c>
-      <c r="L76" s="8">
-        <v>1200</v>
-      </c>
-      <c r="M76" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="N76" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O76" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="Q76" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R76" s="6" t="s">
         <v>24</v>
@@ -4954,16 +4942,16 @@
     </row>
     <row r="77">
       <c r="A77" s="6" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E77" s="6" t="s">
         <v>25</v>
@@ -4972,37 +4960,37 @@
         <v>26</v>
       </c>
       <c r="G77" s="7">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="H77" s="6" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I77" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="J77" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="K77" s="7">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="L77" s="8">
-        <v>1200</v>
+        <v>650</v>
       </c>
       <c r="M77" s="6" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="N77" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O77" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P77" s="6" t="s">
-        <v>96</v>
+        <v>137</v>
       </c>
       <c r="Q77" s="9">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R77" s="6" t="s">
         <v>24</v>
@@ -5016,7 +5004,7 @@
         <v>140</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>24</v>
@@ -5031,7 +5019,7 @@
         <v>26</v>
       </c>
       <c r="G78" s="7">
-        <v>46210</v>
+        <v>46232</v>
       </c>
       <c r="H78" s="6" t="s">
         <v>27</v>
@@ -5049,19 +5037,19 @@
         <v>650</v>
       </c>
       <c r="M78" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N78" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q78" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R78" s="6" t="s">
         <v>24</v>
@@ -5072,10 +5060,10 @@
     </row>
     <row r="79">
       <c r="A79" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>24</v>
@@ -5090,10 +5078,10 @@
         <v>26</v>
       </c>
       <c r="G79" s="7">
-        <v>46232</v>
+        <v>46188</v>
       </c>
       <c r="H79" s="6" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I79" s="7">
         <v>46258</v>
@@ -5108,19 +5096,19 @@
         <v>650</v>
       </c>
       <c r="M79" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N79" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O79" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P79" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q79" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R79" s="6" t="s">
         <v>24</v>
@@ -5131,16 +5119,16 @@
     </row>
     <row r="80">
       <c r="A80" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>25</v>
@@ -5149,10 +5137,10 @@
         <v>26</v>
       </c>
       <c r="G80" s="7">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="H80" s="6" t="s">
-        <v>85</v>
+        <v>27</v>
       </c>
       <c r="I80" s="7">
         <v>46258</v>
@@ -5167,19 +5155,19 @@
         <v>650</v>
       </c>
       <c r="M80" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N80" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O80" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P80" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q80" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R80" s="6" t="s">
         <v>24</v>
@@ -5190,10 +5178,10 @@
     </row>
     <row r="81">
       <c r="A81" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>24</v>
@@ -5208,10 +5196,10 @@
         <v>26</v>
       </c>
       <c r="G81" s="7">
-        <v>46240</v>
+        <v>46212</v>
       </c>
       <c r="H81" s="6" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I81" s="7">
         <v>46258</v>
@@ -5223,22 +5211,22 @@
         <v>46258</v>
       </c>
       <c r="L81" s="8">
-        <v>650</v>
+        <v>680</v>
       </c>
       <c r="M81" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N81" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O81" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P81" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q81" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R81" s="6" t="s">
         <v>24</v>
@@ -5249,10 +5237,10 @@
     </row>
     <row r="82">
       <c r="A82" s="6" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>54</v>
+        <v>129</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>24</v>
@@ -5267,10 +5255,10 @@
         <v>26</v>
       </c>
       <c r="G82" s="7">
-        <v>46188</v>
+        <v>46248</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I82" s="7">
         <v>46258</v>
@@ -5282,22 +5270,22 @@
         <v>46258</v>
       </c>
       <c r="L82" s="8">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="M82" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N82" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q82" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R82" s="6" t="s">
         <v>24</v>
@@ -5308,10 +5296,10 @@
     </row>
     <row r="83">
       <c r="A83" s="6" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>24</v>
@@ -5326,10 +5314,10 @@
         <v>26</v>
       </c>
       <c r="G83" s="7">
-        <v>46248</v>
+        <v>46188</v>
       </c>
       <c r="H83" s="6" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="I83" s="7">
         <v>46258</v>
@@ -5341,22 +5329,22 @@
         <v>46258</v>
       </c>
       <c r="L83" s="8">
-        <v>650</v>
+        <v>700</v>
       </c>
       <c r="M83" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N83" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O83" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P83" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q83" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R83" s="6" t="s">
         <v>24</v>
@@ -5367,7 +5355,7 @@
     </row>
     <row r="84">
       <c r="A84" s="6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>127</v>
@@ -5385,10 +5373,10 @@
         <v>26</v>
       </c>
       <c r="G84" s="7">
-        <v>46212</v>
+        <v>46238</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="I84" s="7">
         <v>46258</v>
@@ -5400,22 +5388,22 @@
         <v>46258</v>
       </c>
       <c r="L84" s="8">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="M84" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N84" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O84" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q84" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R84" s="6" t="s">
         <v>24</v>
@@ -5426,10 +5414,10 @@
     </row>
     <row r="85">
       <c r="A85" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>24</v>
@@ -5444,10 +5432,10 @@
         <v>26</v>
       </c>
       <c r="G85" s="7">
-        <v>46248</v>
+        <v>46225</v>
       </c>
       <c r="H85" s="6" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="I85" s="7">
         <v>46258</v>
@@ -5459,22 +5447,22 @@
         <v>46258</v>
       </c>
       <c r="L85" s="8">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="M85" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N85" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O85" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P85" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q85" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R85" s="6" t="s">
         <v>24</v>
@@ -5485,16 +5473,16 @@
     </row>
     <row r="86">
       <c r="A86" s="6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>89</v>
+        <v>135</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>25</v>
@@ -5503,10 +5491,10 @@
         <v>26</v>
       </c>
       <c r="G86" s="7">
-        <v>46188</v>
+        <v>46238</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="I86" s="7">
         <v>46258</v>
@@ -5518,22 +5506,22 @@
         <v>46258</v>
       </c>
       <c r="L86" s="8">
-        <v>700</v>
+        <v>1200</v>
       </c>
       <c r="M86" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N86" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O86" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q86" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R86" s="6" t="s">
         <v>24</v>
@@ -5544,10 +5532,10 @@
     </row>
     <row r="87">
       <c r="A87" s="6" t="s">
-        <v>150</v>
+        <v>24</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>132</v>
+        <v>42</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>24</v>
@@ -5559,40 +5547,40 @@
         <v>25</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G87" s="7">
-        <v>46238</v>
+        <v>24</v>
+      </c>
+      <c r="G87" s="7" t="s">
+        <v>24</v>
       </c>
       <c r="H87" s="6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I87" s="7">
-        <v>46258</v>
+        <v>45930</v>
       </c>
       <c r="J87" s="7">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="K87" s="7">
-        <v>46258</v>
+        <v>46264</v>
       </c>
       <c r="L87" s="8">
-        <v>700</v>
+        <v>185.5</v>
       </c>
       <c r="M87" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N87" s="9">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="O87" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P87" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q87" s="9">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R87" s="6" t="s">
         <v>24</v>
@@ -5603,10 +5591,10 @@
     </row>
     <row r="88">
       <c r="A88" s="6" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>24</v>
@@ -5621,37 +5609,37 @@
         <v>26</v>
       </c>
       <c r="G88" s="7">
-        <v>46225</v>
+        <v>46248</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="I88" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="J88" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="K88" s="7">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="L88" s="8">
-        <v>800</v>
+        <v>650</v>
       </c>
       <c r="M88" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="N88" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="O88" s="6" t="s">
         <v>24</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="Q88" s="9">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="R88" s="6" t="s">
         <v>24</v>
@@ -5662,16 +5650,16 @@
     </row>
     <row r="89">
       <c r="A89" s="6" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>139</v>
+        <v>114</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>24</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>112</v>
+        <v>24</v>
       </c>
       <c r="E89" s="6" t="s">
         <v